--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1769,13 +1769,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.62511512732</v>
+        <v>46162.79178179398</v>
       </c>
       <c r="C4" s="5">
-        <v>46183.414665324075</v>
+        <v>46183.58133199074</v>
       </c>
       <c r="D4" s="5">
-        <v>46183.41468071759</v>
+        <v>46183.58134738426</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1822,13 +1822,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.62522459491</v>
+        <v>46162.79189126157</v>
       </c>
       <c r="C5" s="9">
-        <v>46183.414629328705</v>
+        <v>46183.58129599537</v>
       </c>
       <c r="D5" s="9">
-        <v>46183.41464973379</v>
+        <v>46183.581316400465</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1887,13 +1887,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.62522767361</v>
+        <v>46162.79189434028</v>
       </c>
       <c r="C6" s="5">
-        <v>46183.41463443287</v>
+        <v>46183.58130109953</v>
       </c>
       <c r="D6" s="5">
-        <v>46183.41464980324</v>
+        <v>46183.58131646991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1952,13 +1952,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.62523457176</v>
+        <v>46162.79190123842</v>
       </c>
       <c r="C7" s="9">
-        <v>46183.41464715278</v>
+        <v>46183.58131381945</v>
       </c>
       <c r="D7" s="9">
-        <v>46183.41466510417</v>
+        <v>46183.58133177084</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2017,13 +2017,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.62523784723</v>
+        <v>46162.791904513884</v>
       </c>
       <c r="C8" s="5">
-        <v>46183.414652974534</v>
+        <v>46183.581319641205</v>
       </c>
       <c r="D8" s="5">
-        <v>46183.41466673611</v>
+        <v>46183.58133340278</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2082,11 +2082,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.62511998843</v>
+        <v>46162.79178665509</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46164.482602222226</v>
+        <v>46164.64926888889</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2129,11 +2129,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.62524114583</v>
+        <v>46162.7919078125</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46183.41466988426</v>
+        <v>46183.581336550924</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2192,11 +2192,11 @@
         <v>54</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.62524625</v>
+        <v>46162.79191291667</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46183.41466920139</v>
+        <v>46183.58133586806</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>55</v>
@@ -2255,11 +2255,11 @@
         <v>58</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.62525138889</v>
+        <v>46162.791918055555</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46183.414669826394</v>
+        <v>46183.58133649305</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2318,11 +2318,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.625256307874</v>
+        <v>46162.79192297454</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46164.521635613426</v>
+        <v>46164.68830228009</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2381,11 +2381,11 @@
         <v>66</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.62512452547</v>
+        <v>46162.791791192125</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46164.49277914352</v>
+        <v>46164.65944581019</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>67</v>
@@ -2428,11 +2428,11 @@
         <v>69</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.62526353009</v>
+        <v>46162.79193019676</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46164.52170275463</v>
+        <v>46164.688369421296</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>70</v>
@@ -2491,11 +2491,11 @@
         <v>72</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.62526864583</v>
+        <v>46162.7919353125</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46164.521699675926</v>
+        <v>46164.6883663426</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>73</v>
@@ -2554,11 +2554,11 @@
         <v>75</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.625273564816</v>
+        <v>46162.79194023148</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46164.521729479166</v>
+        <v>46164.68839614584</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -2617,11 +2617,11 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.62527862268</v>
+        <v>46162.791945289355</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46164.52181248843</v>
+        <v>46164.68847915509</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2680,11 +2680,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.62528289352</v>
+        <v>46162.79194956018</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46164.52180534722</v>
+        <v>46164.68847201389</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2743,11 +2743,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.625286180555</v>
+        <v>46162.79195284723</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46164.52180390046</v>
+        <v>46164.688470567125</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2806,11 +2806,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.625289351854</v>
+        <v>46162.79195601852</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46164.52180297454</v>
+        <v>46164.6884696412</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2869,11 +2869,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.62512967593</v>
+        <v>46162.79179634259</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46164.4935021875</v>
+        <v>46164.66016885417</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2916,11 +2916,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.62529335648</v>
+        <v>46162.79196002315</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46164.52279099537</v>
+        <v>46164.68945766204</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2979,11 +2979,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.625297708335</v>
+        <v>46162.791964375</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46164.52276619213</v>
+        <v>46164.689432858795</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3038,11 +3038,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.62530216435</v>
+        <v>46162.79196883102</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46164.52276291666</v>
+        <v>46164.68942958333</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3097,11 +3097,11 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.62530663195</v>
+        <v>46162.79197329861</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.00878244213</v>
+        <v>46169.17544910879</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3160,11 +3160,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.62531083333</v>
+        <v>46162.791977500005</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46164.52287170139</v>
+        <v>46164.68953836805</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3219,11 +3219,11 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.62531532407</v>
+        <v>46162.79198199074</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46168.00598047454</v>
+        <v>46168.172647141204</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3278,11 +3278,11 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.625319872684</v>
+        <v>46162.79198653935</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46164.52298150463</v>
+        <v>46164.6896481713</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3341,11 +3341,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.62532415509</v>
+        <v>46162.79199082176</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46175.00378561343</v>
+        <v>46175.170452280094</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3400,11 +3400,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.62532864584</v>
+        <v>46162.791995312495</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46164.52295708333</v>
+        <v>46164.689623750004</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3459,11 +3459,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.625333240736</v>
+        <v>46162.79199990741</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46164.52295274306</v>
+        <v>46164.68961940972</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3518,11 +3518,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.62533775463</v>
+        <v>46162.792004421295</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46164.52311444444</v>
+        <v>46164.68978111111</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3581,11 +3581,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.62534211806</v>
+        <v>46162.79200878472</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46164.52307152778</v>
+        <v>46164.68973819444</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3640,11 +3640,11 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.62534672454</v>
+        <v>46162.792013391205</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46164.523068483795</v>
+        <v>46164.68973515046</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -3699,11 +3699,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.625351423616</v>
+        <v>46162.79201809027</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46164.523207465274</v>
+        <v>46164.689874131946</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3762,11 +3762,11 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.6254083449</v>
+        <v>46162.79207501157</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46164.52317696759</v>
+        <v>46164.68984363426</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3815,11 +3815,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.625413587964</v>
+        <v>46162.79208025463</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46164.52317409722</v>
+        <v>46164.68984076389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3868,11 +3868,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.62541833334</v>
+        <v>46162.792085</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46164.52337886574</v>
+        <v>46164.69004553241</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3931,11 +3931,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.6254225</v>
+        <v>46162.792089166665</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46164.523292199076</v>
+        <v>46164.68995886574</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3984,11 +3984,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.62542693287</v>
+        <v>46162.792093599535</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.523289247685</v>
+        <v>46164.68995591435</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4037,11 +4037,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.6254371875</v>
+        <v>46162.79210385417</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46164.5233225463</v>
+        <v>46164.68998921296</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4090,11 +4090,11 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.62544063658</v>
+        <v>46162.79210730324</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46164.52343339121</v>
+        <v>46164.690100057865</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4153,11 +4153,11 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.62544451389</v>
+        <v>46162.792111180555</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46164.52349128472</v>
+        <v>46164.690157951394</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4206,11 +4206,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.62544935185</v>
+        <v>46162.79211601852</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46164.523488680556</v>
+        <v>46164.69015534723</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -4259,11 +4259,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.625134131944</v>
+        <v>46162.791800798615</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46164.49223611111</v>
+        <v>46164.65890277778</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4306,11 +4306,11 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.625454548615</v>
+        <v>46162.79212121527</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46179.02939460648</v>
+        <v>46179.19606127315</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4369,11 +4369,11 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.625460034724</v>
+        <v>46162.79212670139</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46164.523564814815</v>
+        <v>46164.69023148148</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4432,11 +4432,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.62546642361</v>
+        <v>46162.792133090275</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.52356090277</v>
+        <v>46164.690227569445</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>83</v>
@@ -4495,11 +4495,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.625480428236</v>
+        <v>46162.79214709491</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46164.52360884259</v>
+        <v>46164.69027550926</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4558,11 +4558,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.625484108794</v>
+        <v>46162.792150775465</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46164.523701805556</v>
+        <v>46164.69036847222</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4611,11 +4611,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.62548818287</v>
+        <v>46162.792154849536</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46164.52369920139</v>
+        <v>46164.69036586805</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4664,11 +4664,11 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.62549208333</v>
+        <v>46162.79215875</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46164.52369637731</v>
+        <v>46164.69036304398</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -4717,11 +4717,11 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.62549497685</v>
+        <v>46162.79216164352</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46164.523692268514</v>
+        <v>46164.690358935186</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4770,11 +4770,11 @@
         <v>195</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.62554516204</v>
+        <v>46162.7922118287</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.500513541665</v>
+        <v>46164.66718020833</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -4817,11 +4817,11 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.625553425925</v>
+        <v>46162.7922200926</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46164.52381886574</v>
+        <v>46164.69048553241</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>199</v>
@@ -4880,11 +4880,11 @@
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.62555895833</v>
+        <v>46162.792225625</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.52388792824</v>
+        <v>46164.69055459491</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>204</v>
@@ -4943,11 +4943,11 @@
         <v>207</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.625565636576</v>
+        <v>46162.79223230324</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46164.52381575231</v>
+        <v>46164.690482418984</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>208</v>
@@ -5006,11 +5006,11 @@
         <v>210</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.62557070602</v>
+        <v>46162.79223737269</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46164.52388519676</v>
+        <v>46164.69055186343</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>211</v>
@@ -5069,11 +5069,11 @@
         <v>213</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.62557578704</v>
+        <v>46162.7922424537</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46164.52381239583</v>
+        <v>46164.6904790625</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>214</v>
@@ -5132,11 +5132,11 @@
         <v>216</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.62558024305</v>
+        <v>46162.792246909725</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.52388266203</v>
+        <v>46164.690549328705</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5195,11 +5195,11 @@
         <v>217</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.62558502315</v>
+        <v>46162.79225168981</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46164.50232085648</v>
+        <v>46164.66898752315</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5242,11 +5242,11 @@
         <v>220</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.6255878125</v>
+        <v>46162.792254479165</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.52405841435</v>
+        <v>46164.69072508102</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>
@@ -5305,11 +5305,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.62559255787</v>
+        <v>46162.79225922454</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.5240165162</v>
+        <v>46164.69068318287</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>190</v>
@@ -5358,11 +5358,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.62559891204</v>
+        <v>46162.792265578704</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.52401381945</v>
+        <v>46164.69068048611</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>190</v>
@@ -5411,11 +5411,11 @@
         <v>229</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.62560534722</v>
+        <v>46162.79227201389</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.52401086806</v>
+        <v>46164.69067753472</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>190</v>
@@ -5464,11 +5464,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.62561162037</v>
+        <v>46162.79227828704</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46164.52400670139</v>
+        <v>46164.69067336805</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>190</v>
@@ -5517,11 +5517,11 @@
         <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.625655358795</v>
+        <v>46162.79232202546</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46164.52418478009</v>
+        <v>46164.69085144676</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>234</v>
@@ -5580,11 +5580,11 @@
         <v>235</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.62565987269</v>
+        <v>46162.79232653935</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46164.524149606485</v>
+        <v>46164.69081627315</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>190</v>
@@ -5633,11 +5633,11 @@
         <v>238</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.625665983796</v>
+        <v>46162.79233265047</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46164.52414706019</v>
+        <v>46164.69081372685</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5686,11 +5686,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.625671539354</v>
+        <v>46162.79233820602</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46164.52414630787</v>
+        <v>46164.690812974535</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -5739,11 +5739,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.62567717592</v>
+        <v>46162.79234384259</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46164.524145034724</v>
+        <v>46164.69081170139</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -5792,11 +5792,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.62574747685</v>
+        <v>46162.79241414352</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46164.52430971064</v>
+        <v>46164.690976377315</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>243</v>
@@ -5855,11 +5855,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.62575375</v>
+        <v>46162.79242041666</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46164.52427967593</v>
+        <v>46164.69094634259</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -5908,11 +5908,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.625766550926</v>
+        <v>46162.79243321759</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46164.52427657407</v>
+        <v>46164.69094324074</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -5961,11 +5961,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.625772893516</v>
+        <v>46162.79243956019</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46164.52426950232</v>
+        <v>46164.69093616898</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6014,11 +6014,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.625779849535</v>
+        <v>46162.79244651621</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.5242687963</v>
+        <v>46164.69093546296</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6067,11 +6067,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.625811446764</v>
+        <v>46162.79247811342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46164.504105960645</v>
+        <v>46164.670772627316</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6114,11 +6114,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.62581513889</v>
+        <v>46162.792481805554</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46171.032529421296</v>
+        <v>46171.19919608797</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>254</v>
@@ -6177,11 +6177,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.62582282408</v>
+        <v>46162.79248949074</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46164.52444709491</v>
+        <v>46164.691113761575</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>257</v>
@@ -6240,11 +6240,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.62583023148</v>
+        <v>46162.79249689815</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.52444390046</v>
+        <v>46164.69111056713</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6303,11 +6303,11 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.6258377662</v>
+        <v>46162.79250443287</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.52443952546</v>
+        <v>46164.69110619213</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6366,11 +6366,11 @@
         <v>264</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.6258428125</v>
+        <v>46162.79250947917</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.517869247684</v>
+        <v>46164.68453591435</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>265</v>
@@ -6413,11 +6413,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.62584628472</v>
+        <v>46162.79251295139</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.524581516205</v>
+        <v>46164.69124818287</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6476,11 +6476,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.625862071756</v>
+        <v>46162.79252873843</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.52455164352</v>
+        <v>46164.69121831018</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6529,11 +6529,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.62586685186</v>
+        <v>46162.792533518514</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.524549050926</v>
+        <v>46164.6912157176</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6582,11 +6582,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.62587158565</v>
+        <v>46162.79253825231</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.52454670139</v>
+        <v>46164.69121336806</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -6635,11 +6635,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.62587653935</v>
+        <v>46162.792543206015</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.524542824074</v>
+        <v>46164.691209490746</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -6688,11 +6688,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.62594607639</v>
+        <v>46162.792612743055</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46164.524713032406</v>
+        <v>46164.69137969907</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>278</v>
@@ -6751,11 +6751,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.62595178241</v>
+        <v>46162.79261844908</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46164.524674872686</v>
+        <v>46164.69134153935</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>190</v>
@@ -6804,11 +6804,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.62595806713</v>
+        <v>46162.7926247338</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46164.524672314816</v>
+        <v>46164.69133898148</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>190</v>
@@ -6857,11 +6857,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.6259640162</v>
+        <v>46162.792630682874</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46164.52466957176</v>
+        <v>46164.69133623842</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>190</v>
@@ -6910,11 +6910,11 @@
         <v>285</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.62597111111</v>
+        <v>46162.79263777778</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.52466570602</v>
+        <v>46164.691332372684</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>190</v>
@@ -6963,11 +6963,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.626019375</v>
+        <v>46162.79268604166</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46164.524833738426</v>
+        <v>46164.6915004051</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7026,11 +7026,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.62602403935</v>
+        <v>46162.79269070602</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46164.52480820601</v>
+        <v>46164.691474872685</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>190</v>
@@ -7079,11 +7079,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.626030405096</v>
+        <v>46162.79269707176</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46164.524804733795</v>
+        <v>46164.69147140047</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>190</v>
@@ -7132,11 +7132,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.62603690972</v>
+        <v>46162.792703576386</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46164.52480150463</v>
+        <v>46164.691468171295</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>190</v>
@@ -7185,11 +7185,11 @@
         <v>294</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.62604379629</v>
+        <v>46162.79271046296</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.52479821759</v>
+        <v>46164.69146488426</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7238,11 +7238,11 @@
         <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.626078194444</v>
+        <v>46162.792744861115</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46164.52495327547</v>
+        <v>46164.691619942125</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>298</v>
@@ -7301,11 +7301,11 @@
         <v>299</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.62608315972</v>
+        <v>46162.79274982639</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46164.52492054398</v>
+        <v>46164.69158721065</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7354,11 +7354,11 @@
         <v>302</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.626088923615</v>
+        <v>46162.79275559028</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46164.5249171412</v>
+        <v>46164.69158380787</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7407,11 +7407,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.62609451389</v>
+        <v>46162.79276118056</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46164.52491439815</v>
+        <v>46164.69158106481</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>190</v>
@@ -7460,11 +7460,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.62610108797</v>
+        <v>46162.792767754625</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.52490980324</v>
+        <v>46164.69157646991</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>190</v>
@@ -7513,11 +7513,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.62619030093</v>
+        <v>46162.79285696759</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.525072881945</v>
+        <v>46164.69173954861</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>308</v>
@@ -7576,11 +7576,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.6261958449</v>
+        <v>46162.792862511575</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.525042002315</v>
+        <v>46164.69170866898</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>190</v>
@@ -7629,11 +7629,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.62620145833</v>
+        <v>46162.792868125005</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.52503929398</v>
+        <v>46164.69170596065</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>190</v>
@@ -7682,11 +7682,11 @@
         <v>313</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.62620708333</v>
+        <v>46162.792873750004</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.525036273146</v>
+        <v>46164.69170293982</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>190</v>
@@ -7735,11 +7735,11 @@
         <v>314</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.62621266204</v>
+        <v>46162.7928793287</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.52503152778</v>
+        <v>46164.691698194445</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7788,11 +7788,11 @@
         <v>315</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.62624103009</v>
+        <v>46162.792907696756</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.52519069445</v>
+        <v>46164.69185736111</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>316</v>
@@ -7849,11 +7849,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.62624622685</v>
+        <v>46162.79291289352</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.52515765047</v>
+        <v>46164.69182431713</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -7902,11 +7902,11 @@
         <v>320</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.626250914356</v>
+        <v>46162.79291758101</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.52515489583</v>
+        <v>46164.691821562505</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -7955,11 +7955,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.626255787036</v>
+        <v>46162.79292245371</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.52515248842</v>
+        <v>46164.691819155094</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8008,11 +8008,11 @@
         <v>322</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.62626590278</v>
+        <v>46162.79293256944</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.52514842592</v>
+        <v>46164.69181509259</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>
@@ -8061,11 +8061,11 @@
         <v>323</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.626337395835</v>
+        <v>46162.7930040625</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.518794965275</v>
+        <v>46164.68546163195</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>324</v>
@@ -8108,11 +8108,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.626341400464</v>
+        <v>46162.79300806713</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46164.525584849536</v>
+        <v>46164.6922515162</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>327</v>
@@ -8171,11 +8171,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.62635180556</v>
+        <v>46162.79301847222</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46164.525564814816</v>
+        <v>46164.69223148148</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8224,11 +8224,11 @@
         <v>333</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.626358587964</v>
+        <v>46162.79302525463</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46164.52556148148</v>
+        <v>46164.69222814815</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8277,11 +8277,11 @@
         <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.6263634375</v>
+        <v>46162.79303010416</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46164.525558587964</v>
+        <v>46164.69222525463</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8330,11 +8330,11 @@
         <v>336</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.62636815972</v>
+        <v>46162.79303482639</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.52555344907</v>
+        <v>46164.69222011574</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8383,11 +8383,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.6263962963</v>
+        <v>46162.79306296296</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.52570229166</v>
+        <v>46164.692368958335</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>338</v>
@@ -8446,11 +8446,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.62640114583</v>
+        <v>46162.7930678125</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.52566752315</v>
+        <v>46164.692334189815</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8499,11 +8499,11 @@
         <v>341</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.626405613424</v>
+        <v>46162.793072280096</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.52566484954</v>
+        <v>46164.6923315162</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8552,11 +8552,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.62641030093</v>
+        <v>46162.79307696759</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.525662141205</v>
+        <v>46164.69232880787</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8605,11 +8605,11 @@
         <v>344</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.62641509259</v>
+        <v>46162.79308175926</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.52565760417</v>
+        <v>46164.69232427083</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8658,11 +8658,11 @@
         <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.626479583334</v>
+        <v>46162.79314625</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46164.52582030093</v>
+        <v>46164.69248696759</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>346</v>
@@ -8721,11 +8721,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.626484884255</v>
+        <v>46162.793151550926</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46164.525794085646</v>
+        <v>46164.69246075231</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8774,11 +8774,11 @@
         <v>349</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.6264921875</v>
+        <v>46162.79315885417</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46164.52579143518</v>
+        <v>46164.692458101854</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -8827,11 +8827,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.62649834491</v>
+        <v>46162.79316501158</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46164.52578892361</v>
+        <v>46164.69245559028</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -8880,11 +8880,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.62650319445</v>
+        <v>46162.79316986111</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.525784618054</v>
+        <v>46164.69245128472</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>190</v>
@@ -8933,11 +8933,11 @@
         <v>354</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.62653059028</v>
+        <v>46162.79319725695</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.52595978009</v>
+        <v>46164.69262644676</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>355</v>
@@ -8996,11 +8996,11 @@
         <v>357</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.62653543982</v>
+        <v>46162.79320210648</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46164.52592063657</v>
+        <v>46164.692587303245</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9049,11 +9049,11 @@
         <v>358</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.62653944445</v>
+        <v>46162.793206111106</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46164.52591784722</v>
+        <v>46164.69258451389</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9102,11 +9102,11 @@
         <v>359</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.62654328704</v>
+        <v>46162.7932099537</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46164.52591521991</v>
+        <v>46164.69258188657</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9155,11 +9155,11 @@
         <v>360</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.62654733796</v>
+        <v>46162.79321400463</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46164.525910752316</v>
+        <v>46164.69257741898</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9208,11 +9208,11 @@
         <v>361</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.62657099537</v>
+        <v>46162.79323766204</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.51925614583</v>
+        <v>46164.685922812496</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>362</v>
@@ -9255,11 +9255,11 @@
         <v>364</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.62657396991</v>
+        <v>46162.79324063657</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46164.526027175925</v>
+        <v>46164.69269384259</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>365</v>
@@ -9318,11 +9318,11 @@
         <v>368</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.62657862269</v>
+        <v>46162.79324528935</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46164.52606778935</v>
+        <v>46164.69273445602</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>369</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46183.581336550924</v>
+        <v>46195.59182194444</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1769,13 +1769,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.79178179398</v>
+        <v>46162.62511512732</v>
       </c>
       <c r="C4" s="5">
-        <v>46183.58133199074</v>
+        <v>46183.414665324075</v>
       </c>
       <c r="D4" s="5">
-        <v>46183.58134738426</v>
+        <v>46183.41468071759</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1822,13 +1822,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.79189126157</v>
+        <v>46162.62522459491</v>
       </c>
       <c r="C5" s="9">
-        <v>46183.58129599537</v>
+        <v>46183.414629328705</v>
       </c>
       <c r="D5" s="9">
-        <v>46183.581316400465</v>
+        <v>46183.41464973379</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1887,13 +1887,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.79189434028</v>
+        <v>46162.62522767361</v>
       </c>
       <c r="C6" s="5">
-        <v>46183.58130109953</v>
+        <v>46183.41463443287</v>
       </c>
       <c r="D6" s="5">
-        <v>46183.58131646991</v>
+        <v>46183.41464980324</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1952,13 +1952,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.79190123842</v>
+        <v>46162.62523457176</v>
       </c>
       <c r="C7" s="9">
-        <v>46183.58131381945</v>
+        <v>46183.41464715278</v>
       </c>
       <c r="D7" s="9">
-        <v>46183.58133177084</v>
+        <v>46183.41466510417</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2017,13 +2017,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.791904513884</v>
+        <v>46162.62523784723</v>
       </c>
       <c r="C8" s="5">
-        <v>46183.581319641205</v>
+        <v>46183.414652974534</v>
       </c>
       <c r="D8" s="5">
-        <v>46183.58133340278</v>
+        <v>46183.41466673611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2082,11 +2082,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.79178665509</v>
+        <v>46162.62511998843</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46164.64926888889</v>
+        <v>46164.482602222226</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2129,11 +2129,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.7919078125</v>
+        <v>46162.62524114583</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.59182194444</v>
+        <v>46195.42515527778</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2192,11 +2192,11 @@
         <v>54</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.79191291667</v>
+        <v>46162.62524625</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46183.58133586806</v>
+        <v>46183.41466920139</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>55</v>
@@ -2255,11 +2255,11 @@
         <v>58</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.791918055555</v>
+        <v>46162.62525138889</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46183.58133649305</v>
+        <v>46183.414669826394</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2318,11 +2318,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.79192297454</v>
+        <v>46162.625256307874</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46164.68830228009</v>
+        <v>46164.521635613426</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2381,11 +2381,11 @@
         <v>66</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.791791192125</v>
+        <v>46162.62512452547</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46164.65944581019</v>
+        <v>46164.49277914352</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>67</v>
@@ -2428,11 +2428,11 @@
         <v>69</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.79193019676</v>
+        <v>46162.62526353009</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46164.688369421296</v>
+        <v>46164.52170275463</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>70</v>
@@ -2491,11 +2491,11 @@
         <v>72</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.7919353125</v>
+        <v>46162.62526864583</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46164.6883663426</v>
+        <v>46164.521699675926</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>73</v>
@@ -2554,11 +2554,11 @@
         <v>75</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.79194023148</v>
+        <v>46162.625273564816</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46164.68839614584</v>
+        <v>46164.521729479166</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -2617,11 +2617,11 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.791945289355</v>
+        <v>46162.62527862268</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46164.68847915509</v>
+        <v>46164.52181248843</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2680,11 +2680,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.79194956018</v>
+        <v>46162.62528289352</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46164.68847201389</v>
+        <v>46164.52180534722</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2743,11 +2743,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.79195284723</v>
+        <v>46162.625286180555</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46164.688470567125</v>
+        <v>46164.52180390046</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2806,11 +2806,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.79195601852</v>
+        <v>46162.625289351854</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46164.6884696412</v>
+        <v>46164.52180297454</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2869,11 +2869,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.79179634259</v>
+        <v>46162.62512967593</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46164.66016885417</v>
+        <v>46164.4935021875</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2916,11 +2916,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.79196002315</v>
+        <v>46162.62529335648</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46164.68945766204</v>
+        <v>46164.52279099537</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2979,11 +2979,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.791964375</v>
+        <v>46162.625297708335</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46164.689432858795</v>
+        <v>46164.52276619213</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3038,11 +3038,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.79196883102</v>
+        <v>46162.62530216435</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46164.68942958333</v>
+        <v>46164.52276291666</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3097,11 +3097,11 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.79197329861</v>
+        <v>46162.62530663195</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.17544910879</v>
+        <v>46169.00878244213</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3160,11 +3160,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.791977500005</v>
+        <v>46162.62531083333</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46164.68953836805</v>
+        <v>46164.52287170139</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3219,11 +3219,11 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.79198199074</v>
+        <v>46162.62531532407</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46168.172647141204</v>
+        <v>46168.00598047454</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3278,11 +3278,11 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.79198653935</v>
+        <v>46162.625319872684</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46164.6896481713</v>
+        <v>46164.52298150463</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3341,11 +3341,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.79199082176</v>
+        <v>46162.62532415509</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46175.170452280094</v>
+        <v>46175.00378561343</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3400,11 +3400,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.791995312495</v>
+        <v>46162.62532864584</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46164.689623750004</v>
+        <v>46164.52295708333</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3459,11 +3459,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.79199990741</v>
+        <v>46162.625333240736</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46164.68961940972</v>
+        <v>46164.52295274306</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3518,11 +3518,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.792004421295</v>
+        <v>46162.62533775463</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46164.68978111111</v>
+        <v>46164.52311444444</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3581,11 +3581,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.79200878472</v>
+        <v>46162.62534211806</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46164.68973819444</v>
+        <v>46164.52307152778</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3640,11 +3640,11 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.792013391205</v>
+        <v>46162.62534672454</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46164.68973515046</v>
+        <v>46164.523068483795</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -3699,11 +3699,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.79201809027</v>
+        <v>46162.625351423616</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46164.689874131946</v>
+        <v>46164.523207465274</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3762,11 +3762,11 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.79207501157</v>
+        <v>46162.6254083449</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46164.68984363426</v>
+        <v>46164.52317696759</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3815,11 +3815,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.79208025463</v>
+        <v>46162.625413587964</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46164.68984076389</v>
+        <v>46164.52317409722</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3868,11 +3868,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.792085</v>
+        <v>46162.62541833334</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46164.69004553241</v>
+        <v>46164.52337886574</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3931,11 +3931,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.792089166665</v>
+        <v>46162.6254225</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46164.68995886574</v>
+        <v>46164.523292199076</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3984,11 +3984,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.792093599535</v>
+        <v>46162.62542693287</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.68995591435</v>
+        <v>46164.523289247685</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4037,11 +4037,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.79210385417</v>
+        <v>46162.6254371875</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46164.68998921296</v>
+        <v>46164.5233225463</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4090,11 +4090,11 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.79210730324</v>
+        <v>46162.62544063658</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46164.690100057865</v>
+        <v>46164.52343339121</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4153,11 +4153,11 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.792111180555</v>
+        <v>46162.62544451389</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46164.690157951394</v>
+        <v>46164.52349128472</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4206,11 +4206,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.79211601852</v>
+        <v>46162.62544935185</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46164.69015534723</v>
+        <v>46164.523488680556</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -4259,11 +4259,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.791800798615</v>
+        <v>46162.625134131944</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46164.65890277778</v>
+        <v>46164.49223611111</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4306,11 +4306,11 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.79212121527</v>
+        <v>46162.625454548615</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46179.19606127315</v>
+        <v>46179.02939460648</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4369,11 +4369,11 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.79212670139</v>
+        <v>46162.625460034724</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46164.69023148148</v>
+        <v>46164.523564814815</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4432,11 +4432,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.792133090275</v>
+        <v>46162.62546642361</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.690227569445</v>
+        <v>46164.52356090277</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>83</v>
@@ -4495,11 +4495,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.79214709491</v>
+        <v>46162.625480428236</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46164.69027550926</v>
+        <v>46164.52360884259</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4558,11 +4558,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.792150775465</v>
+        <v>46162.625484108794</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46164.69036847222</v>
+        <v>46164.523701805556</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4611,11 +4611,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.792154849536</v>
+        <v>46162.62548818287</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46164.69036586805</v>
+        <v>46164.52369920139</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4664,11 +4664,11 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.79215875</v>
+        <v>46162.62549208333</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46164.69036304398</v>
+        <v>46164.52369637731</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -4717,11 +4717,11 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.79216164352</v>
+        <v>46162.62549497685</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46164.690358935186</v>
+        <v>46164.523692268514</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4770,11 +4770,11 @@
         <v>195</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.7922118287</v>
+        <v>46162.62554516204</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.66718020833</v>
+        <v>46164.500513541665</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -4817,11 +4817,11 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.7922200926</v>
+        <v>46162.625553425925</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46164.69048553241</v>
+        <v>46164.52381886574</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>199</v>
@@ -4880,11 +4880,11 @@
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.792225625</v>
+        <v>46162.62555895833</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.69055459491</v>
+        <v>46164.52388792824</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>204</v>
@@ -4943,11 +4943,11 @@
         <v>207</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.79223230324</v>
+        <v>46162.625565636576</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46164.690482418984</v>
+        <v>46164.52381575231</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>208</v>
@@ -5006,11 +5006,11 @@
         <v>210</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.79223737269</v>
+        <v>46162.62557070602</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46164.69055186343</v>
+        <v>46164.52388519676</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>211</v>
@@ -5069,11 +5069,11 @@
         <v>213</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.7922424537</v>
+        <v>46162.62557578704</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46164.6904790625</v>
+        <v>46164.52381239583</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>214</v>
@@ -5132,11 +5132,11 @@
         <v>216</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.792246909725</v>
+        <v>46162.62558024305</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.690549328705</v>
+        <v>46164.52388266203</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5195,11 +5195,11 @@
         <v>217</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.79225168981</v>
+        <v>46162.62558502315</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46164.66898752315</v>
+        <v>46164.50232085648</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5242,11 +5242,11 @@
         <v>220</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.792254479165</v>
+        <v>46162.6255878125</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.69072508102</v>
+        <v>46164.52405841435</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>
@@ -5305,11 +5305,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.79225922454</v>
+        <v>46162.62559255787</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.69068318287</v>
+        <v>46164.5240165162</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>190</v>
@@ -5358,11 +5358,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.792265578704</v>
+        <v>46162.62559891204</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.69068048611</v>
+        <v>46164.52401381945</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>190</v>
@@ -5411,11 +5411,11 @@
         <v>229</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.79227201389</v>
+        <v>46162.62560534722</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.69067753472</v>
+        <v>46164.52401086806</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>190</v>
@@ -5464,11 +5464,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.79227828704</v>
+        <v>46162.62561162037</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46164.69067336805</v>
+        <v>46164.52400670139</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>190</v>
@@ -5517,11 +5517,11 @@
         <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.79232202546</v>
+        <v>46162.625655358795</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46164.69085144676</v>
+        <v>46164.52418478009</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>234</v>
@@ -5580,11 +5580,11 @@
         <v>235</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.79232653935</v>
+        <v>46162.62565987269</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46164.69081627315</v>
+        <v>46164.524149606485</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>190</v>
@@ -5633,11 +5633,11 @@
         <v>238</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.79233265047</v>
+        <v>46162.625665983796</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46164.69081372685</v>
+        <v>46164.52414706019</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5686,11 +5686,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.79233820602</v>
+        <v>46162.625671539354</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46164.690812974535</v>
+        <v>46164.52414630787</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -5739,11 +5739,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.79234384259</v>
+        <v>46162.62567717592</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46164.69081170139</v>
+        <v>46164.524145034724</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -5792,11 +5792,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.79241414352</v>
+        <v>46162.62574747685</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46164.690976377315</v>
+        <v>46164.52430971064</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>243</v>
@@ -5855,11 +5855,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.79242041666</v>
+        <v>46162.62575375</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46164.69094634259</v>
+        <v>46164.52427967593</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -5908,11 +5908,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.79243321759</v>
+        <v>46162.625766550926</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46164.69094324074</v>
+        <v>46164.52427657407</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -5961,11 +5961,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.79243956019</v>
+        <v>46162.625772893516</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46164.69093616898</v>
+        <v>46164.52426950232</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6014,11 +6014,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.79244651621</v>
+        <v>46162.625779849535</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.69093546296</v>
+        <v>46164.5242687963</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6067,11 +6067,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.79247811342</v>
+        <v>46162.625811446764</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46164.670772627316</v>
+        <v>46164.504105960645</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6114,11 +6114,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.792481805554</v>
+        <v>46162.62581513889</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46171.19919608797</v>
+        <v>46171.032529421296</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>254</v>
@@ -6177,11 +6177,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.79248949074</v>
+        <v>46162.62582282408</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46164.691113761575</v>
+        <v>46164.52444709491</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>257</v>
@@ -6240,11 +6240,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.79249689815</v>
+        <v>46162.62583023148</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.69111056713</v>
+        <v>46164.52444390046</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6303,11 +6303,11 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.79250443287</v>
+        <v>46162.6258377662</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.69110619213</v>
+        <v>46164.52443952546</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6366,11 +6366,11 @@
         <v>264</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.79250947917</v>
+        <v>46162.6258428125</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.68453591435</v>
+        <v>46164.517869247684</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>265</v>
@@ -6413,11 +6413,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.79251295139</v>
+        <v>46162.62584628472</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.69124818287</v>
+        <v>46164.524581516205</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6476,11 +6476,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.79252873843</v>
+        <v>46162.625862071756</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.69121831018</v>
+        <v>46164.52455164352</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6529,11 +6529,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.792533518514</v>
+        <v>46162.62586685186</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.6912157176</v>
+        <v>46164.524549050926</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6582,11 +6582,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.79253825231</v>
+        <v>46162.62587158565</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.69121336806</v>
+        <v>46164.52454670139</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -6635,11 +6635,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.792543206015</v>
+        <v>46162.62587653935</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.691209490746</v>
+        <v>46164.524542824074</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -6688,11 +6688,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.792612743055</v>
+        <v>46162.62594607639</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46164.69137969907</v>
+        <v>46164.524713032406</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>278</v>
@@ -6751,11 +6751,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.79261844908</v>
+        <v>46162.62595178241</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46164.69134153935</v>
+        <v>46164.524674872686</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>190</v>
@@ -6804,11 +6804,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.7926247338</v>
+        <v>46162.62595806713</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46164.69133898148</v>
+        <v>46164.524672314816</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>190</v>
@@ -6857,11 +6857,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.792630682874</v>
+        <v>46162.6259640162</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46164.69133623842</v>
+        <v>46164.52466957176</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>190</v>
@@ -6910,11 +6910,11 @@
         <v>285</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.79263777778</v>
+        <v>46162.62597111111</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.691332372684</v>
+        <v>46164.52466570602</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>190</v>
@@ -6963,11 +6963,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.79268604166</v>
+        <v>46162.626019375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46164.6915004051</v>
+        <v>46164.524833738426</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7026,11 +7026,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.79269070602</v>
+        <v>46162.62602403935</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46164.691474872685</v>
+        <v>46164.52480820601</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>190</v>
@@ -7079,11 +7079,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.79269707176</v>
+        <v>46162.626030405096</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46164.69147140047</v>
+        <v>46164.524804733795</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>190</v>
@@ -7132,11 +7132,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.792703576386</v>
+        <v>46162.62603690972</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46164.691468171295</v>
+        <v>46164.52480150463</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>190</v>
@@ -7185,11 +7185,11 @@
         <v>294</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.79271046296</v>
+        <v>46162.62604379629</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.69146488426</v>
+        <v>46164.52479821759</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7238,11 +7238,11 @@
         <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.792744861115</v>
+        <v>46162.626078194444</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46164.691619942125</v>
+        <v>46164.52495327547</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>298</v>
@@ -7301,11 +7301,11 @@
         <v>299</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.79274982639</v>
+        <v>46162.62608315972</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46164.69158721065</v>
+        <v>46164.52492054398</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7354,11 +7354,11 @@
         <v>302</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.79275559028</v>
+        <v>46162.626088923615</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46164.69158380787</v>
+        <v>46164.5249171412</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7407,11 +7407,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.79276118056</v>
+        <v>46162.62609451389</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46164.69158106481</v>
+        <v>46164.52491439815</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>190</v>
@@ -7460,11 +7460,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.792767754625</v>
+        <v>46162.62610108797</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.69157646991</v>
+        <v>46164.52490980324</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>190</v>
@@ -7513,11 +7513,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.79285696759</v>
+        <v>46162.62619030093</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.69173954861</v>
+        <v>46164.525072881945</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>308</v>
@@ -7576,11 +7576,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.792862511575</v>
+        <v>46162.6261958449</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.69170866898</v>
+        <v>46164.525042002315</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>190</v>
@@ -7629,11 +7629,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.792868125005</v>
+        <v>46162.62620145833</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.69170596065</v>
+        <v>46164.52503929398</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>190</v>
@@ -7682,11 +7682,11 @@
         <v>313</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.792873750004</v>
+        <v>46162.62620708333</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.69170293982</v>
+        <v>46164.525036273146</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>190</v>
@@ -7735,11 +7735,11 @@
         <v>314</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.7928793287</v>
+        <v>46162.62621266204</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.691698194445</v>
+        <v>46164.52503152778</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7788,11 +7788,11 @@
         <v>315</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.792907696756</v>
+        <v>46162.62624103009</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.69185736111</v>
+        <v>46164.52519069445</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>316</v>
@@ -7849,11 +7849,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.79291289352</v>
+        <v>46162.62624622685</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.69182431713</v>
+        <v>46164.52515765047</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -7902,11 +7902,11 @@
         <v>320</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.79291758101</v>
+        <v>46162.626250914356</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.691821562505</v>
+        <v>46164.52515489583</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -7955,11 +7955,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.79292245371</v>
+        <v>46162.626255787036</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.691819155094</v>
+        <v>46164.52515248842</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8008,11 +8008,11 @@
         <v>322</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.79293256944</v>
+        <v>46162.62626590278</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.69181509259</v>
+        <v>46164.52514842592</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>
@@ -8061,11 +8061,11 @@
         <v>323</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.7930040625</v>
+        <v>46162.626337395835</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.68546163195</v>
+        <v>46164.518794965275</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>324</v>
@@ -8108,11 +8108,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.79300806713</v>
+        <v>46162.626341400464</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46164.6922515162</v>
+        <v>46164.525584849536</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>327</v>
@@ -8171,11 +8171,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.79301847222</v>
+        <v>46162.62635180556</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46164.69223148148</v>
+        <v>46164.525564814816</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8224,11 +8224,11 @@
         <v>333</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.79302525463</v>
+        <v>46162.626358587964</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46164.69222814815</v>
+        <v>46164.52556148148</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8277,11 +8277,11 @@
         <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.79303010416</v>
+        <v>46162.6263634375</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46164.69222525463</v>
+        <v>46164.525558587964</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8330,11 +8330,11 @@
         <v>336</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.79303482639</v>
+        <v>46162.62636815972</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.69222011574</v>
+        <v>46164.52555344907</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8383,11 +8383,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.79306296296</v>
+        <v>46162.6263962963</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.692368958335</v>
+        <v>46164.52570229166</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>338</v>
@@ -8446,11 +8446,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.7930678125</v>
+        <v>46162.62640114583</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.692334189815</v>
+        <v>46164.52566752315</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8499,11 +8499,11 @@
         <v>341</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.793072280096</v>
+        <v>46162.626405613424</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.6923315162</v>
+        <v>46164.52566484954</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8552,11 +8552,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.79307696759</v>
+        <v>46162.62641030093</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.69232880787</v>
+        <v>46164.525662141205</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8605,11 +8605,11 @@
         <v>344</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.79308175926</v>
+        <v>46162.62641509259</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.69232427083</v>
+        <v>46164.52565760417</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8658,11 +8658,11 @@
         <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.79314625</v>
+        <v>46162.626479583334</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46164.69248696759</v>
+        <v>46164.52582030093</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>346</v>
@@ -8721,11 +8721,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.793151550926</v>
+        <v>46162.626484884255</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46164.69246075231</v>
+        <v>46164.525794085646</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8774,11 +8774,11 @@
         <v>349</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.79315885417</v>
+        <v>46162.6264921875</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46164.692458101854</v>
+        <v>46164.52579143518</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -8827,11 +8827,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.79316501158</v>
+        <v>46162.62649834491</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46164.69245559028</v>
+        <v>46164.52578892361</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -8880,11 +8880,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.79316986111</v>
+        <v>46162.62650319445</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.69245128472</v>
+        <v>46164.525784618054</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>190</v>
@@ -8933,11 +8933,11 @@
         <v>354</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.79319725695</v>
+        <v>46162.62653059028</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.69262644676</v>
+        <v>46164.52595978009</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>355</v>
@@ -8996,11 +8996,11 @@
         <v>357</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.79320210648</v>
+        <v>46162.62653543982</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46164.692587303245</v>
+        <v>46164.52592063657</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9049,11 +9049,11 @@
         <v>358</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.793206111106</v>
+        <v>46162.62653944445</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46164.69258451389</v>
+        <v>46164.52591784722</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9102,11 +9102,11 @@
         <v>359</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.7932099537</v>
+        <v>46162.62654328704</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46164.69258188657</v>
+        <v>46164.52591521991</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9155,11 +9155,11 @@
         <v>360</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.79321400463</v>
+        <v>46162.62654733796</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46164.69257741898</v>
+        <v>46164.525910752316</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9208,11 +9208,11 @@
         <v>361</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.79323766204</v>
+        <v>46162.62657099537</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.685922812496</v>
+        <v>46164.51925614583</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>362</v>
@@ -9255,11 +9255,11 @@
         <v>364</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.79324063657</v>
+        <v>46162.62657396991</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46164.69269384259</v>
+        <v>46164.526027175925</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>365</v>
@@ -9318,11 +9318,11 @@
         <v>368</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.79324528935</v>
+        <v>46162.62657862269</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46164.69273445602</v>
+        <v>46164.52606778935</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>369</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1769,13 +1769,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.62511512732</v>
+        <v>46162.79178179398</v>
       </c>
       <c r="C4" s="5">
-        <v>46183.414665324075</v>
+        <v>46183.58133199074</v>
       </c>
       <c r="D4" s="5">
-        <v>46183.41468071759</v>
+        <v>46183.58134738426</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1822,13 +1822,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.62522459491</v>
+        <v>46162.79189126157</v>
       </c>
       <c r="C5" s="9">
-        <v>46183.414629328705</v>
+        <v>46183.58129599537</v>
       </c>
       <c r="D5" s="9">
-        <v>46183.41464973379</v>
+        <v>46183.581316400465</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1887,13 +1887,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.62522767361</v>
+        <v>46162.79189434028</v>
       </c>
       <c r="C6" s="5">
-        <v>46183.41463443287</v>
+        <v>46183.58130109953</v>
       </c>
       <c r="D6" s="5">
-        <v>46183.41464980324</v>
+        <v>46183.58131646991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1952,13 +1952,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.62523457176</v>
+        <v>46162.79190123842</v>
       </c>
       <c r="C7" s="9">
-        <v>46183.41464715278</v>
+        <v>46183.58131381945</v>
       </c>
       <c r="D7" s="9">
-        <v>46183.41466510417</v>
+        <v>46183.58133177084</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2017,13 +2017,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.62523784723</v>
+        <v>46162.791904513884</v>
       </c>
       <c r="C8" s="5">
-        <v>46183.414652974534</v>
+        <v>46183.581319641205</v>
       </c>
       <c r="D8" s="5">
-        <v>46183.41466673611</v>
+        <v>46183.58133340278</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2082,11 +2082,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.62511998843</v>
+        <v>46162.79178665509</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46164.482602222226</v>
+        <v>46164.64926888889</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2129,11 +2129,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.62524114583</v>
+        <v>46162.7919078125</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.42515527778</v>
+        <v>46195.59182194444</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2192,11 +2192,11 @@
         <v>54</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.62524625</v>
+        <v>46162.79191291667</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46183.41466920139</v>
+        <v>46183.58133586806</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>55</v>
@@ -2255,11 +2255,11 @@
         <v>58</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.62525138889</v>
+        <v>46162.791918055555</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46183.414669826394</v>
+        <v>46183.58133649305</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2318,11 +2318,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.625256307874</v>
+        <v>46162.79192297454</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46164.521635613426</v>
+        <v>46164.68830228009</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2381,11 +2381,11 @@
         <v>66</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.62512452547</v>
+        <v>46162.791791192125</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46164.49277914352</v>
+        <v>46164.65944581019</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>67</v>
@@ -2428,11 +2428,11 @@
         <v>69</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.62526353009</v>
+        <v>46162.79193019676</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46164.52170275463</v>
+        <v>46164.688369421296</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>70</v>
@@ -2491,11 +2491,11 @@
         <v>72</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.62526864583</v>
+        <v>46162.7919353125</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46164.521699675926</v>
+        <v>46164.6883663426</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>73</v>
@@ -2554,11 +2554,11 @@
         <v>75</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.625273564816</v>
+        <v>46162.79194023148</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46164.521729479166</v>
+        <v>46164.68839614584</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -2617,11 +2617,11 @@
         <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.62527862268</v>
+        <v>46162.791945289355</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46164.52181248843</v>
+        <v>46164.68847915509</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>80</v>
@@ -2680,11 +2680,11 @@
         <v>85</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.62528289352</v>
+        <v>46162.79194956018</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46164.52180534722</v>
+        <v>46164.68847201389</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>86</v>
@@ -2743,11 +2743,11 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.625286180555</v>
+        <v>46162.79195284723</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46164.52180390046</v>
+        <v>46164.688470567125</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2806,11 +2806,11 @@
         <v>91</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.625289351854</v>
+        <v>46162.79195601852</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46164.52180297454</v>
+        <v>46164.6884696412</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>92</v>
@@ -2869,11 +2869,11 @@
         <v>94</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.62512967593</v>
+        <v>46162.79179634259</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46164.4935021875</v>
+        <v>46164.66016885417</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>95</v>
@@ -2916,11 +2916,11 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.62529335648</v>
+        <v>46162.79196002315</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46164.52279099537</v>
+        <v>46164.68945766204</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2979,11 +2979,11 @@
         <v>102</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.625297708335</v>
+        <v>46162.791964375</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46164.52276619213</v>
+        <v>46164.689432858795</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3038,11 +3038,11 @@
         <v>105</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.62530216435</v>
+        <v>46162.79196883102</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46164.52276291666</v>
+        <v>46164.68942958333</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3097,11 +3097,11 @@
         <v>108</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.62530663195</v>
+        <v>46162.79197329861</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.00878244213</v>
+        <v>46169.17544910879</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3160,11 +3160,11 @@
         <v>111</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.62531083333</v>
+        <v>46162.791977500005</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46164.52287170139</v>
+        <v>46164.68953836805</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>
@@ -3219,11 +3219,11 @@
         <v>114</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.62531532407</v>
+        <v>46162.79198199074</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46168.00598047454</v>
+        <v>46168.172647141204</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>115</v>
@@ -3278,11 +3278,11 @@
         <v>117</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.625319872684</v>
+        <v>46162.79198653935</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46164.52298150463</v>
+        <v>46164.6896481713</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>118</v>
@@ -3341,11 +3341,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.62532415509</v>
+        <v>46162.79199082176</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46175.00378561343</v>
+        <v>46175.170452280094</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3400,11 +3400,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.62532864584</v>
+        <v>46162.791995312495</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46164.52295708333</v>
+        <v>46164.689623750004</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3459,11 +3459,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.625333240736</v>
+        <v>46162.79199990741</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46164.52295274306</v>
+        <v>46164.68961940972</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3518,11 +3518,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.62533775463</v>
+        <v>46162.792004421295</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46164.52311444444</v>
+        <v>46164.68978111111</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>130</v>
@@ -3581,11 +3581,11 @@
         <v>134</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.62534211806</v>
+        <v>46162.79200878472</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46164.52307152778</v>
+        <v>46164.68973819444</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>135</v>
@@ -3640,11 +3640,11 @@
         <v>137</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.62534672454</v>
+        <v>46162.792013391205</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46164.523068483795</v>
+        <v>46164.68973515046</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>138</v>
@@ -3699,11 +3699,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.625351423616</v>
+        <v>46162.79201809027</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46164.523207465274</v>
+        <v>46164.689874131946</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>
@@ -3762,11 +3762,11 @@
         <v>143</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.6254083449</v>
+        <v>46162.79207501157</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46164.52317696759</v>
+        <v>46164.68984363426</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>87</v>
@@ -3815,11 +3815,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.625413587964</v>
+        <v>46162.79208025463</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46164.52317409722</v>
+        <v>46164.68984076389</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3868,11 +3868,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.62541833334</v>
+        <v>46162.792085</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46164.52337886574</v>
+        <v>46164.69004553241</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3931,11 +3931,11 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.6254225</v>
+        <v>46162.792089166665</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46164.523292199076</v>
+        <v>46164.68995886574</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>93</v>
@@ -3984,11 +3984,11 @@
         <v>155</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.62542693287</v>
+        <v>46162.792093599535</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.523289247685</v>
+        <v>46164.68995591435</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>156</v>
@@ -4037,11 +4037,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.6254371875</v>
+        <v>46162.79210385417</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46164.5233225463</v>
+        <v>46164.68998921296</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4090,11 +4090,11 @@
         <v>162</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.62544063658</v>
+        <v>46162.79210730324</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46164.52343339121</v>
+        <v>46164.690100057865</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>163</v>
@@ -4153,11 +4153,11 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.62544451389</v>
+        <v>46162.792111180555</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46164.52349128472</v>
+        <v>46164.690157951394</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>90</v>
@@ -4206,11 +4206,11 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.62544935185</v>
+        <v>46162.79211601852</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46164.523488680556</v>
+        <v>46164.69015534723</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>168</v>
@@ -4259,11 +4259,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.625134131944</v>
+        <v>46162.791800798615</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46164.49223611111</v>
+        <v>46164.65890277778</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4306,11 +4306,11 @@
         <v>173</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.625454548615</v>
+        <v>46162.79212121527</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46179.02939460648</v>
+        <v>46179.19606127315</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>174</v>
@@ -4369,11 +4369,11 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.625460034724</v>
+        <v>46162.79212670139</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46164.523564814815</v>
+        <v>46164.69023148148</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4432,11 +4432,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.62546642361</v>
+        <v>46162.792133090275</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.52356090277</v>
+        <v>46164.690227569445</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>83</v>
@@ -4495,11 +4495,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.625480428236</v>
+        <v>46162.79214709491</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46164.52360884259</v>
+        <v>46164.69027550926</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4558,11 +4558,11 @@
         <v>189</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.625484108794</v>
+        <v>46162.792150775465</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46164.523701805556</v>
+        <v>46164.69036847222</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4611,11 +4611,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.62548818287</v>
+        <v>46162.792154849536</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46164.52369920139</v>
+        <v>46164.69036586805</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>190</v>
@@ -4664,11 +4664,11 @@
         <v>193</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.62549208333</v>
+        <v>46162.79215875</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46164.52369637731</v>
+        <v>46164.69036304398</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>190</v>
@@ -4717,11 +4717,11 @@
         <v>194</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.62549497685</v>
+        <v>46162.79216164352</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46164.523692268514</v>
+        <v>46164.690358935186</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>190</v>
@@ -4770,11 +4770,11 @@
         <v>195</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.62554516204</v>
+        <v>46162.7922118287</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.500513541665</v>
+        <v>46164.66718020833</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>196</v>
@@ -4817,11 +4817,11 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.625553425925</v>
+        <v>46162.7922200926</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46164.52381886574</v>
+        <v>46164.69048553241</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>199</v>
@@ -4880,11 +4880,11 @@
         <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.62555895833</v>
+        <v>46162.792225625</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.52388792824</v>
+        <v>46164.69055459491</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>204</v>
@@ -4943,11 +4943,11 @@
         <v>207</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.625565636576</v>
+        <v>46162.79223230324</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46164.52381575231</v>
+        <v>46164.690482418984</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>208</v>
@@ -5006,11 +5006,11 @@
         <v>210</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.62557070602</v>
+        <v>46162.79223737269</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46164.52388519676</v>
+        <v>46164.69055186343</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>211</v>
@@ -5069,11 +5069,11 @@
         <v>213</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.62557578704</v>
+        <v>46162.7922424537</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46164.52381239583</v>
+        <v>46164.6904790625</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>214</v>
@@ -5132,11 +5132,11 @@
         <v>216</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.62558024305</v>
+        <v>46162.792246909725</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.52388266203</v>
+        <v>46164.690549328705</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5195,11 +5195,11 @@
         <v>217</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.62558502315</v>
+        <v>46162.79225168981</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46164.50232085648</v>
+        <v>46164.66898752315</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5242,11 +5242,11 @@
         <v>220</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.6255878125</v>
+        <v>46162.792254479165</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.52405841435</v>
+        <v>46164.69072508102</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>
@@ -5305,11 +5305,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.62559255787</v>
+        <v>46162.79225922454</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.5240165162</v>
+        <v>46164.69068318287</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>190</v>
@@ -5358,11 +5358,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.62559891204</v>
+        <v>46162.792265578704</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.52401381945</v>
+        <v>46164.69068048611</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>190</v>
@@ -5411,11 +5411,11 @@
         <v>229</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.62560534722</v>
+        <v>46162.79227201389</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.52401086806</v>
+        <v>46164.69067753472</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>190</v>
@@ -5464,11 +5464,11 @@
         <v>232</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.62561162037</v>
+        <v>46162.79227828704</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46164.52400670139</v>
+        <v>46164.69067336805</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>190</v>
@@ -5517,11 +5517,11 @@
         <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.625655358795</v>
+        <v>46162.79232202546</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46164.52418478009</v>
+        <v>46164.69085144676</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>234</v>
@@ -5580,11 +5580,11 @@
         <v>235</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.62565987269</v>
+        <v>46162.79232653935</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46164.524149606485</v>
+        <v>46164.69081627315</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>190</v>
@@ -5633,11 +5633,11 @@
         <v>238</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.625665983796</v>
+        <v>46162.79233265047</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46164.52414706019</v>
+        <v>46164.69081372685</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>190</v>
@@ -5686,11 +5686,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.625671539354</v>
+        <v>46162.79233820602</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46164.52414630787</v>
+        <v>46164.690812974535</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>190</v>
@@ -5739,11 +5739,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.62567717592</v>
+        <v>46162.79234384259</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46164.524145034724</v>
+        <v>46164.69081170139</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>190</v>
@@ -5792,11 +5792,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.62574747685</v>
+        <v>46162.79241414352</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46164.52430971064</v>
+        <v>46164.690976377315</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>243</v>
@@ -5855,11 +5855,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.62575375</v>
+        <v>46162.79242041666</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46164.52427967593</v>
+        <v>46164.69094634259</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>190</v>
@@ -5908,11 +5908,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.625766550926</v>
+        <v>46162.79243321759</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46164.52427657407</v>
+        <v>46164.69094324074</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>190</v>
@@ -5961,11 +5961,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.625772893516</v>
+        <v>46162.79243956019</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46164.52426950232</v>
+        <v>46164.69093616898</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>190</v>
@@ -6014,11 +6014,11 @@
         <v>250</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.625779849535</v>
+        <v>46162.79244651621</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.5242687963</v>
+        <v>46164.69093546296</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>190</v>
@@ -6067,11 +6067,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.625811446764</v>
+        <v>46162.79247811342</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46164.504105960645</v>
+        <v>46164.670772627316</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>196</v>
@@ -6114,11 +6114,11 @@
         <v>253</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.62581513889</v>
+        <v>46162.792481805554</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46171.032529421296</v>
+        <v>46171.19919608797</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>254</v>
@@ -6177,11 +6177,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.62582282408</v>
+        <v>46162.79248949074</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46164.52444709491</v>
+        <v>46164.691113761575</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>257</v>
@@ -6240,11 +6240,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.62583023148</v>
+        <v>46162.79249689815</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.52444390046</v>
+        <v>46164.69111056713</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6303,11 +6303,11 @@
         <v>261</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.6258377662</v>
+        <v>46162.79250443287</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.52443952546</v>
+        <v>46164.69110619213</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6366,11 +6366,11 @@
         <v>264</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.6258428125</v>
+        <v>46162.79250947917</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.517869247684</v>
+        <v>46164.68453591435</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>265</v>
@@ -6413,11 +6413,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.62584628472</v>
+        <v>46162.79251295139</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.524581516205</v>
+        <v>46164.69124818287</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6476,11 +6476,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.625862071756</v>
+        <v>46162.79252873843</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.52455164352</v>
+        <v>46164.69121831018</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>190</v>
@@ -6529,11 +6529,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.62586685186</v>
+        <v>46162.792533518514</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.524549050926</v>
+        <v>46164.6912157176</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>190</v>
@@ -6582,11 +6582,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.62587158565</v>
+        <v>46162.79253825231</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.52454670139</v>
+        <v>46164.69121336806</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>190</v>
@@ -6635,11 +6635,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.62587653935</v>
+        <v>46162.792543206015</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.524542824074</v>
+        <v>46164.691209490746</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>190</v>
@@ -6688,11 +6688,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.62594607639</v>
+        <v>46162.792612743055</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46164.524713032406</v>
+        <v>46164.69137969907</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>278</v>
@@ -6751,11 +6751,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.62595178241</v>
+        <v>46162.79261844908</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46164.524674872686</v>
+        <v>46164.69134153935</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>190</v>
@@ -6804,11 +6804,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.62595806713</v>
+        <v>46162.7926247338</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46164.524672314816</v>
+        <v>46164.69133898148</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>190</v>
@@ -6857,11 +6857,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.6259640162</v>
+        <v>46162.792630682874</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46164.52466957176</v>
+        <v>46164.69133623842</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>190</v>
@@ -6910,11 +6910,11 @@
         <v>285</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.62597111111</v>
+        <v>46162.79263777778</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.52466570602</v>
+        <v>46164.691332372684</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>190</v>
@@ -6963,11 +6963,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.626019375</v>
+        <v>46162.79268604166</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46164.524833738426</v>
+        <v>46164.6915004051</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>287</v>
@@ -7026,11 +7026,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.62602403935</v>
+        <v>46162.79269070602</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46164.52480820601</v>
+        <v>46164.691474872685</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>190</v>
@@ -7079,11 +7079,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.626030405096</v>
+        <v>46162.79269707176</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46164.524804733795</v>
+        <v>46164.69147140047</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>190</v>
@@ -7132,11 +7132,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.62603690972</v>
+        <v>46162.792703576386</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46164.52480150463</v>
+        <v>46164.691468171295</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>190</v>
@@ -7185,11 +7185,11 @@
         <v>294</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.62604379629</v>
+        <v>46162.79271046296</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.52479821759</v>
+        <v>46164.69146488426</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>190</v>
@@ -7238,11 +7238,11 @@
         <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.626078194444</v>
+        <v>46162.792744861115</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46164.52495327547</v>
+        <v>46164.691619942125</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>298</v>
@@ -7301,11 +7301,11 @@
         <v>299</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.62608315972</v>
+        <v>46162.79274982639</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46164.52492054398</v>
+        <v>46164.69158721065</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>190</v>
@@ -7354,11 +7354,11 @@
         <v>302</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.626088923615</v>
+        <v>46162.79275559028</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46164.5249171412</v>
+        <v>46164.69158380787</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>190</v>
@@ -7407,11 +7407,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.62609451389</v>
+        <v>46162.79276118056</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46164.52491439815</v>
+        <v>46164.69158106481</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>190</v>
@@ -7460,11 +7460,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.62610108797</v>
+        <v>46162.792767754625</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.52490980324</v>
+        <v>46164.69157646991</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>190</v>
@@ -7513,11 +7513,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.62619030093</v>
+        <v>46162.79285696759</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.525072881945</v>
+        <v>46164.69173954861</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>308</v>
@@ -7576,11 +7576,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.6261958449</v>
+        <v>46162.792862511575</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.525042002315</v>
+        <v>46164.69170866898</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>190</v>
@@ -7629,11 +7629,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.62620145833</v>
+        <v>46162.792868125005</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.52503929398</v>
+        <v>46164.69170596065</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>190</v>
@@ -7682,11 +7682,11 @@
         <v>313</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.62620708333</v>
+        <v>46162.792873750004</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.525036273146</v>
+        <v>46164.69170293982</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>190</v>
@@ -7735,11 +7735,11 @@
         <v>314</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.62621266204</v>
+        <v>46162.7928793287</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.52503152778</v>
+        <v>46164.691698194445</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>190</v>
@@ -7788,11 +7788,11 @@
         <v>315</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.62624103009</v>
+        <v>46162.792907696756</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.52519069445</v>
+        <v>46164.69185736111</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>316</v>
@@ -7849,11 +7849,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.62624622685</v>
+        <v>46162.79291289352</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.52515765047</v>
+        <v>46164.69182431713</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>190</v>
@@ -7902,11 +7902,11 @@
         <v>320</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.626250914356</v>
+        <v>46162.79291758101</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.52515489583</v>
+        <v>46164.691821562505</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>190</v>
@@ -7955,11 +7955,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.626255787036</v>
+        <v>46162.79292245371</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.52515248842</v>
+        <v>46164.691819155094</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>190</v>
@@ -8008,11 +8008,11 @@
         <v>322</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.62626590278</v>
+        <v>46162.79293256944</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.52514842592</v>
+        <v>46164.69181509259</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>190</v>
@@ -8061,11 +8061,11 @@
         <v>323</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.626337395835</v>
+        <v>46162.7930040625</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.518794965275</v>
+        <v>46164.68546163195</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>324</v>
@@ -8108,11 +8108,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.626341400464</v>
+        <v>46162.79300806713</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46164.525584849536</v>
+        <v>46164.6922515162</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>327</v>
@@ -8171,11 +8171,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.62635180556</v>
+        <v>46162.79301847222</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46164.525564814816</v>
+        <v>46164.69223148148</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>190</v>
@@ -8224,11 +8224,11 @@
         <v>333</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.626358587964</v>
+        <v>46162.79302525463</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46164.52556148148</v>
+        <v>46164.69222814815</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>190</v>
@@ -8277,11 +8277,11 @@
         <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.6263634375</v>
+        <v>46162.79303010416</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46164.525558587964</v>
+        <v>46164.69222525463</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>190</v>
@@ -8330,11 +8330,11 @@
         <v>336</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.62636815972</v>
+        <v>46162.79303482639</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.52555344907</v>
+        <v>46164.69222011574</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>190</v>
@@ -8383,11 +8383,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.6263962963</v>
+        <v>46162.79306296296</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.52570229166</v>
+        <v>46164.692368958335</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>338</v>
@@ -8446,11 +8446,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.62640114583</v>
+        <v>46162.7930678125</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.52566752315</v>
+        <v>46164.692334189815</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>190</v>
@@ -8499,11 +8499,11 @@
         <v>341</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.626405613424</v>
+        <v>46162.793072280096</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.52566484954</v>
+        <v>46164.6923315162</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>190</v>
@@ -8552,11 +8552,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.62641030093</v>
+        <v>46162.79307696759</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.525662141205</v>
+        <v>46164.69232880787</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>190</v>
@@ -8605,11 +8605,11 @@
         <v>344</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.62641509259</v>
+        <v>46162.79308175926</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.52565760417</v>
+        <v>46164.69232427083</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>190</v>
@@ -8658,11 +8658,11 @@
         <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.626479583334</v>
+        <v>46162.79314625</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46164.52582030093</v>
+        <v>46164.69248696759</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>346</v>
@@ -8721,11 +8721,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.626484884255</v>
+        <v>46162.793151550926</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46164.525794085646</v>
+        <v>46164.69246075231</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>190</v>
@@ -8774,11 +8774,11 @@
         <v>349</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.6264921875</v>
+        <v>46162.79315885417</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46164.52579143518</v>
+        <v>46164.692458101854</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>190</v>
@@ -8827,11 +8827,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.62649834491</v>
+        <v>46162.79316501158</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46164.52578892361</v>
+        <v>46164.69245559028</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>190</v>
@@ -8880,11 +8880,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.62650319445</v>
+        <v>46162.79316986111</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.525784618054</v>
+        <v>46164.69245128472</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>190</v>
@@ -8933,11 +8933,11 @@
         <v>354</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.62653059028</v>
+        <v>46162.79319725695</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.52595978009</v>
+        <v>46164.69262644676</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>355</v>
@@ -8996,11 +8996,11 @@
         <v>357</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.62653543982</v>
+        <v>46162.79320210648</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46164.52592063657</v>
+        <v>46164.692587303245</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>190</v>
@@ -9049,11 +9049,11 @@
         <v>358</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.62653944445</v>
+        <v>46162.793206111106</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46164.52591784722</v>
+        <v>46164.69258451389</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>190</v>
@@ -9102,11 +9102,11 @@
         <v>359</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.62654328704</v>
+        <v>46162.7932099537</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46164.52591521991</v>
+        <v>46164.69258188657</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>190</v>
@@ -9155,11 +9155,11 @@
         <v>360</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.62654733796</v>
+        <v>46162.79321400463</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46164.525910752316</v>
+        <v>46164.69257741898</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>190</v>
@@ -9208,11 +9208,11 @@
         <v>361</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.62657099537</v>
+        <v>46162.79323766204</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.51925614583</v>
+        <v>46164.685922812496</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>362</v>
@@ -9255,11 +9255,11 @@
         <v>364</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.62657396991</v>
+        <v>46162.79324063657</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46164.526027175925</v>
+        <v>46164.69269384259</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>365</v>
@@ -9318,11 +9318,11 @@
         <v>368</v>
       </c>
       <c r="B137" s="9">
-        <v>46162.62657862269</v>
+        <v>46162.79324528935</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46164.52606778935</v>
+        <v>46164.69273445602</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>369</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46195.59182194444</v>
+        <v>46196.593818877314</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46164.65944581019</v>
+        <v>46197.5874947338</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>67</v>
@@ -2556,9 +2556,11 @@
       <c r="B17" s="9">
         <v>46162.79194023148</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9">
+        <v>46197.5874865625</v>
+      </c>
       <c r="D17" s="9">
-        <v>46164.68839614584</v>
+        <v>46197.587506446755</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -2606,10 +2608,10 @@
         <v>52</v>
       </c>
       <c r="T17" s="10">
-        <v>0</v>
-      </c>
-      <c r="U17" s="11" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -3164,7 +3166,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46164.68953836805</v>
+        <v>46197.58749420139</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>112</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="372">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -176,7 +176,9 @@
     <t>cperez@zitron.com</t>
   </si>
   <si>
-    <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
+    <t xml:space="preserve">MOTOR
+        OT 4326 — ZVN 1-12-55/4 -- COD 350015
+</t>
   </si>
   <si>
     <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
@@ -185,106 +187,118 @@
     <t>Baja</t>
   </si>
   <si>
+    <t>1214982558008064</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodete:
+        OT 4326 Ventilador ZVN 1-12-55/4 --- COD. ALABES: 300004
+</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta alabes,propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>1214982580298731</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P.1553
+        OT 4326: 4 ventiladores ZVN 1-12-55/4
+    Planos para:
+        Ventilador ZVN 1-12-55/4 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 120/200 + VENT + FAR 120/200 + Difusor 120-160 / long 160
+        Alcance Chile: TOBERA + REJILLA + VENT
+        Alcance Colombia: FAR + DIFUSOR
+    Rodete:
+        Ventilador ZVN 1-12-55/4 --- ALABES: 300004
+    Tratamiento superficial:
+        Estándar Zitrón con 2 capas y color de terminación Blanco RAL 9001.
+    Datos eléctricos para el motor:
+        440V, 60HZ, IP55, IE-3, 1000 MSNM.
+        Incluye: Sensor de vibraciones VKV 021 y Graseras automáticas con protección mecánica.
+</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1214982508454946</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
-    <t>1214982558008064</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Selección de Rodete:
-        Rodete de placas s/plano 3073.00
-        Alabe s/ plano 3073.01
-        Z8 N600
-        Código 300003
-        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
-</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta alabes,propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>1214982580298731</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1214982508454946</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
+    <t>1214969047721205</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete,propuesta Corte Laser,propuesta motor,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1214982580322545</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1214982580322567</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1214982595205412</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1214982558032148</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214969047721205</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete,propuesta Corte Laser,propuesta motor,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1214982580322545</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1214982580322567</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1214982595205412</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1214982558032148</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser</t>
   </si>
   <si>
     <t>1214982558032165</t>
@@ -2086,7 +2100,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46164.64926888889</v>
+        <v>46197.66270453704</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2131,9 +2145,11 @@
       <c r="B10" s="5">
         <v>46162.7919078125</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46197.659032407406</v>
+      </c>
       <c r="D10" s="5">
-        <v>46196.593818877314</v>
+        <v>46197.65904699074</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2181,25 +2197,27 @@
         <v>52</v>
       </c>
       <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="12" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="9">
         <v>46162.79191291667</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46197.660673125</v>
+      </c>
       <c r="D11" s="9">
-        <v>46183.58133586806</v>
+        <v>46197.66068810185</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
@@ -2220,7 +2238,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2232,7 +2250,7 @@
         <v>37</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q11" s="9">
         <v>46149</v>
@@ -2244,25 +2262,27 @@
         <v>52</v>
       </c>
       <c r="T11" s="10">
-        <v>0</v>
-      </c>
-      <c r="U11" s="12" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="5">
         <v>46162.791918055555</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46197.66269631944</v>
+      </c>
       <c r="D12" s="5">
-        <v>46183.58133649305</v>
+        <v>46197.66271325231</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2283,7 +2303,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2307,10 +2327,10 @@
         <v>52</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="12" t="s">
-        <v>53</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -2322,7 +2342,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46164.68830228009</v>
+        <v>46197.66271351852</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2372,7 +2392,7 @@
       <c r="T13" s="10">
         <v>0</v>
       </c>
-      <c r="U13" s="11" t="s">
+      <c r="U13" s="12" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2432,7 +2452,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46164.688369421296</v>
+        <v>46197.659049317124</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>70</v>
@@ -2482,7 +2502,7 @@
       <c r="T15" s="10">
         <v>0</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="U15" s="12" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2495,7 +2515,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46164.6883663426</v>
+        <v>46197.66069275463</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>73</v>
@@ -2528,7 +2548,7 @@
         <v>67</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>74</v>
@@ -2545,7 +2565,7 @@
       <c r="T16" s="6">
         <v>0</v>
       </c>
-      <c r="U16" s="11" t="s">
+      <c r="U16" s="12" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2560,7 +2580,7 @@
         <v>46197.5874865625</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.587506446755</v>
+        <v>46197.6606925</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>76</v>
@@ -2593,7 +2613,7 @@
         <v>67</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P17" s="10" t="s">
         <v>78</v>
@@ -2610,8 +2630,8 @@
       <c r="T17" s="10">
         <v>1</v>
       </c>
-      <c r="U17" s="7" t="s">
-        <v>27</v>
+      <c r="U17" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2674,12 +2694,12 @@
         <v>0</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" s="9">
         <v>46162.79194956018</v>
@@ -2689,7 +2709,7 @@
         <v>46164.68847201389</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2722,7 +2742,7 @@
         <v>83</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2737,12 +2757,12 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" s="5">
         <v>46162.79195284723</v>
@@ -2752,7 +2772,7 @@
         <v>46164.688470567125</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2785,7 +2805,7 @@
         <v>83</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2800,12 +2820,12 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B21" s="9">
         <v>46162.79195601852</v>
@@ -2815,7 +2835,7 @@
         <v>46164.6884696412</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2848,7 +2868,7 @@
         <v>83</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q21" s="9">
         <v>46237</v>
@@ -2863,12 +2883,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B22" s="5">
         <v>46162.79179634259</v>
@@ -2878,7 +2898,7 @@
         <v>46164.66016885417</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2902,7 +2922,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2915,7 +2935,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="9">
         <v>46162.79196002315</v>
@@ -2925,16 +2945,16 @@
         <v>46164.68945766204</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
@@ -2952,13 +2972,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="9">
         <v>46162</v>
@@ -2973,12 +2993,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
         <v>46162.791964375</v>
@@ -2988,16 +3008,16 @@
         <v>46164.689432858795</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I24" s="5">
         <v>46162</v>
@@ -3015,13 +3035,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>73</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3032,12 +3052,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="9">
         <v>46162.79196883102</v>
@@ -3047,16 +3067,16 @@
         <v>46164.68942958333</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I25" s="9">
         <v>46167</v>
@@ -3074,13 +3094,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3091,12 +3111,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46162.79197329861</v>
@@ -3106,16 +3126,16 @@
         <v>46169.17544910879</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
@@ -3133,13 +3153,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q26" s="5">
         <v>46162</v>
@@ -3154,12 +3174,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="9">
         <v>46162.791977500005</v>
@@ -3169,16 +3189,16 @@
         <v>46197.58749420139</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I27" s="9">
         <v>46162</v>
@@ -3196,13 +3216,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>76</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3213,12 +3233,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="5">
         <v>46162.79198199074</v>
@@ -3228,16 +3248,16 @@
         <v>46168.172647141204</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I28" s="5">
         <v>46167</v>
@@ -3255,13 +3275,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3272,12 +3292,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B29" s="9">
         <v>46162.79198653935</v>
@@ -3287,16 +3307,16 @@
         <v>46164.6896481713</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3314,13 +3334,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q29" s="9">
         <v>46155</v>
@@ -3335,12 +3355,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46162.79199082176</v>
@@ -3350,16 +3370,16 @@
         <v>46175.170452280094</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I30" s="5">
         <v>46155</v>
@@ -3377,13 +3397,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>70</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3394,12 +3414,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46162.791995312495</v>
@@ -3409,16 +3429,16 @@
         <v>46164.689623750004</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3436,13 +3456,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3453,12 +3473,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46162.79199990741</v>
@@ -3468,16 +3488,16 @@
         <v>46164.68961940972</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I32" s="5">
         <v>46176</v>
@@ -3495,13 +3515,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3512,12 +3532,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46162.792004421295</v>
@@ -3527,16 +3547,16 @@
         <v>46164.68978111111</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
@@ -3554,13 +3574,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q33" s="9">
         <v>46239</v>
@@ -3575,12 +3595,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46162.79200878472</v>
@@ -3590,16 +3610,16 @@
         <v>46164.68973819444</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I34" s="5">
         <v>46239</v>
@@ -3617,13 +3637,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>80</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3634,12 +3654,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="9">
         <v>46162.792013391205</v>
@@ -3649,16 +3669,16 @@
         <v>46164.68973515046</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I35" s="9">
         <v>46241</v>
@@ -3676,13 +3696,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3693,12 +3713,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79201809027</v>
@@ -3708,16 +3728,16 @@
         <v>46164.689874131946</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
@@ -3735,10 +3755,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3756,12 +3776,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79207501157</v>
@@ -3771,16 +3791,16 @@
         <v>46164.68984363426</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46239</v>
@@ -3798,13 +3818,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3814,7 +3834,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46162.79208025463</v>
@@ -3824,16 +3844,16 @@
         <v>46164.68984076389</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46241</v>
@@ -3851,13 +3871,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3867,7 +3887,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792085</v>
@@ -3877,16 +3897,16 @@
         <v>46164.69004553241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3904,10 +3924,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3925,12 +3945,12 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792089166665</v>
@@ -3940,16 +3960,16 @@
         <v>46164.68995886574</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I40" s="5">
         <v>46239</v>
@@ -3967,13 +3987,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3983,7 +4003,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B41" s="9">
         <v>46162.792093599535</v>
@@ -3993,16 +4013,16 @@
         <v>46164.68995591435</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="9">
         <v>46248</v>
@@ -4020,13 +4040,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4036,7 +4056,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210385417</v>
@@ -4046,16 +4066,16 @@
         <v>46164.68998921296</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I42" s="5">
         <v>46279</v>
@@ -4073,10 +4093,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4089,7 +4109,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B43" s="9">
         <v>46162.79210730324</v>
@@ -4099,16 +4119,16 @@
         <v>46164.690100057865</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
@@ -4126,10 +4146,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4147,12 +4167,12 @@
         <v>0</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46162.792111180555</v>
@@ -4162,16 +4182,16 @@
         <v>46164.690157951394</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I44" s="5">
         <v>46239</v>
@@ -4189,13 +4209,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4205,7 +4225,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46162.79211601852</v>
@@ -4215,16 +4235,16 @@
         <v>46164.69015534723</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I45" s="9">
         <v>46241</v>
@@ -4242,13 +4262,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4258,7 +4278,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46162.791800798615</v>
@@ -4268,7 +4288,7 @@
         <v>46164.65890277778</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4292,7 +4312,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4305,26 +4325,26 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212121527</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46179.19606127315</v>
+        <v>46197.66271414352</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I47" s="9">
         <v>46160</v>
@@ -4342,13 +4362,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46160</v>
@@ -4362,13 +4382,13 @@
       <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="11" t="s">
+      <c r="U47" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46162.79212670139</v>
@@ -4378,16 +4398,16 @@
         <v>46164.69023148148</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I48" s="5">
         <v>46216</v>
@@ -4405,13 +4425,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46216</v>
@@ -4426,12 +4446,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46162.792133090275</v>
@@ -4447,10 +4467,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I49" s="9">
         <v>46234</v>
@@ -4468,13 +4488,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q49" s="9">
         <v>46234</v>
@@ -4489,12 +4509,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46162.79214709491</v>
@@ -4504,16 +4524,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4531,10 +4551,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4552,12 +4572,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792150775465</v>
@@ -4567,16 +4587,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4594,13 +4614,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4610,7 +4630,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46162.792154849536</v>
@@ -4620,16 +4640,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4647,13 +4667,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4663,7 +4683,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79215875</v>
@@ -4673,16 +4693,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4700,13 +4720,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4716,7 +4736,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46162.79216164352</v>
@@ -4726,16 +4746,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="5">
         <v>46322</v>
@@ -4753,13 +4773,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4769,7 +4789,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922118287</v>
@@ -4779,7 +4799,7 @@
         <v>46164.66718020833</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4803,7 +4823,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4816,7 +4836,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46162.7922200926</v>
@@ -4826,16 +4846,16 @@
         <v>46164.69048553241</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I56" s="5">
         <v>46252</v>
@@ -4853,13 +4873,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46252</v>
@@ -4874,12 +4894,12 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46162.792225625</v>
@@ -4889,16 +4909,16 @@
         <v>46164.69055459491</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I57" s="9">
         <v>46254</v>
@@ -4916,13 +4936,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46254</v>
@@ -4937,12 +4957,12 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223230324</v>
@@ -4952,16 +4972,16 @@
         <v>46164.690482418984</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I58" s="5">
         <v>46252</v>
@@ -4979,13 +4999,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="5">
         <v>46252</v>
@@ -5000,12 +5020,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
         <v>46162.79223737269</v>
@@ -5015,16 +5035,16 @@
         <v>46164.69055186343</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I59" s="9">
         <v>46254</v>
@@ -5042,13 +5062,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="9">
         <v>46254</v>
@@ -5063,12 +5083,12 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46162.7922424537</v>
@@ -5078,16 +5098,16 @@
         <v>46164.6904790625</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46252</v>
@@ -5105,13 +5125,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q60" s="5">
         <v>46252</v>
@@ -5126,12 +5146,12 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46162.792246909725</v>
@@ -5141,16 +5161,16 @@
         <v>46164.690549328705</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I61" s="9">
         <v>46254</v>
@@ -5168,13 +5188,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="9">
         <v>46254</v>
@@ -5189,12 +5209,12 @@
         <v>0</v>
       </c>
       <c r="U61" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
         <v>46162.79225168981</v>
@@ -5204,7 +5224,7 @@
         <v>46164.66898752315</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5228,7 +5248,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5241,7 +5261,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46162.792254479165</v>
@@ -5251,16 +5271,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5278,13 +5298,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q63" s="9">
         <v>46258</v>
@@ -5299,12 +5319,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46162.79225922454</v>
@@ -5314,16 +5334,16 @@
         <v>46164.69068318287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5341,13 +5361,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5357,7 +5377,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46162.792265578704</v>
@@ -5367,16 +5387,16 @@
         <v>46164.69068048611</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5394,13 +5414,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5410,7 +5430,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227201389</v>
@@ -5420,16 +5440,16 @@
         <v>46164.69067753472</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5447,13 +5467,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5463,7 +5483,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79227828704</v>
@@ -5473,16 +5493,16 @@
         <v>46164.69067336805</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I67" s="9">
         <v>46258</v>
@@ -5500,13 +5520,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5516,7 +5536,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232202546</v>
@@ -5526,16 +5546,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5553,13 +5573,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q68" s="5">
         <v>46267</v>
@@ -5574,12 +5594,12 @@
         <v>0</v>
       </c>
       <c r="U68" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79232653935</v>
@@ -5589,16 +5609,16 @@
         <v>46164.69081627315</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5616,13 +5636,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5632,7 +5652,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233265047</v>
@@ -5642,16 +5662,16 @@
         <v>46164.69081372685</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5669,13 +5689,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5685,7 +5705,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79233820602</v>
@@ -5695,16 +5715,16 @@
         <v>46164.690812974535</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5722,13 +5742,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5738,7 +5758,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79234384259</v>
@@ -5748,16 +5768,16 @@
         <v>46164.69081170139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -5775,13 +5795,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5791,7 +5811,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79241414352</v>
@@ -5801,16 +5821,16 @@
         <v>46164.690976377315</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5828,13 +5848,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q73" s="9">
         <v>46289</v>
@@ -5849,12 +5869,12 @@
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79242041666</v>
@@ -5864,16 +5884,16 @@
         <v>46164.69094634259</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -5891,13 +5911,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5907,7 +5927,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243321759</v>
@@ -5917,16 +5937,16 @@
         <v>46164.69094324074</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -5944,13 +5964,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5960,7 +5980,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79243956019</v>
@@ -5970,16 +5990,16 @@
         <v>46164.69093616898</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -5997,13 +6017,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6013,7 +6033,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79244651621</v>
@@ -6023,16 +6043,16 @@
         <v>46164.69093546296</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I77" s="9">
         <v>46289</v>
@@ -6050,13 +6070,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6066,7 +6086,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46162.79247811342</v>
@@ -6076,7 +6096,7 @@
         <v>46164.670772627316</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6100,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6113,7 +6133,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
         <v>46162.792481805554</v>
@@ -6123,16 +6143,16 @@
         <v>46171.19919608797</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I79" s="9">
         <v>46169</v>
@@ -6150,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q79" s="9">
         <v>46169</v>
@@ -6171,12 +6191,12 @@
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79248949074</v>
@@ -6186,16 +6206,16 @@
         <v>46164.691113761575</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I80" s="5">
         <v>46279</v>
@@ -6213,13 +6233,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q80" s="5">
         <v>46279</v>
@@ -6234,12 +6254,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79249689815</v>
@@ -6249,16 +6269,16 @@
         <v>46164.69111056713</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I81" s="9">
         <v>46302</v>
@@ -6276,13 +6296,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q81" s="9">
         <v>46302</v>
@@ -6297,12 +6317,12 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250443287</v>
@@ -6312,16 +6332,16 @@
         <v>46164.69110619213</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I82" s="5">
         <v>46280</v>
@@ -6339,13 +6359,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q82" s="5">
         <v>46280</v>
@@ -6360,12 +6380,12 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79250947917</v>
@@ -6375,7 +6395,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6399,7 +6419,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6412,7 +6432,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79251295139</v>
@@ -6422,7 +6442,7 @@
         <v>46164.69124818287</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6449,13 +6469,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q84" s="5">
         <v>46293</v>
@@ -6470,12 +6490,12 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B85" s="9">
         <v>46162.79252873843</v>
@@ -6485,7 +6505,7 @@
         <v>46164.69121831018</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6512,10 +6532,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6528,7 +6548,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B86" s="5">
         <v>46162.792533518514</v>
@@ -6538,7 +6558,7 @@
         <v>46164.6912157176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6565,10 +6585,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6581,7 +6601,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B87" s="9">
         <v>46162.79253825231</v>
@@ -6591,7 +6611,7 @@
         <v>46164.69121336806</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6618,13 +6638,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6634,7 +6654,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792543206015</v>
@@ -6644,7 +6664,7 @@
         <v>46164.691209490746</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6671,13 +6691,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6687,7 +6707,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B89" s="9">
         <v>46162.792612743055</v>
@@ -6697,7 +6717,7 @@
         <v>46164.69137969907</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6724,13 +6744,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q89" s="9">
         <v>46311</v>
@@ -6745,12 +6765,12 @@
         <v>0</v>
       </c>
       <c r="U89" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B90" s="5">
         <v>46162.79261844908</v>
@@ -6760,7 +6780,7 @@
         <v>46164.69134153935</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6787,13 +6807,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6803,7 +6823,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B91" s="9">
         <v>46162.7926247338</v>
@@ -6813,7 +6833,7 @@
         <v>46164.69133898148</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6840,13 +6860,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6856,7 +6876,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B92" s="5">
         <v>46162.792630682874</v>
@@ -6866,7 +6886,7 @@
         <v>46164.69133623842</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6893,13 +6913,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6909,7 +6929,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79263777778</v>
@@ -6919,7 +6939,7 @@
         <v>46164.691332372684</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6946,13 +6966,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6962,7 +6982,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79268604166</v>
@@ -6972,7 +6992,7 @@
         <v>46164.6915004051</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6999,13 +7019,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q94" s="5">
         <v>46315</v>
@@ -7020,12 +7040,12 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269070602</v>
@@ -7035,7 +7055,7 @@
         <v>46164.691474872685</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7062,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7078,7 +7098,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B96" s="5">
         <v>46162.79269707176</v>
@@ -7088,7 +7108,7 @@
         <v>46164.69147140047</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7115,13 +7135,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7131,7 +7151,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B97" s="9">
         <v>46162.792703576386</v>
@@ -7141,7 +7161,7 @@
         <v>46164.691468171295</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7168,13 +7188,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7184,7 +7204,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B98" s="5">
         <v>46162.79271046296</v>
@@ -7194,7 +7214,7 @@
         <v>46164.69146488426</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7221,13 +7241,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7237,7 +7257,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B99" s="9">
         <v>46162.792744861115</v>
@@ -7247,7 +7267,7 @@
         <v>46164.691619942125</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7274,13 +7294,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q99" s="9">
         <v>46317</v>
@@ -7295,12 +7315,12 @@
         <v>0</v>
       </c>
       <c r="U99" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79274982639</v>
@@ -7310,7 +7330,7 @@
         <v>46164.69158721065</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7337,13 +7357,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7353,7 +7373,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79275559028</v>
@@ -7363,7 +7383,7 @@
         <v>46164.69158380787</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7390,13 +7410,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7406,7 +7426,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46162.79276118056</v>
@@ -7416,7 +7436,7 @@
         <v>46164.69158106481</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7443,13 +7463,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7459,7 +7479,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" s="9">
         <v>46162.792767754625</v>
@@ -7469,7 +7489,7 @@
         <v>46164.69157646991</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7496,13 +7516,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7512,7 +7532,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
         <v>46162.79285696759</v>
@@ -7522,7 +7542,7 @@
         <v>46164.69173954861</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7549,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q104" s="5">
         <v>46321</v>
@@ -7570,12 +7590,12 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792862511575</v>
@@ -7585,7 +7605,7 @@
         <v>46164.69170866898</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7612,13 +7632,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7628,7 +7648,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792868125005</v>
@@ -7638,7 +7658,7 @@
         <v>46164.69170596065</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7665,13 +7685,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7681,7 +7701,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B107" s="9">
         <v>46162.792873750004</v>
@@ -7691,7 +7711,7 @@
         <v>46164.69170293982</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7718,13 +7738,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7734,7 +7754,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B108" s="5">
         <v>46162.7928793287</v>
@@ -7744,7 +7764,7 @@
         <v>46164.691698194445</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7771,13 +7791,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7787,7 +7807,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B109" s="9">
         <v>46162.792907696756</v>
@@ -7797,7 +7817,7 @@
         <v>46164.69185736111</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7822,13 +7842,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q109" s="9">
         <v>46323</v>
@@ -7843,12 +7863,12 @@
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291289352</v>
@@ -7858,7 +7878,7 @@
         <v>46164.69182431713</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7885,13 +7905,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7901,7 +7921,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79291758101</v>
@@ -7911,7 +7931,7 @@
         <v>46164.691821562505</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7938,13 +7958,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7954,7 +7974,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79292245371</v>
@@ -7964,7 +7984,7 @@
         <v>46164.691819155094</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7991,13 +8011,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8007,7 +8027,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B113" s="9">
         <v>46162.79293256944</v>
@@ -8017,7 +8037,7 @@
         <v>46164.69181509259</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8044,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8060,7 +8080,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B114" s="5">
         <v>46162.7930040625</v>
@@ -8070,7 +8090,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8094,7 +8114,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8107,7 +8127,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79300806713</v>
@@ -8117,16 +8137,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8144,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q115" s="9">
         <v>46324</v>
@@ -8165,12 +8185,12 @@
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79301847222</v>
@@ -8180,16 +8200,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8207,13 +8227,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8223,7 +8243,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79302525463</v>
@@ -8233,16 +8253,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8260,13 +8280,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8276,7 +8296,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303010416</v>
@@ -8286,16 +8306,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8313,13 +8333,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8329,7 +8349,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79303482639</v>
@@ -8339,16 +8359,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I119" s="9">
         <v>46324</v>
@@ -8366,13 +8386,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8382,7 +8402,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B120" s="5">
         <v>46162.79306296296</v>
@@ -8392,7 +8412,7 @@
         <v>46164.692368958335</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8419,13 +8439,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q120" s="5">
         <v>46325</v>
@@ -8440,12 +8460,12 @@
         <v>0</v>
       </c>
       <c r="U120" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B121" s="9">
         <v>46162.7930678125</v>
@@ -8455,7 +8475,7 @@
         <v>46164.692334189815</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8482,13 +8502,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8498,7 +8518,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B122" s="5">
         <v>46162.793072280096</v>
@@ -8508,7 +8528,7 @@
         <v>46164.6923315162</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8535,13 +8555,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8551,7 +8571,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79307696759</v>
@@ -8561,7 +8581,7 @@
         <v>46164.69232880787</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8588,13 +8608,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8604,7 +8624,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79308175926</v>
@@ -8614,7 +8634,7 @@
         <v>46164.69232427083</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8641,13 +8661,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8657,7 +8677,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B125" s="9">
         <v>46162.79314625</v>
@@ -8667,16 +8687,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8694,13 +8714,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q125" s="9">
         <v>46328</v>
@@ -8715,12 +8735,12 @@
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B126" s="5">
         <v>46162.793151550926</v>
@@ -8730,16 +8750,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8757,13 +8777,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8773,7 +8793,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79315885417</v>
@@ -8783,16 +8803,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8810,13 +8830,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8826,7 +8846,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316501158</v>
@@ -8836,16 +8856,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8863,13 +8883,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8879,7 +8899,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79316986111</v>
@@ -8889,16 +8909,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I129" s="9">
         <v>46328</v>
@@ -8916,13 +8936,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8932,7 +8952,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79319725695</v>
@@ -8942,16 +8962,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -8969,13 +8989,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q130" s="5">
         <v>46329</v>
@@ -8990,12 +9010,12 @@
         <v>0</v>
       </c>
       <c r="U130" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B131" s="9">
         <v>46162.79320210648</v>
@@ -9005,16 +9025,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9032,13 +9052,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9048,7 +9068,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B132" s="5">
         <v>46162.793206111106</v>
@@ -9058,16 +9078,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9085,13 +9105,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9101,7 +9121,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B133" s="9">
         <v>46162.7932099537</v>
@@ -9111,16 +9131,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9138,13 +9158,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9154,7 +9174,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79321400463</v>
@@ -9164,16 +9184,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I134" s="5">
         <v>46329</v>
@@ -9191,13 +9211,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9207,7 +9227,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79323766204</v>
@@ -9217,7 +9237,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9241,7 +9261,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9254,7 +9274,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324063657</v>
@@ -9264,16 +9284,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I136" s="5">
         <v>46330</v>
@@ -9291,13 +9311,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>
@@ -9312,12 +9332,12 @@
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B137" s="9">
         <v>46162.79324528935</v>
@@ -9327,7 +9347,7 @@
         <v>46164.69273445602</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9354,13 +9374,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q137" s="9">
         <v>46330</v>
@@ -9375,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="U137" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="374">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -571,28 +571,34 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214995680435931</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214995680437154</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214995680435931</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214995680437154</t>
   </si>
   <si>
     <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,propuesta Corte Laser,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,Propuesta Corte plasma ,Propuesta Mecanizado,Propuesta Fabricación externa ,OT 4326- ZVN 1-12-55/4</t>
@@ -4285,7 +4291,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46164.65890277778</v>
+        <v>46197.68071909722</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4330,9 +4336,11 @@
       <c r="B47" s="9">
         <v>46162.79212121527</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46197.680713587964</v>
+      </c>
       <c r="D47" s="9">
-        <v>46197.66271414352</v>
+        <v>46197.68073020833</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4380,10 +4388,10 @@
         <v>33</v>
       </c>
       <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4395,7 +4403,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46164.69023148148</v>
+        <v>46197.680719490745</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>180</v>
@@ -4467,10 +4475,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I49" s="9">
         <v>46234</v>
@@ -4494,7 +4502,7 @@
         <v>180</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q49" s="9">
         <v>46234</v>
@@ -4514,7 +4522,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46162.79214709491</v>
@@ -4524,16 +4532,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4554,7 +4562,7 @@
         <v>172</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4577,7 +4585,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792150775465</v>
@@ -4587,16 +4595,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4614,13 +4622,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4630,7 +4638,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
         <v>46162.792154849536</v>
@@ -4640,16 +4648,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4667,13 +4675,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4683,7 +4691,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79215875</v>
@@ -4693,16 +4701,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4720,13 +4728,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4736,7 +4744,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46162.79216164352</v>
@@ -4746,16 +4754,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I54" s="5">
         <v>46322</v>
@@ -4773,13 +4781,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4789,7 +4797,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922118287</v>
@@ -4799,7 +4807,7 @@
         <v>46164.66718020833</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>25</v>
@@ -4823,7 +4831,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>26</v>
@@ -4836,7 +4844,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46162.7922200926</v>
@@ -4846,16 +4854,16 @@
         <v>46164.69048553241</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I56" s="5">
         <v>46252</v>
@@ -4873,13 +4881,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q56" s="5">
         <v>46252</v>
@@ -4899,7 +4907,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9">
         <v>46162.792225625</v>
@@ -4909,7 +4917,7 @@
         <v>46164.69055459491</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -4936,13 +4944,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q57" s="9">
         <v>46254</v>
@@ -4962,7 +4970,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223230324</v>
@@ -4972,16 +4980,16 @@
         <v>46164.690482418984</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I58" s="5">
         <v>46252</v>
@@ -4999,13 +5007,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>147</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="5">
         <v>46252</v>
@@ -5025,7 +5033,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46162.79223737269</v>
@@ -5035,7 +5043,7 @@
         <v>46164.69055186343</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5062,13 +5070,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="9">
         <v>46254</v>
@@ -5088,7 +5096,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46162.7922424537</v>
@@ -5098,16 +5106,16 @@
         <v>46164.6904790625</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I60" s="5">
         <v>46252</v>
@@ -5125,13 +5133,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q60" s="5">
         <v>46252</v>
@@ -5151,7 +5159,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B61" s="9">
         <v>46162.792246909725</v>
@@ -5161,7 +5169,7 @@
         <v>46164.690549328705</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5188,13 +5196,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>213</v>
       </c>
       <c r="Q61" s="9">
         <v>46254</v>
@@ -5214,7 +5222,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46162.79225168981</v>
@@ -5224,7 +5232,7 @@
         <v>46164.66898752315</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5248,7 +5256,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5261,7 +5269,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B63" s="9">
         <v>46162.792254479165</v>
@@ -5271,16 +5279,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5298,13 +5306,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q63" s="9">
         <v>46258</v>
@@ -5324,7 +5332,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B64" s="5">
         <v>46162.79225922454</v>
@@ -5334,16 +5342,16 @@
         <v>46164.69068318287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5361,13 +5369,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5377,7 +5385,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B65" s="9">
         <v>46162.792265578704</v>
@@ -5387,16 +5395,16 @@
         <v>46164.69068048611</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5414,13 +5422,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5430,7 +5438,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227201389</v>
@@ -5440,16 +5448,16 @@
         <v>46164.69067753472</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5467,13 +5475,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5483,7 +5491,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79227828704</v>
@@ -5493,16 +5501,16 @@
         <v>46164.69067336805</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I67" s="9">
         <v>46258</v>
@@ -5520,13 +5528,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O67" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="P67" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5536,7 +5544,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232202546</v>
@@ -5546,16 +5554,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5573,13 +5581,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q68" s="5">
         <v>46267</v>
@@ -5599,7 +5607,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79232653935</v>
@@ -5609,16 +5617,16 @@
         <v>46164.69081627315</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5636,13 +5644,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5652,7 +5660,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233265047</v>
@@ -5662,16 +5670,16 @@
         <v>46164.69081372685</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5689,13 +5697,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5705,7 +5713,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79233820602</v>
@@ -5715,16 +5723,16 @@
         <v>46164.690812974535</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5742,13 +5750,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5758,7 +5766,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79234384259</v>
@@ -5768,16 +5776,16 @@
         <v>46164.69081170139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -5795,13 +5803,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5811,7 +5819,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79241414352</v>
@@ -5821,7 +5829,7 @@
         <v>46164.690976377315</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5848,13 +5856,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q73" s="9">
         <v>46289</v>
@@ -5874,7 +5882,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79242041666</v>
@@ -5884,7 +5892,7 @@
         <v>46164.69094634259</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5911,13 +5919,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5927,7 +5935,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243321759</v>
@@ -5937,7 +5945,7 @@
         <v>46164.69094324074</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5964,13 +5972,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5980,7 +5988,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79243956019</v>
@@ -5990,7 +5998,7 @@
         <v>46164.69093616898</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6017,13 +6025,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6033,7 +6041,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79244651621</v>
@@ -6043,7 +6051,7 @@
         <v>46164.69093546296</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6070,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6086,7 +6094,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B78" s="5">
         <v>46162.79247811342</v>
@@ -6096,7 +6104,7 @@
         <v>46164.670772627316</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6120,7 +6128,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6133,7 +6141,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B79" s="9">
         <v>46162.792481805554</v>
@@ -6143,16 +6151,16 @@
         <v>46171.19919608797</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I79" s="9">
         <v>46169</v>
@@ -6170,13 +6178,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>116</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q79" s="9">
         <v>46169</v>
@@ -6196,7 +6204,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79248949074</v>
@@ -6206,16 +6214,16 @@
         <v>46164.691113761575</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I80" s="5">
         <v>46279</v>
@@ -6233,13 +6241,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q80" s="5">
         <v>46279</v>
@@ -6259,7 +6267,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79249689815</v>
@@ -6269,16 +6277,16 @@
         <v>46164.69111056713</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I81" s="9">
         <v>46302</v>
@@ -6296,13 +6304,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>125</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q81" s="9">
         <v>46302</v>
@@ -6322,7 +6330,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250443287</v>
@@ -6332,16 +6340,16 @@
         <v>46164.69110619213</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I82" s="5">
         <v>46280</v>
@@ -6359,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>157</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q82" s="5">
         <v>46280</v>
@@ -6385,7 +6393,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79250947917</v>
@@ -6395,7 +6403,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>25</v>
@@ -6419,7 +6427,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>26</v>
@@ -6432,7 +6440,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79251295139</v>
@@ -6442,7 +6450,7 @@
         <v>46164.69124818287</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6469,13 +6477,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q84" s="5">
         <v>46293</v>
@@ -6495,7 +6503,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B85" s="9">
         <v>46162.79252873843</v>
@@ -6505,7 +6513,7 @@
         <v>46164.69121831018</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6532,10 +6540,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6548,7 +6556,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B86" s="5">
         <v>46162.792533518514</v>
@@ -6558,7 +6566,7 @@
         <v>46164.6912157176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6585,10 +6593,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6601,7 +6609,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B87" s="9">
         <v>46162.79253825231</v>
@@ -6611,7 +6619,7 @@
         <v>46164.69121336806</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6638,13 +6646,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6654,7 +6662,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792543206015</v>
@@ -6664,7 +6672,7 @@
         <v>46164.691209490746</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6691,13 +6699,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6707,7 +6715,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B89" s="9">
         <v>46162.792612743055</v>
@@ -6717,7 +6725,7 @@
         <v>46164.69137969907</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6744,13 +6752,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q89" s="9">
         <v>46311</v>
@@ -6770,7 +6778,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B90" s="5">
         <v>46162.79261844908</v>
@@ -6780,7 +6788,7 @@
         <v>46164.69134153935</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6807,13 +6815,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6823,7 +6831,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B91" s="9">
         <v>46162.7926247338</v>
@@ -6833,7 +6841,7 @@
         <v>46164.69133898148</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6860,13 +6868,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6876,7 +6884,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B92" s="5">
         <v>46162.792630682874</v>
@@ -6886,7 +6894,7 @@
         <v>46164.69133623842</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6913,13 +6921,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6929,7 +6937,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79263777778</v>
@@ -6939,7 +6947,7 @@
         <v>46164.691332372684</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6966,13 +6974,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6982,7 +6990,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79268604166</v>
@@ -6992,7 +7000,7 @@
         <v>46164.6915004051</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7019,13 +7027,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q94" s="5">
         <v>46315</v>
@@ -7045,7 +7053,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269070602</v>
@@ -7055,7 +7063,7 @@
         <v>46164.691474872685</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7082,13 +7090,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O95" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="P95" s="10" t="s">
         <v>290</v>
-      </c>
-      <c r="P95" s="10" t="s">
-        <v>288</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7098,7 +7106,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B96" s="5">
         <v>46162.79269707176</v>
@@ -7108,7 +7116,7 @@
         <v>46164.69147140047</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7135,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7151,7 +7159,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B97" s="9">
         <v>46162.792703576386</v>
@@ -7161,7 +7169,7 @@
         <v>46164.691468171295</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7188,13 +7196,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7204,7 +7212,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B98" s="5">
         <v>46162.79271046296</v>
@@ -7214,7 +7222,7 @@
         <v>46164.69146488426</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7241,13 +7249,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7257,7 +7265,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B99" s="9">
         <v>46162.792744861115</v>
@@ -7267,7 +7275,7 @@
         <v>46164.691619942125</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7294,13 +7302,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q99" s="9">
         <v>46317</v>
@@ -7320,7 +7328,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79274982639</v>
@@ -7330,7 +7338,7 @@
         <v>46164.69158721065</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7357,13 +7365,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7373,7 +7381,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79275559028</v>
@@ -7383,7 +7391,7 @@
         <v>46164.69158380787</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7410,13 +7418,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7426,7 +7434,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B102" s="5">
         <v>46162.79276118056</v>
@@ -7436,7 +7444,7 @@
         <v>46164.69158106481</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7463,13 +7471,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7479,7 +7487,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B103" s="9">
         <v>46162.792767754625</v>
@@ -7489,7 +7497,7 @@
         <v>46164.69157646991</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7516,13 +7524,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7532,7 +7540,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B104" s="5">
         <v>46162.79285696759</v>
@@ -7542,7 +7550,7 @@
         <v>46164.69173954861</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7569,13 +7577,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q104" s="5">
         <v>46321</v>
@@ -7595,7 +7603,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792862511575</v>
@@ -7605,7 +7613,7 @@
         <v>46164.69170866898</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7632,13 +7640,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7648,7 +7656,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792868125005</v>
@@ -7658,7 +7666,7 @@
         <v>46164.69170596065</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7685,13 +7693,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7701,7 +7709,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B107" s="9">
         <v>46162.792873750004</v>
@@ -7711,7 +7719,7 @@
         <v>46164.69170293982</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7738,13 +7746,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7754,7 +7762,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B108" s="5">
         <v>46162.7928793287</v>
@@ -7764,7 +7772,7 @@
         <v>46164.691698194445</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7791,13 +7799,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7807,7 +7815,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B109" s="9">
         <v>46162.792907696756</v>
@@ -7817,7 +7825,7 @@
         <v>46164.69185736111</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7842,13 +7850,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q109" s="9">
         <v>46323</v>
@@ -7868,7 +7876,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291289352</v>
@@ -7878,7 +7886,7 @@
         <v>46164.69182431713</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7905,13 +7913,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7921,7 +7929,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79291758101</v>
@@ -7931,7 +7939,7 @@
         <v>46164.691821562505</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7958,13 +7966,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7974,7 +7982,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79292245371</v>
@@ -7984,7 +7992,7 @@
         <v>46164.691819155094</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8011,13 +8019,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8027,7 +8035,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B113" s="9">
         <v>46162.79293256944</v>
@@ -8037,7 +8045,7 @@
         <v>46164.69181509259</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8064,13 +8072,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8080,7 +8088,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B114" s="5">
         <v>46162.7930040625</v>
@@ -8090,7 +8098,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>25</v>
@@ -8114,7 +8122,7 @@
         <v>26</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>26</v>
@@ -8127,7 +8135,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79300806713</v>
@@ -8137,16 +8145,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8164,13 +8172,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q115" s="9">
         <v>46324</v>
@@ -8190,7 +8198,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79301847222</v>
@@ -8200,16 +8208,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8227,13 +8235,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8243,7 +8251,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79302525463</v>
@@ -8253,16 +8261,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8280,13 +8288,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8296,7 +8304,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303010416</v>
@@ -8306,16 +8314,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8333,13 +8341,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8349,7 +8357,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79303482639</v>
@@ -8359,16 +8367,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I119" s="9">
         <v>46324</v>
@@ -8386,13 +8394,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8402,7 +8410,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B120" s="5">
         <v>46162.79306296296</v>
@@ -8412,7 +8420,7 @@
         <v>46164.692368958335</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8439,13 +8447,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q120" s="5">
         <v>46325</v>
@@ -8465,7 +8473,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B121" s="9">
         <v>46162.7930678125</v>
@@ -8475,7 +8483,7 @@
         <v>46164.692334189815</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8502,13 +8510,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8518,7 +8526,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B122" s="5">
         <v>46162.793072280096</v>
@@ -8528,7 +8536,7 @@
         <v>46164.6923315162</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8555,13 +8563,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8571,7 +8579,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79307696759</v>
@@ -8581,7 +8589,7 @@
         <v>46164.69232880787</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8608,13 +8616,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8624,7 +8632,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79308175926</v>
@@ -8634,7 +8642,7 @@
         <v>46164.69232427083</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8661,13 +8669,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8677,7 +8685,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B125" s="9">
         <v>46162.79314625</v>
@@ -8687,16 +8695,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8714,13 +8722,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q125" s="9">
         <v>46328</v>
@@ -8740,7 +8748,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B126" s="5">
         <v>46162.793151550926</v>
@@ -8750,16 +8758,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8777,13 +8785,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8793,7 +8801,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79315885417</v>
@@ -8803,16 +8811,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8830,13 +8838,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8846,7 +8854,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316501158</v>
@@ -8856,16 +8864,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8883,13 +8891,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8899,7 +8907,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79316986111</v>
@@ -8909,16 +8917,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I129" s="9">
         <v>46328</v>
@@ -8936,13 +8944,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8952,7 +8960,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79319725695</v>
@@ -8962,16 +8970,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -8989,13 +8997,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q130" s="5">
         <v>46329</v>
@@ -9015,7 +9023,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B131" s="9">
         <v>46162.79320210648</v>
@@ -9025,16 +9033,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9052,13 +9060,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9068,7 +9076,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B132" s="5">
         <v>46162.793206111106</v>
@@ -9078,16 +9086,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9105,13 +9113,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9121,7 +9129,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B133" s="9">
         <v>46162.7932099537</v>
@@ -9131,16 +9139,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9158,13 +9166,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9174,7 +9182,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79321400463</v>
@@ -9184,16 +9192,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I134" s="5">
         <v>46329</v>
@@ -9211,13 +9219,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9227,7 +9235,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79323766204</v>
@@ -9237,7 +9245,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>25</v>
@@ -9261,7 +9269,7 @@
         <v>26</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>26</v>
@@ -9274,7 +9282,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324063657</v>
@@ -9284,16 +9292,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I136" s="5">
         <v>46330</v>
@@ -9311,13 +9319,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>
@@ -9337,7 +9345,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B137" s="9">
         <v>46162.79324528935</v>
@@ -9347,7 +9355,7 @@
         <v>46164.69273445602</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9374,13 +9382,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q137" s="9">
         <v>46330</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -3491,7 +3491,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46164.68961940972</v>
+        <v>46197.70226908565</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="368">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -161,7 +161,7 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Basica Motor,Ingenieria basica Rodete,Ingenieria Detalle</t>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214982558008041</t>
@@ -181,7 +181,7 @@
 </t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta motor</t>
   </si>
   <si>
     <t>Baja</t>
@@ -198,7 +198,7 @@
 </t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta alabes,propuesta nucleo rodete</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta alabes,propuesta nucleo rodete</t>
   </si>
   <si>
     <t>1214982580298731</t>
@@ -223,22 +223,7 @@
 </t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1214982508454946</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
+    <t>Ingenieria Jefe de proyecto:,Planos preliminar</t>
   </si>
   <si>
     <t>1214969047721205</t>
@@ -1160,9 +1145,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Despacho</t>
   </si>
 </sst>
 </file>
@@ -1686,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U137"/>
+  <dimension ref="A1:U136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2106,7 +2088,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46197.66270453704</v>
+        <v>46197.77681821759</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2133,7 +2115,7 @@
         <v>26</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>26</v>
@@ -2142,7 +2124,9 @@
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
+      <c r="U9" s="12" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -2155,7 +2139,7 @@
         <v>46197.659032407406</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.65904699074</v>
+        <v>46197.776808263894</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2220,7 +2204,7 @@
         <v>46197.660673125</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.66068810185</v>
+        <v>46197.77680832176</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>54</v>
@@ -2285,7 +2269,7 @@
         <v>46197.66269631944</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.66271325231</v>
+        <v>46197.776808344905</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2344,30 +2328,24 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.79192297454</v>
+        <v>46162.791791192125</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46197.66271351852</v>
+        <v>46197.5874947338</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="9">
-        <v>46149</v>
-      </c>
-      <c r="J13" s="9">
-        <v>46157</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
       <c r="K13" s="10" t="s">
         <v>26</v>
       </c>
@@ -2375,56 +2353,52 @@
         <v>26</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>63</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>46149</v>
-      </c>
-      <c r="R13" s="9">
-        <v>46157</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T13" s="10">
-        <v>0</v>
-      </c>
-      <c r="U13" s="12" t="s">
-        <v>65</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.791791192125</v>
+        <v>46162.79193019676</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.5874947338</v>
+        <v>46197.659049317124</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
+        <v>48</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="5">
+        <v>46153</v>
+      </c>
+      <c r="J14" s="5">
+        <v>46154</v>
+      </c>
       <c r="K14" s="6" t="s">
         <v>26</v>
       </c>
@@ -2432,36 +2406,46 @@
         <v>26</v>
       </c>
       <c r="M14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>46153</v>
+      </c>
+      <c r="R14" s="5">
+        <v>46154</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="N14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="U14" s="12" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.79193019676</v>
+        <v>46162.7919353125</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46197.659049317124</v>
+        <v>46197.66069275463</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2473,10 +2457,10 @@
         <v>49</v>
       </c>
       <c r="I15" s="9">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="J15" s="9">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="K15" s="10" t="s">
         <v>26</v>
@@ -2488,19 +2472,19 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q15" s="9">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="R15" s="9">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="S15" s="7" t="s">
         <v>52</v>
@@ -2509,31 +2493,33 @@
         <v>0</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46162.79194023148</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46197.5874865625</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46197.6606925</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="5">
-        <v>46162.7919353125</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="5">
-        <v>46197.66069275463</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="H16" s="6" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="I16" s="5">
         <v>46160</v>
@@ -2551,13 +2537,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>54</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="5">
         <v>46160</v>
@@ -2569,42 +2555,40 @@
         <v>52</v>
       </c>
       <c r="T16" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46162.791945289355</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9">
+        <v>46164.68847915509</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="9">
-        <v>46162.79194023148</v>
-      </c>
-      <c r="C17" s="9">
-        <v>46197.5874865625</v>
-      </c>
-      <c r="D17" s="9">
-        <v>46197.6606925</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>77</v>
       </c>
       <c r="I17" s="9">
-        <v>46160</v>
+        <v>46237</v>
       </c>
       <c r="J17" s="9">
-        <v>46161</v>
+        <v>46238</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>26</v>
@@ -2616,52 +2600,52 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="9">
-        <v>46160</v>
+        <v>46237</v>
       </c>
       <c r="R17" s="9">
-        <v>46161</v>
+        <v>46238</v>
       </c>
       <c r="S17" s="7" t="s">
         <v>52</v>
       </c>
       <c r="T17" s="10">
-        <v>1</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>65</v>
+        <v>0</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.791945289355</v>
+        <v>46162.79194956018</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46164.68847915509</v>
+        <v>46164.68847201389</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I18" s="5">
         <v>46237</v>
@@ -2679,13 +2663,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="Q18" s="5">
         <v>46237</v>
@@ -2700,31 +2684,31 @@
         <v>0</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.79194956018</v>
+        <v>46162.79195284723</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46164.68847201389</v>
+        <v>46164.688470567125</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I19" s="9">
         <v>46237</v>
@@ -2742,13 +2726,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2763,31 +2747,31 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.79195284723</v>
+        <v>46162.79195601852</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46164.688470567125</v>
+        <v>46164.6884696412</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I20" s="5">
         <v>46237</v>
@@ -2805,13 +2789,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2826,38 +2810,32 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.79195601852</v>
+        <v>46162.79179634259</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46164.6884696412</v>
+        <v>46164.66016885417</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="9">
-        <v>46237</v>
-      </c>
-      <c r="J21" s="9">
-        <v>46238</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
       <c r="K21" s="10" t="s">
         <v>26</v>
       </c>
@@ -2865,56 +2843,52 @@
         <v>26</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>46237</v>
-      </c>
-      <c r="R21" s="9">
-        <v>46238</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.79179634259</v>
+        <v>46162.79196002315</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46164.66016885417</v>
+        <v>46164.68945766204</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+      <c r="I22" s="5">
+        <v>46162</v>
+      </c>
+      <c r="J22" s="5">
+        <v>46276</v>
+      </c>
       <c r="K22" s="6" t="s">
         <v>26</v>
       </c>
@@ -2922,33 +2896,43 @@
         <v>26</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>46162</v>
+      </c>
+      <c r="R22" s="5">
+        <v>46276</v>
+      </c>
+      <c r="S22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T22" s="6">
+        <v>0</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>98</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.79196002315</v>
+        <v>46162.791964375</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46164.68945766204</v>
+        <v>46164.689432858795</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>99</v>
@@ -2957,16 +2941,16 @@
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
       </c>
       <c r="J23" s="9">
-        <v>46276</v>
+        <v>46164</v>
       </c>
       <c r="K23" s="10" t="s">
         <v>26</v>
@@ -2978,20 +2962,16 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>46162</v>
-      </c>
-      <c r="R23" s="9">
-        <v>46276</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
         <v>52</v>
       </c>
@@ -2999,37 +2979,37 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.791964375</v>
+        <v>46162.79196883102</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46164.689432858795</v>
+        <v>46164.68942958333</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="J24" s="5">
-        <v>46164</v>
+        <v>46276</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
@@ -3041,13 +3021,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="O24" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="O24" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="P24" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3058,37 +3038,37 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.79196883102</v>
+        <v>46162.79197329861</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46164.68942958333</v>
+        <v>46169.17544910879</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I25" s="9">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="J25" s="9">
-        <v>46276</v>
+        <v>46168</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>26</v>
@@ -3100,54 +3080,58 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="7" t="s">
-        <v>52</v>
+        <v>91</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>46162</v>
+      </c>
+      <c r="R25" s="9">
+        <v>46168</v>
+      </c>
+      <c r="S25" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T25" s="10">
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.79197329861</v>
+        <v>46162.791977500005</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46169.17544910879</v>
+        <v>46197.58749420139</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
       </c>
       <c r="J26" s="5">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>26</v>
@@ -3159,58 +3143,54 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>46162</v>
-      </c>
-      <c r="R26" s="5">
-        <v>46168</v>
-      </c>
-      <c r="S26" s="11" t="s">
-        <v>33</v>
+        <v>109</v>
+      </c>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.791977500005</v>
+        <v>46162.79198199074</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.58749420139</v>
+        <v>46168.172647141204</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I27" s="9">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="J27" s="9">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="K27" s="10" t="s">
         <v>26</v>
@@ -3222,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3239,37 +3219,37 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.79198199074</v>
+        <v>46162.79198653935</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46168.172647141204</v>
+        <v>46164.6896481713</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="J28" s="5">
-        <v>46168</v>
+        <v>46301</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
@@ -3281,16 +3261,20 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>46155</v>
+      </c>
+      <c r="R28" s="5">
+        <v>46301</v>
+      </c>
       <c r="S28" s="7" t="s">
         <v>52</v>
       </c>
@@ -3298,37 +3282,37 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.79198653935</v>
+        <v>46162.79199082176</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46164.6896481713</v>
+        <v>46175.170452280094</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
       </c>
       <c r="J29" s="9">
-        <v>46301</v>
+        <v>46175</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>26</v>
@@ -3340,20 +3324,16 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q29" s="9">
-        <v>46155</v>
-      </c>
-      <c r="R29" s="9">
-        <v>46301</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
         <v>52</v>
       </c>
@@ -3361,37 +3341,37 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.79199082176</v>
+        <v>46162.791995312495</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46175.170452280094</v>
+        <v>46164.689623750004</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="J30" s="5">
-        <v>46175</v>
+        <v>46301</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -3403,13 +3383,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3420,37 +3400,37 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.791995312495</v>
+        <v>46162.79199990741</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46164.689623750004</v>
+        <v>46197.70226908565</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
       </c>
       <c r="J31" s="9">
-        <v>46301</v>
+        <v>46213</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>26</v>
@@ -3462,13 +3442,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3479,37 +3459,37 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.79199990741</v>
+        <v>46162.792004421295</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46197.70226908565</v>
+        <v>46164.68978111111</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="I32" s="5">
-        <v>46176</v>
+        <v>46239</v>
       </c>
       <c r="J32" s="5">
-        <v>46213</v>
+        <v>46251</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3521,16 +3501,20 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>46239</v>
+      </c>
+      <c r="R32" s="5">
+        <v>46251</v>
+      </c>
       <c r="S32" s="7" t="s">
         <v>52</v>
       </c>
@@ -3538,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3546,11 +3530,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.792004421295</v>
+        <v>46162.79200878472</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46164.68978111111</v>
+        <v>46164.68973819444</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3559,16 +3543,16 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
       </c>
       <c r="J33" s="9">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>26</v>
@@ -3580,20 +3564,16 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q33" s="9">
-        <v>46239</v>
-      </c>
-      <c r="R33" s="9">
-        <v>46251</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
       <c r="S33" s="7" t="s">
         <v>52</v>
       </c>
@@ -3601,37 +3581,37 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.79200878472</v>
+        <v>46162.792013391205</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46164.68973819444</v>
+        <v>46164.68973515046</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="J34" s="5">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3643,13 +3623,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="O34" s="6" t="s">
-        <v>80</v>
-      </c>
       <c r="P34" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3660,34 +3640,34 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.792013391205</v>
+        <v>46162.79201809027</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46164.68973515046</v>
+        <v>46164.689874131946</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I35" s="9">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="J35" s="9">
         <v>46251</v>
@@ -3702,16 +3682,20 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>46239</v>
+      </c>
+      <c r="R35" s="9">
+        <v>46251</v>
+      </c>
       <c r="S35" s="7" t="s">
         <v>52</v>
       </c>
@@ -3719,37 +3703,37 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.79201809027</v>
+        <v>46162.79207501157</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46164.689874131946</v>
+        <v>46164.68984363426</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
       </c>
       <c r="J36" s="5">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>26</v>
@@ -3761,58 +3745,48 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q36" s="5">
-        <v>46239</v>
-      </c>
-      <c r="R36" s="5">
-        <v>46251</v>
-      </c>
-      <c r="S36" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.79207501157</v>
+        <v>46162.79208025463</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46164.68984363426</v>
+        <v>46164.68984076389</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I37" s="9">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="J37" s="9">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>26</v>
@@ -3824,13 +3798,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3840,32 +3814,32 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.79208025463</v>
+        <v>46162.792085</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46164.68984076389</v>
+        <v>46164.69004553241</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>133</v>
-      </c>
       <c r="I38" s="5">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="J38" s="5">
-        <v>46251</v>
+        <v>46279</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>26</v>
@@ -3877,48 +3851,58 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>46239</v>
+      </c>
+      <c r="R38" s="5">
+        <v>46279</v>
+      </c>
+      <c r="S38" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T38" s="6">
+        <v>0</v>
+      </c>
+      <c r="U38" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.792085</v>
+        <v>46162.792089166665</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46164.69004553241</v>
+        <v>46164.68995886574</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
       </c>
       <c r="J39" s="9">
-        <v>46279</v>
+        <v>46247</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3930,58 +3914,48 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>46239</v>
-      </c>
-      <c r="R39" s="9">
-        <v>46279</v>
-      </c>
-      <c r="S39" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.792089166665</v>
+        <v>46162.792093599535</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46164.68995886574</v>
+        <v>46164.68995591435</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="J40" s="5">
-        <v>46247</v>
+        <v>46276</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -3993,13 +3967,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4009,50 +3983,50 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.792093599535</v>
+        <v>46162.79210385417</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.68995591435</v>
+        <v>46164.68998921296</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="H41" s="10" t="s">
+      <c r="I41" s="9">
+        <v>46279</v>
+      </c>
+      <c r="J41" s="9">
+        <v>46279</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="O41" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I41" s="9">
-        <v>46248</v>
-      </c>
-      <c r="J41" s="9">
-        <v>46276</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>94</v>
-      </c>
       <c r="P41" s="10" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4062,85 +4036,95 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.79210385417</v>
+        <v>46162.79210730324</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46164.68998921296</v>
+        <v>46164.690100057865</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I42" s="5">
+        <v>46239</v>
+      </c>
+      <c r="J42" s="5">
+        <v>46251</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="O42" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I42" s="5">
-        <v>46279</v>
-      </c>
-      <c r="J42" s="5">
-        <v>46279</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>157</v>
-      </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
+      <c r="Q42" s="5">
+        <v>46239</v>
+      </c>
+      <c r="R42" s="5">
+        <v>46251</v>
+      </c>
+      <c r="S42" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0</v>
+      </c>
+      <c r="U42" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.79210730324</v>
+        <v>46162.792111180555</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46164.690100057865</v>
+        <v>46164.690157951394</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>86</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
       </c>
       <c r="J43" s="9">
-        <v>46251</v>
+        <v>46240</v>
       </c>
       <c r="K43" s="10" t="s">
         <v>26</v>
@@ -4152,58 +4136,48 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q43" s="9">
-        <v>46239</v>
-      </c>
-      <c r="R43" s="9">
-        <v>46251</v>
-      </c>
-      <c r="S43" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T43" s="10">
-        <v>0</v>
-      </c>
-      <c r="U43" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.792111180555</v>
+        <v>46162.79211601852</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46164.690157951394</v>
+        <v>46164.69015534723</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="I44" s="5">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="J44" s="5">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4215,13 +4189,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4231,33 +4205,27 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.79211601852</v>
+        <v>46162.791800798615</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46164.69015534723</v>
+        <v>46197.68071909722</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="I45" s="9">
-        <v>46241</v>
-      </c>
-      <c r="J45" s="9">
-        <v>46251</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
       <c r="K45" s="10" t="s">
         <v>26</v>
       </c>
@@ -4265,16 +4233,16 @@
         <v>26</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4284,27 +4252,35 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46162.79212121527</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46197.680713587964</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46197.68073020833</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B46" s="5">
-        <v>46162.791800798615</v>
-      </c>
-      <c r="C46" s="6"/>
-      <c r="D46" s="5">
-        <v>46197.68071909722</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
+      <c r="I46" s="5">
+        <v>46160</v>
+      </c>
+      <c r="J46" s="5">
+        <v>46178</v>
+      </c>
       <c r="K46" s="6" t="s">
         <v>26</v>
       </c>
@@ -4312,35 +4288,43 @@
         <v>26</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P46" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="P46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="Q46" s="5">
+        <v>46160</v>
+      </c>
+      <c r="R46" s="5">
+        <v>46178</v>
+      </c>
+      <c r="S46" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.79212121527</v>
-      </c>
-      <c r="C47" s="9">
-        <v>46197.680713587964</v>
-      </c>
+        <v>46162.79212670139</v>
+      </c>
+      <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46197.68073020833</v>
+        <v>46197.680719490745</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4349,79 +4333,79 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="I47" s="9">
+        <v>46216</v>
+      </c>
+      <c r="J47" s="9">
+        <v>46233</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="O47" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="P47" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="I47" s="9">
-        <v>46160</v>
-      </c>
-      <c r="J47" s="9">
-        <v>46178</v>
-      </c>
-      <c r="K47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>178</v>
-      </c>
       <c r="Q47" s="9">
-        <v>46160</v>
+        <v>46216</v>
       </c>
       <c r="R47" s="9">
-        <v>46178</v>
-      </c>
-      <c r="S47" s="11" t="s">
-        <v>33</v>
+        <v>46233</v>
+      </c>
+      <c r="S47" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="T47" s="10">
-        <v>1</v>
-      </c>
-      <c r="U47" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U47" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.79212670139</v>
+        <v>46162.792133090275</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46197.680719490745</v>
+        <v>46164.690227569445</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>177</v>
-      </c>
       <c r="I48" s="5">
-        <v>46216</v>
+        <v>46234</v>
       </c>
       <c r="J48" s="5">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>26</v>
@@ -4433,19 +4417,19 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="P48" s="6" t="s">
-        <v>182</v>
-      </c>
       <c r="Q48" s="5">
-        <v>46216</v>
+        <v>46234</v>
       </c>
       <c r="R48" s="5">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="S48" s="7" t="s">
         <v>52</v>
@@ -4454,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="U48" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.792133090275</v>
+        <v>46162.79214709491</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.690227569445</v>
+        <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
@@ -4481,10 +4465,10 @@
         <v>185</v>
       </c>
       <c r="I49" s="9">
-        <v>46234</v>
+        <v>46322</v>
       </c>
       <c r="J49" s="9">
-        <v>46234</v>
+        <v>46322</v>
       </c>
       <c r="K49" s="10" t="s">
         <v>26</v>
@@ -4496,19 +4480,19 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="Q49" s="9">
-        <v>46234</v>
+        <v>46322</v>
       </c>
       <c r="R49" s="9">
-        <v>46234</v>
+        <v>46322</v>
       </c>
       <c r="S49" s="7" t="s">
         <v>52</v>
@@ -4517,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4525,11 +4509,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.79214709491</v>
+        <v>46162.792150775465</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46164.69027550926</v>
+        <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4538,10 +4522,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4559,52 +4543,42 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q50" s="5">
-        <v>46322</v>
-      </c>
-      <c r="R50" s="5">
-        <v>46322</v>
-      </c>
-      <c r="S50" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6"/>
+      <c r="T50" s="6"/>
+      <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.792150775465</v>
+        <v>46162.792154849536</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46164.69036847222</v>
+        <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4622,13 +4596,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="O51" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="O51" s="10" t="s">
-        <v>193</v>
-      </c>
       <c r="P51" s="10" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4638,26 +4612,26 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.792154849536</v>
+        <v>46162.79215875</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46164.69036586805</v>
+        <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4675,13 +4649,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="O52" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="O52" s="6" t="s">
-        <v>193</v>
-      </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4691,26 +4665,26 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.79215875</v>
+        <v>46162.79216164352</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46164.69036304398</v>
+        <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4728,13 +4702,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="O53" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="O53" s="10" t="s">
-        <v>193</v>
-      </c>
       <c r="P53" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4744,33 +4718,27 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.79216164352</v>
+        <v>46162.7922118287</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46164.690358935186</v>
+        <v>46164.66718020833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="I54" s="5">
-        <v>46322</v>
-      </c>
-      <c r="J54" s="5">
-        <v>46322</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
       <c r="K54" s="6" t="s">
         <v>26</v>
       </c>
@@ -4778,16 +4746,16 @@
         <v>26</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>26</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4797,27 +4765,33 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.7922118287</v>
+        <v>46162.7922200926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.66718020833</v>
+        <v>46164.69048553241</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
+      <c r="I55" s="9">
+        <v>46252</v>
+      </c>
+      <c r="J55" s="9">
+        <v>46253</v>
+      </c>
       <c r="K55" s="10" t="s">
         <v>26</v>
       </c>
@@ -4825,33 +4799,43 @@
         <v>26</v>
       </c>
       <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O55" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q55" s="9">
+        <v>46252</v>
+      </c>
+      <c r="R55" s="9">
+        <v>46253</v>
+      </c>
+      <c r="S55" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="N55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
+      <c r="U55" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>201</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.7922200926</v>
+        <v>46162.792225625</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46164.69048553241</v>
+        <v>46164.69055459491</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -4860,40 +4844,40 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I56" s="5">
+        <v>46254</v>
+      </c>
+      <c r="J56" s="5">
+        <v>46255</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O56" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="P56" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="I56" s="5">
-        <v>46252</v>
-      </c>
-      <c r="J56" s="5">
-        <v>46253</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>205</v>
-      </c>
       <c r="Q56" s="5">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="R56" s="5">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="S56" s="7" t="s">
         <v>52</v>
@@ -4902,61 +4886,61 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.792225625</v>
+        <v>46162.79223230324</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.69055459491</v>
+        <v>46164.690482418984</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I57" s="9">
+        <v>46252</v>
+      </c>
+      <c r="J57" s="9">
+        <v>46253</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="P57" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I57" s="9">
-        <v>46254</v>
-      </c>
-      <c r="J57" s="9">
-        <v>46255</v>
-      </c>
-      <c r="K57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="O57" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="P57" s="10" t="s">
-        <v>209</v>
-      </c>
       <c r="Q57" s="9">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="R57" s="9">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="S57" s="7" t="s">
         <v>52</v>
@@ -4965,37 +4949,37 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.79223230324</v>
+        <v>46162.79223737269</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46164.690482418984</v>
+        <v>46164.69055186343</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="I58" s="5">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J58" s="5">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>26</v>
@@ -5007,19 +4991,19 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="5">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="R58" s="5">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="S58" s="7" t="s">
         <v>52</v>
@@ -5028,37 +5012,37 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.79223737269</v>
+        <v>46162.7922424537</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46164.69055186343</v>
+        <v>46164.6904790625</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="I59" s="9">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="J59" s="9">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>26</v>
@@ -5070,19 +5054,19 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="9">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="R59" s="9">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="S59" s="7" t="s">
         <v>52</v>
@@ -5091,37 +5075,37 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.7922424537</v>
+        <v>46162.792246909725</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46164.6904790625</v>
+        <v>46164.690549328705</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="I60" s="5">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J60" s="5">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
@@ -5133,19 +5117,19 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="Q60" s="5">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="R60" s="5">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="S60" s="7" t="s">
         <v>52</v>
@@ -5154,38 +5138,32 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.792246909725</v>
+        <v>46162.79225168981</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.690549328705</v>
+        <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I61" s="9">
-        <v>46254</v>
-      </c>
-      <c r="J61" s="9">
-        <v>46255</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
       <c r="K61" s="10" t="s">
         <v>26</v>
       </c>
@@ -5193,56 +5171,52 @@
         <v>26</v>
       </c>
       <c r="M61" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>199</v>
+        <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>217</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q61" s="9">
-        <v>46254</v>
-      </c>
-      <c r="R61" s="9">
-        <v>46255</v>
-      </c>
-      <c r="S61" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.79225168981</v>
+        <v>46162.792254479165</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46164.66898752315</v>
+        <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
+      <c r="I62" s="5">
+        <v>46258</v>
+      </c>
+      <c r="J62" s="5">
+        <v>46266</v>
+      </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
       </c>
@@ -5250,45 +5224,55 @@
         <v>26</v>
       </c>
       <c r="M62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>46258</v>
+      </c>
+      <c r="R62" s="5">
+        <v>46266</v>
+      </c>
+      <c r="S62" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T62" s="6">
         <v>0</v>
       </c>
-      <c r="N62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
+      <c r="U62" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.792254479165</v>
+        <v>46162.79225922454</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.69072508102</v>
+        <v>46164.69068318287</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5306,52 +5290,42 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q63" s="9">
-        <v>46258</v>
-      </c>
-      <c r="R63" s="9">
-        <v>46266</v>
-      </c>
-      <c r="S63" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T63" s="10">
-        <v>0</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.79225922454</v>
+        <v>46162.792265578704</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.69068318287</v>
+        <v>46164.69068048611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5369,13 +5343,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5385,26 +5359,26 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.792265578704</v>
+        <v>46162.79227201389</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.69068048611</v>
+        <v>46164.69067753472</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5422,10 +5396,10 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>229</v>
@@ -5438,26 +5412,26 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.79227201389</v>
+        <v>46162.79227828704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.69067753472</v>
+        <v>46164.69067336805</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5475,13 +5449,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5491,32 +5465,32 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.79227828704</v>
+        <v>46162.79232202546</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46164.69067336805</v>
+        <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I67" s="9">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="J67" s="9">
-        <v>46266</v>
+        <v>46288</v>
       </c>
       <c r="K67" s="10" t="s">
         <v>26</v>
@@ -5528,42 +5502,52 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
+        <v>216</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>46267</v>
+      </c>
+      <c r="R67" s="9">
+        <v>46288</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T67" s="10">
+        <v>0</v>
+      </c>
+      <c r="U67" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.79232202546</v>
+        <v>46162.79232653935</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46164.69085144676</v>
+        <v>46164.69081627315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5581,52 +5565,42 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q68" s="5">
-        <v>46267</v>
-      </c>
-      <c r="R68" s="5">
-        <v>46288</v>
-      </c>
-      <c r="S68" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.79232653935</v>
+        <v>46162.79233265047</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46164.69081627315</v>
+        <v>46164.69081372685</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5644,13 +5618,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5660,26 +5634,26 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.79233265047</v>
+        <v>46162.79233820602</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46164.69081372685</v>
+        <v>46164.690812974535</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5697,13 +5671,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5713,26 +5687,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.79233820602</v>
+        <v>46162.79234384259</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46164.690812974535</v>
+        <v>46164.69081170139</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5750,13 +5724,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5766,32 +5740,32 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.79234384259</v>
+        <v>46162.79241414352</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46164.69081170139</v>
+        <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>226</v>
+        <v>157</v>
       </c>
       <c r="I72" s="5">
-        <v>46267</v>
+        <v>46289</v>
       </c>
       <c r="J72" s="5">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5803,42 +5777,52 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-      <c r="U72" s="6"/>
+        <v>216</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>46289</v>
+      </c>
+      <c r="R72" s="5">
+        <v>46290</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T72" s="6">
+        <v>0</v>
+      </c>
+      <c r="U72" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.79241414352</v>
+        <v>46162.79242041666</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46164.690976377315</v>
+        <v>46164.69094634259</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5856,52 +5840,42 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q73" s="9">
-        <v>46289</v>
-      </c>
-      <c r="R73" s="9">
-        <v>46290</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.79242041666</v>
+        <v>46162.79243321759</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46164.69094634259</v>
+        <v>46164.69094324074</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -5919,13 +5893,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5935,26 +5909,26 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.79243321759</v>
+        <v>46162.79243956019</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46164.69094324074</v>
+        <v>46164.69093616898</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -5972,13 +5946,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5988,26 +5962,26 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.79243956019</v>
+        <v>46162.79244651621</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46164.69093616898</v>
+        <v>46164.69093546296</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6025,13 +5999,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6041,33 +6015,27 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.79244651621</v>
+        <v>46162.79247811342</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.69093546296</v>
+        <v>46164.670772627316</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="I77" s="9">
-        <v>46289</v>
-      </c>
-      <c r="J77" s="9">
-        <v>46290</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H77" s="10"/>
+      <c r="I77" s="10"/>
+      <c r="J77" s="10"/>
       <c r="K77" s="10" t="s">
         <v>26</v>
       </c>
@@ -6075,16 +6043,16 @@
         <v>26</v>
       </c>
       <c r="M77" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>246</v>
+        <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>26</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6094,27 +6062,33 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.79247811342</v>
+        <v>46162.792481805554</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46164.670772627316</v>
+        <v>46171.19919608797</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
+      <c r="I78" s="5">
+        <v>46169</v>
+      </c>
+      <c r="J78" s="5">
+        <v>46170</v>
+      </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
       </c>
@@ -6122,51 +6096,61 @@
         <v>26</v>
       </c>
       <c r="M78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>46169</v>
+      </c>
+      <c r="R78" s="5">
+        <v>46170</v>
+      </c>
+      <c r="S78" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T78" s="6">
         <v>0</v>
       </c>
-      <c r="N78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+      <c r="U78" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.792481805554</v>
+        <v>46162.79248949074</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46171.19919608797</v>
+        <v>46164.691113761575</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I79" s="9">
-        <v>46169</v>
+        <v>46279</v>
       </c>
       <c r="J79" s="9">
-        <v>46170</v>
+        <v>46280</v>
       </c>
       <c r="K79" s="10" t="s">
         <v>26</v>
@@ -6178,82 +6162,82 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q79" s="9">
-        <v>46169</v>
+        <v>46279</v>
       </c>
       <c r="R79" s="9">
-        <v>46170</v>
-      </c>
-      <c r="S79" s="11" t="s">
-        <v>33</v>
+        <v>46280</v>
+      </c>
+      <c r="S79" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="T79" s="10">
         <v>0</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.79248949074</v>
+        <v>46162.79249689815</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46164.691113761575</v>
+        <v>46164.69111056713</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H80" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="I80" s="5">
+        <v>46302</v>
+      </c>
+      <c r="J80" s="5">
+        <v>46303</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="I80" s="5">
-        <v>46279</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46280</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>261</v>
-      </c>
       <c r="Q80" s="5">
-        <v>46279</v>
+        <v>46302</v>
       </c>
       <c r="R80" s="5">
-        <v>46280</v>
+        <v>46303</v>
       </c>
       <c r="S80" s="7" t="s">
         <v>52</v>
@@ -6262,37 +6246,37 @@
         <v>0</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.79249689815</v>
+        <v>46162.79250443287</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.69111056713</v>
+        <v>46164.69110619213</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I81" s="9">
-        <v>46302</v>
+        <v>46280</v>
       </c>
       <c r="J81" s="9">
-        <v>46303</v>
+        <v>46281</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
@@ -6304,19 +6288,19 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="Q81" s="9">
-        <v>46302</v>
+        <v>46280</v>
       </c>
       <c r="R81" s="9">
-        <v>46303</v>
+        <v>46281</v>
       </c>
       <c r="S81" s="7" t="s">
         <v>52</v>
@@ -6325,38 +6309,32 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.79250443287</v>
+        <v>46162.79250947917</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.69110619213</v>
+        <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="I82" s="5">
-        <v>46280</v>
-      </c>
-      <c r="J82" s="5">
-        <v>46281</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
       <c r="K82" s="6" t="s">
         <v>26</v>
       </c>
@@ -6364,56 +6342,52 @@
         <v>26</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>199</v>
+        <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>157</v>
+        <v>264</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>46280</v>
-      </c>
-      <c r="R82" s="5">
-        <v>46281</v>
-      </c>
-      <c r="S82" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.79250947917</v>
+        <v>46162.79251295139</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.68453591435</v>
+        <v>46164.69124818287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I83" s="9">
+        <v>46293</v>
+      </c>
+      <c r="J83" s="9">
+        <v>46310</v>
+      </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
       </c>
@@ -6421,45 +6395,55 @@
         <v>26</v>
       </c>
       <c r="M83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="P83" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>46293</v>
+      </c>
+      <c r="R83" s="9">
+        <v>46310</v>
+      </c>
+      <c r="S83" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T83" s="10">
         <v>0</v>
       </c>
-      <c r="N83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O83" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="10"/>
-      <c r="T83" s="10"/>
-      <c r="U83" s="10"/>
+      <c r="U83" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.79251295139</v>
+        <v>46162.79252873843</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.69124818287</v>
+        <v>46164.69121831018</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I84" s="5">
         <v>46293</v>
@@ -6477,52 +6461,42 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q84" s="5">
-        <v>46293</v>
-      </c>
-      <c r="R84" s="5">
-        <v>46310</v>
-      </c>
-      <c r="S84" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.79252873843</v>
+        <v>46162.792533518514</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.69121831018</v>
+        <v>46164.6912157176</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I85" s="9">
         <v>46293</v>
@@ -6540,10 +6514,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6556,26 +6530,26 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.792533518514</v>
+        <v>46162.79253825231</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.6912157176</v>
+        <v>46164.69121336806</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I86" s="5">
         <v>46293</v>
@@ -6593,13 +6567,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>274</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>26</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6609,26 +6583,26 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.79253825231</v>
+        <v>46162.792543206015</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.69121336806</v>
+        <v>46164.691209490746</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I87" s="9">
         <v>46293</v>
@@ -6646,13 +6620,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6662,32 +6636,32 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.792543206015</v>
+        <v>46162.792612743055</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.691209490746</v>
+        <v>46164.69137969907</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>193</v>
+        <v>276</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I88" s="5">
-        <v>46293</v>
+        <v>46311</v>
       </c>
       <c r="J88" s="5">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
@@ -6699,42 +6673,52 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+        <v>263</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>46311</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46314</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T88" s="6">
+        <v>0</v>
+      </c>
+      <c r="U88" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.792612743055</v>
+        <v>46162.79261844908</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46164.69137969907</v>
+        <v>46164.69134153935</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>281</v>
+        <v>188</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I89" s="9">
         <v>46311</v>
@@ -6752,52 +6736,42 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>215</v>
+        <v>278</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q89" s="9">
-        <v>46311</v>
-      </c>
-      <c r="R89" s="9">
-        <v>46314</v>
-      </c>
-      <c r="S89" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T89" s="10">
-        <v>0</v>
-      </c>
-      <c r="U89" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.79261844908</v>
+        <v>46162.7926247338</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46164.69134153935</v>
+        <v>46164.69133898148</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I90" s="5">
         <v>46311</v>
@@ -6815,13 +6789,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6831,26 +6805,26 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.7926247338</v>
+        <v>46162.792630682874</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46164.69133898148</v>
+        <v>46164.69133623842</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I91" s="9">
         <v>46311</v>
@@ -6868,13 +6842,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6884,26 +6858,26 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.792630682874</v>
+        <v>46162.79263777778</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46164.69133623842</v>
+        <v>46164.691332372684</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I92" s="5">
         <v>46311</v>
@@ -6921,13 +6895,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6937,32 +6911,32 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.79263777778</v>
+        <v>46162.79268604166</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.691332372684</v>
+        <v>46164.6915004051</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>193</v>
+        <v>285</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I93" s="9">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="J93" s="9">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>26</v>
@@ -6974,42 +6948,52 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>287</v>
+        <v>210</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q93" s="10"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="10"/>
-      <c r="T93" s="10"/>
-      <c r="U93" s="10"/>
+        <v>263</v>
+      </c>
+      <c r="Q93" s="9">
+        <v>46315</v>
+      </c>
+      <c r="R93" s="9">
+        <v>46316</v>
+      </c>
+      <c r="S93" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T93" s="10">
+        <v>0</v>
+      </c>
+      <c r="U93" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.79268604166</v>
+        <v>46162.79269070602</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46164.6915004051</v>
+        <v>46164.691474872685</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I94" s="5">
         <v>46315</v>
@@ -7027,52 +7011,42 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>215</v>
+        <v>287</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q94" s="5">
-        <v>46315</v>
-      </c>
-      <c r="R94" s="5">
-        <v>46316</v>
-      </c>
-      <c r="S94" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.79269070602</v>
+        <v>46162.79269707176</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46164.691474872685</v>
+        <v>46164.69147140047</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I95" s="9">
         <v>46315</v>
@@ -7090,13 +7064,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7106,26 +7080,26 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.79269707176</v>
+        <v>46162.792703576386</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46164.69147140047</v>
+        <v>46164.691468171295</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I96" s="5">
         <v>46315</v>
@@ -7143,13 +7117,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7159,26 +7133,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.792703576386</v>
+        <v>46162.79271046296</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46164.691468171295</v>
+        <v>46164.69146488426</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I97" s="9">
         <v>46315</v>
@@ -7196,13 +7170,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="O97" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>294</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>296</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7212,32 +7186,32 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.79271046296</v>
+        <v>46162.792744861115</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.69146488426</v>
+        <v>46164.691619942125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>193</v>
+        <v>296</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I98" s="5">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="J98" s="5">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -7249,42 +7223,52 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>298</v>
+        <v>210</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6"/>
-      <c r="S98" s="6"/>
-      <c r="T98" s="6"/>
-      <c r="U98" s="6"/>
+        <v>263</v>
+      </c>
+      <c r="Q98" s="5">
+        <v>46317</v>
+      </c>
+      <c r="R98" s="5">
+        <v>46318</v>
+      </c>
+      <c r="S98" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T98" s="6">
+        <v>0</v>
+      </c>
+      <c r="U98" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.792744861115</v>
+        <v>46162.79274982639</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46164.691619942125</v>
+        <v>46164.69158721065</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>301</v>
+        <v>188</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I99" s="9">
         <v>46317</v>
@@ -7302,52 +7286,42 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>215</v>
+        <v>298</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q99" s="9">
-        <v>46317</v>
-      </c>
-      <c r="R99" s="9">
-        <v>46318</v>
-      </c>
-      <c r="S99" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T99" s="10">
-        <v>0</v>
-      </c>
-      <c r="U99" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
+      <c r="U99" s="10"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.79274982639</v>
+        <v>46162.79275559028</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46164.69158721065</v>
+        <v>46164.69158380787</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I100" s="5">
         <v>46317</v>
@@ -7365,13 +7339,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7381,26 +7355,26 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.79275559028</v>
+        <v>46162.79276118056</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46164.69158380787</v>
+        <v>46164.69158106481</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I101" s="9">
         <v>46317</v>
@@ -7418,13 +7392,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7434,26 +7408,26 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.79276118056</v>
+        <v>46162.792767754625</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46164.69158106481</v>
+        <v>46164.69157646991</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I102" s="5">
         <v>46317</v>
@@ -7471,13 +7445,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7487,32 +7461,32 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.792767754625</v>
+        <v>46162.79285696759</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.69157646991</v>
+        <v>46164.69173954861</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>193</v>
+        <v>306</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I103" s="9">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="J103" s="9">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="K103" s="10" t="s">
         <v>26</v>
@@ -7524,42 +7498,52 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>309</v>
+        <v>210</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q103" s="10"/>
-      <c r="R103" s="10"/>
-      <c r="S103" s="10"/>
-      <c r="T103" s="10"/>
-      <c r="U103" s="10"/>
+        <v>263</v>
+      </c>
+      <c r="Q103" s="9">
+        <v>46321</v>
+      </c>
+      <c r="R103" s="9">
+        <v>46321</v>
+      </c>
+      <c r="S103" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T103" s="10">
+        <v>0</v>
+      </c>
+      <c r="U103" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.79285696759</v>
+        <v>46162.792862511575</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.69173954861</v>
+        <v>46164.69170866898</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>311</v>
+        <v>188</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I104" s="5">
         <v>46321</v>
@@ -7577,52 +7561,42 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q104" s="5">
-        <v>46321</v>
-      </c>
-      <c r="R104" s="5">
-        <v>46321</v>
-      </c>
-      <c r="S104" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T104" s="6">
-        <v>0</v>
-      </c>
-      <c r="U104" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="6"/>
+      <c r="T104" s="6"/>
+      <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.792862511575</v>
+        <v>46162.792868125005</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.69170866898</v>
+        <v>46164.69170596065</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I105" s="9">
         <v>46321</v>
@@ -7640,13 +7614,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7656,26 +7630,26 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.792868125005</v>
+        <v>46162.792873750004</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.69170596065</v>
+        <v>46164.69170293982</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I106" s="5">
         <v>46321</v>
@@ -7693,13 +7667,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7709,26 +7683,26 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.792873750004</v>
+        <v>46162.7928793287</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.69170293982</v>
+        <v>46164.691698194445</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I107" s="9">
         <v>46321</v>
@@ -7746,13 +7720,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7762,32 +7736,30 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.7928793287</v>
+        <v>46162.792907696756</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.691698194445</v>
+        <v>46164.69185736111</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>193</v>
+        <v>314</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I108" s="5">
-        <v>46321</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I108" s="6"/>
       <c r="J108" s="5">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>26</v>
@@ -7799,44 +7771,56 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6"/>
-      <c r="S108" s="6"/>
-      <c r="T108" s="6"/>
-      <c r="U108" s="6"/>
+      <c r="Q108" s="5">
+        <v>46323</v>
+      </c>
+      <c r="R108" s="5">
+        <v>46323</v>
+      </c>
+      <c r="S108" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T108" s="6">
+        <v>0</v>
+      </c>
+      <c r="U108" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.792907696756</v>
+        <v>46162.79291289352</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.69185736111</v>
+        <v>46164.69182431713</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>319</v>
+        <v>188</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I109" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="I109" s="9">
+        <v>46323</v>
+      </c>
       <c r="J109" s="9">
         <v>46323</v>
       </c>
@@ -7850,52 +7834,42 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q109" s="9">
-        <v>46323</v>
-      </c>
-      <c r="R109" s="9">
-        <v>46323</v>
-      </c>
-      <c r="S109" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T109" s="10">
-        <v>0</v>
-      </c>
-      <c r="U109" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="Q109" s="10"/>
+      <c r="R109" s="10"/>
+      <c r="S109" s="10"/>
+      <c r="T109" s="10"/>
+      <c r="U109" s="10"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.79291289352</v>
+        <v>46162.79291758101</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.69182431713</v>
+        <v>46164.691821562505</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I110" s="5">
         <v>46323</v>
@@ -7913,13 +7887,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7929,26 +7903,26 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.79291758101</v>
+        <v>46162.79292245371</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.691821562505</v>
+        <v>46164.691819155094</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I111" s="9">
         <v>46323</v>
@@ -7966,13 +7940,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7982,26 +7956,26 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.79292245371</v>
+        <v>46162.79293256944</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.691819155094</v>
+        <v>46164.69181509259</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I112" s="5">
         <v>46323</v>
@@ -8019,13 +7993,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8035,33 +8009,27 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.79293256944</v>
+        <v>46162.7930040625</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.69181509259</v>
+        <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I113" s="9">
-        <v>46323</v>
-      </c>
-      <c r="J113" s="9">
-        <v>46323</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H113" s="10"/>
+      <c r="I113" s="10"/>
+      <c r="J113" s="10"/>
       <c r="K113" s="10" t="s">
         <v>26</v>
       </c>
@@ -8069,16 +8037,16 @@
         <v>26</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>319</v>
+        <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>322</v>
+        <v>26</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -8088,27 +8056,33 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.7930040625</v>
+        <v>46162.79300806713</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.68546163195</v>
+        <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="6"/>
+      <c r="I114" s="5">
+        <v>46324</v>
+      </c>
+      <c r="J114" s="5">
+        <v>46324</v>
+      </c>
       <c r="K114" s="6" t="s">
         <v>26</v>
       </c>
@@ -8116,45 +8090,55 @@
         <v>26</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>26</v>
+        <v>322</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>328</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
+        <v>322</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>46324</v>
+      </c>
+      <c r="R114" s="5">
+        <v>46324</v>
+      </c>
+      <c r="S114" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T114" s="6">
+        <v>0</v>
+      </c>
+      <c r="U114" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>329</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.79300806713</v>
+        <v>46162.79301847222</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46164.6922515162</v>
+        <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>330</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8172,52 +8156,42 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>333</v>
+        <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q115" s="9">
-        <v>46324</v>
-      </c>
-      <c r="R115" s="9">
-        <v>46324</v>
-      </c>
-      <c r="S115" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T115" s="10">
-        <v>0</v>
-      </c>
-      <c r="U115" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="Q115" s="10"/>
+      <c r="R115" s="10"/>
+      <c r="S115" s="10"/>
+      <c r="T115" s="10"/>
+      <c r="U115" s="10"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.79301847222</v>
+        <v>46162.79302525463</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46164.69223148148</v>
+        <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8235,13 +8209,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P116" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="O116" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>335</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8251,26 +8225,26 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.79302525463</v>
+        <v>46162.79303010416</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46164.69222814815</v>
+        <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8288,13 +8262,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8304,26 +8278,26 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.79303010416</v>
+        <v>46162.79303482639</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46164.69222525463</v>
+        <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8341,13 +8315,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8357,32 +8331,32 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.79303482639</v>
+        <v>46162.79306296296</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.69222011574</v>
+        <v>46164.692368958335</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>331</v>
+        <v>72</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>332</v>
+        <v>72</v>
       </c>
       <c r="I119" s="9">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="J119" s="9">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K119" s="10" t="s">
         <v>26</v>
@@ -8394,42 +8368,52 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q119" s="10"/>
-      <c r="R119" s="10"/>
-      <c r="S119" s="10"/>
-      <c r="T119" s="10"/>
-      <c r="U119" s="10"/>
+        <v>322</v>
+      </c>
+      <c r="Q119" s="9">
+        <v>46325</v>
+      </c>
+      <c r="R119" s="9">
+        <v>46325</v>
+      </c>
+      <c r="S119" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T119" s="10">
+        <v>0</v>
+      </c>
+      <c r="U119" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.79306296296</v>
+        <v>46162.7930678125</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.692368958335</v>
+        <v>46164.692334189815</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>341</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I120" s="5">
         <v>46325</v>
@@ -8447,52 +8431,42 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q120" s="5">
-        <v>46325</v>
-      </c>
-      <c r="R120" s="5">
-        <v>46325</v>
-      </c>
-      <c r="S120" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T120" s="6">
-        <v>0</v>
-      </c>
-      <c r="U120" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="Q120" s="6"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="6"/>
+      <c r="T120" s="6"/>
+      <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.7930678125</v>
+        <v>46162.793072280096</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.692334189815</v>
+        <v>46164.6923315162</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I121" s="9">
         <v>46325</v>
@@ -8510,13 +8484,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8526,26 +8500,26 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.793072280096</v>
+        <v>46162.79307696759</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.6923315162</v>
+        <v>46164.69232880787</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I122" s="5">
         <v>46325</v>
@@ -8563,13 +8537,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P122" s="6" t="s">
         <v>341</v>
-      </c>
-      <c r="O122" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8579,26 +8553,26 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.79307696759</v>
+        <v>46162.79308175926</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.69232880787</v>
+        <v>46164.69232427083</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I123" s="9">
         <v>46325</v>
@@ -8616,13 +8590,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8632,32 +8606,32 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.79308175926</v>
+        <v>46162.79314625</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.69232427083</v>
+        <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>193</v>
+        <v>344</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="I124" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J124" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>26</v>
@@ -8669,42 +8643,52 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="Q124" s="6"/>
-      <c r="R124" s="6"/>
-      <c r="S124" s="6"/>
-      <c r="T124" s="6"/>
-      <c r="U124" s="6"/>
+        <v>322</v>
+      </c>
+      <c r="Q124" s="5">
+        <v>46328</v>
+      </c>
+      <c r="R124" s="5">
+        <v>46328</v>
+      </c>
+      <c r="S124" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T124" s="6">
+        <v>0</v>
+      </c>
+      <c r="U124" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.79314625</v>
+        <v>46162.793151550926</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46164.69248696759</v>
+        <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>349</v>
+        <v>188</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8722,52 +8706,42 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q125" s="9">
-        <v>46328</v>
-      </c>
-      <c r="R125" s="9">
-        <v>46328</v>
-      </c>
-      <c r="S125" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T125" s="10">
-        <v>0</v>
-      </c>
-      <c r="U125" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="Q125" s="10"/>
+      <c r="R125" s="10"/>
+      <c r="S125" s="10"/>
+      <c r="T125" s="10"/>
+      <c r="U125" s="10"/>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.793151550926</v>
+        <v>46162.79315885417</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46164.69246075231</v>
+        <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8785,13 +8759,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8801,26 +8775,26 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.79315885417</v>
+        <v>46162.79316501158</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46164.692458101854</v>
+        <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8838,13 +8812,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="O127" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P127" s="10" t="s">
         <v>349</v>
-      </c>
-      <c r="O127" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="P127" s="10" t="s">
-        <v>351</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8854,26 +8828,26 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.79316501158</v>
+        <v>46162.79316986111</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46164.69245559028</v>
+        <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8891,13 +8865,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8907,32 +8881,32 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.79316986111</v>
+        <v>46162.79319725695</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.69245128472</v>
+        <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>193</v>
+        <v>353</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I129" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J129" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K129" s="10" t="s">
         <v>26</v>
@@ -8944,42 +8918,52 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q129" s="10"/>
-      <c r="R129" s="10"/>
-      <c r="S129" s="10"/>
-      <c r="T129" s="10"/>
-      <c r="U129" s="10"/>
+        <v>354</v>
+      </c>
+      <c r="Q129" s="9">
+        <v>46329</v>
+      </c>
+      <c r="R129" s="9">
+        <v>46329</v>
+      </c>
+      <c r="S129" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T129" s="10">
+        <v>0</v>
+      </c>
+      <c r="U129" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.79319725695</v>
+        <v>46162.79320210648</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.69262644676</v>
+        <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>358</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -8997,52 +8981,42 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q130" s="5">
-        <v>46329</v>
-      </c>
-      <c r="R130" s="5">
-        <v>46329</v>
-      </c>
-      <c r="S130" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T130" s="6">
-        <v>0</v>
-      </c>
-      <c r="U130" s="11" t="s">
-        <v>85</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="Q130" s="6"/>
+      <c r="R130" s="6"/>
+      <c r="S130" s="6"/>
+      <c r="T130" s="6"/>
+      <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.79320210648</v>
+        <v>46162.793206111106</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46164.692587303245</v>
+        <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9060,13 +9034,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9076,26 +9050,26 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.793206111106</v>
+        <v>46162.7932099537</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46164.69258451389</v>
+        <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9113,13 +9087,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9129,26 +9103,26 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.7932099537</v>
+        <v>46162.79321400463</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46164.69258188657</v>
+        <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9166,13 +9140,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9182,33 +9156,27 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.79321400463</v>
+        <v>46162.79323766204</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46164.69257741898</v>
+        <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>193</v>
+        <v>360</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="I134" s="5">
-        <v>46329</v>
-      </c>
-      <c r="J134" s="5">
-        <v>46329</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6"/>
       <c r="K134" s="6" t="s">
         <v>26</v>
       </c>
@@ -9216,16 +9184,16 @@
         <v>26</v>
       </c>
       <c r="M134" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>358</v>
+        <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>193</v>
+        <v>361</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>358</v>
+        <v>26</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9235,27 +9203,33 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.79323766204</v>
+        <v>46162.79324063657</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.685922812496</v>
+        <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="F135" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H135" s="10"/>
-      <c r="I135" s="10"/>
-      <c r="J135" s="10"/>
+      <c r="I135" s="9">
+        <v>46330</v>
+      </c>
+      <c r="J135" s="9">
+        <v>46338</v>
+      </c>
       <c r="K135" s="10" t="s">
         <v>26</v>
       </c>
@@ -9263,45 +9237,55 @@
         <v>26</v>
       </c>
       <c r="M135" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N135" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="O135" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="P135" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q135" s="9">
+        <v>46330</v>
+      </c>
+      <c r="R135" s="9">
+        <v>46338</v>
+      </c>
+      <c r="S135" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T135" s="10">
         <v>0</v>
       </c>
-      <c r="N135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O135" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="P135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q135" s="10"/>
-      <c r="R135" s="10"/>
-      <c r="S135" s="10"/>
-      <c r="T135" s="10"/>
-      <c r="U135" s="10"/>
+      <c r="U135" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.79324063657</v>
+        <v>46162.79324528935</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46164.69269384259</v>
+        <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>369</v>
+        <v>48</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>370</v>
+        <v>49</v>
       </c>
       <c r="I136" s="5">
         <v>46330</v>
@@ -9319,13 +9303,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>
@@ -9340,70 +9324,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A137" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="B137" s="9">
-        <v>46162.79324528935</v>
-      </c>
-      <c r="C137" s="10"/>
-      <c r="D137" s="9">
-        <v>46164.69273445602</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="F137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G137" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I137" s="9">
-        <v>46330</v>
-      </c>
-      <c r="J137" s="9">
-        <v>46338</v>
-      </c>
-      <c r="K137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N137" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="O137" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="P137" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q137" s="9">
-        <v>46330</v>
-      </c>
-      <c r="R137" s="9">
-        <v>46338</v>
-      </c>
-      <c r="S137" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T137" s="10">
-        <v>0</v>
-      </c>
-      <c r="U137" s="11" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46197.5874947338</v>
+        <v>46198.681430613426</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2377,9 +2377,11 @@
       <c r="B14" s="5">
         <v>46162.79193019676</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46198.68140460648</v>
+      </c>
       <c r="D14" s="5">
-        <v>46197.659049317124</v>
+        <v>46198.68142037037</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2427,10 +2429,10 @@
         <v>52</v>
       </c>
       <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -2440,9 +2442,11 @@
       <c r="B15" s="9">
         <v>46162.7919353125</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46198.68142288194</v>
+      </c>
       <c r="D15" s="9">
-        <v>46197.66069275463</v>
+        <v>46198.68143896991</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2490,10 +2494,10 @@
         <v>52</v>
       </c>
       <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2822,7 +2826,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46164.66016885417</v>
+        <v>46198.685960648145</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>91</v>
@@ -2867,9 +2871,11 @@
       <c r="B22" s="5">
         <v>46162.79196002315</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46198.68595238426</v>
+      </c>
       <c r="D22" s="5">
-        <v>46164.68945766204</v>
+        <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>94</v>
@@ -2917,10 +2923,10 @@
         <v>52</v>
       </c>
       <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -2930,9 +2936,11 @@
       <c r="B23" s="9">
         <v>46162.791964375</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46198.685906238425</v>
+      </c>
       <c r="D23" s="9">
-        <v>46164.689432858795</v>
+        <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>99</v>
@@ -2989,9 +2997,11 @@
       <c r="B24" s="5">
         <v>46162.79196883102</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46198.68593903935</v>
+      </c>
       <c r="D24" s="5">
-        <v>46164.68942958333</v>
+        <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3229,9 +3239,11 @@
       <c r="B28" s="5">
         <v>46162.79198653935</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46198.685692280094</v>
+      </c>
       <c r="D28" s="5">
-        <v>46164.6896481713</v>
+        <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3279,10 +3291,10 @@
         <v>52</v>
       </c>
       <c r="T28" s="6">
-        <v>0</v>
-      </c>
-      <c r="U28" s="11" t="s">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="U28" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3292,9 +3304,11 @@
       <c r="B29" s="9">
         <v>46162.79199082176</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9">
+        <v>46198.68152349537</v>
+      </c>
       <c r="D29" s="9">
-        <v>46175.170452280094</v>
+        <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3351,9 +3365,11 @@
       <c r="B30" s="5">
         <v>46162.791995312495</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46198.68567659722</v>
+      </c>
       <c r="D30" s="5">
-        <v>46164.689623750004</v>
+        <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3410,9 +3426,11 @@
       <c r="B31" s="9">
         <v>46162.79199990741</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9">
+        <v>46198.681561550926</v>
+      </c>
       <c r="D31" s="9">
-        <v>46197.70226908565</v>
+        <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -4324,7 +4342,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46197.680719490745</v>
+        <v>46198.681576041665</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4374,8 +4392,8 @@
       <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="11" t="s">
-        <v>80</v>
+      <c r="U47" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -6132,7 +6150,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46164.691113761575</v>
+        <v>46198.68596158565</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6182,8 +6200,8 @@
       <c r="T79" s="10">
         <v>0</v>
       </c>
-      <c r="U79" s="11" t="s">
-        <v>80</v>
+      <c r="U79" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6195,7 +6213,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46164.69111056713</v>
+        <v>46198.68569559028</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6245,8 +6263,8 @@
       <c r="T80" s="6">
         <v>0</v>
       </c>
-      <c r="U80" s="11" t="s">
-        <v>80</v>
+      <c r="U80" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="368">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -283,67 +283,67 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser</t>
   </si>
   <si>
+    <t>1214982558032165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Corte plasma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma </t>
+  </si>
+  <si>
+    <t>1214982508467769</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado</t>
+  </si>
+  <si>
+    <t>1214982508467781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa</t>
+  </si>
+  <si>
+    <t>1214969047721207</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>rodete,Motor,Materiales corte Laser,Alabe</t>
+  </si>
+  <si>
+    <t>1214982580348395</t>
+  </si>
+  <si>
+    <t>Alabe</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>1214982580348412</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe,Alabe</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214982558032165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Corte plasma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma </t>
-  </si>
-  <si>
-    <t>1214982508467769</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado</t>
-  </si>
-  <si>
-    <t>1214982508467781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa</t>
-  </si>
-  <si>
-    <t>1214969047721207</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>rodete,Motor,Materiales corte Laser,Alabe</t>
-  </si>
-  <si>
-    <t>1214982580348395</t>
-  </si>
-  <si>
-    <t>Alabe</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>1214982580348412</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe,Alabe</t>
   </si>
   <si>
     <t>1214982387972692</t>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46164.68847915509</v>
+        <v>46198.78275258101</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2624,23 +2624,23 @@
       <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U17" s="11" t="s">
-        <v>80</v>
+      <c r="U17" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5">
         <v>46162.79194956018</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46164.68847201389</v>
+        <v>46198.78275320602</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2673,7 +2673,7 @@
         <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46237</v>
@@ -2687,23 +2687,23 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
-        <v>80</v>
+      <c r="U18" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>46162.79195284723</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46164.688470567125</v>
+        <v>46198.782752604166</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2736,7 +2736,7 @@
         <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2750,23 +2750,23 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
-        <v>80</v>
+      <c r="U19" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46162.79195601852</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46164.6884696412</v>
+        <v>46198.78275268518</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2799,7 +2799,7 @@
         <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2813,13 +2813,13 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="11" t="s">
-        <v>80</v>
+      <c r="U20" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46162.79179634259</v>
@@ -2829,7 +2829,7 @@
         <v>46198.685960648145</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2853,7 +2853,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46162.79196002315</v>
@@ -2878,16 +2878,16 @@
         <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2905,13 +2905,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46162.791964375</v>
@@ -2943,16 +2943,16 @@
         <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
@@ -2970,13 +2970,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3010,10 +3010,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46167</v>
@@ -3031,10 +3031,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>103</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3069,10 +3069,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46162</v>
@@ -3090,13 +3090,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>106</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q25" s="9">
         <v>46162</v>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3132,10 +3132,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3191,10 +3191,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46167</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3252,10 +3252,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3273,13 +3273,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>115</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q28" s="5">
         <v>46155</v>
@@ -3317,10 +3317,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3378,10 +3378,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3439,10 +3439,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3519,13 +3519,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q32" s="5">
         <v>46239</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3658,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3700,7 +3700,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>138</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3736,7 +3736,7 @@
         <v>46164.68984363426</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3766,7 +3766,7 @@
         <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>140</v>
@@ -3819,7 +3819,7 @@
         <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>143</v>
@@ -3869,7 +3869,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>148</v>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3905,7 +3905,7 @@
         <v>46164.68995886574</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -3935,7 +3935,7 @@
         <v>145</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>150</v>
@@ -3988,7 +3988,7 @@
         <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>153</v>
@@ -4091,7 +4091,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>160</v>
@@ -4112,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4127,7 +4127,7 @@
         <v>46164.690157951394</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4157,7 +4157,7 @@
         <v>159</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>162</v>
@@ -4210,7 +4210,7 @@
         <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>165</v>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46197.68071909722</v>
+        <v>46198.78268122685</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4266,7 +4266,9 @@
       <c r="R45" s="10"/>
       <c r="S45" s="10"/>
       <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
+      <c r="U45" s="12" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
@@ -4340,9 +4342,11 @@
       <c r="B47" s="9">
         <v>46162.79212670139</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46198.78266340277</v>
+      </c>
       <c r="D47" s="9">
-        <v>46198.681576041665</v>
+        <v>46198.78268157407</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4390,10 +4394,10 @@
         <v>52</v>
       </c>
       <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U47" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4403,9 +4407,11 @@
       <c r="B48" s="5">
         <v>46162.792133090275</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46198.78271623843</v>
+      </c>
       <c r="D48" s="5">
-        <v>46164.690227569445</v>
+        <v>46198.7827322338</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>78</v>
@@ -4453,10 +4459,10 @@
         <v>52</v>
       </c>
       <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="U48" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4519,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4841,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4904,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4967,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5030,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5093,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="U59" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5156,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5266,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5541,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5553,7 +5559,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46164.69081627315</v>
+        <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>188</v>
@@ -5606,7 +5612,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46164.69081372685</v>
+        <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>188</v>
@@ -5659,7 +5665,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46164.690812974535</v>
+        <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>188</v>
@@ -5712,7 +5718,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46164.69081170139</v>
+        <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>188</v>
@@ -5816,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5828,7 +5834,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46164.69094634259</v>
+        <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>188</v>
@@ -5881,7 +5887,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46164.69094324074</v>
+        <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>188</v>
@@ -5934,7 +5940,7 @@
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46164.69093616898</v>
+        <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>188</v>
@@ -5987,7 +5993,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46164.69093546296</v>
+        <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>188</v>
@@ -6138,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6327,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6437,7 +6443,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6712,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6724,7 +6730,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46164.69134153935</v>
+        <v>46198.78274127315</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>188</v>
@@ -6777,7 +6783,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46164.69133898148</v>
+        <v>46198.782722233795</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>188</v>
@@ -6830,7 +6836,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46164.69133623842</v>
+        <v>46198.78272511574</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>188</v>
@@ -6883,7 +6889,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46164.691332372684</v>
+        <v>46198.782724108794</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>188</v>
@@ -6987,7 +6993,7 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -6999,7 +7005,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46164.691474872685</v>
+        <v>46198.78272271991</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>188</v>
@@ -7052,7 +7058,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46164.69147140047</v>
+        <v>46198.78272560185</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>188</v>
@@ -7105,7 +7111,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46164.691468171295</v>
+        <v>46198.78273373842</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>188</v>
@@ -7158,7 +7164,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46164.69146488426</v>
+        <v>46198.78272606482</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>188</v>
@@ -7262,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7274,7 +7280,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46164.69158721065</v>
+        <v>46198.78272754629</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>188</v>
@@ -7327,7 +7333,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46164.69158380787</v>
+        <v>46198.78272310185</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>188</v>
@@ -7380,7 +7386,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46164.69158106481</v>
+        <v>46198.782727893515</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>188</v>
@@ -7433,7 +7439,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46164.69157646991</v>
+        <v>46198.782728391205</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>188</v>
@@ -7537,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7810,7 +7816,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8132,7 +8138,7 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8407,7 +8413,7 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8682,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -8957,7 +8963,7 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -9279,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9342,7 +9348,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1771,13 +1771,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.79178179398</v>
+        <v>46162.62511512732</v>
       </c>
       <c r="C4" s="5">
-        <v>46183.58133199074</v>
+        <v>46183.414665324075</v>
       </c>
       <c r="D4" s="5">
-        <v>46183.58134738426</v>
+        <v>46183.41468071759</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1824,13 +1824,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.79189126157</v>
+        <v>46162.62522459491</v>
       </c>
       <c r="C5" s="9">
-        <v>46183.58129599537</v>
+        <v>46183.414629328705</v>
       </c>
       <c r="D5" s="9">
-        <v>46183.581316400465</v>
+        <v>46183.41464973379</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1889,13 +1889,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.79189434028</v>
+        <v>46162.62522767361</v>
       </c>
       <c r="C6" s="5">
-        <v>46183.58130109953</v>
+        <v>46183.41463443287</v>
       </c>
       <c r="D6" s="5">
-        <v>46183.58131646991</v>
+        <v>46183.41464980324</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1954,13 +1954,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.79190123842</v>
+        <v>46162.62523457176</v>
       </c>
       <c r="C7" s="9">
-        <v>46183.58131381945</v>
+        <v>46183.41464715278</v>
       </c>
       <c r="D7" s="9">
-        <v>46183.58133177084</v>
+        <v>46183.41466510417</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2019,13 +2019,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.791904513884</v>
+        <v>46162.62523784723</v>
       </c>
       <c r="C8" s="5">
-        <v>46183.581319641205</v>
+        <v>46183.414652974534</v>
       </c>
       <c r="D8" s="5">
-        <v>46183.58133340278</v>
+        <v>46183.41466673611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2084,11 +2084,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.79178665509</v>
+        <v>46162.62511998843</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46197.77681821759</v>
+        <v>46197.61015155092</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2133,13 +2133,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.7919078125</v>
+        <v>46162.62524114583</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.659032407406</v>
+        <v>46197.49236574074</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.776808263894</v>
+        <v>46197.61014159722</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2198,13 +2198,13 @@
         <v>53</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.79191291667</v>
+        <v>46162.62524625</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.660673125</v>
+        <v>46197.494006458335</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.77680832176</v>
+        <v>46197.610141655096</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>54</v>
@@ -2263,13 +2263,13 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.791918055555</v>
+        <v>46162.62525138889</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.66269631944</v>
+        <v>46197.49602965278</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.776808344905</v>
+        <v>46197.61014167824</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2328,11 +2328,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.791791192125</v>
+        <v>46162.62512452547</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46198.681430613426</v>
+        <v>46198.51476394676</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2375,13 +2375,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.79193019676</v>
+        <v>46162.62526353009</v>
       </c>
       <c r="C14" s="5">
-        <v>46198.68140460648</v>
+        <v>46198.51473793981</v>
       </c>
       <c r="D14" s="5">
-        <v>46198.68142037037</v>
+        <v>46198.514753703705</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2440,13 +2440,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.7919353125</v>
+        <v>46162.62526864583</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.68142288194</v>
+        <v>46198.51475621528</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.68143896991</v>
+        <v>46198.51477230324</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2505,13 +2505,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.79194023148</v>
+        <v>46162.625273564816</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.5874865625</v>
+        <v>46197.42081989584</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.6606925</v>
+        <v>46197.49402583334</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2570,11 +2570,11 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.791945289355</v>
+        <v>46162.62527862268</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46198.78275258101</v>
+        <v>46198.61608591436</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2633,11 +2633,11 @@
         <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.79194956018</v>
+        <v>46162.62528289352</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.78275320602</v>
+        <v>46198.61608653935</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2696,11 +2696,11 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.79195284723</v>
+        <v>46162.625286180555</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.782752604166</v>
+        <v>46198.6160859375</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2759,11 +2759,11 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.79195601852</v>
+        <v>46162.625289351854</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.78275268518</v>
+        <v>46198.61608601852</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2822,11 +2822,11 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.79179634259</v>
+        <v>46162.62512967593</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.685960648145</v>
+        <v>46198.51929398148</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2869,13 +2869,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.79196002315</v>
+        <v>46162.62529335648</v>
       </c>
       <c r="C22" s="5">
-        <v>46198.68595238426</v>
+        <v>46198.51928571759</v>
       </c>
       <c r="D22" s="5">
-        <v>46198.68596357639</v>
+        <v>46198.519296909726</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2934,13 +2934,13 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.791964375</v>
+        <v>46162.625297708335</v>
       </c>
       <c r="C23" s="9">
-        <v>46198.685906238425</v>
+        <v>46198.51923957176</v>
       </c>
       <c r="D23" s="9">
-        <v>46198.68590748843</v>
+        <v>46198.519240821755</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2995,13 +2995,13 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.79196883102</v>
+        <v>46162.62530216435</v>
       </c>
       <c r="C24" s="5">
-        <v>46198.68593903935</v>
+        <v>46198.51927237269</v>
       </c>
       <c r="D24" s="5">
-        <v>46198.6859406713</v>
+        <v>46198.51927400463</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3056,11 +3056,11 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.79197329861</v>
+        <v>46162.62530663195</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.17544910879</v>
+        <v>46169.00878244213</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3119,11 +3119,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.791977500005</v>
+        <v>46162.62531083333</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.58749420139</v>
+        <v>46197.42082753472</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3178,11 +3178,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.79198199074</v>
+        <v>46162.62531532407</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46168.172647141204</v>
+        <v>46168.00598047454</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3237,13 +3237,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.79198653935</v>
+        <v>46162.625319872684</v>
       </c>
       <c r="C28" s="5">
-        <v>46198.685692280094</v>
+        <v>46198.51902561342</v>
       </c>
       <c r="D28" s="5">
-        <v>46198.68573546296</v>
+        <v>46198.5190687963</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3302,13 +3302,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.79199082176</v>
+        <v>46162.62532415509</v>
       </c>
       <c r="C29" s="9">
-        <v>46198.68152349537</v>
+        <v>46198.514856828704</v>
       </c>
       <c r="D29" s="9">
-        <v>46198.68152484954</v>
+        <v>46198.51485818287</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3363,13 +3363,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.791995312495</v>
+        <v>46162.62532864584</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.68567659722</v>
+        <v>46198.519009930555</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.68567791667</v>
+        <v>46198.51901125</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3424,13 +3424,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.79199990741</v>
+        <v>46162.625333240736</v>
       </c>
       <c r="C31" s="9">
-        <v>46198.681561550926</v>
+        <v>46198.514894884254</v>
       </c>
       <c r="D31" s="9">
-        <v>46198.68156315973</v>
+        <v>46198.514896493056</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3485,11 +3485,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.792004421295</v>
+        <v>46162.62533775463</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46164.68978111111</v>
+        <v>46164.52311444444</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3548,11 +3548,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.79200878472</v>
+        <v>46162.62534211806</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46164.68973819444</v>
+        <v>46164.52307152778</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3607,11 +3607,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.792013391205</v>
+        <v>46162.62534672454</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46164.68973515046</v>
+        <v>46164.523068483795</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3666,11 +3666,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.79201809027</v>
+        <v>46162.625351423616</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46164.689874131946</v>
+        <v>46164.523207465274</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3729,11 +3729,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.79207501157</v>
+        <v>46162.6254083449</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46164.68984363426</v>
+        <v>46164.52317696759</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>82</v>
@@ -3782,11 +3782,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.79208025463</v>
+        <v>46162.625413587964</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46164.68984076389</v>
+        <v>46164.52317409722</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3835,11 +3835,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.792085</v>
+        <v>46162.62541833334</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46164.69004553241</v>
+        <v>46164.52337886574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3898,11 +3898,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.792089166665</v>
+        <v>46162.6254225</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46164.68995886574</v>
+        <v>46164.523292199076</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>88</v>
@@ -3951,11 +3951,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.792093599535</v>
+        <v>46162.62542693287</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46164.68995591435</v>
+        <v>46164.523289247685</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4004,11 +4004,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.79210385417</v>
+        <v>46162.6254371875</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.68998921296</v>
+        <v>46164.5233225463</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -4057,11 +4057,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.79210730324</v>
+        <v>46162.62544063658</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46164.690100057865</v>
+        <v>46164.52343339121</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4120,11 +4120,11 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.792111180555</v>
+        <v>46162.62544451389</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46164.690157951394</v>
+        <v>46164.52349128472</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>85</v>
@@ -4173,11 +4173,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.79211601852</v>
+        <v>46162.62544935185</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46164.69015534723</v>
+        <v>46164.523488680556</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -4226,11 +4226,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.791800798615</v>
+        <v>46162.625134131944</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46198.78268122685</v>
+        <v>46198.61601456019</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4275,13 +4275,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.79212121527</v>
+        <v>46162.625454548615</v>
       </c>
       <c r="C46" s="5">
-        <v>46197.680713587964</v>
+        <v>46197.51404692129</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.68073020833</v>
+        <v>46197.51406354167</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4340,13 +4340,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.79212670139</v>
+        <v>46162.625460034724</v>
       </c>
       <c r="C47" s="9">
-        <v>46198.78266340277</v>
+        <v>46198.615996736116</v>
       </c>
       <c r="D47" s="9">
-        <v>46198.78268157407</v>
+        <v>46198.616014907406</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4405,13 +4405,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.792133090275</v>
+        <v>46162.62546642361</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.78271623843</v>
+        <v>46198.61604957176</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.7827322338</v>
+        <v>46198.61606556713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>78</v>
@@ -4470,11 +4470,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.79214709491</v>
+        <v>46162.625480428236</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.69027550926</v>
+        <v>46164.52360884259</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4533,11 +4533,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.792150775465</v>
+        <v>46162.625484108794</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46164.69036847222</v>
+        <v>46164.523701805556</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4586,11 +4586,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.792154849536</v>
+        <v>46162.62548818287</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46164.69036586805</v>
+        <v>46164.52369920139</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4639,11 +4639,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.79215875</v>
+        <v>46162.62549208333</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46164.69036304398</v>
+        <v>46164.52369637731</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4692,11 +4692,11 @@
         <v>192</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.79216164352</v>
+        <v>46162.62549497685</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46164.690358935186</v>
+        <v>46164.523692268514</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>188</v>
@@ -4745,11 +4745,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.7922118287</v>
+        <v>46162.62554516204</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46164.66718020833</v>
+        <v>46164.500513541665</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4792,11 +4792,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.7922200926</v>
+        <v>46162.625553425925</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.69048553241</v>
+        <v>46164.52381886574</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4855,11 +4855,11 @@
         <v>201</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.792225625</v>
+        <v>46162.62555895833</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46164.69055459491</v>
+        <v>46164.52388792824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -4918,11 +4918,11 @@
         <v>205</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.79223230324</v>
+        <v>46162.625565636576</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.690482418984</v>
+        <v>46164.52381575231</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -4981,11 +4981,11 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.79223737269</v>
+        <v>46162.62557070602</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46164.69055186343</v>
+        <v>46164.52388519676</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -5044,11 +5044,11 @@
         <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.7922424537</v>
+        <v>46162.62557578704</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46164.6904790625</v>
+        <v>46164.52381239583</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>212</v>
@@ -5107,11 +5107,11 @@
         <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.792246909725</v>
+        <v>46162.62558024305</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46164.690549328705</v>
+        <v>46164.52388266203</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5170,11 +5170,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.79225168981</v>
+        <v>46162.62558502315</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.66898752315</v>
+        <v>46164.50232085648</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>
@@ -5217,11 +5217,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.792254479165</v>
+        <v>46162.6255878125</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46164.69072508102</v>
+        <v>46164.52405841435</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5280,11 +5280,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.79225922454</v>
+        <v>46162.62559255787</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.69068318287</v>
+        <v>46164.5240165162</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>188</v>
@@ -5333,11 +5333,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.792265578704</v>
+        <v>46162.62559891204</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.69068048611</v>
+        <v>46164.52401381945</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>188</v>
@@ -5386,11 +5386,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.79227201389</v>
+        <v>46162.62560534722</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.69067753472</v>
+        <v>46164.52401086806</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>188</v>
@@ -5439,11 +5439,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.79227828704</v>
+        <v>46162.62561162037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.69067336805</v>
+        <v>46164.52400670139</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>188</v>
@@ -5492,11 +5492,11 @@
         <v>231</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.79232202546</v>
+        <v>46162.625655358795</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46164.69085144676</v>
+        <v>46164.52418478009</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>232</v>
@@ -5555,11 +5555,11 @@
         <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.79232653935</v>
+        <v>46162.62565987269</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46198.782724606484</v>
+        <v>46198.61605793981</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>188</v>
@@ -5608,11 +5608,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.79233265047</v>
+        <v>46162.625665983796</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46198.78272363426</v>
+        <v>46198.61605696759</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>188</v>
@@ -5661,11 +5661,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.79233820602</v>
+        <v>46162.625671539354</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46198.78273228009</v>
+        <v>46198.61606561343</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>188</v>
@@ -5714,11 +5714,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.79234384259</v>
+        <v>46162.62567717592</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46198.782732824075</v>
+        <v>46198.61606615741</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>188</v>
@@ -5767,11 +5767,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.79241414352</v>
+        <v>46162.62574747685</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46164.690976377315</v>
+        <v>46164.52430971064</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5830,11 +5830,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.79242041666</v>
+        <v>46162.62575375</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46198.78273341435</v>
+        <v>46198.61606674769</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>188</v>
@@ -5883,11 +5883,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.79243321759</v>
+        <v>46162.625766550926</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.78272657408</v>
+        <v>46198.61605990741</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>188</v>
@@ -5936,11 +5936,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.79243956019</v>
+        <v>46162.625772893516</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46198.78272707176</v>
+        <v>46198.6160604051</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>188</v>
@@ -5989,11 +5989,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.79244651621</v>
+        <v>46162.625779849535</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.78272166666</v>
+        <v>46198.616055</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>188</v>
@@ -6042,11 +6042,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.79247811342</v>
+        <v>46162.625811446764</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.670772627316</v>
+        <v>46164.504105960645</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>194</v>
@@ -6089,11 +6089,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.792481805554</v>
+        <v>46162.62581513889</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46171.19919608797</v>
+        <v>46171.032529421296</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6152,11 +6152,11 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.79248949074</v>
+        <v>46162.62582282408</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.68596158565</v>
+        <v>46198.51929491898</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6215,11 +6215,11 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.79249689815</v>
+        <v>46162.62583023148</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.68569559028</v>
+        <v>46198.51902892361</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6278,11 +6278,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.79250443287</v>
+        <v>46162.6258377662</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.69110619213</v>
+        <v>46164.52443952546</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6341,11 +6341,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.79250947917</v>
+        <v>46162.6258428125</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.68453591435</v>
+        <v>46164.517869247684</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6388,11 +6388,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.79251295139</v>
+        <v>46162.62584628472</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.69124818287</v>
+        <v>46164.524581516205</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>266</v>
@@ -6451,11 +6451,11 @@
         <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.79252873843</v>
+        <v>46162.625862071756</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.69121831018</v>
+        <v>46164.52455164352</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>188</v>
@@ -6504,11 +6504,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.792533518514</v>
+        <v>46162.62586685186</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.6912157176</v>
+        <v>46164.524549050926</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>188</v>
@@ -6557,11 +6557,11 @@
         <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.79253825231</v>
+        <v>46162.62587158565</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.69121336806</v>
+        <v>46164.52454670139</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>188</v>
@@ -6610,11 +6610,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.792543206015</v>
+        <v>46162.62587653935</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.691209490746</v>
+        <v>46164.524542824074</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>188</v>
@@ -6663,11 +6663,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.792612743055</v>
+        <v>46162.62594607639</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.69137969907</v>
+        <v>46164.524713032406</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>276</v>
@@ -6726,11 +6726,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.79261844908</v>
+        <v>46162.62595178241</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46198.78274127315</v>
+        <v>46198.616074606485</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>188</v>
@@ -6779,11 +6779,11 @@
         <v>280</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.7926247338</v>
+        <v>46162.62595806713</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46198.782722233795</v>
+        <v>46198.61605556713</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>188</v>
@@ -6832,11 +6832,11 @@
         <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.792630682874</v>
+        <v>46162.6259640162</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46198.78272511574</v>
+        <v>46198.61605844907</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>188</v>
@@ -6885,11 +6885,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.79263777778</v>
+        <v>46162.62597111111</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.782724108794</v>
+        <v>46198.61605744213</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>188</v>
@@ -6938,11 +6938,11 @@
         <v>284</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.79268604166</v>
+        <v>46162.626019375</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.6915004051</v>
+        <v>46164.524833738426</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>285</v>
@@ -7001,11 +7001,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.79269070602</v>
+        <v>46162.62602403935</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46198.78272271991</v>
+        <v>46198.616056053244</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>188</v>
@@ -7054,11 +7054,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.79269707176</v>
+        <v>46162.626030405096</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46198.78272560185</v>
+        <v>46198.616058935186</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>188</v>
@@ -7107,11 +7107,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.792703576386</v>
+        <v>46162.62603690972</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46198.78273373842</v>
+        <v>46198.61606707176</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>188</v>
@@ -7160,11 +7160,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.79271046296</v>
+        <v>46162.62604379629</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46198.78272606482</v>
+        <v>46198.61605939815</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>188</v>
@@ -7213,11 +7213,11 @@
         <v>295</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.792744861115</v>
+        <v>46162.626078194444</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.691619942125</v>
+        <v>46164.52495327547</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>296</v>
@@ -7276,11 +7276,11 @@
         <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.79274982639</v>
+        <v>46162.62608315972</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46198.78272754629</v>
+        <v>46198.616060879634</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>188</v>
@@ -7329,11 +7329,11 @@
         <v>300</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.79275559028</v>
+        <v>46162.626088923615</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46198.78272310185</v>
+        <v>46198.61605643519</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>188</v>
@@ -7382,11 +7382,11 @@
         <v>301</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.79276118056</v>
+        <v>46162.62609451389</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46198.782727893515</v>
+        <v>46198.61606122685</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>188</v>
@@ -7435,11 +7435,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.792767754625</v>
+        <v>46162.62610108797</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46198.782728391205</v>
+        <v>46198.61606172453</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>188</v>
@@ -7488,11 +7488,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.79285696759</v>
+        <v>46162.62619030093</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.69173954861</v>
+        <v>46164.525072881945</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>306</v>
@@ -7551,11 +7551,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.792862511575</v>
+        <v>46162.6261958449</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.69170866898</v>
+        <v>46164.525042002315</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>188</v>
@@ -7604,11 +7604,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.792868125005</v>
+        <v>46162.62620145833</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.69170596065</v>
+        <v>46164.52503929398</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>188</v>
@@ -7657,11 +7657,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.792873750004</v>
+        <v>46162.62620708333</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.69170293982</v>
+        <v>46164.525036273146</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>188</v>
@@ -7710,11 +7710,11 @@
         <v>312</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.7928793287</v>
+        <v>46162.62621266204</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.691698194445</v>
+        <v>46164.52503152778</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>188</v>
@@ -7763,11 +7763,11 @@
         <v>313</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.792907696756</v>
+        <v>46162.62624103009</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.69185736111</v>
+        <v>46164.52519069445</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>314</v>
@@ -7824,11 +7824,11 @@
         <v>316</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.79291289352</v>
+        <v>46162.62624622685</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.69182431713</v>
+        <v>46164.52515765047</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>188</v>
@@ -7877,11 +7877,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.79291758101</v>
+        <v>46162.626250914356</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.691821562505</v>
+        <v>46164.52515489583</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>188</v>
@@ -7930,11 +7930,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.79292245371</v>
+        <v>46162.626255787036</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.691819155094</v>
+        <v>46164.52515248842</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>188</v>
@@ -7983,11 +7983,11 @@
         <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.79293256944</v>
+        <v>46162.62626590278</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.69181509259</v>
+        <v>46164.52514842592</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>188</v>
@@ -8036,11 +8036,11 @@
         <v>321</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.7930040625</v>
+        <v>46162.626337395835</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.68546163195</v>
+        <v>46164.518794965275</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>322</v>
@@ -8083,11 +8083,11 @@
         <v>324</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.79300806713</v>
+        <v>46162.626341400464</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.6922515162</v>
+        <v>46164.525584849536</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>325</v>
@@ -8146,11 +8146,11 @@
         <v>329</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.79301847222</v>
+        <v>46162.62635180556</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46164.69223148148</v>
+        <v>46164.525564814816</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>188</v>
@@ -8199,11 +8199,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.79302525463</v>
+        <v>46162.626358587964</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46164.69222814815</v>
+        <v>46164.52556148148</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>188</v>
@@ -8252,11 +8252,11 @@
         <v>332</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.79303010416</v>
+        <v>46162.6263634375</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46164.69222525463</v>
+        <v>46164.525558587964</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>188</v>
@@ -8305,11 +8305,11 @@
         <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.79303482639</v>
+        <v>46162.62636815972</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46164.69222011574</v>
+        <v>46164.52555344907</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>188</v>
@@ -8358,11 +8358,11 @@
         <v>335</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.79306296296</v>
+        <v>46162.6263962963</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.692368958335</v>
+        <v>46164.52570229166</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>336</v>
@@ -8421,11 +8421,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.7930678125</v>
+        <v>46162.62640114583</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.692334189815</v>
+        <v>46164.52566752315</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>188</v>
@@ -8474,11 +8474,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.793072280096</v>
+        <v>46162.626405613424</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.6923315162</v>
+        <v>46164.52566484954</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>188</v>
@@ -8527,11 +8527,11 @@
         <v>340</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.79307696759</v>
+        <v>46162.62641030093</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.69232880787</v>
+        <v>46164.525662141205</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>188</v>
@@ -8580,11 +8580,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.79308175926</v>
+        <v>46162.62641509259</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.69232427083</v>
+        <v>46164.52565760417</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>188</v>
@@ -8633,11 +8633,11 @@
         <v>343</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.79314625</v>
+        <v>46162.626479583334</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.69248696759</v>
+        <v>46164.52582030093</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>344</v>
@@ -8696,11 +8696,11 @@
         <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.793151550926</v>
+        <v>46162.626484884255</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46164.69246075231</v>
+        <v>46164.525794085646</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>188</v>
@@ -8749,11 +8749,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.79315885417</v>
+        <v>46162.6264921875</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46164.692458101854</v>
+        <v>46164.52579143518</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>188</v>
@@ -8802,11 +8802,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.79316501158</v>
+        <v>46162.62649834491</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46164.69245559028</v>
+        <v>46164.52578892361</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>188</v>
@@ -8855,11 +8855,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.79316986111</v>
+        <v>46162.62650319445</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46164.69245128472</v>
+        <v>46164.525784618054</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>188</v>
@@ -8908,11 +8908,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.79319725695</v>
+        <v>46162.62653059028</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.69262644676</v>
+        <v>46164.52595978009</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>353</v>
@@ -8971,11 +8971,11 @@
         <v>355</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.79320210648</v>
+        <v>46162.62653543982</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.692587303245</v>
+        <v>46164.52592063657</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>188</v>
@@ -9024,11 +9024,11 @@
         <v>356</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.793206111106</v>
+        <v>46162.62653944445</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46164.69258451389</v>
+        <v>46164.52591784722</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>188</v>
@@ -9077,11 +9077,11 @@
         <v>357</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.7932099537</v>
+        <v>46162.62654328704</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46164.69258188657</v>
+        <v>46164.52591521991</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>188</v>
@@ -9130,11 +9130,11 @@
         <v>358</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.79321400463</v>
+        <v>46162.62654733796</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46164.69257741898</v>
+        <v>46164.525910752316</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>188</v>
@@ -9183,11 +9183,11 @@
         <v>359</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.79323766204</v>
+        <v>46162.62657099537</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46164.685922812496</v>
+        <v>46164.51925614583</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>360</v>
@@ -9230,11 +9230,11 @@
         <v>362</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.79324063657</v>
+        <v>46162.62657396991</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.69269384259</v>
+        <v>46164.526027175925</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>363</v>
@@ -9293,11 +9293,11 @@
         <v>366</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.79324528935</v>
+        <v>46162.62657862269</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46197.77680827546</v>
+        <v>46197.61014160879</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>367</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1771,13 +1771,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.62511512732</v>
+        <v>46162.79178179398</v>
       </c>
       <c r="C4" s="5">
-        <v>46183.414665324075</v>
+        <v>46183.58133199074</v>
       </c>
       <c r="D4" s="5">
-        <v>46183.41468071759</v>
+        <v>46183.58134738426</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1824,13 +1824,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.62522459491</v>
+        <v>46162.79189126157</v>
       </c>
       <c r="C5" s="9">
-        <v>46183.414629328705</v>
+        <v>46183.58129599537</v>
       </c>
       <c r="D5" s="9">
-        <v>46183.41464973379</v>
+        <v>46183.581316400465</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1889,13 +1889,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.62522767361</v>
+        <v>46162.79189434028</v>
       </c>
       <c r="C6" s="5">
-        <v>46183.41463443287</v>
+        <v>46183.58130109953</v>
       </c>
       <c r="D6" s="5">
-        <v>46183.41464980324</v>
+        <v>46183.58131646991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1954,13 +1954,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.62523457176</v>
+        <v>46162.79190123842</v>
       </c>
       <c r="C7" s="9">
-        <v>46183.41464715278</v>
+        <v>46183.58131381945</v>
       </c>
       <c r="D7" s="9">
-        <v>46183.41466510417</v>
+        <v>46183.58133177084</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2019,13 +2019,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.62523784723</v>
+        <v>46162.791904513884</v>
       </c>
       <c r="C8" s="5">
-        <v>46183.414652974534</v>
+        <v>46183.581319641205</v>
       </c>
       <c r="D8" s="5">
-        <v>46183.41466673611</v>
+        <v>46183.58133340278</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2084,11 +2084,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.62511998843</v>
+        <v>46162.79178665509</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46197.61015155092</v>
+        <v>46197.77681821759</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2133,13 +2133,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.62524114583</v>
+        <v>46162.7919078125</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.49236574074</v>
+        <v>46197.659032407406</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.61014159722</v>
+        <v>46197.776808263894</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2198,13 +2198,13 @@
         <v>53</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.62524625</v>
+        <v>46162.79191291667</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.494006458335</v>
+        <v>46197.660673125</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.610141655096</v>
+        <v>46197.77680832176</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>54</v>
@@ -2263,13 +2263,13 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.62525138889</v>
+        <v>46162.791918055555</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.49602965278</v>
+        <v>46197.66269631944</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.61014167824</v>
+        <v>46197.776808344905</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2328,11 +2328,11 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.62512452547</v>
+        <v>46162.791791192125</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46198.51476394676</v>
+        <v>46198.681430613426</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2375,13 +2375,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.62526353009</v>
+        <v>46162.79193019676</v>
       </c>
       <c r="C14" s="5">
-        <v>46198.51473793981</v>
+        <v>46198.68140460648</v>
       </c>
       <c r="D14" s="5">
-        <v>46198.514753703705</v>
+        <v>46198.68142037037</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2440,13 +2440,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.62526864583</v>
+        <v>46162.7919353125</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.51475621528</v>
+        <v>46198.68142288194</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.51477230324</v>
+        <v>46198.68143896991</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2505,13 +2505,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.625273564816</v>
+        <v>46162.79194023148</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.42081989584</v>
+        <v>46197.5874865625</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.49402583334</v>
+        <v>46197.6606925</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2570,11 +2570,11 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.62527862268</v>
+        <v>46162.791945289355</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46198.61608591436</v>
+        <v>46198.78275258101</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2633,11 +2633,11 @@
         <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.62528289352</v>
+        <v>46162.79194956018</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.61608653935</v>
+        <v>46198.78275320602</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2696,11 +2696,11 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.625286180555</v>
+        <v>46162.79195284723</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.6160859375</v>
+        <v>46198.782752604166</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2759,11 +2759,11 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.625289351854</v>
+        <v>46162.79195601852</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.61608601852</v>
+        <v>46198.78275268518</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2822,11 +2822,11 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.62512967593</v>
+        <v>46162.79179634259</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.51929398148</v>
+        <v>46198.685960648145</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2869,13 +2869,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.62529335648</v>
+        <v>46162.79196002315</v>
       </c>
       <c r="C22" s="5">
-        <v>46198.51928571759</v>
+        <v>46198.68595238426</v>
       </c>
       <c r="D22" s="5">
-        <v>46198.519296909726</v>
+        <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2934,13 +2934,13 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.625297708335</v>
+        <v>46162.791964375</v>
       </c>
       <c r="C23" s="9">
-        <v>46198.51923957176</v>
+        <v>46198.685906238425</v>
       </c>
       <c r="D23" s="9">
-        <v>46198.519240821755</v>
+        <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -2995,13 +2995,13 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.62530216435</v>
+        <v>46162.79196883102</v>
       </c>
       <c r="C24" s="5">
-        <v>46198.51927237269</v>
+        <v>46198.68593903935</v>
       </c>
       <c r="D24" s="5">
-        <v>46198.51927400463</v>
+        <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3056,11 +3056,11 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.62530663195</v>
+        <v>46162.79197329861</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.00878244213</v>
+        <v>46169.17544910879</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3119,11 +3119,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.62531083333</v>
+        <v>46162.791977500005</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.42082753472</v>
+        <v>46197.58749420139</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3178,11 +3178,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.62531532407</v>
+        <v>46162.79198199074</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46168.00598047454</v>
+        <v>46168.172647141204</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3237,13 +3237,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.625319872684</v>
+        <v>46162.79198653935</v>
       </c>
       <c r="C28" s="5">
-        <v>46198.51902561342</v>
+        <v>46198.685692280094</v>
       </c>
       <c r="D28" s="5">
-        <v>46198.5190687963</v>
+        <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3302,13 +3302,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.62532415509</v>
+        <v>46162.79199082176</v>
       </c>
       <c r="C29" s="9">
-        <v>46198.514856828704</v>
+        <v>46198.68152349537</v>
       </c>
       <c r="D29" s="9">
-        <v>46198.51485818287</v>
+        <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3363,13 +3363,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.62532864584</v>
+        <v>46162.791995312495</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.519009930555</v>
+        <v>46198.68567659722</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.51901125</v>
+        <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3424,13 +3424,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.625333240736</v>
+        <v>46162.79199990741</v>
       </c>
       <c r="C31" s="9">
-        <v>46198.514894884254</v>
+        <v>46198.681561550926</v>
       </c>
       <c r="D31" s="9">
-        <v>46198.514896493056</v>
+        <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3485,11 +3485,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.62533775463</v>
+        <v>46162.792004421295</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46164.52311444444</v>
+        <v>46164.68978111111</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3548,11 +3548,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.62534211806</v>
+        <v>46162.79200878472</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46164.52307152778</v>
+        <v>46164.68973819444</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3607,11 +3607,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.62534672454</v>
+        <v>46162.792013391205</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46164.523068483795</v>
+        <v>46164.68973515046</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3666,11 +3666,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.625351423616</v>
+        <v>46162.79201809027</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46164.523207465274</v>
+        <v>46164.689874131946</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3729,11 +3729,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.6254083449</v>
+        <v>46162.79207501157</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46164.52317696759</v>
+        <v>46164.68984363426</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>82</v>
@@ -3782,11 +3782,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.625413587964</v>
+        <v>46162.79208025463</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46164.52317409722</v>
+        <v>46164.68984076389</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3835,11 +3835,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.62541833334</v>
+        <v>46162.792085</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46164.52337886574</v>
+        <v>46164.69004553241</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3898,11 +3898,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.6254225</v>
+        <v>46162.792089166665</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46164.523292199076</v>
+        <v>46164.68995886574</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>88</v>
@@ -3951,11 +3951,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.62542693287</v>
+        <v>46162.792093599535</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46164.523289247685</v>
+        <v>46164.68995591435</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4004,11 +4004,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.6254371875</v>
+        <v>46162.79210385417</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.5233225463</v>
+        <v>46164.68998921296</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -4057,11 +4057,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.62544063658</v>
+        <v>46162.79210730324</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46164.52343339121</v>
+        <v>46164.690100057865</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4120,11 +4120,11 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.62544451389</v>
+        <v>46162.792111180555</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46164.52349128472</v>
+        <v>46164.690157951394</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>85</v>
@@ -4173,11 +4173,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.62544935185</v>
+        <v>46162.79211601852</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46164.523488680556</v>
+        <v>46164.69015534723</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -4226,11 +4226,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.625134131944</v>
+        <v>46162.791800798615</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46198.61601456019</v>
+        <v>46198.78268122685</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4275,13 +4275,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.625454548615</v>
+        <v>46162.79212121527</v>
       </c>
       <c r="C46" s="5">
-        <v>46197.51404692129</v>
+        <v>46197.680713587964</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.51406354167</v>
+        <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4340,13 +4340,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.625460034724</v>
+        <v>46162.79212670139</v>
       </c>
       <c r="C47" s="9">
-        <v>46198.615996736116</v>
+        <v>46198.78266340277</v>
       </c>
       <c r="D47" s="9">
-        <v>46198.616014907406</v>
+        <v>46198.78268157407</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4405,13 +4405,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.62546642361</v>
+        <v>46162.792133090275</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.61604957176</v>
+        <v>46198.78271623843</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.61606556713</v>
+        <v>46198.7827322338</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>78</v>
@@ -4470,11 +4470,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.625480428236</v>
+        <v>46162.79214709491</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.52360884259</v>
+        <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4533,11 +4533,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.625484108794</v>
+        <v>46162.792150775465</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46164.523701805556</v>
+        <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4586,11 +4586,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.62548818287</v>
+        <v>46162.792154849536</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46164.52369920139</v>
+        <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4639,11 +4639,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.62549208333</v>
+        <v>46162.79215875</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46164.52369637731</v>
+        <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4692,11 +4692,11 @@
         <v>192</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.62549497685</v>
+        <v>46162.79216164352</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46164.523692268514</v>
+        <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>188</v>
@@ -4745,11 +4745,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.62554516204</v>
+        <v>46162.7922118287</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46164.500513541665</v>
+        <v>46164.66718020833</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4792,11 +4792,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.625553425925</v>
+        <v>46162.7922200926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.52381886574</v>
+        <v>46164.69048553241</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4855,11 +4855,11 @@
         <v>201</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.62555895833</v>
+        <v>46162.792225625</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46164.52388792824</v>
+        <v>46164.69055459491</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -4918,11 +4918,11 @@
         <v>205</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.625565636576</v>
+        <v>46162.79223230324</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.52381575231</v>
+        <v>46164.690482418984</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -4981,11 +4981,11 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.62557070602</v>
+        <v>46162.79223737269</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46164.52388519676</v>
+        <v>46164.69055186343</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -5044,11 +5044,11 @@
         <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.62557578704</v>
+        <v>46162.7922424537</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46164.52381239583</v>
+        <v>46164.6904790625</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>212</v>
@@ -5107,11 +5107,11 @@
         <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.62558024305</v>
+        <v>46162.792246909725</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46164.52388266203</v>
+        <v>46164.690549328705</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5170,11 +5170,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.62558502315</v>
+        <v>46162.79225168981</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.50232085648</v>
+        <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>
@@ -5217,11 +5217,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.6255878125</v>
+        <v>46162.792254479165</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46164.52405841435</v>
+        <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5280,11 +5280,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.62559255787</v>
+        <v>46162.79225922454</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.5240165162</v>
+        <v>46164.69068318287</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>188</v>
@@ -5333,11 +5333,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.62559891204</v>
+        <v>46162.792265578704</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.52401381945</v>
+        <v>46164.69068048611</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>188</v>
@@ -5386,11 +5386,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.62560534722</v>
+        <v>46162.79227201389</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.52401086806</v>
+        <v>46164.69067753472</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>188</v>
@@ -5439,11 +5439,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.62561162037</v>
+        <v>46162.79227828704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.52400670139</v>
+        <v>46164.69067336805</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>188</v>
@@ -5492,11 +5492,11 @@
         <v>231</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.625655358795</v>
+        <v>46162.79232202546</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46164.52418478009</v>
+        <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>232</v>
@@ -5555,11 +5555,11 @@
         <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.62565987269</v>
+        <v>46162.79232653935</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46198.61605793981</v>
+        <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>188</v>
@@ -5608,11 +5608,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.625665983796</v>
+        <v>46162.79233265047</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46198.61605696759</v>
+        <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>188</v>
@@ -5661,11 +5661,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.625671539354</v>
+        <v>46162.79233820602</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46198.61606561343</v>
+        <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>188</v>
@@ -5714,11 +5714,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.62567717592</v>
+        <v>46162.79234384259</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46198.61606615741</v>
+        <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>188</v>
@@ -5767,11 +5767,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.62574747685</v>
+        <v>46162.79241414352</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46164.52430971064</v>
+        <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5830,11 +5830,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.62575375</v>
+        <v>46162.79242041666</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46198.61606674769</v>
+        <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>188</v>
@@ -5883,11 +5883,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.625766550926</v>
+        <v>46162.79243321759</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.61605990741</v>
+        <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>188</v>
@@ -5936,11 +5936,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.625772893516</v>
+        <v>46162.79243956019</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46198.6160604051</v>
+        <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>188</v>
@@ -5989,11 +5989,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.625779849535</v>
+        <v>46162.79244651621</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.616055</v>
+        <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>188</v>
@@ -6042,11 +6042,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.625811446764</v>
+        <v>46162.79247811342</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.504105960645</v>
+        <v>46164.670772627316</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>194</v>
@@ -6089,11 +6089,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.62581513889</v>
+        <v>46162.792481805554</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46171.032529421296</v>
+        <v>46171.19919608797</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6152,11 +6152,11 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.62582282408</v>
+        <v>46162.79248949074</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.51929491898</v>
+        <v>46198.68596158565</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6215,11 +6215,11 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.62583023148</v>
+        <v>46162.79249689815</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.51902892361</v>
+        <v>46198.68569559028</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6278,11 +6278,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.6258377662</v>
+        <v>46162.79250443287</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.52443952546</v>
+        <v>46164.69110619213</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6341,11 +6341,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.6258428125</v>
+        <v>46162.79250947917</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.517869247684</v>
+        <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6388,11 +6388,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.62584628472</v>
+        <v>46162.79251295139</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.524581516205</v>
+        <v>46164.69124818287</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>266</v>
@@ -6451,11 +6451,11 @@
         <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.625862071756</v>
+        <v>46162.79252873843</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.52455164352</v>
+        <v>46164.69121831018</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>188</v>
@@ -6504,11 +6504,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.62586685186</v>
+        <v>46162.792533518514</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.524549050926</v>
+        <v>46164.6912157176</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>188</v>
@@ -6557,11 +6557,11 @@
         <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.62587158565</v>
+        <v>46162.79253825231</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.52454670139</v>
+        <v>46164.69121336806</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>188</v>
@@ -6610,11 +6610,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.62587653935</v>
+        <v>46162.792543206015</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.524542824074</v>
+        <v>46164.691209490746</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>188</v>
@@ -6663,11 +6663,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.62594607639</v>
+        <v>46162.792612743055</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.524713032406</v>
+        <v>46164.69137969907</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>276</v>
@@ -6726,11 +6726,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.62595178241</v>
+        <v>46162.79261844908</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46198.616074606485</v>
+        <v>46198.78274127315</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>188</v>
@@ -6779,11 +6779,11 @@
         <v>280</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.62595806713</v>
+        <v>46162.7926247338</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46198.61605556713</v>
+        <v>46198.782722233795</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>188</v>
@@ -6832,11 +6832,11 @@
         <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.6259640162</v>
+        <v>46162.792630682874</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46198.61605844907</v>
+        <v>46198.78272511574</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>188</v>
@@ -6885,11 +6885,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.62597111111</v>
+        <v>46162.79263777778</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.61605744213</v>
+        <v>46198.782724108794</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>188</v>
@@ -6938,11 +6938,11 @@
         <v>284</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.626019375</v>
+        <v>46162.79268604166</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.524833738426</v>
+        <v>46164.6915004051</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>285</v>
@@ -7001,11 +7001,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.62602403935</v>
+        <v>46162.79269070602</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46198.616056053244</v>
+        <v>46198.78272271991</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>188</v>
@@ -7054,11 +7054,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.626030405096</v>
+        <v>46162.79269707176</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46198.616058935186</v>
+        <v>46198.78272560185</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>188</v>
@@ -7107,11 +7107,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.62603690972</v>
+        <v>46162.792703576386</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46198.61606707176</v>
+        <v>46198.78273373842</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>188</v>
@@ -7160,11 +7160,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.62604379629</v>
+        <v>46162.79271046296</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46198.61605939815</v>
+        <v>46198.78272606482</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>188</v>
@@ -7213,11 +7213,11 @@
         <v>295</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.626078194444</v>
+        <v>46162.792744861115</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.52495327547</v>
+        <v>46164.691619942125</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>296</v>
@@ -7276,11 +7276,11 @@
         <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.62608315972</v>
+        <v>46162.79274982639</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46198.616060879634</v>
+        <v>46198.78272754629</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>188</v>
@@ -7329,11 +7329,11 @@
         <v>300</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.626088923615</v>
+        <v>46162.79275559028</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46198.61605643519</v>
+        <v>46198.78272310185</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>188</v>
@@ -7382,11 +7382,11 @@
         <v>301</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.62609451389</v>
+        <v>46162.79276118056</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46198.61606122685</v>
+        <v>46198.782727893515</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>188</v>
@@ -7435,11 +7435,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.62610108797</v>
+        <v>46162.792767754625</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46198.61606172453</v>
+        <v>46198.782728391205</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>188</v>
@@ -7488,11 +7488,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.62619030093</v>
+        <v>46162.79285696759</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.525072881945</v>
+        <v>46164.69173954861</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>306</v>
@@ -7551,11 +7551,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.6261958449</v>
+        <v>46162.792862511575</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.525042002315</v>
+        <v>46164.69170866898</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>188</v>
@@ -7604,11 +7604,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.62620145833</v>
+        <v>46162.792868125005</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.52503929398</v>
+        <v>46164.69170596065</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>188</v>
@@ -7657,11 +7657,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.62620708333</v>
+        <v>46162.792873750004</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.525036273146</v>
+        <v>46164.69170293982</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>188</v>
@@ -7710,11 +7710,11 @@
         <v>312</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.62621266204</v>
+        <v>46162.7928793287</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.52503152778</v>
+        <v>46164.691698194445</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>188</v>
@@ -7763,11 +7763,11 @@
         <v>313</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.62624103009</v>
+        <v>46162.792907696756</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.52519069445</v>
+        <v>46164.69185736111</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>314</v>
@@ -7824,11 +7824,11 @@
         <v>316</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.62624622685</v>
+        <v>46162.79291289352</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.52515765047</v>
+        <v>46164.69182431713</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>188</v>
@@ -7877,11 +7877,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.626250914356</v>
+        <v>46162.79291758101</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.52515489583</v>
+        <v>46164.691821562505</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>188</v>
@@ -7930,11 +7930,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.626255787036</v>
+        <v>46162.79292245371</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.52515248842</v>
+        <v>46164.691819155094</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>188</v>
@@ -7983,11 +7983,11 @@
         <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.62626590278</v>
+        <v>46162.79293256944</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.52514842592</v>
+        <v>46164.69181509259</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>188</v>
@@ -8036,11 +8036,11 @@
         <v>321</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.626337395835</v>
+        <v>46162.7930040625</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.518794965275</v>
+        <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>322</v>
@@ -8083,11 +8083,11 @@
         <v>324</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.626341400464</v>
+        <v>46162.79300806713</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.525584849536</v>
+        <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>325</v>
@@ -8146,11 +8146,11 @@
         <v>329</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.62635180556</v>
+        <v>46162.79301847222</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46164.525564814816</v>
+        <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>188</v>
@@ -8199,11 +8199,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.626358587964</v>
+        <v>46162.79302525463</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46164.52556148148</v>
+        <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>188</v>
@@ -8252,11 +8252,11 @@
         <v>332</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.6263634375</v>
+        <v>46162.79303010416</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46164.525558587964</v>
+        <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>188</v>
@@ -8305,11 +8305,11 @@
         <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.62636815972</v>
+        <v>46162.79303482639</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46164.52555344907</v>
+        <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>188</v>
@@ -8358,11 +8358,11 @@
         <v>335</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.6263962963</v>
+        <v>46162.79306296296</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.52570229166</v>
+        <v>46164.692368958335</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>336</v>
@@ -8421,11 +8421,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.62640114583</v>
+        <v>46162.7930678125</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.52566752315</v>
+        <v>46164.692334189815</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>188</v>
@@ -8474,11 +8474,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.626405613424</v>
+        <v>46162.793072280096</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.52566484954</v>
+        <v>46164.6923315162</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>188</v>
@@ -8527,11 +8527,11 @@
         <v>340</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.62641030093</v>
+        <v>46162.79307696759</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.525662141205</v>
+        <v>46164.69232880787</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>188</v>
@@ -8580,11 +8580,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.62641509259</v>
+        <v>46162.79308175926</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.52565760417</v>
+        <v>46164.69232427083</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>188</v>
@@ -8633,11 +8633,11 @@
         <v>343</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.626479583334</v>
+        <v>46162.79314625</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.52582030093</v>
+        <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>344</v>
@@ -8696,11 +8696,11 @@
         <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.626484884255</v>
+        <v>46162.793151550926</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46164.525794085646</v>
+        <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>188</v>
@@ -8749,11 +8749,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.6264921875</v>
+        <v>46162.79315885417</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46164.52579143518</v>
+        <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>188</v>
@@ -8802,11 +8802,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.62649834491</v>
+        <v>46162.79316501158</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46164.52578892361</v>
+        <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>188</v>
@@ -8855,11 +8855,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.62650319445</v>
+        <v>46162.79316986111</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46164.525784618054</v>
+        <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>188</v>
@@ -8908,11 +8908,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.62653059028</v>
+        <v>46162.79319725695</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.52595978009</v>
+        <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>353</v>
@@ -8971,11 +8971,11 @@
         <v>355</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.62653543982</v>
+        <v>46162.79320210648</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.52592063657</v>
+        <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>188</v>
@@ -9024,11 +9024,11 @@
         <v>356</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.62653944445</v>
+        <v>46162.793206111106</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46164.52591784722</v>
+        <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>188</v>
@@ -9077,11 +9077,11 @@
         <v>357</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.62654328704</v>
+        <v>46162.7932099537</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46164.52591521991</v>
+        <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>188</v>
@@ -9130,11 +9130,11 @@
         <v>358</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.62654733796</v>
+        <v>46162.79321400463</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46164.525910752316</v>
+        <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>188</v>
@@ -9183,11 +9183,11 @@
         <v>359</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.62657099537</v>
+        <v>46162.79323766204</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46164.51925614583</v>
+        <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>360</v>
@@ -9230,11 +9230,11 @@
         <v>362</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.62657396991</v>
+        <v>46162.79324063657</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.526027175925</v>
+        <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>363</v>
@@ -9293,11 +9293,11 @@
         <v>366</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.62657862269</v>
+        <v>46162.79324528935</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46197.61014160879</v>
+        <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>367</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="368">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -2330,9 +2330,11 @@
       <c r="B13" s="9">
         <v>46162.791791192125</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9">
+        <v>46204.8976890162</v>
+      </c>
       <c r="D13" s="9">
-        <v>46198.681430613426</v>
+        <v>46204.89769989584</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2367,8 +2369,12 @@
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
+      <c r="T13" s="10">
+        <v>1</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -2572,9 +2578,11 @@
       <c r="B17" s="9">
         <v>46162.791945289355</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9">
+        <v>46204.89537108796</v>
+      </c>
       <c r="D17" s="9">
-        <v>46198.78275258101</v>
+        <v>46204.89660072917</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2622,10 +2630,10 @@
         <v>52</v>
       </c>
       <c r="T17" s="10">
-        <v>0</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2635,9 +2643,11 @@
       <c r="B18" s="5">
         <v>46162.79194956018</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46204.89540233796</v>
+      </c>
       <c r="D18" s="5">
-        <v>46198.78275320602</v>
+        <v>46204.897086157405</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2685,10 +2695,10 @@
         <v>52</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2698,9 +2708,11 @@
       <c r="B19" s="9">
         <v>46162.79195284723</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46204.898560891204</v>
+      </c>
       <c r="D19" s="9">
-        <v>46198.782752604166</v>
+        <v>46204.8990687037</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2748,10 +2760,10 @@
         <v>52</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2761,9 +2773,11 @@
       <c r="B20" s="5">
         <v>46162.79195601852</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46204.8976750463</v>
+      </c>
       <c r="D20" s="5">
-        <v>46198.78275268518</v>
+        <v>46204.89768974537</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2811,10 +2825,10 @@
         <v>52</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -3552,7 +3566,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46164.68973819444</v>
+        <v>46204.89538238426</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3733,7 +3747,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46164.68984363426</v>
+        <v>46204.895408599536</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>82</v>
@@ -3902,7 +3916,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46164.68995886574</v>
+        <v>46204.89768113426</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>88</v>
@@ -4124,7 +4138,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46164.690157951394</v>
+        <v>46204.898568460645</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>85</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -2777,7 +2777,7 @@
         <v>46204.8976750463</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.89768974537</v>
+        <v>46204.91486320602</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1771,13 +1771,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.79178179398</v>
+        <v>46162.62511512732</v>
       </c>
       <c r="C4" s="5">
-        <v>46183.58133199074</v>
+        <v>46183.414665324075</v>
       </c>
       <c r="D4" s="5">
-        <v>46183.58134738426</v>
+        <v>46183.41468071759</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1824,13 +1824,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.79189126157</v>
+        <v>46162.62522459491</v>
       </c>
       <c r="C5" s="9">
-        <v>46183.58129599537</v>
+        <v>46183.414629328705</v>
       </c>
       <c r="D5" s="9">
-        <v>46183.581316400465</v>
+        <v>46183.41464973379</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1889,13 +1889,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.79189434028</v>
+        <v>46162.62522767361</v>
       </c>
       <c r="C6" s="5">
-        <v>46183.58130109953</v>
+        <v>46183.41463443287</v>
       </c>
       <c r="D6" s="5">
-        <v>46183.58131646991</v>
+        <v>46183.41464980324</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1954,13 +1954,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.79190123842</v>
+        <v>46162.62523457176</v>
       </c>
       <c r="C7" s="9">
-        <v>46183.58131381945</v>
+        <v>46183.41464715278</v>
       </c>
       <c r="D7" s="9">
-        <v>46183.58133177084</v>
+        <v>46183.41466510417</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2019,13 +2019,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.791904513884</v>
+        <v>46162.62523784723</v>
       </c>
       <c r="C8" s="5">
-        <v>46183.581319641205</v>
+        <v>46183.414652974534</v>
       </c>
       <c r="D8" s="5">
-        <v>46183.58133340278</v>
+        <v>46183.41466673611</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2084,11 +2084,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.79178665509</v>
+        <v>46162.62511998843</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46197.77681821759</v>
+        <v>46197.61015155092</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2133,13 +2133,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.7919078125</v>
+        <v>46162.62524114583</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.659032407406</v>
+        <v>46197.49236574074</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.776808263894</v>
+        <v>46197.61014159722</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2198,13 +2198,13 @@
         <v>53</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.79191291667</v>
+        <v>46162.62524625</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.660673125</v>
+        <v>46197.494006458335</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.77680832176</v>
+        <v>46197.610141655096</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>54</v>
@@ -2263,13 +2263,13 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.791918055555</v>
+        <v>46162.62525138889</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.66269631944</v>
+        <v>46197.49602965278</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.776808344905</v>
+        <v>46197.61014167824</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2328,13 +2328,13 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.791791192125</v>
+        <v>46162.62512452547</v>
       </c>
       <c r="C13" s="9">
-        <v>46204.8976890162</v>
+        <v>46204.73102234954</v>
       </c>
       <c r="D13" s="9">
-        <v>46204.89769989584</v>
+        <v>46204.73103322917</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2381,13 +2381,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.79193019676</v>
+        <v>46162.62526353009</v>
       </c>
       <c r="C14" s="5">
-        <v>46198.68140460648</v>
+        <v>46198.51473793981</v>
       </c>
       <c r="D14" s="5">
-        <v>46198.68142037037</v>
+        <v>46198.514753703705</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2446,13 +2446,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.7919353125</v>
+        <v>46162.62526864583</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.68142288194</v>
+        <v>46198.51475621528</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.68143896991</v>
+        <v>46198.51477230324</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2511,13 +2511,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.79194023148</v>
+        <v>46162.625273564816</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.5874865625</v>
+        <v>46197.42081989584</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.6606925</v>
+        <v>46197.49402583334</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2576,13 +2576,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.791945289355</v>
+        <v>46162.62527862268</v>
       </c>
       <c r="C17" s="9">
-        <v>46204.89537108796</v>
+        <v>46204.7287044213</v>
       </c>
       <c r="D17" s="9">
-        <v>46204.89660072917</v>
+        <v>46204.7299340625</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2641,13 +2641,13 @@
         <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.79194956018</v>
+        <v>46162.62528289352</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.89540233796</v>
+        <v>46204.72873567129</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.897086157405</v>
+        <v>46204.73041949074</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2706,13 +2706,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.79195284723</v>
+        <v>46162.625286180555</v>
       </c>
       <c r="C19" s="9">
-        <v>46204.898560891204</v>
+        <v>46204.73189422453</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.8990687037</v>
+        <v>46204.732402037036</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2771,13 +2771,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.79195601852</v>
+        <v>46162.625289351854</v>
       </c>
       <c r="C20" s="5">
-        <v>46204.8976750463</v>
+        <v>46204.73100837963</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.91486320602</v>
+        <v>46204.74819653935</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2836,11 +2836,11 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.79179634259</v>
+        <v>46162.62512967593</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.685960648145</v>
+        <v>46198.51929398148</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2883,13 +2883,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.79196002315</v>
+        <v>46162.62529335648</v>
       </c>
       <c r="C22" s="5">
-        <v>46198.68595238426</v>
+        <v>46198.51928571759</v>
       </c>
       <c r="D22" s="5">
-        <v>46198.68596357639</v>
+        <v>46198.519296909726</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2948,13 +2948,13 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.791964375</v>
+        <v>46162.625297708335</v>
       </c>
       <c r="C23" s="9">
-        <v>46198.685906238425</v>
+        <v>46198.51923957176</v>
       </c>
       <c r="D23" s="9">
-        <v>46198.68590748843</v>
+        <v>46198.519240821755</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -3009,13 +3009,13 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.79196883102</v>
+        <v>46162.62530216435</v>
       </c>
       <c r="C24" s="5">
-        <v>46198.68593903935</v>
+        <v>46198.51927237269</v>
       </c>
       <c r="D24" s="5">
-        <v>46198.6859406713</v>
+        <v>46198.51927400463</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3070,11 +3070,11 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.79197329861</v>
+        <v>46162.62530663195</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.17544910879</v>
+        <v>46169.00878244213</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3133,11 +3133,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.791977500005</v>
+        <v>46162.62531083333</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.58749420139</v>
+        <v>46197.42082753472</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3192,11 +3192,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.79198199074</v>
+        <v>46162.62531532407</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46168.172647141204</v>
+        <v>46168.00598047454</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3251,13 +3251,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.79198653935</v>
+        <v>46162.625319872684</v>
       </c>
       <c r="C28" s="5">
-        <v>46198.685692280094</v>
+        <v>46198.51902561342</v>
       </c>
       <c r="D28" s="5">
-        <v>46198.68573546296</v>
+        <v>46198.5190687963</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3316,13 +3316,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.79199082176</v>
+        <v>46162.62532415509</v>
       </c>
       <c r="C29" s="9">
-        <v>46198.68152349537</v>
+        <v>46198.514856828704</v>
       </c>
       <c r="D29" s="9">
-        <v>46198.68152484954</v>
+        <v>46198.51485818287</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3377,13 +3377,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.791995312495</v>
+        <v>46162.62532864584</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.68567659722</v>
+        <v>46198.519009930555</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.68567791667</v>
+        <v>46198.51901125</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3438,13 +3438,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.79199990741</v>
+        <v>46162.625333240736</v>
       </c>
       <c r="C31" s="9">
-        <v>46198.681561550926</v>
+        <v>46198.514894884254</v>
       </c>
       <c r="D31" s="9">
-        <v>46198.68156315973</v>
+        <v>46198.514896493056</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3499,11 +3499,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.792004421295</v>
+        <v>46162.62533775463</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46164.68978111111</v>
+        <v>46164.52311444444</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3562,11 +3562,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.79200878472</v>
+        <v>46162.62534211806</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46204.89538238426</v>
+        <v>46204.72871571759</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3621,11 +3621,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.792013391205</v>
+        <v>46162.62534672454</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46164.68973515046</v>
+        <v>46164.523068483795</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3680,11 +3680,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.79201809027</v>
+        <v>46162.625351423616</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46164.689874131946</v>
+        <v>46164.523207465274</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3743,11 +3743,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.79207501157</v>
+        <v>46162.6254083449</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46204.895408599536</v>
+        <v>46204.72874193287</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>82</v>
@@ -3796,11 +3796,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.79208025463</v>
+        <v>46162.625413587964</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46164.68984076389</v>
+        <v>46164.52317409722</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3849,11 +3849,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.792085</v>
+        <v>46162.62541833334</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46164.69004553241</v>
+        <v>46164.52337886574</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3912,11 +3912,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.792089166665</v>
+        <v>46162.6254225</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46204.89768113426</v>
+        <v>46204.731014467594</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>88</v>
@@ -3965,11 +3965,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.792093599535</v>
+        <v>46162.62542693287</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46164.68995591435</v>
+        <v>46164.523289247685</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4018,11 +4018,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.79210385417</v>
+        <v>46162.6254371875</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.68998921296</v>
+        <v>46164.5233225463</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -4071,11 +4071,11 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.79210730324</v>
+        <v>46162.62544063658</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46164.690100057865</v>
+        <v>46164.52343339121</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4134,11 +4134,11 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.792111180555</v>
+        <v>46162.62544451389</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46204.898568460645</v>
+        <v>46204.73190179398</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>85</v>
@@ -4187,11 +4187,11 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.79211601852</v>
+        <v>46162.62544935185</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46164.69015534723</v>
+        <v>46164.523488680556</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -4240,11 +4240,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.791800798615</v>
+        <v>46162.625134131944</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46198.78268122685</v>
+        <v>46198.61601456019</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4289,13 +4289,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.79212121527</v>
+        <v>46162.625454548615</v>
       </c>
       <c r="C46" s="5">
-        <v>46197.680713587964</v>
+        <v>46197.51404692129</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.68073020833</v>
+        <v>46197.51406354167</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4354,13 +4354,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.79212670139</v>
+        <v>46162.625460034724</v>
       </c>
       <c r="C47" s="9">
-        <v>46198.78266340277</v>
+        <v>46198.615996736116</v>
       </c>
       <c r="D47" s="9">
-        <v>46198.78268157407</v>
+        <v>46198.616014907406</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4419,13 +4419,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.792133090275</v>
+        <v>46162.62546642361</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.78271623843</v>
+        <v>46198.61604957176</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.7827322338</v>
+        <v>46198.61606556713</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>78</v>
@@ -4484,11 +4484,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.79214709491</v>
+        <v>46162.625480428236</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.69027550926</v>
+        <v>46164.52360884259</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4547,11 +4547,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.792150775465</v>
+        <v>46162.625484108794</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46164.69036847222</v>
+        <v>46164.523701805556</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4600,11 +4600,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.792154849536</v>
+        <v>46162.62548818287</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46164.69036586805</v>
+        <v>46164.52369920139</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4653,11 +4653,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.79215875</v>
+        <v>46162.62549208333</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46164.69036304398</v>
+        <v>46164.52369637731</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4706,11 +4706,11 @@
         <v>192</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.79216164352</v>
+        <v>46162.62549497685</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46164.690358935186</v>
+        <v>46164.523692268514</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>188</v>
@@ -4759,11 +4759,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.7922118287</v>
+        <v>46162.62554516204</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46164.66718020833</v>
+        <v>46164.500513541665</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4806,11 +4806,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.7922200926</v>
+        <v>46162.625553425925</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.69048553241</v>
+        <v>46164.52381886574</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4869,11 +4869,11 @@
         <v>201</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.792225625</v>
+        <v>46162.62555895833</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46164.69055459491</v>
+        <v>46164.52388792824</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -4932,11 +4932,11 @@
         <v>205</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.79223230324</v>
+        <v>46162.625565636576</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.690482418984</v>
+        <v>46164.52381575231</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -4995,11 +4995,11 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.79223737269</v>
+        <v>46162.62557070602</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46164.69055186343</v>
+        <v>46164.52388519676</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -5058,11 +5058,11 @@
         <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.7922424537</v>
+        <v>46162.62557578704</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46164.6904790625</v>
+        <v>46164.52381239583</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>212</v>
@@ -5121,11 +5121,11 @@
         <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.792246909725</v>
+        <v>46162.62558024305</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46164.690549328705</v>
+        <v>46164.52388266203</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5184,11 +5184,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.79225168981</v>
+        <v>46162.62558502315</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.66898752315</v>
+        <v>46164.50232085648</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>
@@ -5231,11 +5231,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.792254479165</v>
+        <v>46162.6255878125</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46164.69072508102</v>
+        <v>46164.52405841435</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5294,11 +5294,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.79225922454</v>
+        <v>46162.62559255787</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.69068318287</v>
+        <v>46164.5240165162</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>188</v>
@@ -5347,11 +5347,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.792265578704</v>
+        <v>46162.62559891204</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.69068048611</v>
+        <v>46164.52401381945</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>188</v>
@@ -5400,11 +5400,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.79227201389</v>
+        <v>46162.62560534722</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.69067753472</v>
+        <v>46164.52401086806</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>188</v>
@@ -5453,11 +5453,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.79227828704</v>
+        <v>46162.62561162037</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.69067336805</v>
+        <v>46164.52400670139</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>188</v>
@@ -5506,11 +5506,11 @@
         <v>231</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.79232202546</v>
+        <v>46162.625655358795</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46164.69085144676</v>
+        <v>46164.52418478009</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>232</v>
@@ -5569,11 +5569,11 @@
         <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.79232653935</v>
+        <v>46162.62565987269</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46198.782724606484</v>
+        <v>46198.61605793981</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>188</v>
@@ -5622,11 +5622,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.79233265047</v>
+        <v>46162.625665983796</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46198.78272363426</v>
+        <v>46198.61605696759</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>188</v>
@@ -5675,11 +5675,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.79233820602</v>
+        <v>46162.625671539354</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46198.78273228009</v>
+        <v>46198.61606561343</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>188</v>
@@ -5728,11 +5728,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.79234384259</v>
+        <v>46162.62567717592</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46198.782732824075</v>
+        <v>46198.61606615741</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>188</v>
@@ -5781,11 +5781,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.79241414352</v>
+        <v>46162.62574747685</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46164.690976377315</v>
+        <v>46164.52430971064</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5844,11 +5844,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.79242041666</v>
+        <v>46162.62575375</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46198.78273341435</v>
+        <v>46198.61606674769</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>188</v>
@@ -5897,11 +5897,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.79243321759</v>
+        <v>46162.625766550926</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.78272657408</v>
+        <v>46198.61605990741</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>188</v>
@@ -5950,11 +5950,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.79243956019</v>
+        <v>46162.625772893516</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46198.78272707176</v>
+        <v>46198.6160604051</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>188</v>
@@ -6003,11 +6003,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.79244651621</v>
+        <v>46162.625779849535</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.78272166666</v>
+        <v>46198.616055</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>188</v>
@@ -6056,11 +6056,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.79247811342</v>
+        <v>46162.625811446764</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.670772627316</v>
+        <v>46164.504105960645</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>194</v>
@@ -6103,11 +6103,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.792481805554</v>
+        <v>46162.62581513889</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46171.19919608797</v>
+        <v>46171.032529421296</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6166,11 +6166,11 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.79248949074</v>
+        <v>46162.62582282408</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.68596158565</v>
+        <v>46198.51929491898</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6229,11 +6229,11 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.79249689815</v>
+        <v>46162.62583023148</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.68569559028</v>
+        <v>46198.51902892361</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6292,11 +6292,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.79250443287</v>
+        <v>46162.6258377662</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.69110619213</v>
+        <v>46164.52443952546</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6355,11 +6355,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.79250947917</v>
+        <v>46162.6258428125</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.68453591435</v>
+        <v>46164.517869247684</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6402,11 +6402,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.79251295139</v>
+        <v>46162.62584628472</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.69124818287</v>
+        <v>46164.524581516205</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>266</v>
@@ -6465,11 +6465,11 @@
         <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.79252873843</v>
+        <v>46162.625862071756</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.69121831018</v>
+        <v>46164.52455164352</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>188</v>
@@ -6518,11 +6518,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.792533518514</v>
+        <v>46162.62586685186</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.6912157176</v>
+        <v>46164.524549050926</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>188</v>
@@ -6571,11 +6571,11 @@
         <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.79253825231</v>
+        <v>46162.62587158565</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.69121336806</v>
+        <v>46164.52454670139</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>188</v>
@@ -6624,11 +6624,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.792543206015</v>
+        <v>46162.62587653935</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.691209490746</v>
+        <v>46164.524542824074</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>188</v>
@@ -6677,11 +6677,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.792612743055</v>
+        <v>46162.62594607639</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.69137969907</v>
+        <v>46164.524713032406</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>276</v>
@@ -6740,11 +6740,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.79261844908</v>
+        <v>46162.62595178241</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46198.78274127315</v>
+        <v>46198.616074606485</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>188</v>
@@ -6793,11 +6793,11 @@
         <v>280</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.7926247338</v>
+        <v>46162.62595806713</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46198.782722233795</v>
+        <v>46198.61605556713</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>188</v>
@@ -6846,11 +6846,11 @@
         <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.792630682874</v>
+        <v>46162.6259640162</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46198.78272511574</v>
+        <v>46198.61605844907</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>188</v>
@@ -6899,11 +6899,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.79263777778</v>
+        <v>46162.62597111111</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.782724108794</v>
+        <v>46198.61605744213</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>188</v>
@@ -6952,11 +6952,11 @@
         <v>284</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.79268604166</v>
+        <v>46162.626019375</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.6915004051</v>
+        <v>46164.524833738426</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>285</v>
@@ -7015,11 +7015,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.79269070602</v>
+        <v>46162.62602403935</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46198.78272271991</v>
+        <v>46198.616056053244</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>188</v>
@@ -7068,11 +7068,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.79269707176</v>
+        <v>46162.626030405096</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46198.78272560185</v>
+        <v>46198.616058935186</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>188</v>
@@ -7121,11 +7121,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.792703576386</v>
+        <v>46162.62603690972</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46198.78273373842</v>
+        <v>46198.61606707176</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>188</v>
@@ -7174,11 +7174,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.79271046296</v>
+        <v>46162.62604379629</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46198.78272606482</v>
+        <v>46198.61605939815</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>188</v>
@@ -7227,11 +7227,11 @@
         <v>295</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.792744861115</v>
+        <v>46162.626078194444</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.691619942125</v>
+        <v>46164.52495327547</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>296</v>
@@ -7290,11 +7290,11 @@
         <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.79274982639</v>
+        <v>46162.62608315972</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46198.78272754629</v>
+        <v>46198.616060879634</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>188</v>
@@ -7343,11 +7343,11 @@
         <v>300</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.79275559028</v>
+        <v>46162.626088923615</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46198.78272310185</v>
+        <v>46198.61605643519</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>188</v>
@@ -7396,11 +7396,11 @@
         <v>301</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.79276118056</v>
+        <v>46162.62609451389</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46198.782727893515</v>
+        <v>46198.61606122685</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>188</v>
@@ -7449,11 +7449,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.792767754625</v>
+        <v>46162.62610108797</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46198.782728391205</v>
+        <v>46198.61606172453</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>188</v>
@@ -7502,11 +7502,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.79285696759</v>
+        <v>46162.62619030093</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.69173954861</v>
+        <v>46164.525072881945</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>306</v>
@@ -7565,11 +7565,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.792862511575</v>
+        <v>46162.6261958449</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.69170866898</v>
+        <v>46164.525042002315</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>188</v>
@@ -7618,11 +7618,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.792868125005</v>
+        <v>46162.62620145833</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.69170596065</v>
+        <v>46164.52503929398</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>188</v>
@@ -7671,11 +7671,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.792873750004</v>
+        <v>46162.62620708333</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.69170293982</v>
+        <v>46164.525036273146</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>188</v>
@@ -7724,11 +7724,11 @@
         <v>312</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.7928793287</v>
+        <v>46162.62621266204</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.691698194445</v>
+        <v>46164.52503152778</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>188</v>
@@ -7777,11 +7777,11 @@
         <v>313</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.792907696756</v>
+        <v>46162.62624103009</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.69185736111</v>
+        <v>46164.52519069445</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>314</v>
@@ -7838,11 +7838,11 @@
         <v>316</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.79291289352</v>
+        <v>46162.62624622685</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.69182431713</v>
+        <v>46164.52515765047</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>188</v>
@@ -7891,11 +7891,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.79291758101</v>
+        <v>46162.626250914356</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.691821562505</v>
+        <v>46164.52515489583</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>188</v>
@@ -7944,11 +7944,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.79292245371</v>
+        <v>46162.626255787036</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.691819155094</v>
+        <v>46164.52515248842</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>188</v>
@@ -7997,11 +7997,11 @@
         <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.79293256944</v>
+        <v>46162.62626590278</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.69181509259</v>
+        <v>46164.52514842592</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>188</v>
@@ -8050,11 +8050,11 @@
         <v>321</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.7930040625</v>
+        <v>46162.626337395835</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.68546163195</v>
+        <v>46164.518794965275</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>322</v>
@@ -8097,11 +8097,11 @@
         <v>324</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.79300806713</v>
+        <v>46162.626341400464</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.6922515162</v>
+        <v>46164.525584849536</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>325</v>
@@ -8160,11 +8160,11 @@
         <v>329</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.79301847222</v>
+        <v>46162.62635180556</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46164.69223148148</v>
+        <v>46164.525564814816</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>188</v>
@@ -8213,11 +8213,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.79302525463</v>
+        <v>46162.626358587964</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46164.69222814815</v>
+        <v>46164.52556148148</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>188</v>
@@ -8266,11 +8266,11 @@
         <v>332</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.79303010416</v>
+        <v>46162.6263634375</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46164.69222525463</v>
+        <v>46164.525558587964</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>188</v>
@@ -8319,11 +8319,11 @@
         <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.79303482639</v>
+        <v>46162.62636815972</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46164.69222011574</v>
+        <v>46164.52555344907</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>188</v>
@@ -8372,11 +8372,11 @@
         <v>335</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.79306296296</v>
+        <v>46162.6263962963</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.692368958335</v>
+        <v>46164.52570229166</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>336</v>
@@ -8435,11 +8435,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.7930678125</v>
+        <v>46162.62640114583</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.692334189815</v>
+        <v>46164.52566752315</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>188</v>
@@ -8488,11 +8488,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.793072280096</v>
+        <v>46162.626405613424</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.6923315162</v>
+        <v>46164.52566484954</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>188</v>
@@ -8541,11 +8541,11 @@
         <v>340</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.79307696759</v>
+        <v>46162.62641030093</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.69232880787</v>
+        <v>46164.525662141205</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>188</v>
@@ -8594,11 +8594,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.79308175926</v>
+        <v>46162.62641509259</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.69232427083</v>
+        <v>46164.52565760417</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>188</v>
@@ -8647,11 +8647,11 @@
         <v>343</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.79314625</v>
+        <v>46162.626479583334</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.69248696759</v>
+        <v>46164.52582030093</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>344</v>
@@ -8710,11 +8710,11 @@
         <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.793151550926</v>
+        <v>46162.626484884255</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46164.69246075231</v>
+        <v>46164.525794085646</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>188</v>
@@ -8763,11 +8763,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.79315885417</v>
+        <v>46162.6264921875</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46164.692458101854</v>
+        <v>46164.52579143518</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>188</v>
@@ -8816,11 +8816,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.79316501158</v>
+        <v>46162.62649834491</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46164.69245559028</v>
+        <v>46164.52578892361</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>188</v>
@@ -8869,11 +8869,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.79316986111</v>
+        <v>46162.62650319445</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46164.69245128472</v>
+        <v>46164.525784618054</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>188</v>
@@ -8922,11 +8922,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.79319725695</v>
+        <v>46162.62653059028</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.69262644676</v>
+        <v>46164.52595978009</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>353</v>
@@ -8985,11 +8985,11 @@
         <v>355</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.79320210648</v>
+        <v>46162.62653543982</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.692587303245</v>
+        <v>46164.52592063657</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>188</v>
@@ -9038,11 +9038,11 @@
         <v>356</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.793206111106</v>
+        <v>46162.62653944445</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46164.69258451389</v>
+        <v>46164.52591784722</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>188</v>
@@ -9091,11 +9091,11 @@
         <v>357</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.7932099537</v>
+        <v>46162.62654328704</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46164.69258188657</v>
+        <v>46164.52591521991</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>188</v>
@@ -9144,11 +9144,11 @@
         <v>358</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.79321400463</v>
+        <v>46162.62654733796</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46164.69257741898</v>
+        <v>46164.525910752316</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>188</v>
@@ -9197,11 +9197,11 @@
         <v>359</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.79323766204</v>
+        <v>46162.62657099537</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46164.685922812496</v>
+        <v>46164.51925614583</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>360</v>
@@ -9244,11 +9244,11 @@
         <v>362</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.79324063657</v>
+        <v>46162.62657396991</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.69269384259</v>
+        <v>46164.526027175925</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>363</v>
@@ -9307,11 +9307,11 @@
         <v>366</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.79324528935</v>
+        <v>46162.62657862269</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46197.77680827546</v>
+        <v>46197.61014160879</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>367</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1771,13 +1771,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46162.62511512732</v>
+        <v>46162.79178179398</v>
       </c>
       <c r="C4" s="5">
-        <v>46183.414665324075</v>
+        <v>46183.58133199074</v>
       </c>
       <c r="D4" s="5">
-        <v>46183.41468071759</v>
+        <v>46183.58134738426</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1824,13 +1824,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46162.62522459491</v>
+        <v>46162.79189126157</v>
       </c>
       <c r="C5" s="9">
-        <v>46183.414629328705</v>
+        <v>46183.58129599537</v>
       </c>
       <c r="D5" s="9">
-        <v>46183.41464973379</v>
+        <v>46183.581316400465</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1889,13 +1889,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46162.62522767361</v>
+        <v>46162.79189434028</v>
       </c>
       <c r="C6" s="5">
-        <v>46183.41463443287</v>
+        <v>46183.58130109953</v>
       </c>
       <c r="D6" s="5">
-        <v>46183.41464980324</v>
+        <v>46183.58131646991</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1954,13 +1954,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46162.62523457176</v>
+        <v>46162.79190123842</v>
       </c>
       <c r="C7" s="9">
-        <v>46183.41464715278</v>
+        <v>46183.58131381945</v>
       </c>
       <c r="D7" s="9">
-        <v>46183.41466510417</v>
+        <v>46183.58133177084</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2019,13 +2019,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46162.62523784723</v>
+        <v>46162.791904513884</v>
       </c>
       <c r="C8" s="5">
-        <v>46183.414652974534</v>
+        <v>46183.581319641205</v>
       </c>
       <c r="D8" s="5">
-        <v>46183.41466673611</v>
+        <v>46183.58133340278</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2084,11 +2084,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="9">
-        <v>46162.62511998843</v>
+        <v>46162.79178665509</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46197.61015155092</v>
+        <v>46197.77681821759</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -2133,13 +2133,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46162.62524114583</v>
+        <v>46162.7919078125</v>
       </c>
       <c r="C10" s="5">
-        <v>46197.49236574074</v>
+        <v>46197.659032407406</v>
       </c>
       <c r="D10" s="5">
-        <v>46197.61014159722</v>
+        <v>46197.776808263894</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2198,13 +2198,13 @@
         <v>53</v>
       </c>
       <c r="B11" s="9">
-        <v>46162.62524625</v>
+        <v>46162.79191291667</v>
       </c>
       <c r="C11" s="9">
-        <v>46197.494006458335</v>
+        <v>46197.660673125</v>
       </c>
       <c r="D11" s="9">
-        <v>46197.610141655096</v>
+        <v>46197.77680832176</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>54</v>
@@ -2263,13 +2263,13 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46162.62525138889</v>
+        <v>46162.791918055555</v>
       </c>
       <c r="C12" s="5">
-        <v>46197.49602965278</v>
+        <v>46197.66269631944</v>
       </c>
       <c r="D12" s="5">
-        <v>46197.61014167824</v>
+        <v>46197.776808344905</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2328,13 +2328,13 @@
         <v>61</v>
       </c>
       <c r="B13" s="9">
-        <v>46162.62512452547</v>
+        <v>46162.791791192125</v>
       </c>
       <c r="C13" s="9">
-        <v>46204.73102234954</v>
+        <v>46204.8976890162</v>
       </c>
       <c r="D13" s="9">
-        <v>46204.73103322917</v>
+        <v>46204.89769989584</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>62</v>
@@ -2381,13 +2381,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46162.62526353009</v>
+        <v>46162.79193019676</v>
       </c>
       <c r="C14" s="5">
-        <v>46198.51473793981</v>
+        <v>46198.68140460648</v>
       </c>
       <c r="D14" s="5">
-        <v>46198.514753703705</v>
+        <v>46198.68142037037</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2446,13 +2446,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="9">
-        <v>46162.62526864583</v>
+        <v>46162.7919353125</v>
       </c>
       <c r="C15" s="9">
-        <v>46198.51475621528</v>
+        <v>46198.68142288194</v>
       </c>
       <c r="D15" s="9">
-        <v>46198.51477230324</v>
+        <v>46198.68143896991</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>68</v>
@@ -2511,13 +2511,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="5">
-        <v>46162.625273564816</v>
+        <v>46162.79194023148</v>
       </c>
       <c r="C16" s="5">
-        <v>46197.42081989584</v>
+        <v>46197.5874865625</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.49402583334</v>
+        <v>46197.6606925</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>71</v>
@@ -2576,13 +2576,13 @@
         <v>74</v>
       </c>
       <c r="B17" s="9">
-        <v>46162.62527862268</v>
+        <v>46162.791945289355</v>
       </c>
       <c r="C17" s="9">
-        <v>46204.7287044213</v>
+        <v>46204.89537108796</v>
       </c>
       <c r="D17" s="9">
-        <v>46204.7299340625</v>
+        <v>46204.89660072917</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>75</v>
@@ -2641,13 +2641,13 @@
         <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>46162.62528289352</v>
+        <v>46162.79194956018</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.72873567129</v>
+        <v>46204.89540233796</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.73041949074</v>
+        <v>46204.897086157405</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>81</v>
@@ -2706,13 +2706,13 @@
         <v>83</v>
       </c>
       <c r="B19" s="9">
-        <v>46162.625286180555</v>
+        <v>46162.79195284723</v>
       </c>
       <c r="C19" s="9">
-        <v>46204.73189422453</v>
+        <v>46204.898560891204</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.732402037036</v>
+        <v>46204.8990687037</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>84</v>
@@ -2771,13 +2771,13 @@
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>46162.625289351854</v>
+        <v>46162.79195601852</v>
       </c>
       <c r="C20" s="5">
-        <v>46204.73100837963</v>
+        <v>46204.8976750463</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.74819653935</v>
+        <v>46204.91486320602</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>87</v>
@@ -2836,11 +2836,11 @@
         <v>89</v>
       </c>
       <c r="B21" s="9">
-        <v>46162.62512967593</v>
+        <v>46162.79179634259</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.51929398148</v>
+        <v>46198.685960648145</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2883,13 +2883,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46162.62529335648</v>
+        <v>46162.79196002315</v>
       </c>
       <c r="C22" s="5">
-        <v>46198.51928571759</v>
+        <v>46198.68595238426</v>
       </c>
       <c r="D22" s="5">
-        <v>46198.519296909726</v>
+        <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2948,13 +2948,13 @@
         <v>97</v>
       </c>
       <c r="B23" s="9">
-        <v>46162.625297708335</v>
+        <v>46162.791964375</v>
       </c>
       <c r="C23" s="9">
-        <v>46198.51923957176</v>
+        <v>46198.685906238425</v>
       </c>
       <c r="D23" s="9">
-        <v>46198.519240821755</v>
+        <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>98</v>
@@ -3009,13 +3009,13 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46162.62530216435</v>
+        <v>46162.79196883102</v>
       </c>
       <c r="C24" s="5">
-        <v>46198.51927237269</v>
+        <v>46198.68593903935</v>
       </c>
       <c r="D24" s="5">
-        <v>46198.51927400463</v>
+        <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3070,11 +3070,11 @@
         <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46162.62530663195</v>
+        <v>46162.79197329861</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46169.00878244213</v>
+        <v>46169.17544910879</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3133,11 +3133,11 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46162.62531083333</v>
+        <v>46162.791977500005</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.42082753472</v>
+        <v>46197.58749420139</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3192,11 +3192,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46162.62531532407</v>
+        <v>46162.79198199074</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46168.00598047454</v>
+        <v>46168.172647141204</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3251,13 +3251,13 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46162.625319872684</v>
+        <v>46162.79198653935</v>
       </c>
       <c r="C28" s="5">
-        <v>46198.51902561342</v>
+        <v>46198.685692280094</v>
       </c>
       <c r="D28" s="5">
-        <v>46198.5190687963</v>
+        <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3316,13 +3316,13 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46162.62532415509</v>
+        <v>46162.79199082176</v>
       </c>
       <c r="C29" s="9">
-        <v>46198.514856828704</v>
+        <v>46198.68152349537</v>
       </c>
       <c r="D29" s="9">
-        <v>46198.51485818287</v>
+        <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3377,13 +3377,13 @@
         <v>119</v>
       </c>
       <c r="B30" s="5">
-        <v>46162.62532864584</v>
+        <v>46162.791995312495</v>
       </c>
       <c r="C30" s="5">
-        <v>46198.519009930555</v>
+        <v>46198.68567659722</v>
       </c>
       <c r="D30" s="5">
-        <v>46198.51901125</v>
+        <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>120</v>
@@ -3438,13 +3438,13 @@
         <v>122</v>
       </c>
       <c r="B31" s="9">
-        <v>46162.625333240736</v>
+        <v>46162.79199990741</v>
       </c>
       <c r="C31" s="9">
-        <v>46198.514894884254</v>
+        <v>46198.681561550926</v>
       </c>
       <c r="D31" s="9">
-        <v>46198.514896493056</v>
+        <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>123</v>
@@ -3499,11 +3499,11 @@
         <v>125</v>
       </c>
       <c r="B32" s="5">
-        <v>46162.62533775463</v>
+        <v>46162.792004421295</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46164.52311444444</v>
+        <v>46205.611174351856</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3562,11 +3562,13 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46162.62534211806</v>
-      </c>
-      <c r="C33" s="10"/>
+        <v>46162.79200878472</v>
+      </c>
+      <c r="C33" s="9">
+        <v>46205.61116773148</v>
+      </c>
       <c r="D33" s="9">
-        <v>46204.72871571759</v>
+        <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>131</v>
@@ -3621,11 +3623,11 @@
         <v>133</v>
       </c>
       <c r="B34" s="5">
-        <v>46162.62534672454</v>
+        <v>46162.792013391205</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46164.523068483795</v>
+        <v>46205.6111755787</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3680,11 +3682,11 @@
         <v>136</v>
       </c>
       <c r="B35" s="9">
-        <v>46162.625351423616</v>
+        <v>46162.79201809027</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46164.523207465274</v>
+        <v>46205.61150788194</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3743,11 +3745,13 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46162.6254083449</v>
-      </c>
-      <c r="C36" s="6"/>
+        <v>46162.79207501157</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46205.61150291667</v>
+      </c>
       <c r="D36" s="5">
-        <v>46204.72874193287</v>
+        <v>46205.611504409724</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>82</v>
@@ -3796,11 +3800,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46162.625413587964</v>
+        <v>46162.79208025463</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46164.52317409722</v>
+        <v>46205.61173695602</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3849,11 +3853,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46162.62541833334</v>
+        <v>46162.792085</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46164.52337886574</v>
+        <v>46164.69004553241</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3912,11 +3916,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46162.6254225</v>
+        <v>46162.792089166665</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46204.731014467594</v>
+        <v>46204.89768113426</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>88</v>
@@ -3965,11 +3969,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46162.62542693287</v>
+        <v>46162.792093599535</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46164.523289247685</v>
+        <v>46164.68995591435</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4018,11 +4022,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46162.6254371875</v>
+        <v>46162.79210385417</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.5233225463</v>
+        <v>46164.68998921296</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -4071,11 +4075,13 @@
         <v>158</v>
       </c>
       <c r="B42" s="5">
-        <v>46162.62544063658</v>
-      </c>
-      <c r="C42" s="6"/>
+        <v>46162.79210730324</v>
+      </c>
+      <c r="C42" s="5">
+        <v>46205.61214109954</v>
+      </c>
       <c r="D42" s="5">
-        <v>46164.52343339121</v>
+        <v>46205.612154409726</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>159</v>
@@ -4123,10 +4129,10 @@
         <v>52</v>
       </c>
       <c r="T42" s="6">
-        <v>0</v>
-      </c>
-      <c r="U42" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U42" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4134,11 +4140,13 @@
         <v>161</v>
       </c>
       <c r="B43" s="9">
-        <v>46162.62544451389</v>
-      </c>
-      <c r="C43" s="10"/>
+        <v>46162.792111180555</v>
+      </c>
+      <c r="C43" s="9">
+        <v>46205.611928252314</v>
+      </c>
       <c r="D43" s="9">
-        <v>46204.73190179398</v>
+        <v>46205.612088877315</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>85</v>
@@ -4187,11 +4195,13 @@
         <v>163</v>
       </c>
       <c r="B44" s="5">
-        <v>46162.62544935185</v>
-      </c>
-      <c r="C44" s="6"/>
+        <v>46162.79211601852</v>
+      </c>
+      <c r="C44" s="5">
+        <v>46205.612127650464</v>
+      </c>
       <c r="D44" s="5">
-        <v>46164.523488680556</v>
+        <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -4240,11 +4250,11 @@
         <v>166</v>
       </c>
       <c r="B45" s="9">
-        <v>46162.625134131944</v>
+        <v>46162.791800798615</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46198.61601456019</v>
+        <v>46198.78268122685</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4289,13 +4299,13 @@
         <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46162.625454548615</v>
+        <v>46162.79212121527</v>
       </c>
       <c r="C46" s="5">
-        <v>46197.51404692129</v>
+        <v>46197.680713587964</v>
       </c>
       <c r="D46" s="5">
-        <v>46197.51406354167</v>
+        <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>170</v>
@@ -4354,13 +4364,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46162.625460034724</v>
+        <v>46162.79212670139</v>
       </c>
       <c r="C47" s="9">
-        <v>46198.615996736116</v>
+        <v>46198.78266340277</v>
       </c>
       <c r="D47" s="9">
-        <v>46198.616014907406</v>
+        <v>46198.78268157407</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4419,13 +4429,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46162.62546642361</v>
+        <v>46162.792133090275</v>
       </c>
       <c r="C48" s="5">
-        <v>46198.61604957176</v>
+        <v>46198.78271623843</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.61606556713</v>
+        <v>46198.7827322338</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>78</v>
@@ -4484,11 +4494,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46162.625480428236</v>
+        <v>46162.79214709491</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.52360884259</v>
+        <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4547,11 +4557,11 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46162.625484108794</v>
+        <v>46162.792150775465</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46164.523701805556</v>
+        <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4600,11 +4610,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46162.62548818287</v>
+        <v>46162.792154849536</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46164.52369920139</v>
+        <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4653,11 +4663,11 @@
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46162.62549208333</v>
+        <v>46162.79215875</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46164.52369637731</v>
+        <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -4706,11 +4716,11 @@
         <v>192</v>
       </c>
       <c r="B53" s="9">
-        <v>46162.62549497685</v>
+        <v>46162.79216164352</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46164.523692268514</v>
+        <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>188</v>
@@ -4759,11 +4769,11 @@
         <v>193</v>
       </c>
       <c r="B54" s="5">
-        <v>46162.62554516204</v>
+        <v>46162.7922118287</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46164.500513541665</v>
+        <v>46164.66718020833</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>194</v>
@@ -4806,11 +4816,11 @@
         <v>196</v>
       </c>
       <c r="B55" s="9">
-        <v>46162.625553425925</v>
+        <v>46162.7922200926</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.52381886574</v>
+        <v>46164.69048553241</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4869,11 +4879,11 @@
         <v>201</v>
       </c>
       <c r="B56" s="5">
-        <v>46162.62555895833</v>
+        <v>46162.792225625</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46164.52388792824</v>
+        <v>46164.69055459491</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -4932,11 +4942,11 @@
         <v>205</v>
       </c>
       <c r="B57" s="9">
-        <v>46162.625565636576</v>
+        <v>46162.79223230324</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.52381575231</v>
+        <v>46164.690482418984</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -4995,11 +5005,11 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46162.62557070602</v>
+        <v>46162.79223737269</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46164.52388519676</v>
+        <v>46164.69055186343</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>209</v>
@@ -5058,11 +5068,11 @@
         <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46162.62557578704</v>
+        <v>46162.7922424537</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46164.52381239583</v>
+        <v>46205.61214489583</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>212</v>
@@ -5112,8 +5122,8 @@
       <c r="T59" s="10">
         <v>0</v>
       </c>
-      <c r="U59" s="11" t="s">
-        <v>100</v>
+      <c r="U59" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5121,11 +5131,11 @@
         <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46162.62558024305</v>
+        <v>46162.792246909725</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46164.52388266203</v>
+        <v>46164.690549328705</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>213</v>
@@ -5184,11 +5194,11 @@
         <v>215</v>
       </c>
       <c r="B61" s="9">
-        <v>46162.62558502315</v>
+        <v>46162.79225168981</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.50232085648</v>
+        <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>216</v>
@@ -5231,11 +5241,11 @@
         <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46162.6255878125</v>
+        <v>46162.792254479165</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46164.52405841435</v>
+        <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>219</v>
@@ -5294,11 +5304,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46162.62559255787</v>
+        <v>46162.79225922454</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.5240165162</v>
+        <v>46164.69068318287</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>188</v>
@@ -5347,11 +5357,11 @@
         <v>225</v>
       </c>
       <c r="B64" s="5">
-        <v>46162.62559891204</v>
+        <v>46162.792265578704</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.52401381945</v>
+        <v>46164.69068048611</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>188</v>
@@ -5400,11 +5410,11 @@
         <v>227</v>
       </c>
       <c r="B65" s="9">
-        <v>46162.62560534722</v>
+        <v>46162.79227201389</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.52401086806</v>
+        <v>46164.69067753472</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>188</v>
@@ -5453,11 +5463,11 @@
         <v>230</v>
       </c>
       <c r="B66" s="5">
-        <v>46162.62561162037</v>
+        <v>46162.79227828704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.52400670139</v>
+        <v>46164.69067336805</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>188</v>
@@ -5506,11 +5516,11 @@
         <v>231</v>
       </c>
       <c r="B67" s="9">
-        <v>46162.625655358795</v>
+        <v>46162.79232202546</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46164.52418478009</v>
+        <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>232</v>
@@ -5569,11 +5579,11 @@
         <v>233</v>
       </c>
       <c r="B68" s="5">
-        <v>46162.62565987269</v>
+        <v>46162.79232653935</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46198.61605793981</v>
+        <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>188</v>
@@ -5622,11 +5632,11 @@
         <v>236</v>
       </c>
       <c r="B69" s="9">
-        <v>46162.625665983796</v>
+        <v>46162.79233265047</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46198.61605696759</v>
+        <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>188</v>
@@ -5675,11 +5685,11 @@
         <v>237</v>
       </c>
       <c r="B70" s="5">
-        <v>46162.625671539354</v>
+        <v>46162.79233820602</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46198.61606561343</v>
+        <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>188</v>
@@ -5728,11 +5738,11 @@
         <v>239</v>
       </c>
       <c r="B71" s="9">
-        <v>46162.62567717592</v>
+        <v>46162.79234384259</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46198.61606615741</v>
+        <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>188</v>
@@ -5781,11 +5791,11 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46162.62574747685</v>
+        <v>46162.79241414352</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46164.52430971064</v>
+        <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5844,11 +5854,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46162.62575375</v>
+        <v>46162.79242041666</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46198.61606674769</v>
+        <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>188</v>
@@ -5897,11 +5907,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46162.625766550926</v>
+        <v>46162.79243321759</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46198.61605990741</v>
+        <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>188</v>
@@ -5950,11 +5960,11 @@
         <v>246</v>
       </c>
       <c r="B75" s="9">
-        <v>46162.625772893516</v>
+        <v>46162.79243956019</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46198.6160604051</v>
+        <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>188</v>
@@ -6003,11 +6013,11 @@
         <v>248</v>
       </c>
       <c r="B76" s="5">
-        <v>46162.625779849535</v>
+        <v>46162.79244651621</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46198.616055</v>
+        <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>188</v>
@@ -6056,11 +6066,11 @@
         <v>249</v>
       </c>
       <c r="B77" s="9">
-        <v>46162.625811446764</v>
+        <v>46162.79247811342</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.504105960645</v>
+        <v>46164.670772627316</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>194</v>
@@ -6103,11 +6113,11 @@
         <v>251</v>
       </c>
       <c r="B78" s="5">
-        <v>46162.62581513889</v>
+        <v>46162.792481805554</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46171.032529421296</v>
+        <v>46171.19919608797</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6166,11 +6176,11 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46162.62582282408</v>
+        <v>46162.79248949074</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.51929491898</v>
+        <v>46198.68596158565</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6229,11 +6239,11 @@
         <v>257</v>
       </c>
       <c r="B80" s="5">
-        <v>46162.62583023148</v>
+        <v>46162.79249689815</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.51902892361</v>
+        <v>46198.68569559028</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6292,11 +6302,11 @@
         <v>259</v>
       </c>
       <c r="B81" s="9">
-        <v>46162.6258377662</v>
+        <v>46162.79250443287</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.52443952546</v>
+        <v>46164.69110619213</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6355,11 +6365,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46162.6258428125</v>
+        <v>46162.79250947917</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.517869247684</v>
+        <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>263</v>
@@ -6402,11 +6412,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46162.62584628472</v>
+        <v>46162.79251295139</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.524581516205</v>
+        <v>46164.69124818287</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>266</v>
@@ -6465,11 +6475,11 @@
         <v>268</v>
       </c>
       <c r="B84" s="5">
-        <v>46162.625862071756</v>
+        <v>46162.79252873843</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.52455164352</v>
+        <v>46164.69121831018</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>188</v>
@@ -6518,11 +6528,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46162.62586685186</v>
+        <v>46162.792533518514</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.524549050926</v>
+        <v>46164.6912157176</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>188</v>
@@ -6571,11 +6581,11 @@
         <v>271</v>
       </c>
       <c r="B86" s="5">
-        <v>46162.62587158565</v>
+        <v>46162.79253825231</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.52454670139</v>
+        <v>46164.69121336806</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>188</v>
@@ -6624,11 +6634,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46162.62587653935</v>
+        <v>46162.792543206015</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.524542824074</v>
+        <v>46164.691209490746</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>188</v>
@@ -6677,11 +6687,11 @@
         <v>275</v>
       </c>
       <c r="B88" s="5">
-        <v>46162.62594607639</v>
+        <v>46162.792612743055</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.524713032406</v>
+        <v>46164.69137969907</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>276</v>
@@ -6740,11 +6750,11 @@
         <v>277</v>
       </c>
       <c r="B89" s="9">
-        <v>46162.62595178241</v>
+        <v>46162.79261844908</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46198.616074606485</v>
+        <v>46198.78274127315</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>188</v>
@@ -6793,11 +6803,11 @@
         <v>280</v>
       </c>
       <c r="B90" s="5">
-        <v>46162.62595806713</v>
+        <v>46162.7926247338</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46198.61605556713</v>
+        <v>46198.782722233795</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>188</v>
@@ -6846,11 +6856,11 @@
         <v>281</v>
       </c>
       <c r="B91" s="9">
-        <v>46162.6259640162</v>
+        <v>46162.792630682874</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46198.61605844907</v>
+        <v>46198.78272511574</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>188</v>
@@ -6899,11 +6909,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46162.62597111111</v>
+        <v>46162.79263777778</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.61605744213</v>
+        <v>46198.782724108794</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>188</v>
@@ -6952,11 +6962,11 @@
         <v>284</v>
       </c>
       <c r="B93" s="9">
-        <v>46162.626019375</v>
+        <v>46162.79268604166</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.524833738426</v>
+        <v>46164.6915004051</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>285</v>
@@ -7015,11 +7025,11 @@
         <v>286</v>
       </c>
       <c r="B94" s="5">
-        <v>46162.62602403935</v>
+        <v>46162.79269070602</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46198.616056053244</v>
+        <v>46198.78272271991</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>188</v>
@@ -7068,11 +7078,11 @@
         <v>288</v>
       </c>
       <c r="B95" s="9">
-        <v>46162.626030405096</v>
+        <v>46162.79269707176</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46198.616058935186</v>
+        <v>46198.78272560185</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>188</v>
@@ -7121,11 +7131,11 @@
         <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46162.62603690972</v>
+        <v>46162.792703576386</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46198.61606707176</v>
+        <v>46198.78273373842</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>188</v>
@@ -7174,11 +7184,11 @@
         <v>292</v>
       </c>
       <c r="B97" s="9">
-        <v>46162.62604379629</v>
+        <v>46162.79271046296</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46198.61605939815</v>
+        <v>46198.78272606482</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>188</v>
@@ -7227,11 +7237,11 @@
         <v>295</v>
       </c>
       <c r="B98" s="5">
-        <v>46162.626078194444</v>
+        <v>46162.792744861115</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.52495327547</v>
+        <v>46164.691619942125</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>296</v>
@@ -7290,11 +7300,11 @@
         <v>297</v>
       </c>
       <c r="B99" s="9">
-        <v>46162.62608315972</v>
+        <v>46162.79274982639</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46198.616060879634</v>
+        <v>46198.78272754629</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>188</v>
@@ -7343,11 +7353,11 @@
         <v>300</v>
       </c>
       <c r="B100" s="5">
-        <v>46162.626088923615</v>
+        <v>46162.79275559028</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46198.61605643519</v>
+        <v>46198.78272310185</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>188</v>
@@ -7396,11 +7406,11 @@
         <v>301</v>
       </c>
       <c r="B101" s="9">
-        <v>46162.62609451389</v>
+        <v>46162.79276118056</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46198.61606122685</v>
+        <v>46198.782727893515</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>188</v>
@@ -7449,11 +7459,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46162.62610108797</v>
+        <v>46162.792767754625</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46198.61606172453</v>
+        <v>46198.782728391205</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>188</v>
@@ -7502,11 +7512,11 @@
         <v>305</v>
       </c>
       <c r="B103" s="9">
-        <v>46162.62619030093</v>
+        <v>46162.79285696759</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.525072881945</v>
+        <v>46164.69173954861</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>306</v>
@@ -7565,11 +7575,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46162.6261958449</v>
+        <v>46162.792862511575</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.525042002315</v>
+        <v>46164.69170866898</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>188</v>
@@ -7618,11 +7628,11 @@
         <v>309</v>
       </c>
       <c r="B105" s="9">
-        <v>46162.62620145833</v>
+        <v>46162.792868125005</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.52503929398</v>
+        <v>46164.69170596065</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>188</v>
@@ -7671,11 +7681,11 @@
         <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46162.62620708333</v>
+        <v>46162.792873750004</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.525036273146</v>
+        <v>46164.69170293982</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>188</v>
@@ -7724,11 +7734,11 @@
         <v>312</v>
       </c>
       <c r="B107" s="9">
-        <v>46162.62621266204</v>
+        <v>46162.7928793287</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.52503152778</v>
+        <v>46164.691698194445</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>188</v>
@@ -7777,11 +7787,11 @@
         <v>313</v>
       </c>
       <c r="B108" s="5">
-        <v>46162.62624103009</v>
+        <v>46162.792907696756</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.52519069445</v>
+        <v>46164.69185736111</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>314</v>
@@ -7838,11 +7848,11 @@
         <v>316</v>
       </c>
       <c r="B109" s="9">
-        <v>46162.62624622685</v>
+        <v>46162.79291289352</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.52515765047</v>
+        <v>46164.69182431713</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>188</v>
@@ -7891,11 +7901,11 @@
         <v>318</v>
       </c>
       <c r="B110" s="5">
-        <v>46162.626250914356</v>
+        <v>46162.79291758101</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.52515489583</v>
+        <v>46164.691821562505</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>188</v>
@@ -7944,11 +7954,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="9">
-        <v>46162.626255787036</v>
+        <v>46162.79292245371</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.52515248842</v>
+        <v>46164.691819155094</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>188</v>
@@ -7997,11 +8007,11 @@
         <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46162.62626590278</v>
+        <v>46162.79293256944</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.52514842592</v>
+        <v>46164.69181509259</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>188</v>
@@ -8050,11 +8060,11 @@
         <v>321</v>
       </c>
       <c r="B113" s="9">
-        <v>46162.626337395835</v>
+        <v>46162.7930040625</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.518794965275</v>
+        <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>322</v>
@@ -8097,11 +8107,11 @@
         <v>324</v>
       </c>
       <c r="B114" s="5">
-        <v>46162.626341400464</v>
+        <v>46162.79300806713</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.525584849536</v>
+        <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>325</v>
@@ -8160,11 +8170,11 @@
         <v>329</v>
       </c>
       <c r="B115" s="9">
-        <v>46162.62635180556</v>
+        <v>46162.79301847222</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46164.525564814816</v>
+        <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>188</v>
@@ -8213,11 +8223,11 @@
         <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46162.626358587964</v>
+        <v>46162.79302525463</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46164.52556148148</v>
+        <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>188</v>
@@ -8266,11 +8276,11 @@
         <v>332</v>
       </c>
       <c r="B117" s="9">
-        <v>46162.6263634375</v>
+        <v>46162.79303010416</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46164.525558587964</v>
+        <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>188</v>
@@ -8319,11 +8329,11 @@
         <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46162.62636815972</v>
+        <v>46162.79303482639</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46164.52555344907</v>
+        <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>188</v>
@@ -8372,11 +8382,11 @@
         <v>335</v>
       </c>
       <c r="B119" s="9">
-        <v>46162.6263962963</v>
+        <v>46162.79306296296</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.52570229166</v>
+        <v>46164.692368958335</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>336</v>
@@ -8435,11 +8445,11 @@
         <v>337</v>
       </c>
       <c r="B120" s="5">
-        <v>46162.62640114583</v>
+        <v>46162.7930678125</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.52566752315</v>
+        <v>46164.692334189815</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>188</v>
@@ -8488,11 +8498,11 @@
         <v>339</v>
       </c>
       <c r="B121" s="9">
-        <v>46162.626405613424</v>
+        <v>46162.793072280096</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.52566484954</v>
+        <v>46164.6923315162</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>188</v>
@@ -8541,11 +8551,11 @@
         <v>340</v>
       </c>
       <c r="B122" s="5">
-        <v>46162.62641030093</v>
+        <v>46162.79307696759</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.525662141205</v>
+        <v>46164.69232880787</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>188</v>
@@ -8594,11 +8604,11 @@
         <v>342</v>
       </c>
       <c r="B123" s="9">
-        <v>46162.62641509259</v>
+        <v>46162.79308175926</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.52565760417</v>
+        <v>46164.69232427083</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>188</v>
@@ -8647,11 +8657,11 @@
         <v>343</v>
       </c>
       <c r="B124" s="5">
-        <v>46162.626479583334</v>
+        <v>46162.79314625</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.52582030093</v>
+        <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>344</v>
@@ -8710,11 +8720,11 @@
         <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46162.626484884255</v>
+        <v>46162.793151550926</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46164.525794085646</v>
+        <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>188</v>
@@ -8763,11 +8773,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46162.6264921875</v>
+        <v>46162.79315885417</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46164.52579143518</v>
+        <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>188</v>
@@ -8816,11 +8826,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="9">
-        <v>46162.62649834491</v>
+        <v>46162.79316501158</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46164.52578892361</v>
+        <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>188</v>
@@ -8869,11 +8879,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46162.62650319445</v>
+        <v>46162.79316986111</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46164.525784618054</v>
+        <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>188</v>
@@ -8922,11 +8932,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="9">
-        <v>46162.62653059028</v>
+        <v>46162.79319725695</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.52595978009</v>
+        <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>353</v>
@@ -8985,11 +8995,11 @@
         <v>355</v>
       </c>
       <c r="B130" s="5">
-        <v>46162.62653543982</v>
+        <v>46162.79320210648</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.52592063657</v>
+        <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>188</v>
@@ -9038,11 +9048,11 @@
         <v>356</v>
       </c>
       <c r="B131" s="9">
-        <v>46162.62653944445</v>
+        <v>46162.793206111106</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46164.52591784722</v>
+        <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>188</v>
@@ -9091,11 +9101,11 @@
         <v>357</v>
       </c>
       <c r="B132" s="5">
-        <v>46162.62654328704</v>
+        <v>46162.7932099537</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46164.52591521991</v>
+        <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>188</v>
@@ -9144,11 +9154,11 @@
         <v>358</v>
       </c>
       <c r="B133" s="9">
-        <v>46162.62654733796</v>
+        <v>46162.79321400463</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46164.525910752316</v>
+        <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>188</v>
@@ -9197,11 +9207,11 @@
         <v>359</v>
       </c>
       <c r="B134" s="5">
-        <v>46162.62657099537</v>
+        <v>46162.79323766204</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46164.51925614583</v>
+        <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>360</v>
@@ -9244,11 +9254,11 @@
         <v>362</v>
       </c>
       <c r="B135" s="9">
-        <v>46162.62657396991</v>
+        <v>46162.79324063657</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.526027175925</v>
+        <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>363</v>
@@ -9307,11 +9317,11 @@
         <v>366</v>
       </c>
       <c r="B136" s="5">
-        <v>46162.62657862269</v>
+        <v>46162.79324528935</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46197.61014160879</v>
+        <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>367</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -3855,9 +3855,11 @@
       <c r="B38" s="5">
         <v>46162.792085</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46209.624663807874</v>
+      </c>
       <c r="D38" s="5">
-        <v>46164.69004553241</v>
+        <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3905,10 +3907,10 @@
         <v>52</v>
       </c>
       <c r="T38" s="6">
-        <v>0</v>
-      </c>
-      <c r="U38" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U38" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3918,9 +3920,11 @@
       <c r="B39" s="9">
         <v>46162.792089166665</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46209.62451545139</v>
+      </c>
       <c r="D39" s="9">
-        <v>46204.89768113426</v>
+        <v>46209.624517187505</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>88</v>
@@ -3971,9 +3975,11 @@
       <c r="B40" s="5">
         <v>46162.792093599535</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46209.62457579861</v>
+      </c>
       <c r="D40" s="5">
-        <v>46164.68995591435</v>
+        <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>152</v>
@@ -4026,7 +4032,7 @@
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46164.68998921296</v>
+        <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -6306,7 +6312,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46164.69110619213</v>
+        <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6356,8 +6362,8 @@
       <c r="T81" s="10">
         <v>0</v>
       </c>
-      <c r="U81" s="11" t="s">
-        <v>100</v>
+      <c r="U81" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.685960648145</v>
+        <v>46209.81743361111</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -3501,9 +3501,11 @@
       <c r="B32" s="5">
         <v>46162.792004421295</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46209.817423472225</v>
+      </c>
       <c r="D32" s="5">
-        <v>46205.611174351856</v>
+        <v>46209.81743660879</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3551,10 +3553,10 @@
         <v>52</v>
       </c>
       <c r="T32" s="6">
-        <v>0</v>
-      </c>
-      <c r="U32" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U32" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3625,9 +3627,11 @@
       <c r="B34" s="5">
         <v>46162.792013391205</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46209.81740934028</v>
+      </c>
       <c r="D34" s="5">
-        <v>46205.6111755787</v>
+        <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>134</v>
@@ -3684,9 +3688,11 @@
       <c r="B35" s="9">
         <v>46162.79201809027</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46209.81753880787</v>
+      </c>
       <c r="D35" s="9">
-        <v>46205.61150788194</v>
+        <v>46209.81754938657</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>137</v>
@@ -3734,10 +3740,10 @@
         <v>52</v>
       </c>
       <c r="T35" s="10">
-        <v>0</v>
-      </c>
-      <c r="U35" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3802,9 +3808,11 @@
       <c r="B37" s="9">
         <v>46162.79208025463</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9">
+        <v>46209.81752493056</v>
+      </c>
       <c r="D37" s="9">
-        <v>46205.61173695602</v>
+        <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -4826,7 +4834,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46164.69048553241</v>
+        <v>46209.81742680556</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4876,8 +4884,8 @@
       <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="U55" s="11" t="s">
-        <v>100</v>
+      <c r="U55" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4952,7 +4960,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46164.690482418984</v>
+        <v>46209.81754253472</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -5002,8 +5010,8 @@
       <c r="T57" s="10">
         <v>0</v>
       </c>
-      <c r="U57" s="11" t="s">
-        <v>100</v>
+      <c r="U57" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -4266,9 +4266,11 @@
       <c r="B45" s="9">
         <v>46162.791800798615</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46210.529382106484</v>
+      </c>
       <c r="D45" s="9">
-        <v>46198.78268122685</v>
+        <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>167</v>
@@ -4303,9 +4305,11 @@
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
       <c r="S45" s="10"/>
-      <c r="T45" s="10"/>
-      <c r="U45" s="12" t="s">
-        <v>45</v>
+      <c r="T45" s="10">
+        <v>1</v>
+      </c>
+      <c r="U45" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="368">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46209.81743361111</v>
+        <v>46212.655108425926</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2876,7 +2876,9 @@
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
+      <c r="U21" s="12" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
@@ -3072,9 +3074,11 @@
       <c r="B25" s="9">
         <v>46162.79197329861</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46212.65508898148</v>
+      </c>
       <c r="D25" s="9">
-        <v>46169.17544910879</v>
+        <v>46212.65520907407</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>105</v>
@@ -3122,10 +3126,10 @@
         <v>33</v>
       </c>
       <c r="T25" s="10">
-        <v>0</v>
-      </c>
-      <c r="U25" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3135,9 +3139,11 @@
       <c r="B26" s="5">
         <v>46162.791977500005</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46212.65503487269</v>
+      </c>
       <c r="D26" s="5">
-        <v>46197.58749420139</v>
+        <v>46212.65503678241</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3194,9 +3200,11 @@
       <c r="B27" s="9">
         <v>46162.79198199074</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46212.655068796295</v>
+      </c>
       <c r="D27" s="9">
-        <v>46168.172647141204</v>
+        <v>46212.65507065972</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -6088,7 +6096,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46164.670772627316</v>
+        <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>194</v>
@@ -6124,7 +6132,9 @@
       <c r="R77" s="10"/>
       <c r="S77" s="10"/>
       <c r="T77" s="10"/>
-      <c r="U77" s="10"/>
+      <c r="U77" s="12" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
@@ -6133,9 +6143,11 @@
       <c r="B78" s="5">
         <v>46162.792481805554</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46212.6552719676</v>
+      </c>
       <c r="D78" s="5">
-        <v>46171.19919608797</v>
+        <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>252</v>
@@ -6183,10 +6195,10 @@
         <v>33</v>
       </c>
       <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U78" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6196,9 +6208,11 @@
       <c r="B79" s="9">
         <v>46162.79248949074</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="9">
+        <v>46212.65527831019</v>
+      </c>
       <c r="D79" s="9">
-        <v>46198.68596158565</v>
+        <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>255</v>
@@ -6246,10 +6260,10 @@
         <v>52</v>
       </c>
       <c r="T79" s="10">
-        <v>0</v>
-      </c>
-      <c r="U79" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U79" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6259,9 +6273,11 @@
       <c r="B80" s="5">
         <v>46162.79249689815</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46212.65563663194</v>
+      </c>
       <c r="D80" s="5">
-        <v>46198.68569559028</v>
+        <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>258</v>
@@ -6309,10 +6325,10 @@
         <v>52</v>
       </c>
       <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="12" t="s">
-        <v>45</v>
+        <v>1</v>
+      </c>
+      <c r="U80" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6772,7 +6788,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46198.78274127315</v>
+        <v>46212.655287326386</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>188</v>
@@ -6825,7 +6841,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46198.782722233795</v>
+        <v>46212.655288587965</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>188</v>
@@ -6878,7 +6894,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46198.78272511574</v>
+        <v>46212.655289953706</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>188</v>
@@ -6931,7 +6947,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46198.782724108794</v>
+        <v>46212.65528899306</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>188</v>
@@ -7047,7 +7063,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46198.78272271991</v>
+        <v>46212.65528011574</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>188</v>
@@ -7100,7 +7116,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46198.78272560185</v>
+        <v>46212.65528133102</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>188</v>
@@ -7153,7 +7169,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46198.78273373842</v>
+        <v>46212.65528245371</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>188</v>
@@ -7206,7 +7222,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46198.78272606482</v>
+        <v>46212.65528189814</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>188</v>
@@ -7322,7 +7338,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46198.78272754629</v>
+        <v>46212.655646238425</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>188</v>
@@ -7375,7 +7391,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46198.78272310185</v>
+        <v>46212.65564513889</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>188</v>
@@ -7428,7 +7444,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46198.782727893515</v>
+        <v>46212.655646643514</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>188</v>
@@ -7481,7 +7497,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46198.782728391205</v>
+        <v>46212.65564726852</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>188</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="369">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -119,6 +119,39 @@
   </si>
   <si>
     <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buenas,
+Para el pedido 1553 Aris Mining, se tienen:
+        4 ventiladores ZVN 1-7-37/2,
+        8 ventiladores ZVN 1-7-63/2,
+        4 ventiladores ZVN 1-12-55/4
+        10 ventiladores ZVN 2-9-103/2
+    Planos para:
+        Ventilador ZVN 1-7-37/2 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 70/100 + VENT + FAR 70/100 + TIPO A
+        Ventilador ZVN 1-7-63/2 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 70/100 + VENT + FAR 70/100 + TIPO A
+        Ventilador ZVN 1-12-55/4 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 120/200 + VENT + FAR 120/200 + Difusor 120-160 / long 160
+        Ventilador ZVN 2-9-103/2 con motor WEG o similar – Alcance: TOBERA + REJILLA + FAR 90/100 + VENT + FAR 90/100 + TIPO A
+        Alcance Chile: TOBERA + REJILLA + VENT
+        Alcance Colombia: FAR + TIPO A + DIFUSOR
+        Planos: hgutierrez@zitron.com, por favor tu apoyo
+    Rodete:
+        Ventilador ZVN 1-7-37/2 --- RODETE: 300059
+        Ventilador ZVN 1-7-63/2 --- RODETE: 300065
+        Ventilador ZVN 1-12-55/4 --- ALABES: 300004
+        Ventilador ZVN 2-9-103/2 --- ALABES: 300000
+    Tratamiento superficial:
+        Estándar Zitrón con 2 capas y color de terminación Blanco RAL 9001.
+    Datos eléctricos para el motor:
+        440V, 60HZ, IP55, IE-3, 1000 MSNM.
+        Incluye: Sensor de vibraciones VKV 021 y Graseras automáticas con protección mecánica.
+    Pedido de referencia: 50001401
+    Fecha de entrega:
+        4 ventiladores ZVN 1-7-37/2 – 18/06/26
+        8 ventiladores ZVN 1-7-63/2 -- 18/06/26
+        4 ventiladores ZVN 1-12-55/4 -- 18/06/26
+        10 ventiladores ZVN 2-9-103/2 – 16/07/26
+</t>
   </si>
   <si>
     <t>1214982387940244</t>
@@ -1895,7 +1928,7 @@
         <v>46183.58130109953</v>
       </c>
       <c r="D6" s="5">
-        <v>46183.58131646991</v>
+        <v>46213.70988059028</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1919,7 +1952,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1951,7 +1984,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="9">
         <v>46162.79190123842</v>
@@ -1963,7 +1996,7 @@
         <v>46183.58133177084</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -1984,7 +2017,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>26</v>
@@ -1996,7 +2029,7 @@
         <v>26</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="9">
         <v>46148</v>
@@ -2016,7 +2049,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="5">
         <v>46162.791904513884</v>
@@ -2028,7 +2061,7 @@
         <v>46183.58133340278</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2049,7 +2082,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -2081,7 +2114,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="9">
         <v>46162.79178665509</v>
@@ -2091,7 +2124,7 @@
         <v>46197.77681821759</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>25</v>
@@ -2115,7 +2148,7 @@
         <v>26</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>26</v>
@@ -2125,12 +2158,12 @@
       <c r="S9" s="10"/>
       <c r="T9" s="10"/>
       <c r="U9" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46162.7919078125</v>
@@ -2142,16 +2175,16 @@
         <v>46197.776808263894</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I10" s="5">
         <v>46149</v>
@@ -2163,19 +2196,19 @@
         <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q10" s="5">
         <v>46149</v>
@@ -2184,7 +2217,7 @@
         <v>46150</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T10" s="6">
         <v>1</v>
@@ -2195,7 +2228,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" s="9">
         <v>46162.79191291667</v>
@@ -2207,16 +2240,16 @@
         <v>46197.77680832176</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I11" s="9">
         <v>46149</v>
@@ -2228,19 +2261,19 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q11" s="9">
         <v>46149</v>
@@ -2249,7 +2282,7 @@
         <v>46157</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T11" s="10">
         <v>1</v>
@@ -2260,7 +2293,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="5">
         <v>46162.791918055555</v>
@@ -2272,16 +2305,16 @@
         <v>46197.776808344905</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I12" s="5">
         <v>46149</v>
@@ -2293,19 +2326,19 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q12" s="5">
         <v>46149</v>
@@ -2314,7 +2347,7 @@
         <v>46157</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
@@ -2325,7 +2358,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="9">
         <v>46162.791791192125</v>
@@ -2337,7 +2370,7 @@
         <v>46204.89769989584</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>25</v>
@@ -2361,7 +2394,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>26</v>
@@ -2378,7 +2411,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="5">
         <v>46162.79193019676</v>
@@ -2390,16 +2423,16 @@
         <v>46198.68142037037</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I14" s="5">
         <v>46153</v>
@@ -2417,13 +2450,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="5">
         <v>46153</v>
@@ -2432,7 +2465,7 @@
         <v>46154</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T14" s="6">
         <v>1</v>
@@ -2443,7 +2476,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="9">
         <v>46162.7919353125</v>
@@ -2455,16 +2488,16 @@
         <v>46198.68143896991</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I15" s="9">
         <v>46160</v>
@@ -2482,13 +2515,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q15" s="9">
         <v>46160</v>
@@ -2497,7 +2530,7 @@
         <v>46161</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15" s="10">
         <v>1</v>
@@ -2508,7 +2541,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46162.79194023148</v>
@@ -2520,16 +2553,16 @@
         <v>46197.6606925</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" s="5">
         <v>46160</v>
@@ -2547,13 +2580,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="5">
         <v>46160</v>
@@ -2562,18 +2595,18 @@
         <v>46161</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" s="9">
         <v>46162.791945289355</v>
@@ -2585,16 +2618,16 @@
         <v>46204.89660072917</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I17" s="9">
         <v>46237</v>
@@ -2612,13 +2645,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q17" s="9">
         <v>46237</v>
@@ -2627,7 +2660,7 @@
         <v>46238</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T17" s="10">
         <v>1</v>
@@ -2638,7 +2671,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="5">
         <v>46162.79194956018</v>
@@ -2650,16 +2683,16 @@
         <v>46204.897086157405</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46237</v>
@@ -2677,13 +2710,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="5">
         <v>46237</v>
@@ -2692,7 +2725,7 @@
         <v>46238</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2703,7 +2736,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
         <v>46162.79195284723</v>
@@ -2715,16 +2748,16 @@
         <v>46204.8990687037</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46237</v>
@@ -2742,13 +2775,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2757,7 +2790,7 @@
         <v>46238</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2768,7 +2801,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46162.79195601852</v>
@@ -2780,16 +2813,16 @@
         <v>46204.91486320602</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46237</v>
@@ -2807,13 +2840,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2822,7 +2855,7 @@
         <v>46238</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2833,7 +2866,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46162.79179634259</v>
@@ -2843,7 +2876,7 @@
         <v>46212.655108425926</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2867,7 +2900,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2877,12 +2910,12 @@
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
       <c r="U21" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46162.79196002315</v>
@@ -2894,16 +2927,16 @@
         <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2921,13 +2954,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2936,7 +2969,7 @@
         <v>46276</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2947,7 +2980,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="9">
         <v>46162.791964375</v>
@@ -2959,16 +2992,16 @@
         <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
@@ -2986,29 +3019,29 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46162.79196883102</v>
@@ -3020,16 +3053,16 @@
         <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46167</v>
@@ -3047,29 +3080,29 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46162.79197329861</v>
@@ -3081,16 +3114,16 @@
         <v>46212.65520907407</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46162</v>
@@ -3108,13 +3141,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q25" s="9">
         <v>46162</v>
@@ -3134,7 +3167,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46162.791977500005</v>
@@ -3146,16 +3179,16 @@
         <v>46212.65503678241</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
@@ -3173,29 +3206,29 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46162.79198199074</v>
@@ -3207,16 +3240,16 @@
         <v>46212.65507065972</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46167</v>
@@ -3234,29 +3267,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46162.79198653935</v>
@@ -3268,16 +3301,16 @@
         <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3295,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q28" s="5">
         <v>46155</v>
@@ -3310,7 +3343,7 @@
         <v>46301</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3321,7 +3354,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46162.79199082176</v>
@@ -3333,16 +3366,16 @@
         <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3360,29 +3393,29 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46162.791995312495</v>
@@ -3394,16 +3427,16 @@
         <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3421,29 +3454,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46162.79199990741</v>
@@ -3455,16 +3488,16 @@
         <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3482,29 +3515,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46162.792004421295</v>
@@ -3516,16 +3549,16 @@
         <v>46209.81743660879</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I32" s="5">
         <v>46239</v>
@@ -3543,13 +3576,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q32" s="5">
         <v>46239</v>
@@ -3558,7 +3591,7 @@
         <v>46251</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3569,7 +3602,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3581,16 +3614,16 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
@@ -3608,29 +3641,29 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3642,16 +3675,16 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3669,29 +3702,29 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3703,16 +3736,16 @@
         <v>46209.81754938657</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="9">
         <v>46239</v>
@@ -3730,10 +3763,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3745,7 +3778,7 @@
         <v>46251</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3756,7 +3789,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3768,16 +3801,16 @@
         <v>46205.611504409724</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
@@ -3795,13 +3828,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3811,7 +3844,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3823,16 +3856,16 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="9">
         <v>46241</v>
@@ -3850,13 +3883,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3866,7 +3899,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3878,16 +3911,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3905,10 +3938,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3920,7 +3953,7 @@
         <v>46279</v>
       </c>
       <c r="S38" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -3931,7 +3964,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3943,16 +3976,16 @@
         <v>46209.624517187505</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3970,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3986,7 +4019,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -3998,16 +4031,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4025,13 +4058,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4041,7 +4074,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4051,16 +4084,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4078,10 +4111,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4094,7 +4127,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4106,16 +4139,16 @@
         <v>46205.612154409726</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I42" s="5">
         <v>46239</v>
@@ -4133,10 +4166,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4148,7 +4181,7 @@
         <v>46251</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -4159,7 +4192,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4171,16 +4204,16 @@
         <v>46205.612088877315</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
@@ -4198,13 +4231,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4214,7 +4247,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4226,16 +4259,16 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4253,13 +4286,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4269,7 +4302,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4281,7 +4314,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4305,7 +4338,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4322,7 +4355,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4334,16 +4367,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4361,13 +4394,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4387,7 +4420,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4399,16 +4432,16 @@
         <v>46198.78268157407</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4426,13 +4459,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4441,7 +4474,7 @@
         <v>46233</v>
       </c>
       <c r="S47" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4452,7 +4485,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4464,16 +4497,16 @@
         <v>46198.7827322338</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4491,13 +4524,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4506,7 +4539,7 @@
         <v>46234</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4517,7 +4550,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4527,16 +4560,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4554,10 +4587,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4569,18 +4602,18 @@
         <v>46322</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4590,16 +4623,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4617,13 +4650,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4633,7 +4666,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4643,16 +4676,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4670,13 +4703,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4686,7 +4719,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4696,16 +4729,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4723,13 +4756,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4739,7 +4772,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4749,16 +4782,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4776,13 +4809,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4792,7 +4825,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4802,7 +4835,7 @@
         <v>46164.66718020833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4826,7 +4859,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4839,7 +4872,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4849,16 +4882,16 @@
         <v>46209.81742680556</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4876,13 +4909,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4891,18 +4924,18 @@
         <v>46253</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4912,16 +4945,16 @@
         <v>46164.69055459491</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4939,13 +4972,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4954,18 +4987,18 @@
         <v>46255</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -4975,16 +5008,16 @@
         <v>46209.81754253472</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5002,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5017,18 +5050,18 @@
         <v>46253</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5038,16 +5071,16 @@
         <v>46164.69055186343</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5065,13 +5098,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5080,18 +5113,18 @@
         <v>46255</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
       <c r="U58" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5101,16 +5134,16 @@
         <v>46205.61214489583</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5128,13 +5161,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5143,18 +5176,18 @@
         <v>46253</v>
       </c>
       <c r="S59" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T59" s="10">
         <v>0</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5164,16 +5197,16 @@
         <v>46164.690549328705</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5191,13 +5224,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5206,18 +5239,18 @@
         <v>46255</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5227,7 +5260,7 @@
         <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5251,7 +5284,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5264,7 +5297,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5274,16 +5307,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5301,13 +5334,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5316,18 +5349,18 @@
         <v>46266</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5337,16 +5370,16 @@
         <v>46164.69068318287</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5364,13 +5397,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5380,7 +5413,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5390,16 +5423,16 @@
         <v>46164.69068048611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5417,13 +5450,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5433,7 +5466,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5443,16 +5476,16 @@
         <v>46164.69067753472</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5470,13 +5503,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5486,7 +5519,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5496,16 +5529,16 @@
         <v>46164.69067336805</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5523,13 +5556,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5539,7 +5572,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5549,16 +5582,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5576,13 +5609,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5591,18 +5624,18 @@
         <v>46288</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5612,16 +5645,16 @@
         <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5639,13 +5672,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5655,7 +5688,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5665,16 +5698,16 @@
         <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5692,13 +5725,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5708,7 +5741,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5718,16 +5751,16 @@
         <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5745,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5761,7 +5794,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5771,16 +5804,16 @@
         <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5798,13 +5831,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5814,7 +5847,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5824,16 +5857,16 @@
         <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5851,13 +5884,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5866,18 +5899,18 @@
         <v>46290</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5887,16 +5920,16 @@
         <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5914,13 +5947,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5930,7 +5963,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -5940,16 +5973,16 @@
         <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -5967,13 +6000,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5983,7 +6016,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -5993,16 +6026,16 @@
         <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6020,13 +6053,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6036,7 +6069,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6046,16 +6079,16 @@
         <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6073,13 +6106,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6089,7 +6122,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6099,7 +6132,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6123,7 +6156,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6133,12 +6166,12 @@
       <c r="S77" s="10"/>
       <c r="T77" s="10"/>
       <c r="U77" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6150,16 +6183,16 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6177,13 +6210,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6203,7 +6236,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6215,16 +6248,16 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6242,13 +6275,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6257,7 +6290,7 @@
         <v>46280</v>
       </c>
       <c r="S79" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6268,7 +6301,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6280,16 +6313,16 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6307,13 +6340,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6322,7 +6355,7 @@
         <v>46303</v>
       </c>
       <c r="S80" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6333,7 +6366,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6343,16 +6376,16 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6370,13 +6403,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6385,18 +6418,18 @@
         <v>46281</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6406,7 +6439,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6430,7 +6463,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6443,7 +6476,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6453,16 +6486,16 @@
         <v>46164.69124818287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" s="9">
         <v>46293</v>
@@ -6480,13 +6513,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6495,18 +6528,18 @@
         <v>46310</v>
       </c>
       <c r="S83" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6516,16 +6549,16 @@
         <v>46164.69121831018</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" s="5">
         <v>46293</v>
@@ -6543,10 +6576,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6559,7 +6592,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6569,16 +6602,16 @@
         <v>46164.6912157176</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" s="9">
         <v>46293</v>
@@ -6596,10 +6629,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6612,7 +6645,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6622,16 +6655,16 @@
         <v>46164.69121336806</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" s="5">
         <v>46293</v>
@@ -6649,13 +6682,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6665,7 +6698,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6675,16 +6708,16 @@
         <v>46164.691209490746</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" s="9">
         <v>46293</v>
@@ -6702,13 +6735,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6718,7 +6751,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6728,16 +6761,16 @@
         <v>46164.69137969907</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" s="5">
         <v>46311</v>
@@ -6755,13 +6788,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6770,18 +6803,18 @@
         <v>46314</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6791,16 +6824,16 @@
         <v>46212.655287326386</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" s="9">
         <v>46311</v>
@@ -6818,13 +6851,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6834,7 +6867,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6844,16 +6877,16 @@
         <v>46212.655288587965</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" s="5">
         <v>46311</v>
@@ -6871,13 +6904,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6887,7 +6920,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -6897,16 +6930,16 @@
         <v>46212.655289953706</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" s="9">
         <v>46311</v>
@@ -6924,13 +6957,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6940,7 +6973,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -6950,16 +6983,16 @@
         <v>46212.65528899306</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" s="5">
         <v>46311</v>
@@ -6977,13 +7010,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6993,7 +7026,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7003,16 +7036,16 @@
         <v>46164.6915004051</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" s="9">
         <v>46315</v>
@@ -7030,13 +7063,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7045,18 +7078,18 @@
         <v>46316</v>
       </c>
       <c r="S93" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T93" s="10">
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7066,16 +7099,16 @@
         <v>46212.65528011574</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" s="5">
         <v>46315</v>
@@ -7093,13 +7126,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7109,7 +7142,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7119,16 +7152,16 @@
         <v>46212.65528133102</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" s="9">
         <v>46315</v>
@@ -7146,13 +7179,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7162,7 +7195,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7172,16 +7205,16 @@
         <v>46212.65528245371</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" s="5">
         <v>46315</v>
@@ -7199,13 +7232,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7215,7 +7248,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7225,16 +7258,16 @@
         <v>46212.65528189814</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" s="9">
         <v>46315</v>
@@ -7252,13 +7285,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7268,7 +7301,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7278,16 +7311,16 @@
         <v>46164.691619942125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" s="5">
         <v>46317</v>
@@ -7305,13 +7338,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7320,18 +7353,18 @@
         <v>46318</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7341,16 +7374,16 @@
         <v>46212.655646238425</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" s="9">
         <v>46317</v>
@@ -7368,13 +7401,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7384,7 +7417,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7394,16 +7427,16 @@
         <v>46212.65564513889</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" s="5">
         <v>46317</v>
@@ -7421,13 +7454,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7437,7 +7470,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7447,16 +7480,16 @@
         <v>46212.655646643514</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" s="9">
         <v>46317</v>
@@ -7474,13 +7507,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7490,7 +7523,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7500,16 +7533,16 @@
         <v>46212.65564726852</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" s="5">
         <v>46317</v>
@@ -7527,13 +7560,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7543,7 +7576,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7553,16 +7586,16 @@
         <v>46164.69173954861</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" s="9">
         <v>46321</v>
@@ -7580,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7595,18 +7628,18 @@
         <v>46321</v>
       </c>
       <c r="S103" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T103" s="10">
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7616,16 +7649,16 @@
         <v>46164.69170866898</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" s="5">
         <v>46321</v>
@@ -7643,13 +7676,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7659,7 +7692,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7669,16 +7702,16 @@
         <v>46164.69170596065</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" s="9">
         <v>46321</v>
@@ -7696,13 +7729,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7712,7 +7745,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7722,16 +7755,16 @@
         <v>46164.69170293982</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I106" s="5">
         <v>46321</v>
@@ -7749,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7765,7 +7798,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7775,16 +7808,16 @@
         <v>46164.691698194445</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I107" s="9">
         <v>46321</v>
@@ -7802,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7818,7 +7851,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7828,16 +7861,16 @@
         <v>46164.69185736111</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7853,13 +7886,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7868,18 +7901,18 @@
         <v>46323</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -7889,16 +7922,16 @@
         <v>46164.69182431713</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I109" s="9">
         <v>46323</v>
@@ -7916,13 +7949,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7932,7 +7965,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -7942,16 +7975,16 @@
         <v>46164.691821562505</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I110" s="5">
         <v>46323</v>
@@ -7969,13 +8002,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7985,7 +8018,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -7995,16 +8028,16 @@
         <v>46164.691819155094</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I111" s="9">
         <v>46323</v>
@@ -8022,13 +8055,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8038,7 +8071,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8048,16 +8081,16 @@
         <v>46164.69181509259</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I112" s="5">
         <v>46323</v>
@@ -8075,13 +8108,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8091,7 +8124,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8101,7 +8134,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8125,7 +8158,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8138,7 +8171,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8148,16 +8181,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8175,13 +8208,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8190,18 +8223,18 @@
         <v>46324</v>
       </c>
       <c r="S114" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8211,16 +8244,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8238,13 +8271,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8254,7 +8287,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8264,16 +8297,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8291,13 +8324,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8307,7 +8340,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8317,16 +8350,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8344,13 +8377,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8360,7 +8393,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8370,16 +8403,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8397,13 +8430,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8413,7 +8446,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8423,16 +8456,16 @@
         <v>46164.692368958335</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I119" s="9">
         <v>46325</v>
@@ -8450,13 +8483,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8465,18 +8498,18 @@
         <v>46325</v>
       </c>
       <c r="S119" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T119" s="10">
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8486,16 +8519,16 @@
         <v>46164.692334189815</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I120" s="5">
         <v>46325</v>
@@ -8513,13 +8546,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8529,7 +8562,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8539,16 +8572,16 @@
         <v>46164.6923315162</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I121" s="9">
         <v>46325</v>
@@ -8566,13 +8599,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8582,7 +8615,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8592,16 +8625,16 @@
         <v>46164.69232880787</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I122" s="5">
         <v>46325</v>
@@ -8619,13 +8652,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8635,7 +8668,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8645,16 +8678,16 @@
         <v>46164.69232427083</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I123" s="9">
         <v>46325</v>
@@ -8672,13 +8705,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8688,7 +8721,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8698,16 +8731,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8725,13 +8758,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8740,18 +8773,18 @@
         <v>46328</v>
       </c>
       <c r="S124" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T124" s="6">
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8761,16 +8794,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8788,13 +8821,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8804,7 +8837,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8814,16 +8847,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8841,13 +8874,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8857,7 +8890,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8867,16 +8900,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8894,13 +8927,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8910,7 +8943,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -8920,16 +8953,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8947,13 +8980,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8963,7 +8996,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -8973,16 +9006,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9000,13 +9033,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9015,18 +9048,18 @@
         <v>46329</v>
       </c>
       <c r="S129" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9036,16 +9069,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9063,13 +9096,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9079,7 +9112,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9089,16 +9122,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9116,13 +9149,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9132,7 +9165,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9142,16 +9175,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9169,13 +9202,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9185,7 +9218,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9195,16 +9228,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9222,13 +9255,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9238,7 +9271,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9248,7 +9281,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9272,7 +9305,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9285,7 +9318,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9295,16 +9328,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9322,13 +9355,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9337,18 +9370,18 @@
         <v>46338</v>
       </c>
       <c r="S135" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T135" s="10">
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9358,16 +9391,16 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I136" s="5">
         <v>46330</v>
@@ -9385,13 +9418,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>
@@ -9400,13 +9433,13 @@
         <v>46338</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="367">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -685,9 +685,6 @@
     <t xml:space="preserve">Control de calidad corte laser </t>
   </si>
   <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
     <t>Bodega:,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
   </si>
   <si>
@@ -697,13 +694,10 @@
     <t>Recepcion Materiales corte plasma</t>
   </si>
   <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+    <t>Control de calidad Corte plasma</t>
   </si>
   <si>
     <t>1214982595357416</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
   </si>
   <si>
     <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
@@ -4830,9 +4824,11 @@
       <c r="B54" s="5">
         <v>46162.7922118287</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46217.58831976852</v>
+      </c>
       <c r="D54" s="5">
-        <v>46164.66718020833</v>
+        <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>195</v>
@@ -4867,8 +4863,12 @@
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
+      <c r="T54" s="6">
+        <v>1</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
@@ -4877,9 +4877,11 @@
       <c r="B55" s="9">
         <v>46162.7922200926</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46217.587680173616</v>
+      </c>
       <c r="D55" s="9">
-        <v>46209.81742680556</v>
+        <v>46217.58769918981</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>198</v>
@@ -4927,10 +4929,10 @@
         <v>53</v>
       </c>
       <c r="T55" s="10">
-        <v>0</v>
-      </c>
-      <c r="U55" s="12" t="s">
-        <v>46</v>
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4940,9 +4942,11 @@
       <c r="B56" s="5">
         <v>46162.792225625</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46217.58784472222</v>
+      </c>
       <c r="D56" s="5">
-        <v>46164.69055459491</v>
+        <v>46217.58785994213</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>203</v>
@@ -4975,10 +4979,10 @@
         <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4990,25 +4994,27 @@
         <v>53</v>
       </c>
       <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46217.58814275463</v>
+      </c>
       <c r="D57" s="9">
-        <v>46209.81754253472</v>
+        <v>46217.58816130787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5041,7 +5047,7 @@
         <v>143</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5053,25 +5059,27 @@
         <v>53</v>
       </c>
       <c r="T57" s="10">
-        <v>0</v>
-      </c>
-      <c r="U57" s="12" t="s">
-        <v>46</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46217.58818075231</v>
+      </c>
       <c r="D58" s="5">
-        <v>46164.69055186343</v>
+        <v>46217.588195752316</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5101,10 +5109,10 @@
         <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5116,25 +5124,27 @@
         <v>53</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46217.588267430554</v>
+      </c>
       <c r="D59" s="9">
-        <v>46205.61214489583</v>
+        <v>46217.58828952546</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5167,7 +5177,7 @@
         <v>165</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5179,25 +5189,27 @@
         <v>53</v>
       </c>
       <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="12" t="s">
-        <v>46</v>
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46217.58830322917</v>
+      </c>
       <c r="D60" s="5">
-        <v>46164.690549328705</v>
+        <v>46217.58832047453</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5227,10 +5239,10 @@
         <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5242,15 +5254,15 @@
         <v>53</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="11" t="s">
-        <v>101</v>
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5260,7 +5272,7 @@
         <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5284,7 +5296,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5297,7 +5309,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5307,16 +5319,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5334,13 +5346,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5360,14 +5372,14 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46164.69068318287</v>
+        <v>46217.58831070602</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>189</v>
@@ -5376,10 +5388,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5397,13 +5409,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5413,14 +5425,14 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46164.69068048611</v>
+        <v>46217.588311886575</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>189</v>
@@ -5429,10 +5441,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5450,13 +5462,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5466,14 +5478,14 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46164.69067753472</v>
+        <v>46217.58831295139</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>189</v>
@@ -5482,10 +5494,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5503,13 +5515,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5519,14 +5531,14 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46164.69067336805</v>
+        <v>46217.58831400463</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>189</v>
@@ -5535,10 +5547,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5556,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5572,7 +5584,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5582,16 +5594,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5609,13 +5621,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5635,7 +5647,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5651,10 +5663,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5672,13 +5684,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="O68" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="O68" s="6" t="s">
-        <v>235</v>
-      </c>
       <c r="P68" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5688,7 +5700,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5704,10 +5716,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5725,13 +5737,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="O69" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="O69" s="10" t="s">
-        <v>235</v>
-      </c>
       <c r="P69" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5741,7 +5753,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5757,10 +5769,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5778,13 +5790,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="O70" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="O70" s="6" t="s">
-        <v>235</v>
-      </c>
       <c r="P70" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5794,7 +5806,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5810,10 +5822,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5831,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="O71" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="O71" s="10" t="s">
-        <v>235</v>
-      </c>
       <c r="P71" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5847,7 +5859,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5857,7 +5869,7 @@
         <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5884,13 +5896,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5910,7 +5922,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5947,13 +5959,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>244</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5963,7 +5975,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -6000,13 +6012,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6016,7 +6028,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6053,13 +6065,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6069,7 +6081,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6106,13 +6118,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6122,7 +6134,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6156,7 +6168,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6171,7 +6183,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6183,7 +6195,7 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6216,7 +6228,7 @@
         <v>112</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6236,7 +6248,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6248,7 +6260,7 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6281,7 +6293,7 @@
         <v>103</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6301,7 +6313,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6313,7 +6325,7 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6346,7 +6358,7 @@
         <v>121</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6366,7 +6378,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6376,7 +6388,7 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6409,7 +6421,7 @@
         <v>153</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6429,7 +6441,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6439,7 +6451,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6463,7 +6475,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6476,7 +6488,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6486,7 +6498,7 @@
         <v>46164.69124818287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6513,13 +6525,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6539,7 +6551,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6576,10 +6588,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6592,7 +6604,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6629,10 +6641,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6645,7 +6657,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6682,13 +6694,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6698,7 +6710,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6735,13 +6747,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6751,7 +6763,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6761,7 +6773,7 @@
         <v>46164.69137969907</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6788,13 +6800,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6814,7 +6826,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6851,13 +6863,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="O89" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="O89" s="10" t="s">
-        <v>279</v>
-      </c>
       <c r="P89" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6867,7 +6879,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6904,13 +6916,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="O90" s="6" t="s">
-        <v>279</v>
-      </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6920,7 +6932,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -6957,13 +6969,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6973,7 +6985,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -7010,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7026,7 +7038,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7036,7 +7048,7 @@
         <v>46164.6915004051</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7063,13 +7075,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7089,7 +7101,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7126,13 +7138,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="O94" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="O94" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7142,7 +7154,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7179,13 +7191,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7195,7 +7207,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7232,13 +7244,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>292</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7248,7 +7260,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7285,13 +7297,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7301,7 +7313,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7311,7 +7323,7 @@
         <v>46164.691619942125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7338,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7364,7 +7376,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7401,13 +7413,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="O99" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="O99" s="10" t="s">
-        <v>299</v>
-      </c>
       <c r="P99" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7417,7 +7429,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7454,13 +7466,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="O100" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="O100" s="6" t="s">
-        <v>299</v>
-      </c>
       <c r="P100" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7470,7 +7482,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7507,13 +7519,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7523,7 +7535,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7560,13 +7572,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7576,7 +7588,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7586,7 +7598,7 @@
         <v>46164.69173954861</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7613,13 +7625,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7639,7 +7651,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7676,13 +7688,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7692,7 +7704,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7729,13 +7741,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7745,7 +7757,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7782,13 +7794,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7798,7 +7810,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7835,13 +7847,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7851,7 +7863,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7861,7 +7873,7 @@
         <v>46164.69185736111</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7886,13 +7898,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7912,7 +7924,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -7949,13 +7961,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7965,7 +7977,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -8002,13 +8014,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8018,7 +8030,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8055,13 +8067,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8071,7 +8083,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8108,13 +8120,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8124,7 +8136,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8134,7 +8146,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8158,7 +8170,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8171,7 +8183,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8181,16 +8193,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G114" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>328</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8208,13 +8220,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8234,7 +8246,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8250,10 +8262,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8271,13 +8283,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8287,7 +8299,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8303,10 +8315,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8324,13 +8336,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8340,7 +8352,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8356,10 +8368,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8377,13 +8389,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8393,7 +8405,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8409,10 +8421,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8430,13 +8442,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8446,7 +8458,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8456,7 +8468,7 @@
         <v>46164.692368958335</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8483,13 +8495,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8509,7 +8521,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8546,13 +8558,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8562,7 +8574,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8599,13 +8611,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8615,7 +8627,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8652,13 +8664,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8668,7 +8680,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8705,13 +8717,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8721,7 +8733,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8731,16 +8743,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8758,13 +8770,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8784,7 +8796,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8800,10 +8812,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8821,13 +8833,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8837,7 +8849,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8853,10 +8865,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8874,13 +8886,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8890,7 +8902,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8906,10 +8918,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8927,13 +8939,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8943,7 +8955,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -8959,10 +8971,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8980,13 +8992,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8996,7 +9008,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9006,16 +9018,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9033,13 +9045,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9059,7 +9071,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9075,10 +9087,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9096,13 +9108,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9112,7 +9124,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9128,10 +9140,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9149,13 +9161,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9165,7 +9177,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9181,10 +9193,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9202,13 +9214,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>189</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9218,7 +9230,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9234,10 +9246,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9255,13 +9267,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>189</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9271,7 +9283,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9281,7 +9293,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9305,7 +9317,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9318,7 +9330,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9328,16 +9340,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="H135" s="10" t="s">
         <v>364</v>
-      </c>
-      <c r="F135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>366</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9355,13 +9367,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9381,7 +9393,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9391,7 +9403,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9418,13 +9430,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="364">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -292,9 +292,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Generación OC Rodete,Propuesta compras:</t>
   </si>
   <si>
@@ -302,12 +299,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2553,11 +2544,9 @@
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H16" s="6"/>
       <c r="I16" s="5">
         <v>46160</v>
       </c>
@@ -2580,7 +2569,7 @@
         <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="5">
         <v>46160</v>
@@ -2600,7 +2589,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" s="9">
         <v>46162.791945289355</v>
@@ -2612,17 +2601,15 @@
         <v>46204.89660072917</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="9">
         <v>46237</v>
       </c>
@@ -2642,10 +2629,10 @@
         <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Q17" s="9">
         <v>46237</v>
@@ -2665,7 +2652,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46162.79194956018</v>
@@ -2677,17 +2664,15 @@
         <v>46204.897086157405</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46237</v>
       </c>
@@ -2707,10 +2692,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46237</v>
@@ -2730,7 +2715,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46162.79195284723</v>
@@ -2742,17 +2727,15 @@
         <v>46204.8990687037</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19" s="9">
         <v>46237</v>
       </c>
@@ -2772,10 +2755,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2795,7 +2778,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46162.79195601852</v>
@@ -2807,17 +2790,15 @@
         <v>46204.91486320602</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46237</v>
       </c>
@@ -2837,10 +2818,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2860,7 +2841,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46162.79179634259</v>
@@ -2870,7 +2851,7 @@
         <v>46212.655108425926</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2894,7 +2875,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2909,7 +2890,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46162.79196002315</v>
@@ -2921,16 +2902,16 @@
         <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2948,13 +2929,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2974,7 +2955,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
         <v>46162.791964375</v>
@@ -2986,16 +2967,16 @@
         <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
@@ -3013,13 +2994,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3030,12 +3011,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46162.79196883102</v>
@@ -3047,16 +3028,16 @@
         <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I24" s="5">
         <v>46167</v>
@@ -3074,13 +3055,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3091,12 +3072,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B25" s="9">
         <v>46162.79197329861</v>
@@ -3108,16 +3089,16 @@
         <v>46212.65520907407</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I25" s="9">
         <v>46162</v>
@@ -3135,13 +3116,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="9">
         <v>46162</v>
@@ -3161,7 +3142,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46162.791977500005</v>
@@ -3173,16 +3154,16 @@
         <v>46212.65503678241</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
@@ -3200,13 +3181,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3217,12 +3198,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46162.79198199074</v>
@@ -3234,16 +3215,16 @@
         <v>46212.65507065972</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I27" s="9">
         <v>46167</v>
@@ -3261,13 +3242,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="O27" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="O27" s="10" t="s">
-        <v>109</v>
-      </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3278,12 +3259,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46162.79198653935</v>
@@ -3295,16 +3276,16 @@
         <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3322,13 +3303,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q28" s="5">
         <v>46155</v>
@@ -3348,7 +3329,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46162.79199082176</v>
@@ -3360,16 +3341,16 @@
         <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3387,13 +3368,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>66</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3404,12 +3385,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B30" s="5">
         <v>46162.791995312495</v>
@@ -3421,16 +3402,16 @@
         <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3448,13 +3429,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="O30" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3465,12 +3446,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B31" s="9">
         <v>46162.79199990741</v>
@@ -3482,16 +3463,16 @@
         <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3509,13 +3490,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="O31" s="10" t="s">
-        <v>118</v>
-      </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3526,12 +3507,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B32" s="5">
         <v>46162.792004421295</v>
@@ -3543,16 +3524,16 @@
         <v>46209.81743660879</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I32" s="5">
         <v>46239</v>
@@ -3570,13 +3551,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="Q32" s="5">
         <v>46239</v>
@@ -3596,7 +3577,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3608,16 +3589,16 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
@@ -3635,13 +3616,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3652,12 +3633,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3669,16 +3650,16 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3696,13 +3677,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3713,12 +3694,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3730,16 +3711,16 @@
         <v>46209.81754938657</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I35" s="9">
         <v>46239</v>
@@ -3757,10 +3738,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3783,7 +3764,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3795,16 +3776,16 @@
         <v>46205.611504409724</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
@@ -3822,13 +3803,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="P36" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3838,7 +3819,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3850,16 +3831,16 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I37" s="9">
         <v>46241</v>
@@ -3877,13 +3858,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3893,7 +3874,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3905,16 +3886,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3932,10 +3913,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3958,7 +3939,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3970,16 +3951,16 @@
         <v>46209.624517187505</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3997,13 +3978,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4013,7 +3994,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4025,16 +4006,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4052,13 +4033,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4068,7 +4049,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4078,16 +4059,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4105,10 +4086,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4121,7 +4102,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4133,16 +4114,16 @@
         <v>46205.612154409726</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I42" s="5">
         <v>46239</v>
@@ -4160,10 +4141,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4186,7 +4167,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4198,16 +4179,16 @@
         <v>46205.612088877315</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
@@ -4225,13 +4206,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="O43" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="P43" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="P43" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4241,7 +4222,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4253,16 +4234,16 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4280,13 +4261,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4296,7 +4277,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4308,7 +4289,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4332,7 +4313,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4349,7 +4330,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4361,16 +4342,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4388,13 +4369,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4414,7 +4395,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4426,16 +4407,16 @@
         <v>46198.78268157407</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4453,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4479,7 +4460,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4491,16 +4472,16 @@
         <v>46198.7827322338</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4518,13 +4499,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4544,7 +4525,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4554,16 +4535,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4581,10 +4562,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4602,12 +4583,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4617,16 +4598,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4644,13 +4625,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4660,7 +4641,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4670,16 +4651,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4697,13 +4678,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4713,7 +4694,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4723,16 +4704,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4750,13 +4731,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4766,7 +4747,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4776,16 +4757,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4803,13 +4784,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4819,7 +4800,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4831,7 +4812,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4855,7 +4836,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4872,7 +4853,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4884,16 +4865,16 @@
         <v>46217.58769918981</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4911,13 +4892,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4937,7 +4918,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4949,16 +4930,16 @@
         <v>46217.58785994213</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4976,13 +4957,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="O56" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="O56" s="6" t="s">
-        <v>198</v>
-      </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -5002,7 +4983,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -5014,16 +4995,16 @@
         <v>46217.58816130787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5041,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5067,7 +5048,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5079,16 +5060,16 @@
         <v>46217.588195752316</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5106,13 +5087,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5132,7 +5113,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5144,16 +5125,16 @@
         <v>46217.58828952546</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5171,13 +5152,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5197,7 +5178,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5209,16 +5190,16 @@
         <v>46217.58832047453</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5236,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5262,7 +5243,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5272,7 +5253,7 @@
         <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5296,7 +5277,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5309,7 +5290,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5319,16 +5300,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5346,13 +5327,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5367,12 +5348,12 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5382,16 +5363,16 @@
         <v>46217.58831070602</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5409,13 +5390,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5425,7 +5406,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5435,16 +5416,16 @@
         <v>46217.588311886575</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5462,13 +5443,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5478,7 +5459,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5488,16 +5469,16 @@
         <v>46217.58831295139</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5515,13 +5496,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5531,7 +5512,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5541,16 +5522,16 @@
         <v>46217.58831400463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5568,13 +5549,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5584,7 +5565,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5594,16 +5575,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5621,13 +5602,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5642,12 +5623,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5657,16 +5638,16 @@
         <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5684,13 +5665,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5700,7 +5681,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5710,16 +5691,16 @@
         <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5737,13 +5718,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="O69" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="O69" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5753,7 +5734,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5763,16 +5744,16 @@
         <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5790,13 +5771,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5806,7 +5787,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5816,16 +5797,16 @@
         <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5843,13 +5824,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5859,7 +5840,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5869,16 +5850,16 @@
         <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5896,13 +5877,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5917,12 +5898,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5932,16 +5913,16 @@
         <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5959,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5975,7 +5956,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -5985,16 +5966,16 @@
         <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -6012,13 +5993,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6028,7 +6009,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6038,16 +6019,16 @@
         <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6065,13 +6046,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6081,7 +6062,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6091,16 +6072,16 @@
         <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6118,13 +6099,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6134,7 +6115,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6144,7 +6125,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6168,7 +6149,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6183,7 +6164,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6195,16 +6176,16 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6222,13 +6203,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6248,7 +6229,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6260,16 +6241,16 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6287,13 +6268,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6313,7 +6294,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6325,16 +6306,16 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6352,13 +6333,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6378,7 +6359,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6388,16 +6369,16 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6415,13 +6396,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6441,7 +6422,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6451,7 +6432,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6475,7 +6456,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6488,7 +6469,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6498,17 +6479,15 @@
         <v>46164.69124818287</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="10"/>
       <c r="I83" s="9">
         <v>46293</v>
       </c>
@@ -6525,13 +6504,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6546,12 +6525,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6561,17 +6540,15 @@
         <v>46164.69121831018</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="5">
         <v>46293</v>
       </c>
@@ -6588,10 +6565,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="O84" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6604,7 +6581,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6614,17 +6591,15 @@
         <v>46164.6912157176</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="10"/>
       <c r="I85" s="9">
         <v>46293</v>
       </c>
@@ -6641,10 +6616,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="O85" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>268</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6657,7 +6632,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6667,17 +6642,15 @@
         <v>46164.69121336806</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46293</v>
       </c>
@@ -6694,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6710,7 +6683,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6720,17 +6693,15 @@
         <v>46164.691209490746</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="10"/>
       <c r="I87" s="9">
         <v>46293</v>
       </c>
@@ -6747,13 +6718,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6763,7 +6734,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6773,17 +6744,15 @@
         <v>46164.69137969907</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46311</v>
       </c>
@@ -6800,13 +6769,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6821,12 +6790,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6836,17 +6805,15 @@
         <v>46212.655287326386</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="10"/>
       <c r="I89" s="9">
         <v>46311</v>
       </c>
@@ -6863,13 +6830,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6879,7 +6846,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6889,17 +6856,15 @@
         <v>46212.655288587965</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="5">
         <v>46311</v>
       </c>
@@ -6916,13 +6881,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6932,7 +6897,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -6942,17 +6907,15 @@
         <v>46212.655289953706</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="10"/>
       <c r="I91" s="9">
         <v>46311</v>
       </c>
@@ -6969,13 +6932,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="O91" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="O91" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6985,7 +6948,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -6995,17 +6958,15 @@
         <v>46212.65528899306</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="5">
         <v>46311</v>
       </c>
@@ -7022,13 +6983,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="P92" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7038,7 +6999,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7048,17 +7009,15 @@
         <v>46164.6915004051</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="10"/>
       <c r="I93" s="9">
         <v>46315</v>
       </c>
@@ -7075,13 +7034,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7096,12 +7055,12 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7111,17 +7070,15 @@
         <v>46212.65528011574</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46315</v>
       </c>
@@ -7138,13 +7095,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7154,7 +7111,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7164,17 +7121,15 @@
         <v>46212.65528133102</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="10"/>
       <c r="I95" s="9">
         <v>46315</v>
       </c>
@@ -7191,13 +7146,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7207,7 +7162,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7217,17 +7172,15 @@
         <v>46212.65528245371</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="5">
         <v>46315</v>
       </c>
@@ -7244,13 +7197,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7260,7 +7213,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7270,17 +7223,15 @@
         <v>46212.65528189814</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="10"/>
       <c r="I97" s="9">
         <v>46315</v>
       </c>
@@ -7297,13 +7248,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7313,7 +7264,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7323,17 +7274,15 @@
         <v>46164.691619942125</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="5">
         <v>46317</v>
       </c>
@@ -7350,13 +7299,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7371,12 +7320,12 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7386,17 +7335,15 @@
         <v>46212.655646238425</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="10"/>
       <c r="I99" s="9">
         <v>46317</v>
       </c>
@@ -7413,13 +7360,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="O99" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="P99" s="10" t="s">
         <v>295</v>
-      </c>
-      <c r="O99" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="P99" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7429,7 +7376,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7439,17 +7386,15 @@
         <v>46212.65564513889</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="5">
         <v>46317</v>
       </c>
@@ -7466,13 +7411,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7482,7 +7427,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7492,17 +7437,15 @@
         <v>46212.655646643514</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="10"/>
       <c r="I101" s="9">
         <v>46317</v>
       </c>
@@ -7519,13 +7462,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7535,7 +7478,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7545,17 +7488,15 @@
         <v>46212.65564726852</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="5">
         <v>46317</v>
       </c>
@@ -7572,13 +7513,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7588,7 +7529,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7598,17 +7539,15 @@
         <v>46164.69173954861</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="10"/>
       <c r="I103" s="9">
         <v>46321</v>
       </c>
@@ -7625,13 +7564,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7646,12 +7585,12 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7661,17 +7600,15 @@
         <v>46164.69170866898</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="5">
         <v>46321</v>
       </c>
@@ -7688,13 +7625,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7704,7 +7641,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7714,17 +7651,15 @@
         <v>46164.69170596065</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="10"/>
       <c r="I105" s="9">
         <v>46321</v>
       </c>
@@ -7741,13 +7676,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7757,7 +7692,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7767,17 +7702,15 @@
         <v>46164.69170293982</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="5">
         <v>46321</v>
       </c>
@@ -7794,13 +7727,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7810,7 +7743,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7820,17 +7753,15 @@
         <v>46164.691698194445</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="10"/>
       <c r="I107" s="9">
         <v>46321</v>
       </c>
@@ -7847,13 +7778,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7863,7 +7794,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7873,17 +7804,15 @@
         <v>46164.69185736111</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
         <v>46323</v>
@@ -7898,13 +7827,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7919,12 +7848,12 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -7934,17 +7863,15 @@
         <v>46164.69182431713</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="10"/>
       <c r="I109" s="9">
         <v>46323</v>
       </c>
@@ -7961,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="O109" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P109" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="O109" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="P109" s="10" t="s">
-        <v>316</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7977,7 +7904,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -7987,17 +7914,15 @@
         <v>46164.691821562505</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="5">
         <v>46323</v>
       </c>
@@ -8014,13 +7939,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="P110" s="6" t="s">
         <v>313</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>316</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8030,7 +7955,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8040,17 +7965,15 @@
         <v>46164.691819155094</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="10"/>
       <c r="I111" s="9">
         <v>46323</v>
       </c>
@@ -8067,13 +7990,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="O111" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="O111" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>316</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8083,7 +8006,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8093,17 +8016,15 @@
         <v>46164.69181509259</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="5">
         <v>46323</v>
       </c>
@@ -8120,13 +8041,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="O112" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="P112" s="6" t="s">
         <v>313</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>316</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8136,7 +8057,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8146,7 +8067,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8170,7 +8091,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8183,7 +8104,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8193,16 +8114,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8220,13 +8141,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8241,12 +8162,12 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8256,16 +8177,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8283,13 +8204,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8299,7 +8220,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8309,16 +8230,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8336,13 +8257,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8352,7 +8273,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8362,16 +8283,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8389,13 +8310,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8405,7 +8326,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8415,16 +8336,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8442,13 +8363,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8458,7 +8379,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8468,17 +8389,15 @@
         <v>46164.692368958335</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="10"/>
       <c r="I119" s="9">
         <v>46325</v>
       </c>
@@ -8495,13 +8414,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8516,12 +8435,12 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8531,17 +8450,15 @@
         <v>46164.692334189815</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="5">
         <v>46325</v>
       </c>
@@ -8558,13 +8475,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8574,7 +8491,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8584,17 +8501,15 @@
         <v>46164.6923315162</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="10"/>
       <c r="I121" s="9">
         <v>46325</v>
       </c>
@@ -8611,13 +8526,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8627,7 +8542,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8637,17 +8552,15 @@
         <v>46164.69232880787</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="5">
         <v>46325</v>
       </c>
@@ -8664,13 +8577,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8680,7 +8593,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8690,17 +8603,15 @@
         <v>46164.69232427083</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="10"/>
       <c r="I123" s="9">
         <v>46325</v>
       </c>
@@ -8717,13 +8628,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8733,7 +8644,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8743,16 +8654,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8770,13 +8681,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8791,12 +8702,12 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8806,16 +8717,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8833,13 +8744,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8849,7 +8760,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8859,16 +8770,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8886,13 +8797,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8902,7 +8813,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8912,16 +8823,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8939,13 +8850,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8955,7 +8866,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -8965,16 +8876,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8992,13 +8903,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9008,7 +8919,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9018,16 +8929,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9045,13 +8956,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9066,12 +8977,12 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9081,16 +8992,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9108,13 +9019,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9124,7 +9035,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9134,16 +9045,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9161,13 +9072,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9177,7 +9088,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9187,16 +9098,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9214,13 +9125,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9230,7 +9141,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9240,16 +9151,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9267,13 +9178,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9283,7 +9194,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9293,7 +9204,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9317,7 +9228,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9330,7 +9241,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9340,16 +9251,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9367,13 +9278,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9388,12 +9299,12 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9403,7 +9314,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9430,13 +9341,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>
@@ -9451,7 +9362,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="365">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Generación OC Rodete,Propuesta compras:</t>
@@ -2535,7 +2538,7 @@
         <v>46197.5874865625</v>
       </c>
       <c r="D16" s="5">
-        <v>46197.6606925</v>
+        <v>46223.575690763886</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2544,9 +2547,11 @@
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I16" s="5">
         <v>46160</v>
       </c>
@@ -2569,7 +2574,7 @@
         <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="5">
         <v>46160</v>
@@ -2589,7 +2594,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" s="9">
         <v>46162.791945289355</v>
@@ -2598,18 +2603,20 @@
         <v>46204.89537108796</v>
       </c>
       <c r="D17" s="9">
-        <v>46204.89660072917</v>
+        <v>46223.57568681713</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I17" s="9">
         <v>46237</v>
       </c>
@@ -2629,10 +2636,10 @@
         <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="9">
         <v>46237</v>
@@ -2652,7 +2659,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
         <v>46162.79194956018</v>
@@ -2661,18 +2668,20 @@
         <v>46204.89540233796</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.897086157405</v>
+        <v>46223.57568328704</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I18" s="5">
         <v>46237</v>
       </c>
@@ -2692,10 +2701,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="5">
         <v>46237</v>
@@ -2715,7 +2724,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
         <v>46162.79195284723</v>
@@ -2724,18 +2733,20 @@
         <v>46204.898560891204</v>
       </c>
       <c r="D19" s="9">
-        <v>46204.8990687037</v>
+        <v>46223.575679988426</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I19" s="9">
         <v>46237</v>
       </c>
@@ -2755,10 +2766,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2778,7 +2789,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46162.79195601852</v>
@@ -2787,18 +2798,20 @@
         <v>46204.8976750463</v>
       </c>
       <c r="D20" s="5">
-        <v>46204.91486320602</v>
+        <v>46223.5756741088</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I20" s="5">
         <v>46237</v>
       </c>
@@ -2818,10 +2831,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2841,7 +2854,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
         <v>46162.79179634259</v>
@@ -2851,7 +2864,7 @@
         <v>46212.655108425926</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2875,7 +2888,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2890,7 +2903,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46162.79196002315</v>
@@ -2902,16 +2915,16 @@
         <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2929,13 +2942,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2955,7 +2968,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="9">
         <v>46162.791964375</v>
@@ -2967,16 +2980,16 @@
         <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
@@ -2994,13 +3007,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3011,12 +3024,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46162.79196883102</v>
@@ -3028,16 +3041,16 @@
         <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I24" s="5">
         <v>46167</v>
@@ -3055,13 +3068,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3072,12 +3085,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="9">
         <v>46162.79197329861</v>
@@ -3089,16 +3102,16 @@
         <v>46212.65520907407</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I25" s="9">
         <v>46162</v>
@@ -3116,13 +3129,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q25" s="9">
         <v>46162</v>
@@ -3142,7 +3155,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46162.791977500005</v>
@@ -3154,16 +3167,16 @@
         <v>46212.65503678241</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
@@ -3181,13 +3194,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3198,12 +3211,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46162.79198199074</v>
@@ -3215,16 +3228,16 @@
         <v>46212.65507065972</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I27" s="9">
         <v>46167</v>
@@ -3242,13 +3255,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3259,12 +3272,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46162.79198653935</v>
@@ -3276,16 +3289,16 @@
         <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3303,13 +3316,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q28" s="5">
         <v>46155</v>
@@ -3329,7 +3342,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46162.79199082176</v>
@@ -3341,16 +3354,16 @@
         <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3368,13 +3381,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>66</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3385,12 +3398,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46162.791995312495</v>
@@ -3402,16 +3415,16 @@
         <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3429,13 +3442,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3446,12 +3459,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46162.79199990741</v>
@@ -3463,16 +3476,16 @@
         <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3490,13 +3503,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3507,12 +3520,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46162.792004421295</v>
@@ -3524,16 +3537,16 @@
         <v>46209.81743660879</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I32" s="5">
         <v>46239</v>
@@ -3551,13 +3564,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q32" s="5">
         <v>46239</v>
@@ -3577,7 +3590,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3589,16 +3602,16 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
@@ -3616,13 +3629,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3633,12 +3646,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3650,16 +3663,16 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3677,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3694,12 +3707,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3711,16 +3724,16 @@
         <v>46209.81754938657</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I35" s="9">
         <v>46239</v>
@@ -3738,10 +3751,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3764,7 +3777,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3776,16 +3789,16 @@
         <v>46205.611504409724</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
@@ -3803,13 +3816,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3819,7 +3832,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3831,16 +3844,16 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I37" s="9">
         <v>46241</v>
@@ -3858,13 +3871,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3874,7 +3887,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3886,16 +3899,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3913,10 +3926,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3939,7 +3952,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3951,16 +3964,16 @@
         <v>46209.624517187505</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3978,13 +3991,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3994,7 +4007,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4006,16 +4019,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4033,13 +4046,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4049,7 +4062,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4059,16 +4072,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4086,10 +4099,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4102,7 +4115,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4114,16 +4127,16 @@
         <v>46205.612154409726</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I42" s="5">
         <v>46239</v>
@@ -4141,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4167,7 +4180,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4179,16 +4192,16 @@
         <v>46205.612088877315</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
@@ -4206,13 +4219,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4222,7 +4235,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4234,16 +4247,16 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4261,13 +4274,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4277,7 +4290,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4289,7 +4302,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4313,7 +4326,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4330,7 +4343,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4342,16 +4355,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4369,13 +4382,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4395,7 +4408,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4407,16 +4420,16 @@
         <v>46198.78268157407</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4434,13 +4447,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4460,7 +4473,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4472,16 +4485,16 @@
         <v>46198.7827322338</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4499,13 +4512,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4525,7 +4538,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4535,16 +4548,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4562,10 +4575,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4583,12 +4596,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4598,16 +4611,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4625,13 +4638,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4641,7 +4654,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4651,16 +4664,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4678,13 +4691,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4694,7 +4707,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4704,16 +4717,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4731,13 +4744,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4747,7 +4760,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4757,16 +4770,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4784,13 +4797,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4800,7 +4813,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4812,7 +4825,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4836,7 +4849,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4853,7 +4866,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4865,16 +4878,16 @@
         <v>46217.58769918981</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4892,13 +4905,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4918,7 +4931,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4930,16 +4943,16 @@
         <v>46217.58785994213</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4957,13 +4970,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4983,7 +4996,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -4995,16 +5008,16 @@
         <v>46217.58816130787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5022,13 +5035,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5048,7 +5061,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5060,16 +5073,16 @@
         <v>46217.588195752316</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5087,13 +5100,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5113,7 +5126,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5125,16 +5138,16 @@
         <v>46217.58828952546</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5152,13 +5165,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5178,7 +5191,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5190,16 +5203,16 @@
         <v>46217.58832047453</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5217,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5243,7 +5256,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5253,7 +5266,7 @@
         <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5277,7 +5290,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5290,7 +5303,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5300,16 +5313,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5327,13 +5340,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5348,12 +5361,12 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5363,16 +5376,16 @@
         <v>46217.58831070602</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5390,13 +5403,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5406,7 +5419,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5416,16 +5429,16 @@
         <v>46217.588311886575</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5443,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5459,7 +5472,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5469,16 +5482,16 @@
         <v>46217.58831295139</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5496,13 +5509,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5512,7 +5525,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5522,16 +5535,16 @@
         <v>46217.58831400463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5549,13 +5562,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5565,7 +5578,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5575,16 +5588,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5602,13 +5615,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5623,12 +5636,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5638,16 +5651,16 @@
         <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5665,13 +5678,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5681,7 +5694,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5691,16 +5704,16 @@
         <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5718,13 +5731,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5734,7 +5747,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5744,16 +5757,16 @@
         <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5771,13 +5784,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5787,7 +5800,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5797,16 +5810,16 @@
         <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5824,13 +5837,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5840,7 +5853,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5850,16 +5863,16 @@
         <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5877,13 +5890,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5898,12 +5911,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5913,16 +5926,16 @@
         <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5940,13 +5953,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5956,7 +5969,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -5966,16 +5979,16 @@
         <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -5993,13 +6006,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6009,7 +6022,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6019,16 +6032,16 @@
         <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6046,13 +6059,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6062,7 +6075,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6072,16 +6085,16 @@
         <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6099,13 +6112,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6115,7 +6128,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6125,7 +6138,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6149,7 +6162,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6164,7 +6177,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6176,16 +6189,16 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6203,13 +6216,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6229,7 +6242,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6241,16 +6254,16 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6268,13 +6281,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6294,7 +6307,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6306,16 +6319,16 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6333,13 +6346,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6359,7 +6372,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6369,16 +6382,16 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6396,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6422,7 +6435,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6432,7 +6445,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6456,7 +6469,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6469,25 +6482,27 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46164.69124818287</v>
+        <v>46223.57585706019</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I83" s="9">
         <v>46293</v>
       </c>
@@ -6504,13 +6519,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6525,30 +6540,32 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46164.69121831018</v>
+        <v>46223.575943020835</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I84" s="5">
         <v>46293</v>
       </c>
@@ -6565,10 +6582,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6581,25 +6598,27 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46164.6912157176</v>
+        <v>46223.57594232639</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I85" s="9">
         <v>46293</v>
       </c>
@@ -6616,10 +6635,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6632,25 +6651,27 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46164.69121336806</v>
+        <v>46223.57594163195</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I86" s="5">
         <v>46293</v>
       </c>
@@ -6667,13 +6688,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6683,25 +6704,27 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46164.691209490746</v>
+        <v>46223.57594097222</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I87" s="9">
         <v>46293</v>
       </c>
@@ -6718,13 +6741,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6734,25 +6757,27 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46164.69137969907</v>
+        <v>46223.575856435185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I88" s="5">
         <v>46311</v>
       </c>
@@ -6769,13 +6794,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6790,30 +6815,32 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46212.655287326386</v>
+        <v>46223.576037604165</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I89" s="9">
         <v>46311</v>
       </c>
@@ -6830,13 +6857,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6846,25 +6873,27 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46212.655288587965</v>
+        <v>46223.57603699074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I90" s="5">
         <v>46311</v>
       </c>
@@ -6881,13 +6910,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6897,25 +6926,27 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46212.655289953706</v>
+        <v>46223.57603633102</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I91" s="9">
         <v>46311</v>
       </c>
@@ -6932,13 +6963,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6948,25 +6979,27 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46212.65528899306</v>
+        <v>46223.576035659724</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I92" s="5">
         <v>46311</v>
       </c>
@@ -6983,13 +7016,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6999,25 +7032,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46164.6915004051</v>
+        <v>46223.57585581018</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I93" s="9">
         <v>46315</v>
       </c>
@@ -7034,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7055,30 +7090,32 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46212.65528011574</v>
+        <v>46223.5761230787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I94" s="5">
         <v>46315</v>
       </c>
@@ -7095,13 +7132,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7111,25 +7148,27 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46212.65528133102</v>
+        <v>46223.57612246528</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I95" s="9">
         <v>46315</v>
       </c>
@@ -7146,13 +7185,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7162,25 +7201,27 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46212.65528245371</v>
+        <v>46223.57612182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I96" s="5">
         <v>46315</v>
       </c>
@@ -7197,13 +7238,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7213,25 +7254,27 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46212.65528189814</v>
+        <v>46223.57612121528</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I97" s="9">
         <v>46315</v>
       </c>
@@ -7248,13 +7291,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7264,25 +7307,27 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46164.691619942125</v>
+        <v>46223.57585515046</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I98" s="5">
         <v>46317</v>
       </c>
@@ -7299,13 +7344,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7320,30 +7365,32 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46212.655646238425</v>
+        <v>46223.57621322917</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I99" s="9">
         <v>46317</v>
       </c>
@@ -7360,13 +7407,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7376,25 +7423,27 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46212.65564513889</v>
+        <v>46223.576212500004</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I100" s="5">
         <v>46317</v>
       </c>
@@ -7411,13 +7460,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7427,25 +7476,27 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46212.655646643514</v>
+        <v>46223.57621184028</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I101" s="9">
         <v>46317</v>
       </c>
@@ -7462,13 +7513,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7478,25 +7529,27 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46212.65564726852</v>
+        <v>46223.57621119213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I102" s="5">
         <v>46317</v>
       </c>
@@ -7513,13 +7566,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7529,25 +7582,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46164.69173954861</v>
+        <v>46223.57585453703</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I103" s="9">
         <v>46321</v>
       </c>
@@ -7564,13 +7619,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7585,30 +7640,32 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46164.69170866898</v>
+        <v>46223.57630975694</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I104" s="5">
         <v>46321</v>
       </c>
@@ -7625,13 +7682,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7641,25 +7698,27 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46164.69170596065</v>
+        <v>46223.57630916667</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I105" s="9">
         <v>46321</v>
       </c>
@@ -7676,13 +7735,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7692,25 +7751,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46164.69170293982</v>
+        <v>46223.57630858796</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I106" s="5">
         <v>46321</v>
       </c>
@@ -7727,13 +7788,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7743,25 +7804,27 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46164.691698194445</v>
+        <v>46223.57630797454</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I107" s="9">
         <v>46321</v>
       </c>
@@ -7778,13 +7841,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7794,25 +7857,27 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46164.69185736111</v>
+        <v>46223.57585388889</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
         <v>46323</v>
@@ -7827,13 +7892,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7848,30 +7913,32 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46164.69182431713</v>
+        <v>46223.5763915162</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I109" s="9">
         <v>46323</v>
       </c>
@@ -7888,13 +7955,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7904,25 +7971,27 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46164.691821562505</v>
+        <v>46223.576390856484</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I110" s="5">
         <v>46323</v>
       </c>
@@ -7939,13 +8008,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7955,25 +8024,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46164.691819155094</v>
+        <v>46223.57639018519</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I111" s="9">
         <v>46323</v>
       </c>
@@ -7990,13 +8061,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8006,25 +8077,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46164.69181509259</v>
+        <v>46223.57638950231</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I112" s="5">
         <v>46323</v>
       </c>
@@ -8041,13 +8114,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8057,7 +8130,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8067,7 +8140,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8091,7 +8164,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8104,7 +8177,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8114,16 +8187,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8141,13 +8214,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8162,12 +8235,12 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8177,16 +8250,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8204,13 +8277,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8220,7 +8293,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8230,16 +8303,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8257,13 +8330,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8273,7 +8346,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8283,16 +8356,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8310,13 +8383,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8326,7 +8399,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8336,16 +8409,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8363,13 +8436,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8379,25 +8452,27 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46164.692368958335</v>
+        <v>46223.57655457176</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I119" s="9">
         <v>46325</v>
       </c>
@@ -8414,13 +8489,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8435,30 +8510,32 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.692334189815</v>
+        <v>46223.57651084491</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I120" s="5">
         <v>46325</v>
       </c>
@@ -8475,13 +8552,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8491,25 +8568,27 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46164.6923315162</v>
+        <v>46223.57651017361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I121" s="9">
         <v>46325</v>
       </c>
@@ -8526,13 +8605,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8542,25 +8621,27 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46164.69232880787</v>
+        <v>46223.57650946759</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I122" s="5">
         <v>46325</v>
       </c>
@@ -8577,13 +8658,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8593,25 +8674,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46164.69232427083</v>
+        <v>46223.57650879629</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I123" s="9">
         <v>46325</v>
       </c>
@@ -8628,13 +8711,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8644,7 +8727,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8654,16 +8737,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8681,13 +8764,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8702,12 +8785,12 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8717,16 +8800,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8744,13 +8827,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8760,7 +8843,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8770,16 +8853,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8797,13 +8880,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8813,7 +8896,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8823,16 +8906,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8850,13 +8933,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8866,7 +8949,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -8876,16 +8959,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8903,13 +8986,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8919,7 +9002,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -8929,16 +9012,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -8956,13 +9039,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -8977,12 +9060,12 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -8992,16 +9075,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9019,13 +9102,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9035,7 +9118,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9045,16 +9128,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9072,13 +9155,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9088,7 +9171,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9098,16 +9181,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9125,13 +9208,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9141,7 +9224,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9151,16 +9234,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9178,13 +9261,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9194,7 +9277,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9204,7 +9287,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9228,7 +9311,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9241,7 +9324,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9251,16 +9334,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9278,13 +9361,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9299,12 +9382,12 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9314,7 +9397,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9341,13 +9424,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>
@@ -9362,7 +9445,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="366">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2550,7 +2553,7 @@
         <v>73</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I16" s="5">
         <v>46160</v>
@@ -2574,7 +2577,7 @@
         <v>55</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q16" s="5">
         <v>46160</v>
@@ -2594,7 +2597,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="9">
         <v>46162.791945289355</v>
@@ -2606,7 +2609,7 @@
         <v>46223.57568681713</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2615,7 +2618,7 @@
         <v>73</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I17" s="9">
         <v>46237</v>
@@ -2636,10 +2639,10 @@
         <v>63</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="9">
         <v>46237</v>
@@ -2659,7 +2662,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5">
         <v>46162.79194956018</v>
@@ -2671,7 +2674,7 @@
         <v>46223.57568328704</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2680,7 +2683,7 @@
         <v>73</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="5">
         <v>46237</v>
@@ -2701,10 +2704,10 @@
         <v>63</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46237</v>
@@ -2724,7 +2727,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>46162.79195284723</v>
@@ -2736,7 +2739,7 @@
         <v>46223.575679988426</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2745,7 +2748,7 @@
         <v>73</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I19" s="9">
         <v>46237</v>
@@ -2766,10 +2769,10 @@
         <v>63</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2789,7 +2792,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46162.79195601852</v>
@@ -2801,7 +2804,7 @@
         <v>46223.5756741088</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2810,7 +2813,7 @@
         <v>73</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I20" s="5">
         <v>46237</v>
@@ -2831,10 +2834,10 @@
         <v>63</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2854,7 +2857,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46162.79179634259</v>
@@ -2864,7 +2867,7 @@
         <v>46212.655108425926</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2888,7 +2891,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2903,7 +2906,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46162.79196002315</v>
@@ -2915,16 +2918,16 @@
         <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2942,13 +2945,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2968,7 +2971,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46162.791964375</v>
@@ -2980,16 +2983,16 @@
         <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
@@ -3007,13 +3010,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3024,12 +3027,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46162.79196883102</v>
@@ -3041,16 +3044,16 @@
         <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46167</v>
@@ -3068,13 +3071,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3085,12 +3088,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46162.79197329861</v>
@@ -3102,16 +3105,16 @@
         <v>46212.65520907407</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="9">
         <v>46162</v>
@@ -3129,13 +3132,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q25" s="9">
         <v>46162</v>
@@ -3155,7 +3158,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46162.791977500005</v>
@@ -3167,16 +3170,16 @@
         <v>46212.65503678241</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
@@ -3194,13 +3197,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3211,12 +3214,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46162.79198199074</v>
@@ -3228,16 +3231,16 @@
         <v>46212.65507065972</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I27" s="9">
         <v>46167</v>
@@ -3255,13 +3258,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3272,12 +3275,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46162.79198653935</v>
@@ -3289,16 +3292,16 @@
         <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3316,13 +3319,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q28" s="5">
         <v>46155</v>
@@ -3342,7 +3345,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46162.79199082176</v>
@@ -3354,16 +3357,16 @@
         <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3381,13 +3384,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>66</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3398,12 +3401,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46162.791995312495</v>
@@ -3415,16 +3418,16 @@
         <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3442,13 +3445,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3459,12 +3462,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46162.79199990741</v>
@@ -3476,16 +3479,16 @@
         <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3503,13 +3506,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3520,12 +3523,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46162.792004421295</v>
@@ -3537,16 +3540,16 @@
         <v>46209.81743660879</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I32" s="5">
         <v>46239</v>
@@ -3564,13 +3567,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q32" s="5">
         <v>46239</v>
@@ -3590,7 +3593,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3602,16 +3605,16 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
@@ -3629,13 +3632,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3646,12 +3649,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3663,16 +3666,16 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3690,13 +3693,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3707,12 +3710,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3724,16 +3727,16 @@
         <v>46209.81754938657</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I35" s="9">
         <v>46239</v>
@@ -3751,10 +3754,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3777,7 +3780,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3789,16 +3792,16 @@
         <v>46205.611504409724</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
@@ -3816,13 +3819,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3832,7 +3835,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3844,16 +3847,16 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I37" s="9">
         <v>46241</v>
@@ -3871,13 +3874,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3887,7 +3890,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3899,16 +3902,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3926,10 +3929,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3952,7 +3955,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3964,16 +3967,16 @@
         <v>46209.624517187505</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3991,13 +3994,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4007,7 +4010,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4019,16 +4022,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4046,13 +4049,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4062,7 +4065,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4072,16 +4075,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4099,10 +4102,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4115,7 +4118,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4127,16 +4130,16 @@
         <v>46205.612154409726</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I42" s="5">
         <v>46239</v>
@@ -4154,10 +4157,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4180,7 +4183,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4192,16 +4195,16 @@
         <v>46205.612088877315</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
@@ -4219,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4235,7 +4238,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4247,16 +4250,16 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4274,13 +4277,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4290,7 +4293,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4302,7 +4305,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4326,7 +4329,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4343,7 +4346,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4355,16 +4358,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4382,13 +4385,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4408,7 +4411,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4420,16 +4423,16 @@
         <v>46198.78268157407</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4447,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4473,7 +4476,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4485,16 +4488,16 @@
         <v>46198.7827322338</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4512,13 +4515,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4538,7 +4541,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4548,16 +4551,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4575,10 +4578,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4596,12 +4599,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4611,16 +4614,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4638,13 +4641,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4654,7 +4657,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4664,16 +4667,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4691,13 +4694,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4707,7 +4710,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4717,16 +4720,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4744,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4760,7 +4763,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4770,16 +4773,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4797,13 +4800,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4813,7 +4816,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4825,7 +4828,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4849,7 +4852,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4866,7 +4869,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4878,16 +4881,16 @@
         <v>46217.58769918981</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4905,13 +4908,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4931,7 +4934,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4943,16 +4946,16 @@
         <v>46217.58785994213</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4970,13 +4973,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4996,7 +4999,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -5008,16 +5011,16 @@
         <v>46217.58816130787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5035,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5061,7 +5064,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5073,16 +5076,16 @@
         <v>46217.588195752316</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5100,13 +5103,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5126,7 +5129,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5138,16 +5141,16 @@
         <v>46217.58828952546</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5165,13 +5168,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5191,7 +5194,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5203,16 +5206,16 @@
         <v>46217.58832047453</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5230,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5256,7 +5259,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5266,7 +5269,7 @@
         <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5290,7 +5293,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5303,7 +5306,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5313,16 +5316,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5340,13 +5343,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5361,12 +5364,12 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5376,16 +5379,16 @@
         <v>46217.58831070602</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5403,13 +5406,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5419,7 +5422,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5429,16 +5432,16 @@
         <v>46217.588311886575</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5456,13 +5459,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5472,7 +5475,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5482,16 +5485,16 @@
         <v>46217.58831295139</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5509,13 +5512,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5525,7 +5528,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5535,16 +5538,16 @@
         <v>46217.58831400463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5562,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5578,7 +5581,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5588,16 +5591,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5615,13 +5618,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5636,12 +5639,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5651,16 +5654,16 @@
         <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5678,13 +5681,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5694,7 +5697,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5704,16 +5707,16 @@
         <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5731,13 +5734,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5747,7 +5750,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5757,16 +5760,16 @@
         <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5784,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5800,7 +5803,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5810,16 +5813,16 @@
         <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5837,13 +5840,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5853,7 +5856,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5863,16 +5866,16 @@
         <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5890,13 +5893,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5911,12 +5914,12 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5926,16 +5929,16 @@
         <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5953,13 +5956,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5969,7 +5972,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -5979,16 +5982,16 @@
         <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -6006,13 +6009,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6022,7 +6025,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6032,16 +6035,16 @@
         <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6059,13 +6062,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6075,7 +6078,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6085,16 +6088,16 @@
         <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6112,13 +6115,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6128,7 +6131,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6138,7 +6141,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6162,7 +6165,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6177,7 +6180,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6189,16 +6192,16 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6216,13 +6219,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6242,7 +6245,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6254,16 +6257,16 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6281,13 +6284,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6307,7 +6310,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6319,16 +6322,16 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6346,13 +6349,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6372,7 +6375,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6382,16 +6385,16 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6409,13 +6412,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6435,7 +6438,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6445,7 +6448,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6469,7 +6472,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6482,7 +6485,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6492,7 +6495,7 @@
         <v>46223.57585706019</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6501,7 +6504,7 @@
         <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I83" s="9">
         <v>46293</v>
@@ -6519,13 +6522,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6540,12 +6543,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6555,7 +6558,7 @@
         <v>46223.575943020835</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6564,7 +6567,7 @@
         <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I84" s="5">
         <v>46293</v>
@@ -6582,10 +6585,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6598,7 +6601,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6608,7 +6611,7 @@
         <v>46223.57594232639</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6617,7 +6620,7 @@
         <v>73</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I85" s="9">
         <v>46293</v>
@@ -6635,10 +6638,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6651,7 +6654,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6661,7 +6664,7 @@
         <v>46223.57594163195</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6670,7 +6673,7 @@
         <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I86" s="5">
         <v>46293</v>
@@ -6688,13 +6691,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6704,7 +6707,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6714,7 +6717,7 @@
         <v>46223.57594097222</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6723,7 +6726,7 @@
         <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I87" s="9">
         <v>46293</v>
@@ -6741,13 +6744,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6757,7 +6760,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6767,7 +6770,7 @@
         <v>46223.575856435185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6776,7 +6779,7 @@
         <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I88" s="5">
         <v>46311</v>
@@ -6794,13 +6797,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6815,12 +6818,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6830,7 +6833,7 @@
         <v>46223.576037604165</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6839,7 +6842,7 @@
         <v>73</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I89" s="9">
         <v>46311</v>
@@ -6857,13 +6860,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6873,7 +6876,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6883,7 +6886,7 @@
         <v>46223.57603699074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6892,7 +6895,7 @@
         <v>73</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I90" s="5">
         <v>46311</v>
@@ -6910,13 +6913,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6926,7 +6929,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -6936,7 +6939,7 @@
         <v>46223.57603633102</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6945,7 +6948,7 @@
         <v>73</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I91" s="9">
         <v>46311</v>
@@ -6963,13 +6966,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6979,7 +6982,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -6989,7 +6992,7 @@
         <v>46223.576035659724</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6998,7 +7001,7 @@
         <v>73</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I92" s="5">
         <v>46311</v>
@@ -7016,13 +7019,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7032,7 +7035,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7042,7 +7045,7 @@
         <v>46223.57585581018</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7051,7 +7054,7 @@
         <v>73</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I93" s="9">
         <v>46315</v>
@@ -7069,13 +7072,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7090,12 +7093,12 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7105,7 +7108,7 @@
         <v>46223.5761230787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7114,7 +7117,7 @@
         <v>73</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I94" s="5">
         <v>46315</v>
@@ -7132,13 +7135,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7148,7 +7151,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7158,7 +7161,7 @@
         <v>46223.57612246528</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7167,7 +7170,7 @@
         <v>73</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I95" s="9">
         <v>46315</v>
@@ -7185,13 +7188,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7201,7 +7204,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7211,7 +7214,7 @@
         <v>46223.57612182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7220,7 +7223,7 @@
         <v>73</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I96" s="5">
         <v>46315</v>
@@ -7238,13 +7241,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7254,7 +7257,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7264,7 +7267,7 @@
         <v>46223.57612121528</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7273,7 +7276,7 @@
         <v>73</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I97" s="9">
         <v>46315</v>
@@ -7291,13 +7294,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7307,7 +7310,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7317,7 +7320,7 @@
         <v>46223.57585515046</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7326,7 +7329,7 @@
         <v>73</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I98" s="5">
         <v>46317</v>
@@ -7344,13 +7347,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7365,12 +7368,12 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7380,7 +7383,7 @@
         <v>46223.57621322917</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7389,7 +7392,7 @@
         <v>73</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I99" s="9">
         <v>46317</v>
@@ -7407,13 +7410,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7423,7 +7426,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7433,7 +7436,7 @@
         <v>46223.576212500004</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7442,7 +7445,7 @@
         <v>73</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I100" s="5">
         <v>46317</v>
@@ -7460,13 +7463,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7476,7 +7479,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7486,7 +7489,7 @@
         <v>46223.57621184028</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7495,7 +7498,7 @@
         <v>73</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I101" s="9">
         <v>46317</v>
@@ -7513,13 +7516,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7529,7 +7532,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7539,7 +7542,7 @@
         <v>46223.57621119213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7548,7 +7551,7 @@
         <v>73</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I102" s="5">
         <v>46317</v>
@@ -7566,13 +7569,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7582,7 +7585,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7592,7 +7595,7 @@
         <v>46223.57585453703</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7601,7 +7604,7 @@
         <v>73</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I103" s="9">
         <v>46321</v>
@@ -7619,13 +7622,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7640,12 +7643,12 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7655,7 +7658,7 @@
         <v>46223.57630975694</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7664,7 +7667,7 @@
         <v>73</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I104" s="5">
         <v>46321</v>
@@ -7682,13 +7685,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7698,7 +7701,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7708,7 +7711,7 @@
         <v>46223.57630916667</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7717,7 +7720,7 @@
         <v>73</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I105" s="9">
         <v>46321</v>
@@ -7735,13 +7738,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7751,7 +7754,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7761,7 +7764,7 @@
         <v>46223.57630858796</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7770,7 +7773,7 @@
         <v>73</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I106" s="5">
         <v>46321</v>
@@ -7788,13 +7791,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7804,7 +7807,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7814,7 +7817,7 @@
         <v>46223.57630797454</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7823,7 +7826,7 @@
         <v>73</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I107" s="9">
         <v>46321</v>
@@ -7841,13 +7844,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7857,7 +7860,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7867,7 +7870,7 @@
         <v>46223.57585388889</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7876,7 +7879,7 @@
         <v>73</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7892,13 +7895,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7913,12 +7916,12 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -7928,7 +7931,7 @@
         <v>46223.5763915162</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7937,7 +7940,7 @@
         <v>73</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I109" s="9">
         <v>46323</v>
@@ -7955,13 +7958,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7971,7 +7974,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -7981,7 +7984,7 @@
         <v>46223.576390856484</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7990,7 +7993,7 @@
         <v>73</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I110" s="5">
         <v>46323</v>
@@ -8008,13 +8011,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8024,7 +8027,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8034,7 +8037,7 @@
         <v>46223.57639018519</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8043,7 +8046,7 @@
         <v>73</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I111" s="9">
         <v>46323</v>
@@ -8061,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8077,7 +8080,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8087,7 +8090,7 @@
         <v>46223.57638950231</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8096,7 +8099,7 @@
         <v>73</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I112" s="5">
         <v>46323</v>
@@ -8114,13 +8117,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8130,7 +8133,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8140,7 +8143,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8164,7 +8167,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8177,7 +8180,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8187,16 +8190,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8214,13 +8217,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8235,12 +8238,12 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8250,16 +8253,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8277,13 +8280,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8293,7 +8296,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8303,16 +8306,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8330,13 +8333,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8346,7 +8349,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8356,16 +8359,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8383,13 +8386,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8399,7 +8402,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8409,16 +8412,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8436,13 +8439,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8452,7 +8455,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8462,7 +8465,7 @@
         <v>46223.57655457176</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8471,7 +8474,7 @@
         <v>73</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I119" s="9">
         <v>46325</v>
@@ -8489,13 +8492,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8510,12 +8513,12 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8525,7 +8528,7 @@
         <v>46223.57651084491</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8534,7 +8537,7 @@
         <v>73</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I120" s="5">
         <v>46325</v>
@@ -8552,13 +8555,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8568,7 +8571,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8578,7 +8581,7 @@
         <v>46223.57651017361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8587,7 +8590,7 @@
         <v>73</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I121" s="9">
         <v>46325</v>
@@ -8605,13 +8608,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8621,7 +8624,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8631,7 +8634,7 @@
         <v>46223.57650946759</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8640,7 +8643,7 @@
         <v>73</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I122" s="5">
         <v>46325</v>
@@ -8658,13 +8661,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8674,7 +8677,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8684,7 +8687,7 @@
         <v>46223.57650879629</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8693,7 +8696,7 @@
         <v>73</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I123" s="9">
         <v>46325</v>
@@ -8711,13 +8714,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8727,7 +8730,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8737,16 +8740,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8764,13 +8767,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8785,12 +8788,12 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8800,16 +8803,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8827,13 +8830,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8843,7 +8846,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8853,16 +8856,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8880,13 +8883,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8896,7 +8899,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8906,16 +8909,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8933,13 +8936,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8949,7 +8952,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -8959,16 +8962,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8986,13 +8989,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9002,7 +9005,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9012,16 +9015,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9039,13 +9042,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9060,12 +9063,12 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9075,16 +9078,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9102,13 +9105,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9118,7 +9121,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9128,16 +9131,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9155,13 +9158,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9171,7 +9174,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9181,16 +9184,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9208,13 +9211,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9224,7 +9227,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9234,16 +9237,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9261,13 +9264,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9277,7 +9280,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9287,7 +9290,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9311,7 +9314,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9324,7 +9327,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9334,16 +9337,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9361,13 +9364,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9382,12 +9385,12 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9397,7 +9400,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9424,13 +9427,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>
@@ -9445,7 +9448,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="367">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214995680437154</t>
@@ -4420,7 +4423,7 @@
         <v>46198.78266340277</v>
       </c>
       <c r="D47" s="9">
-        <v>46198.78268157407</v>
+        <v>46226.18788856482</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>175</v>
@@ -4464,8 +4467,8 @@
       <c r="R47" s="9">
         <v>46233</v>
       </c>
-      <c r="S47" s="7" t="s">
-        <v>53</v>
+      <c r="S47" s="12" t="s">
+        <v>178</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4476,7 +4479,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4494,10 +4497,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4521,7 +4524,7 @@
         <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4541,7 +4544,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4551,16 +4554,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4581,7 +4584,7 @@
         <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4604,7 +4607,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4614,16 +4617,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4641,13 +4644,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4657,7 +4660,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4667,16 +4670,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4694,13 +4697,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4710,7 +4713,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4720,16 +4723,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4747,13 +4750,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4763,7 +4766,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4773,16 +4776,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4800,13 +4803,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4816,7 +4819,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4828,7 +4831,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4852,7 +4855,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4869,7 +4872,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4881,16 +4884,16 @@
         <v>46217.58769918981</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4908,13 +4911,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>134</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4934,7 +4937,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4946,7 +4949,7 @@
         <v>46217.58785994213</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4973,13 +4976,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4999,7 +5002,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -5011,16 +5014,16 @@
         <v>46217.58816130787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5038,13 +5041,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>142</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5064,7 +5067,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5076,7 +5079,7 @@
         <v>46217.588195752316</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5103,13 +5106,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5129,7 +5132,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5141,16 +5144,16 @@
         <v>46217.58828952546</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5168,13 +5171,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>164</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5194,7 +5197,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5206,7 +5209,7 @@
         <v>46217.58832047453</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5233,13 +5236,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5259,7 +5262,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5269,7 +5272,7 @@
         <v>46164.66898752315</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5293,7 +5296,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5306,7 +5309,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5316,16 +5319,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5343,13 +5346,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5369,7 +5372,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5379,16 +5382,16 @@
         <v>46217.58831070602</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5406,13 +5409,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5422,7 +5425,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5432,16 +5435,16 @@
         <v>46217.588311886575</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5459,13 +5462,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5475,7 +5478,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5485,16 +5488,16 @@
         <v>46217.58831295139</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5512,13 +5515,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5528,7 +5531,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5538,16 +5541,16 @@
         <v>46217.58831400463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5565,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5581,7 +5584,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5591,16 +5594,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5618,13 +5621,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5654,16 +5657,16 @@
         <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5681,13 +5684,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5697,7 +5700,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5707,16 +5710,16 @@
         <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5734,13 +5737,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5750,7 +5753,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5760,16 +5763,16 @@
         <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5787,13 +5790,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5803,7 +5806,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5813,16 +5816,16 @@
         <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5840,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5856,7 +5859,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5866,7 +5869,7 @@
         <v>46164.690976377315</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5893,13 +5896,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5919,7 +5922,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5929,7 +5932,7 @@
         <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5956,13 +5959,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5972,7 +5975,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -5982,7 +5985,7 @@
         <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6009,13 +6012,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6025,7 +6028,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6035,7 +6038,7 @@
         <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6062,13 +6065,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6078,7 +6081,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6088,7 +6091,7 @@
         <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6115,13 +6118,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6131,7 +6134,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6141,7 +6144,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6165,7 +6168,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6180,7 +6183,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6192,16 +6195,16 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6219,13 +6222,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6245,7 +6248,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6257,16 +6260,16 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6284,13 +6287,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6310,7 +6313,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6322,16 +6325,16 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6349,13 +6352,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6375,7 +6378,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6385,16 +6388,16 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6412,13 +6415,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6438,7 +6441,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6448,7 +6451,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6472,7 +6475,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6485,7 +6488,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6495,7 +6498,7 @@
         <v>46223.57585706019</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6522,13 +6525,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6548,7 +6551,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6558,7 +6561,7 @@
         <v>46223.575943020835</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6585,10 +6588,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6601,7 +6604,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6611,7 +6614,7 @@
         <v>46223.57594232639</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6638,10 +6641,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6654,7 +6657,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6664,7 +6667,7 @@
         <v>46223.57594163195</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6691,13 +6694,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6707,7 +6710,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6717,7 +6720,7 @@
         <v>46223.57594097222</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6744,13 +6747,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6760,7 +6763,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6770,7 +6773,7 @@
         <v>46223.575856435185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6797,13 +6800,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6823,7 +6826,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6833,7 +6836,7 @@
         <v>46223.576037604165</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6860,13 +6863,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6876,7 +6879,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6886,7 +6889,7 @@
         <v>46223.57603699074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6913,13 +6916,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6929,7 +6932,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -6939,7 +6942,7 @@
         <v>46223.57603633102</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6966,13 +6969,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6982,7 +6985,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -6992,7 +6995,7 @@
         <v>46223.576035659724</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7019,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7035,7 +7038,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7045,7 +7048,7 @@
         <v>46223.57585581018</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7072,13 +7075,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7098,7 +7101,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7108,7 +7111,7 @@
         <v>46223.5761230787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7135,13 +7138,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7151,7 +7154,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7161,7 +7164,7 @@
         <v>46223.57612246528</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7188,13 +7191,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7204,7 +7207,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7214,7 +7217,7 @@
         <v>46223.57612182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7241,13 +7244,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7257,7 +7260,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7267,7 +7270,7 @@
         <v>46223.57612121528</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7294,13 +7297,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7310,7 +7313,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7320,7 +7323,7 @@
         <v>46223.57585515046</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7347,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7373,7 +7376,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7383,7 +7386,7 @@
         <v>46223.57621322917</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7410,13 +7413,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7426,7 +7429,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7436,7 +7439,7 @@
         <v>46223.576212500004</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7463,13 +7466,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7479,7 +7482,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7489,7 +7492,7 @@
         <v>46223.57621184028</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7516,13 +7519,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7532,7 +7535,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7542,7 +7545,7 @@
         <v>46223.57621119213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7569,13 +7572,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7585,7 +7588,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7595,7 +7598,7 @@
         <v>46223.57585453703</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7622,13 +7625,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7648,7 +7651,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7658,7 +7661,7 @@
         <v>46223.57630975694</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7685,13 +7688,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7701,7 +7704,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7711,7 +7714,7 @@
         <v>46223.57630916667</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7738,13 +7741,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7754,7 +7757,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7764,7 +7767,7 @@
         <v>46223.57630858796</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7791,13 +7794,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7807,7 +7810,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7817,7 +7820,7 @@
         <v>46223.57630797454</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7844,13 +7847,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7860,7 +7863,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7870,7 +7873,7 @@
         <v>46223.57585388889</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7895,13 +7898,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7921,7 +7924,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -7931,7 +7934,7 @@
         <v>46223.5763915162</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7958,13 +7961,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7974,7 +7977,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -7984,7 +7987,7 @@
         <v>46223.576390856484</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8011,13 +8014,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8027,7 +8030,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8037,7 +8040,7 @@
         <v>46223.57639018519</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8064,13 +8067,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8080,7 +8083,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8090,7 +8093,7 @@
         <v>46223.57638950231</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8117,13 +8120,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8133,7 +8136,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8143,7 +8146,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8167,7 +8170,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8180,7 +8183,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8190,16 +8193,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8217,13 +8220,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8243,7 +8246,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8253,16 +8256,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8280,13 +8283,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8296,7 +8299,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8306,16 +8309,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8333,13 +8336,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8349,7 +8352,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8359,16 +8362,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8386,13 +8389,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8402,7 +8405,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8412,16 +8415,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8439,13 +8442,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8455,7 +8458,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8465,7 +8468,7 @@
         <v>46223.57655457176</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8492,13 +8495,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8518,7 +8521,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8528,7 +8531,7 @@
         <v>46223.57651084491</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8555,13 +8558,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8571,7 +8574,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8581,7 +8584,7 @@
         <v>46223.57651017361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8608,13 +8611,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8624,7 +8627,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8634,7 +8637,7 @@
         <v>46223.57650946759</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8661,13 +8664,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8677,7 +8680,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8687,7 +8690,7 @@
         <v>46223.57650879629</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8714,13 +8717,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8730,7 +8733,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8740,16 +8743,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8767,13 +8770,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8793,7 +8796,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8803,16 +8806,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8830,13 +8833,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8846,7 +8849,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8856,16 +8859,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8883,13 +8886,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8899,7 +8902,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8909,16 +8912,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8936,13 +8939,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8952,7 +8955,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -8962,16 +8965,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8989,13 +8992,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9005,7 +9008,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9015,16 +9018,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9042,13 +9045,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9068,7 +9071,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9078,16 +9081,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9105,13 +9108,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9121,7 +9124,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9131,16 +9134,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9158,13 +9161,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9174,7 +9177,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9184,16 +9187,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9211,13 +9214,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9227,7 +9230,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9237,16 +9240,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9264,13 +9267,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9280,7 +9283,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9290,7 +9293,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9314,7 +9317,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9327,7 +9330,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9337,16 +9340,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9364,13 +9367,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9390,7 +9393,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9400,7 +9403,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9427,13 +9430,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -4488,7 +4488,7 @@
         <v>46198.78271623843</v>
       </c>
       <c r="D48" s="5">
-        <v>46198.7827322338</v>
+        <v>46227.17694643518</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>78</v>
@@ -4532,8 +4532,8 @@
       <c r="R48" s="5">
         <v>46234</v>
       </c>
-      <c r="S48" s="7" t="s">
-        <v>53</v>
+      <c r="S48" s="12" t="s">
+        <v>178</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46164.66898752315</v>
+        <v>46226.7241608912</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5864,9 +5864,11 @@
       <c r="B72" s="5">
         <v>46162.79241414352</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46226.72415461806</v>
+      </c>
       <c r="D72" s="5">
-        <v>46164.690976377315</v>
+        <v>46226.72417094908</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>240</v>
@@ -5914,10 +5916,10 @@
         <v>53</v>
       </c>
       <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U72" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -313,6 +313,9 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214982558032165</t>
   </si>
   <si>
@@ -605,9 +608,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214995680437154</t>
@@ -2609,7 +2609,7 @@
         <v>46204.89537108796</v>
       </c>
       <c r="D17" s="9">
-        <v>46223.57568681713</v>
+        <v>46231.19123434028</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>77</v>
@@ -2653,8 +2653,8 @@
       <c r="R17" s="9">
         <v>46238</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>53</v>
+      <c r="S17" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="T17" s="10">
         <v>1</v>
@@ -2665,7 +2665,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="5">
         <v>46162.79194956018</v>
@@ -2674,10 +2674,10 @@
         <v>46204.89540233796</v>
       </c>
       <c r="D18" s="5">
-        <v>46223.57568328704</v>
+        <v>46231.19123302083</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2710,7 +2710,7 @@
         <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="5">
         <v>46237</v>
@@ -2718,8 +2718,8 @@
       <c r="R18" s="5">
         <v>46238</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>53</v>
+      <c r="S18" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" s="9">
         <v>46162.79195284723</v>
@@ -2739,10 +2739,10 @@
         <v>46204.898560891204</v>
       </c>
       <c r="D19" s="9">
-        <v>46223.575679988426</v>
+        <v>46231.191234363425</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2775,7 +2775,7 @@
         <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2783,8 +2783,8 @@
       <c r="R19" s="9">
         <v>46238</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>53</v>
+      <c r="S19" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5">
         <v>46162.79195601852</v>
@@ -2804,10 +2804,10 @@
         <v>46204.8976750463</v>
       </c>
       <c r="D20" s="5">
-        <v>46223.5756741088</v>
+        <v>46231.19123306713</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2840,7 +2840,7 @@
         <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2848,8 +2848,8 @@
       <c r="R20" s="5">
         <v>46238</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>53</v>
+      <c r="S20" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" s="9">
         <v>46162.79179634259</v>
@@ -2870,7 +2870,7 @@
         <v>46212.655108425926</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2894,7 +2894,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46162.79196002315</v>
@@ -2921,16 +2921,16 @@
         <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2948,13 +2948,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="9">
         <v>46162.791964375</v>
@@ -2986,16 +2986,16 @@
         <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
@@ -3013,13 +3013,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3030,12 +3030,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46162.79196883102</v>
@@ -3047,16 +3047,16 @@
         <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46167</v>
@@ -3074,13 +3074,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3091,12 +3091,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46162.79197329861</v>
@@ -3108,16 +3108,16 @@
         <v>46212.65520907407</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46162</v>
@@ -3135,13 +3135,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q25" s="9">
         <v>46162</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46162.791977500005</v>
@@ -3173,16 +3173,16 @@
         <v>46212.65503678241</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
@@ -3200,13 +3200,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3217,12 +3217,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46162.79198199074</v>
@@ -3234,16 +3234,16 @@
         <v>46212.65507065972</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46167</v>
@@ -3261,13 +3261,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3278,12 +3278,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46162.79198653935</v>
@@ -3295,16 +3295,16 @@
         <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3322,13 +3322,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q28" s="5">
         <v>46155</v>
@@ -3348,7 +3348,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46162.79199082176</v>
@@ -3360,16 +3360,16 @@
         <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3387,13 +3387,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>66</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3404,12 +3404,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46162.791995312495</v>
@@ -3421,16 +3421,16 @@
         <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3448,13 +3448,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3465,12 +3465,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46162.79199990741</v>
@@ -3482,16 +3482,16 @@
         <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3509,13 +3509,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3526,12 +3526,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46162.792004421295</v>
@@ -3543,16 +3543,16 @@
         <v>46209.81743660879</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I32" s="5">
         <v>46239</v>
@@ -3570,13 +3570,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q32" s="5">
         <v>46239</v>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3608,16 +3608,16 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
@@ -3635,13 +3635,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>77</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3652,12 +3652,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3669,16 +3669,16 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3696,13 +3696,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3713,12 +3713,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3730,16 +3730,16 @@
         <v>46209.81754938657</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="9">
         <v>46239</v>
@@ -3757,10 +3757,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3795,16 +3795,16 @@
         <v>46205.611504409724</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
@@ -3822,13 +3822,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3850,16 +3850,16 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="9">
         <v>46241</v>
@@ -3877,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3905,16 +3905,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3932,10 +3932,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3970,16 +3970,16 @@
         <v>46209.624517187505</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3997,13 +3997,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4013,7 +4013,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4025,16 +4025,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4052,13 +4052,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4078,16 +4078,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4105,10 +4105,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4133,16 +4133,16 @@
         <v>46205.612154409726</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I42" s="5">
         <v>46239</v>
@@ -4160,10 +4160,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4198,16 +4198,16 @@
         <v>46205.612088877315</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
@@ -4225,13 +4225,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4241,7 +4241,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4253,16 +4253,16 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4280,13 +4280,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4308,7 +4308,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4332,7 +4332,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4349,7 +4349,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4361,16 +4361,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4388,13 +4388,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4426,16 +4426,16 @@
         <v>46226.18788856482</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4453,13 +4453,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4468,7 +4468,7 @@
         <v>46233</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>
@@ -4518,10 +4518,10 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>182</v>
@@ -4533,7 +4533,7 @@
         <v>46234</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>
@@ -4581,7 +4581,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>187</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4914,7 +4914,7 @@
         <v>195</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>201</v>
@@ -4955,10 +4955,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -5044,7 +5044,7 @@
         <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>207</v>
@@ -5085,10 +5085,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5174,7 +5174,7 @@
         <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>212</v>
@@ -5215,10 +5215,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5367,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5642,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5877,10 +5877,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5940,10 +5940,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5993,10 +5993,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -6046,10 +6046,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6099,10 +6099,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6227,7 +6227,7 @@
         <v>195</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>252</v>
@@ -6292,7 +6292,7 @@
         <v>195</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>255</v>
@@ -6357,7 +6357,7 @@
         <v>195</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>204</v>
@@ -6420,7 +6420,7 @@
         <v>195</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>260</v>
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6823,7 +6823,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7098,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7373,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7648,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7921,7 +7921,7 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8243,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8518,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8793,7 +8793,7 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -9068,7 +9068,7 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -9390,7 +9390,7 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9453,7 +9453,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -4423,7 +4423,7 @@
         <v>46198.78266340277</v>
       </c>
       <c r="D47" s="9">
-        <v>46226.18788856482</v>
+        <v>46234.17771361111</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4467,8 +4467,8 @@
       <c r="R47" s="9">
         <v>46233</v>
       </c>
-      <c r="S47" s="12" t="s">
-        <v>80</v>
+      <c r="S47" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T47" s="10">
         <v>1</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -4488,7 +4488,7 @@
         <v>46198.78271623843</v>
       </c>
       <c r="D48" s="5">
-        <v>46227.17694643518</v>
+        <v>46235.18067081019</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>78</v>
@@ -4532,8 +4532,8 @@
       <c r="R48" s="5">
         <v>46234</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>80</v>
+      <c r="S48" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T48" s="6">
         <v>1</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="366">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -311,9 +311,6 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales corte Laser</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214982558032165</t>
@@ -2609,7 +2606,7 @@
         <v>46204.89537108796</v>
       </c>
       <c r="D17" s="9">
-        <v>46231.19123434028</v>
+        <v>46239.20109123843</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>77</v>
@@ -2653,8 +2650,8 @@
       <c r="R17" s="9">
         <v>46238</v>
       </c>
-      <c r="S17" s="12" t="s">
-        <v>80</v>
+      <c r="S17" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T17" s="10">
         <v>1</v>
@@ -2665,7 +2662,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5">
         <v>46162.79194956018</v>
@@ -2674,10 +2671,10 @@
         <v>46204.89540233796</v>
       </c>
       <c r="D18" s="5">
-        <v>46231.19123302083</v>
+        <v>46239.20109125</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2710,7 +2707,7 @@
         <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="5">
         <v>46237</v>
@@ -2718,8 +2715,8 @@
       <c r="R18" s="5">
         <v>46238</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>80</v>
+      <c r="S18" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2730,7 +2727,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="9">
         <v>46162.79195284723</v>
@@ -2739,10 +2736,10 @@
         <v>46204.898560891204</v>
       </c>
       <c r="D19" s="9">
-        <v>46231.191234363425</v>
+        <v>46239.20109165509</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2775,7 +2772,7 @@
         <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="9">
         <v>46237</v>
@@ -2783,8 +2780,8 @@
       <c r="R19" s="9">
         <v>46238</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>80</v>
+      <c r="S19" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2795,7 +2792,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46162.79195601852</v>
@@ -2804,10 +2801,10 @@
         <v>46204.8976750463</v>
       </c>
       <c r="D20" s="5">
-        <v>46231.19123306713</v>
+        <v>46239.20109153935</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2840,7 +2837,7 @@
         <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46237</v>
@@ -2848,8 +2845,8 @@
       <c r="R20" s="5">
         <v>46238</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>80</v>
+      <c r="S20" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2860,7 +2857,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9">
         <v>46162.79179634259</v>
@@ -2870,7 +2867,7 @@
         <v>46212.655108425926</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>25</v>
@@ -2894,7 +2891,7 @@
         <v>26</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>26</v>
@@ -2909,7 +2906,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46162.79196002315</v>
@@ -2921,16 +2918,16 @@
         <v>46198.68596357639</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2948,13 +2945,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2974,7 +2971,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" s="9">
         <v>46162.791964375</v>
@@ -2986,16 +2983,16 @@
         <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I23" s="9">
         <v>46162</v>
@@ -3013,13 +3010,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3030,12 +3027,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46162.79196883102</v>
@@ -3047,16 +3044,16 @@
         <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46167</v>
@@ -3074,13 +3071,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3091,12 +3088,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
         <v>46162.79197329861</v>
@@ -3108,16 +3105,16 @@
         <v>46212.65520907407</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I25" s="9">
         <v>46162</v>
@@ -3135,13 +3132,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q25" s="9">
         <v>46162</v>
@@ -3161,7 +3158,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46162.791977500005</v>
@@ -3173,16 +3170,16 @@
         <v>46212.65503678241</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I26" s="5">
         <v>46162</v>
@@ -3200,13 +3197,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3217,12 +3214,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46162.79198199074</v>
@@ -3234,16 +3231,16 @@
         <v>46212.65507065972</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I27" s="9">
         <v>46167</v>
@@ -3261,13 +3258,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3278,12 +3275,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46162.79198653935</v>
@@ -3295,16 +3292,16 @@
         <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46155</v>
@@ -3322,13 +3319,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q28" s="5">
         <v>46155</v>
@@ -3348,7 +3345,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46162.79199082176</v>
@@ -3360,16 +3357,16 @@
         <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46155</v>
@@ -3387,13 +3384,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>66</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3404,12 +3401,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46162.791995312495</v>
@@ -3421,16 +3418,16 @@
         <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3448,13 +3445,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3465,12 +3462,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46162.79199990741</v>
@@ -3482,16 +3479,16 @@
         <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46176</v>
@@ -3509,13 +3506,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3526,12 +3523,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46162.792004421295</v>
@@ -3543,16 +3540,16 @@
         <v>46209.81743660879</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I32" s="5">
         <v>46239</v>
@@ -3570,13 +3567,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q32" s="5">
         <v>46239</v>
@@ -3596,7 +3593,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3608,16 +3605,16 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
@@ -3635,13 +3632,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>77</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3652,12 +3649,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3669,16 +3666,16 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3696,13 +3693,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3713,12 +3710,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3730,16 +3727,16 @@
         <v>46209.81754938657</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="I35" s="9">
         <v>46239</v>
@@ -3757,10 +3754,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3783,7 +3780,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3795,16 +3792,16 @@
         <v>46205.611504409724</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
@@ -3822,13 +3819,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3838,7 +3835,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3850,16 +3847,16 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="I37" s="9">
         <v>46241</v>
@@ -3877,13 +3874,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3893,7 +3890,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3905,16 +3902,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3932,10 +3929,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3958,7 +3955,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3970,16 +3967,16 @@
         <v>46209.624517187505</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3997,13 +3994,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4013,7 +4010,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4025,16 +4022,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4052,13 +4049,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4068,7 +4065,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4078,16 +4075,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="H41" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4105,10 +4102,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4121,7 +4118,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4133,16 +4130,16 @@
         <v>46205.612154409726</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I42" s="5">
         <v>46239</v>
@@ -4160,10 +4157,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4186,7 +4183,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4198,16 +4195,16 @@
         <v>46205.612088877315</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>129</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
@@ -4225,13 +4222,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4241,7 +4238,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4253,16 +4250,16 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4280,13 +4277,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4296,7 +4293,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4308,7 +4305,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4332,7 +4329,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4349,7 +4346,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4361,16 +4358,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4388,13 +4385,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4414,7 +4411,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4426,16 +4423,16 @@
         <v>46234.17771361111</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4453,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4479,7 +4476,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4497,10 +4494,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4518,13 +4515,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4544,7 +4541,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4554,16 +4551,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4581,10 +4578,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4602,12 +4599,12 @@
         <v>0</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4617,16 +4614,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4644,13 +4641,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4660,7 +4657,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4670,16 +4667,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4697,13 +4694,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4713,7 +4710,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4723,16 +4720,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4750,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4766,7 +4763,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4776,16 +4773,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4803,13 +4800,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4819,7 +4816,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4831,7 +4828,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4855,7 +4852,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4872,7 +4869,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4884,16 +4881,16 @@
         <v>46217.58769918981</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4911,13 +4908,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4937,7 +4934,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4949,16 +4946,16 @@
         <v>46217.58785994213</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4976,13 +4973,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -5002,7 +4999,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -5014,16 +5011,16 @@
         <v>46217.58816130787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5041,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5067,7 +5064,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5079,16 +5076,16 @@
         <v>46217.588195752316</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5106,13 +5103,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5132,7 +5129,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5144,16 +5141,16 @@
         <v>46217.58828952546</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5171,13 +5168,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5197,7 +5194,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5209,16 +5206,16 @@
         <v>46217.58832047453</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5236,13 +5233,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5262,7 +5259,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5272,7 +5269,7 @@
         <v>46226.7241608912</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5296,7 +5293,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5309,7 +5306,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5319,16 +5316,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5346,13 +5343,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5367,12 +5364,12 @@
         <v>0</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5382,16 +5379,16 @@
         <v>46217.58831070602</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5409,13 +5406,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5425,7 +5422,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5435,16 +5432,16 @@
         <v>46217.588311886575</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5462,13 +5459,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5478,7 +5475,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5488,16 +5485,16 @@
         <v>46217.58831295139</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5515,13 +5512,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5531,7 +5528,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5541,16 +5538,16 @@
         <v>46217.58831400463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5568,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5584,7 +5581,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5594,16 +5591,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5621,13 +5618,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5642,12 +5639,12 @@
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5657,16 +5654,16 @@
         <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5684,13 +5681,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5700,7 +5697,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5710,16 +5707,16 @@
         <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5737,13 +5734,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5753,7 +5750,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5763,16 +5760,16 @@
         <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5790,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5806,7 +5803,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5816,16 +5813,16 @@
         <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5843,13 +5840,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5859,7 +5856,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5871,16 +5868,16 @@
         <v>46226.72417094908</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5898,13 +5895,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5924,7 +5921,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5934,16 +5931,16 @@
         <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5961,13 +5958,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5977,7 +5974,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -5987,16 +5984,16 @@
         <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -6014,13 +6011,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6030,7 +6027,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6040,16 +6037,16 @@
         <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6067,13 +6064,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6083,7 +6080,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6093,16 +6090,16 @@
         <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6120,13 +6117,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6136,7 +6133,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6146,7 +6143,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6170,7 +6167,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6185,7 +6182,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6197,16 +6194,16 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6224,13 +6221,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6250,7 +6247,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6262,16 +6259,16 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6289,13 +6286,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6315,7 +6312,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6327,16 +6324,16 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6354,13 +6351,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6380,7 +6377,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6390,16 +6387,16 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6417,13 +6414,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6443,7 +6440,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6453,7 +6450,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6477,7 +6474,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6490,7 +6487,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6500,7 +6497,7 @@
         <v>46223.57585706019</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6527,13 +6524,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6548,12 +6545,12 @@
         <v>0</v>
       </c>
       <c r="U83" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6563,7 +6560,7 @@
         <v>46223.575943020835</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6590,10 +6587,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6606,7 +6603,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6616,7 +6613,7 @@
         <v>46223.57594232639</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6643,10 +6640,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6659,7 +6656,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6669,7 +6666,7 @@
         <v>46223.57594163195</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6696,13 +6693,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6712,7 +6709,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6722,7 +6719,7 @@
         <v>46223.57594097222</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6749,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6765,7 +6762,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6775,7 +6772,7 @@
         <v>46223.575856435185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6802,13 +6799,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6823,12 +6820,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6838,7 +6835,7 @@
         <v>46223.576037604165</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6865,13 +6862,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6881,7 +6878,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6891,7 +6888,7 @@
         <v>46223.57603699074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6918,13 +6915,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6934,7 +6931,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -6944,7 +6941,7 @@
         <v>46223.57603633102</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6971,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6987,7 +6984,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -6997,7 +6994,7 @@
         <v>46223.576035659724</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7024,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7040,7 +7037,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7050,7 +7047,7 @@
         <v>46223.57585581018</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7077,13 +7074,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7098,12 +7095,12 @@
         <v>0</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7113,7 +7110,7 @@
         <v>46223.5761230787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7140,13 +7137,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7156,7 +7153,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7166,7 +7163,7 @@
         <v>46223.57612246528</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7193,13 +7190,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7209,7 +7206,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7219,7 +7216,7 @@
         <v>46223.57612182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7246,13 +7243,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7262,7 +7259,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7272,7 +7269,7 @@
         <v>46223.57612121528</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7299,13 +7296,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O97" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7315,7 +7312,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7325,7 +7322,7 @@
         <v>46223.57585515046</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7352,13 +7349,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7373,12 +7370,12 @@
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7388,7 +7385,7 @@
         <v>46223.57621322917</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7415,13 +7412,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O99" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P99" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P99" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7431,7 +7428,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7441,7 +7438,7 @@
         <v>46223.576212500004</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7468,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7484,7 +7481,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7494,7 +7491,7 @@
         <v>46223.57621184028</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7521,13 +7518,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7537,7 +7534,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7547,7 +7544,7 @@
         <v>46223.57621119213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7574,13 +7571,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7590,7 +7587,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7600,7 +7597,7 @@
         <v>46223.57585453703</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7627,13 +7624,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7648,12 +7645,12 @@
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7663,7 +7660,7 @@
         <v>46223.57630975694</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7690,13 +7687,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7706,7 +7703,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7716,7 +7713,7 @@
         <v>46223.57630916667</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7743,13 +7740,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7759,7 +7756,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7769,7 +7766,7 @@
         <v>46223.57630858796</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7796,13 +7793,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7812,7 +7809,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7822,7 +7819,7 @@
         <v>46223.57630797454</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7849,13 +7846,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7865,7 +7862,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7875,7 +7872,7 @@
         <v>46223.57585388889</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7900,13 +7897,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7921,12 +7918,12 @@
         <v>0</v>
       </c>
       <c r="U108" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -7936,7 +7933,7 @@
         <v>46223.5763915162</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7963,13 +7960,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7979,7 +7976,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -7989,7 +7986,7 @@
         <v>46223.576390856484</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8016,13 +8013,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8032,7 +8029,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8042,7 +8039,7 @@
         <v>46223.57639018519</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8069,13 +8066,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8085,7 +8082,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8095,7 +8092,7 @@
         <v>46223.57638950231</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8122,13 +8119,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8138,7 +8135,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8148,7 +8145,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8172,7 +8169,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8185,7 +8182,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8195,16 +8192,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G114" s="6" t="s">
+      <c r="H114" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8222,13 +8219,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8243,12 +8240,12 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8258,16 +8255,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8285,13 +8282,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8301,7 +8298,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8311,16 +8308,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8338,13 +8335,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8354,7 +8351,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8364,16 +8361,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8391,13 +8388,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8407,7 +8404,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8417,16 +8414,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8444,13 +8441,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8460,7 +8457,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8470,7 +8467,7 @@
         <v>46223.57655457176</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8497,13 +8494,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8518,12 +8515,12 @@
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8533,7 +8530,7 @@
         <v>46223.57651084491</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8560,13 +8557,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8576,7 +8573,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8586,7 +8583,7 @@
         <v>46223.57651017361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8613,13 +8610,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8629,7 +8626,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8639,7 +8636,7 @@
         <v>46223.57650946759</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8666,13 +8663,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8682,7 +8679,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8692,7 +8689,7 @@
         <v>46223.57650879629</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8719,13 +8716,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8735,7 +8732,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8745,16 +8742,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8772,13 +8769,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8793,12 +8790,12 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8808,16 +8805,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8835,13 +8832,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8851,7 +8848,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8861,16 +8858,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8888,13 +8885,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8904,7 +8901,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8914,16 +8911,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8941,13 +8938,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8957,7 +8954,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -8967,16 +8964,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8994,13 +8991,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9010,7 +9007,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9020,16 +9017,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9047,13 +9044,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9068,12 +9065,12 @@
         <v>0</v>
       </c>
       <c r="U129" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9083,16 +9080,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9110,13 +9107,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9126,7 +9123,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9136,16 +9133,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9163,13 +9160,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9179,7 +9176,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9189,16 +9186,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9216,13 +9213,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9232,7 +9229,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9242,16 +9239,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9269,13 +9266,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9285,7 +9282,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9295,7 +9292,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9319,7 +9316,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9332,7 +9329,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9342,16 +9339,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="F135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="10" t="s">
+      <c r="H135" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>364</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9369,13 +9366,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9390,12 +9387,12 @@
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9405,7 +9402,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9432,13 +9429,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>
@@ -9453,7 +9450,7 @@
         <v>0</v>
       </c>
       <c r="U136" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="367">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -461,6 +461,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC materiales corte Laser,Fabricacion Corte Laser </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214982558049172</t>
@@ -3537,7 +3540,7 @@
         <v>46209.817423472225</v>
       </c>
       <c r="D32" s="5">
-        <v>46209.81743660879</v>
+        <v>46244.19278438657</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3581,8 +3584,8 @@
       <c r="R32" s="5">
         <v>46251</v>
       </c>
-      <c r="S32" s="7" t="s">
-        <v>53</v>
+      <c r="S32" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3593,7 +3596,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3605,7 +3608,7 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3638,7 +3641,7 @@
         <v>77</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3654,7 +3657,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3666,7 +3669,7 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3696,10 +3699,10 @@
         <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3715,7 +3718,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3724,10 +3727,10 @@
         <v>46209.81753880787</v>
       </c>
       <c r="D35" s="9">
-        <v>46209.81754938657</v>
+        <v>46244.19278449074</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3757,7 +3760,7 @@
         <v>90</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3768,8 +3771,8 @@
       <c r="R35" s="9">
         <v>46251</v>
       </c>
-      <c r="S35" s="7" t="s">
-        <v>53</v>
+      <c r="S35" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3780,7 +3783,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3819,13 +3822,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3835,7 +3838,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3847,7 +3850,7 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3874,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3890,7 +3893,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3902,16 +3905,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3932,7 +3935,7 @@
         <v>90</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3955,7 +3958,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3973,10 +3976,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -3994,13 +3997,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4010,7 +4013,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4022,16 +4025,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4049,13 +4052,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4065,7 +4068,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4075,16 +4078,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4102,10 +4105,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4118,7 +4121,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4127,10 +4130,10 @@
         <v>46205.61214109954</v>
       </c>
       <c r="D42" s="5">
-        <v>46205.612154409726</v>
+        <v>46244.1927846412</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4160,7 +4163,7 @@
         <v>90</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4171,8 +4174,8 @@
       <c r="R42" s="5">
         <v>46251</v>
       </c>
-      <c r="S42" s="7" t="s">
-        <v>53</v>
+      <c r="S42" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -4183,7 +4186,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4222,13 +4225,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4238,7 +4241,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4250,7 +4253,7 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4277,13 +4280,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4293,7 +4296,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4305,7 +4308,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4329,7 +4332,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4346,7 +4349,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4358,16 +4361,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4385,13 +4388,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4411,7 +4414,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4423,16 +4426,16 @@
         <v>46234.17771361111</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4450,13 +4453,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4476,7 +4479,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4494,10 +4497,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4515,13 +4518,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4541,7 +4544,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4551,16 +4554,16 @@
         <v>46164.69027550926</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4578,10 +4581,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4604,7 +4607,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4614,16 +4617,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4641,13 +4644,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4657,7 +4660,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4667,16 +4670,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4694,13 +4697,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4710,7 +4713,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4720,16 +4723,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4747,13 +4750,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4763,7 +4766,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4773,16 +4776,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4800,13 +4803,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4816,7 +4819,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4828,7 +4831,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4852,7 +4855,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4869,7 +4872,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4881,16 +4884,16 @@
         <v>46217.58769918981</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4908,13 +4911,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4934,7 +4937,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4946,16 +4949,16 @@
         <v>46217.58785994213</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4973,13 +4976,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4999,7 +5002,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -5011,16 +5014,16 @@
         <v>46217.58816130787</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5038,13 +5041,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5064,7 +5067,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5076,16 +5079,16 @@
         <v>46217.588195752316</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5103,13 +5106,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5129,7 +5132,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5141,16 +5144,16 @@
         <v>46217.58828952546</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5168,13 +5171,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5194,7 +5197,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5206,16 +5209,16 @@
         <v>46217.58832047453</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5233,13 +5236,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5259,7 +5262,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5269,7 +5272,7 @@
         <v>46226.7241608912</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5293,7 +5296,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5306,7 +5309,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5316,16 +5319,16 @@
         <v>46164.69072508102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5343,13 +5346,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5369,7 +5372,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5379,16 +5382,16 @@
         <v>46217.58831070602</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5406,13 +5409,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5422,7 +5425,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5432,16 +5435,16 @@
         <v>46217.588311886575</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5459,13 +5462,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5475,7 +5478,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5485,16 +5488,16 @@
         <v>46217.58831295139</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5512,13 +5515,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5528,7 +5531,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5538,16 +5541,16 @@
         <v>46217.58831400463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5565,13 +5568,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5581,7 +5584,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5591,16 +5594,16 @@
         <v>46164.69085144676</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5618,13 +5621,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5654,16 +5657,16 @@
         <v>46198.782724606484</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5681,13 +5684,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5697,7 +5700,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5707,16 +5710,16 @@
         <v>46198.78272363426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5734,13 +5737,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5750,7 +5753,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5760,16 +5763,16 @@
         <v>46198.78273228009</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5787,13 +5790,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5803,7 +5806,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5813,16 +5816,16 @@
         <v>46198.782732824075</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5840,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5856,7 +5859,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5868,16 +5871,16 @@
         <v>46226.72417094908</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5895,13 +5898,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5921,7 +5924,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5931,16 +5934,16 @@
         <v>46198.78273341435</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -5958,13 +5961,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5974,7 +5977,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -5984,16 +5987,16 @@
         <v>46198.78272657408</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -6011,13 +6014,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6027,7 +6030,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6037,16 +6040,16 @@
         <v>46198.78272707176</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6064,13 +6067,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6080,7 +6083,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6090,16 +6093,16 @@
         <v>46198.78272166666</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6117,13 +6120,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6133,7 +6136,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6143,7 +6146,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6167,7 +6170,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6182,7 +6185,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6194,16 +6197,16 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6221,13 +6224,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6247,7 +6250,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6259,16 +6262,16 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6286,13 +6289,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6312,7 +6315,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6324,16 +6327,16 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6351,13 +6354,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>
@@ -6377,7 +6380,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6387,16 +6390,16 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6414,13 +6417,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6440,7 +6443,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6450,7 +6453,7 @@
         <v>46164.68453591435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6474,7 +6477,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6487,7 +6490,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6497,7 +6500,7 @@
         <v>46223.57585706019</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6524,13 +6527,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6550,7 +6553,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6560,7 +6563,7 @@
         <v>46223.575943020835</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6587,10 +6590,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6603,7 +6606,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6613,7 +6616,7 @@
         <v>46223.57594232639</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6640,10 +6643,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6656,7 +6659,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6666,7 +6669,7 @@
         <v>46223.57594163195</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6693,13 +6696,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6709,7 +6712,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6719,7 +6722,7 @@
         <v>46223.57594097222</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6746,13 +6749,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6762,7 +6765,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6772,7 +6775,7 @@
         <v>46223.575856435185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6799,13 +6802,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6825,7 +6828,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6835,7 +6838,7 @@
         <v>46223.576037604165</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6862,13 +6865,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6878,7 +6881,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6888,7 +6891,7 @@
         <v>46223.57603699074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6915,13 +6918,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6931,7 +6934,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -6941,7 +6944,7 @@
         <v>46223.57603633102</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6968,13 +6971,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6984,7 +6987,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -6994,7 +6997,7 @@
         <v>46223.576035659724</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7021,13 +7024,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7037,7 +7040,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7047,7 +7050,7 @@
         <v>46223.57585581018</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7074,13 +7077,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7100,7 +7103,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7110,7 +7113,7 @@
         <v>46223.5761230787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7137,13 +7140,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7153,7 +7156,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7163,7 +7166,7 @@
         <v>46223.57612246528</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7190,13 +7193,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7206,7 +7209,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7216,7 +7219,7 @@
         <v>46223.57612182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7243,13 +7246,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7259,7 +7262,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7269,7 +7272,7 @@
         <v>46223.57612121528</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7296,13 +7299,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7312,7 +7315,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7322,7 +7325,7 @@
         <v>46223.57585515046</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7349,13 +7352,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7375,7 +7378,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7385,7 +7388,7 @@
         <v>46223.57621322917</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7412,13 +7415,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7428,7 +7431,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7438,7 +7441,7 @@
         <v>46223.576212500004</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7465,13 +7468,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7481,7 +7484,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7491,7 +7494,7 @@
         <v>46223.57621184028</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7518,13 +7521,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7534,7 +7537,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7544,7 +7547,7 @@
         <v>46223.57621119213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7571,13 +7574,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7587,7 +7590,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7597,7 +7600,7 @@
         <v>46223.57585453703</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7624,13 +7627,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7650,7 +7653,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7660,7 +7663,7 @@
         <v>46223.57630975694</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7687,13 +7690,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7703,7 +7706,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7713,7 +7716,7 @@
         <v>46223.57630916667</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7740,13 +7743,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7756,7 +7759,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7766,7 +7769,7 @@
         <v>46223.57630858796</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7793,13 +7796,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7809,7 +7812,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7819,7 +7822,7 @@
         <v>46223.57630797454</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7846,13 +7849,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7862,7 +7865,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7872,7 +7875,7 @@
         <v>46223.57585388889</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7897,13 +7900,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7923,7 +7926,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -7933,7 +7936,7 @@
         <v>46223.5763915162</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7960,13 +7963,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7976,7 +7979,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -7986,7 +7989,7 @@
         <v>46223.576390856484</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8013,13 +8016,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8029,7 +8032,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8039,7 +8042,7 @@
         <v>46223.57639018519</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8066,13 +8069,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8082,7 +8085,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8092,7 +8095,7 @@
         <v>46223.57638950231</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8119,13 +8122,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8135,7 +8138,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8145,7 +8148,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8169,7 +8172,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8182,7 +8185,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8192,16 +8195,16 @@
         <v>46164.6922515162</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8219,13 +8222,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8245,7 +8248,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8255,16 +8258,16 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8282,13 +8285,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8298,7 +8301,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8308,16 +8311,16 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8335,13 +8338,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8351,7 +8354,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8361,16 +8364,16 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8388,13 +8391,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8404,7 +8407,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8414,16 +8417,16 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8441,13 +8444,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8457,7 +8460,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8467,7 +8470,7 @@
         <v>46223.57655457176</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8494,13 +8497,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8520,7 +8523,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8530,7 +8533,7 @@
         <v>46223.57651084491</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8557,13 +8560,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8573,7 +8576,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8583,7 +8586,7 @@
         <v>46223.57651017361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8610,13 +8613,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8626,7 +8629,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8636,7 +8639,7 @@
         <v>46223.57650946759</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8663,13 +8666,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8679,7 +8682,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8689,7 +8692,7 @@
         <v>46223.57650879629</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8716,13 +8719,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8732,7 +8735,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8742,16 +8745,16 @@
         <v>46164.69248696759</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8769,13 +8772,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8795,7 +8798,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8805,16 +8808,16 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8832,13 +8835,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8848,7 +8851,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8858,16 +8861,16 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8885,13 +8888,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8901,7 +8904,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8911,16 +8914,16 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8938,13 +8941,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8954,7 +8957,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -8964,16 +8967,16 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8991,13 +8994,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9007,7 +9010,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9017,16 +9020,16 @@
         <v>46164.69262644676</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9044,13 +9047,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9070,7 +9073,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9080,16 +9083,16 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9107,13 +9110,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9123,7 +9126,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9133,16 +9136,16 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9160,13 +9163,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9176,7 +9179,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9186,16 +9189,16 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9213,13 +9216,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9229,7 +9232,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9239,16 +9242,16 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9266,13 +9269,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9282,7 +9285,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9292,7 +9295,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9316,7 +9319,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9329,7 +9332,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9339,16 +9342,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9366,13 +9369,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9392,7 +9395,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9402,7 +9405,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9429,13 +9432,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1600" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="367">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -2865,9 +2865,11 @@
       <c r="B21" s="9">
         <v>46162.79179634259</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46245.69090109954</v>
+      </c>
       <c r="D21" s="9">
-        <v>46212.655108425926</v>
+        <v>46245.69091556713</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>90</v>
@@ -2902,9 +2904,11 @@
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
-      <c r="U21" s="12" t="s">
-        <v>46</v>
+      <c r="T21" s="10">
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -5267,9 +5271,11 @@
       <c r="B61" s="9">
         <v>46162.79225168981</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46245.69603590277</v>
+      </c>
       <c r="D61" s="9">
-        <v>46226.7241608912</v>
+        <v>46245.69605130787</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5304,8 +5310,12 @@
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
       <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
+      <c r="T61" s="10">
+        <v>1</v>
+      </c>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
@@ -5314,9 +5324,11 @@
       <c r="B62" s="5">
         <v>46162.792254479165</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46245.69554533565</v>
+      </c>
       <c r="D62" s="5">
-        <v>46164.69072508102</v>
+        <v>46245.69555737269</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5364,10 +5376,10 @@
         <v>53</v>
       </c>
       <c r="T62" s="6">
-        <v>0</v>
-      </c>
-      <c r="U62" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U62" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5377,9 +5389,11 @@
       <c r="B63" s="9">
         <v>46162.79225922454</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46245.69551539352</v>
+      </c>
       <c r="D63" s="9">
-        <v>46217.58831070602</v>
+        <v>46245.69551650463</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>189</v>
@@ -5430,9 +5444,11 @@
       <c r="B64" s="5">
         <v>46162.792265578704</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46245.69550913194</v>
+      </c>
       <c r="D64" s="5">
-        <v>46217.588311886575</v>
+        <v>46245.695510509264</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>189</v>
@@ -5483,9 +5499,11 @@
       <c r="B65" s="9">
         <v>46162.79227201389</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46245.6955271412</v>
+      </c>
       <c r="D65" s="9">
-        <v>46217.58831295139</v>
+        <v>46245.695528564815</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>189</v>
@@ -5536,9 +5554,11 @@
       <c r="B66" s="5">
         <v>46162.79227828704</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46245.69553159722</v>
+      </c>
       <c r="D66" s="5">
-        <v>46217.58831400463</v>
+        <v>46245.69553246528</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>189</v>
@@ -5589,9 +5609,11 @@
       <c r="B67" s="9">
         <v>46162.79232202546</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46245.69565657407</v>
+      </c>
       <c r="D67" s="9">
-        <v>46164.69085144676</v>
+        <v>46245.69566960648</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>231</v>
@@ -5639,10 +5661,10 @@
         <v>53</v>
       </c>
       <c r="T67" s="10">
-        <v>0</v>
-      </c>
-      <c r="U67" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5652,9 +5674,11 @@
       <c r="B68" s="5">
         <v>46162.79232653935</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46245.695620046296</v>
+      </c>
       <c r="D68" s="5">
-        <v>46198.782724606484</v>
+        <v>46245.69562136574</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>189</v>
@@ -5705,9 +5729,11 @@
       <c r="B69" s="9">
         <v>46162.79233265047</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46245.695624201384</v>
+      </c>
       <c r="D69" s="9">
-        <v>46198.78272363426</v>
+        <v>46245.69562572917</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>189</v>
@@ -5758,9 +5784,11 @@
       <c r="B70" s="5">
         <v>46162.79233820602</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46245.69563688658</v>
+      </c>
       <c r="D70" s="5">
-        <v>46198.78273228009</v>
+        <v>46245.69563821759</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>189</v>
@@ -5811,9 +5839,11 @@
       <c r="B71" s="9">
         <v>46162.79234384259</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="9">
+        <v>46245.695641666665</v>
+      </c>
       <c r="D71" s="9">
-        <v>46198.782732824075</v>
+        <v>46245.69564313657</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>189</v>
@@ -5868,7 +5898,7 @@
         <v>46226.72415461806</v>
       </c>
       <c r="D72" s="5">
-        <v>46226.72417094908</v>
+        <v>46245.69596915509</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>240</v>
@@ -5918,8 +5948,8 @@
       <c r="T72" s="6">
         <v>1</v>
       </c>
-      <c r="U72" s="7" t="s">
-        <v>27</v>
+      <c r="U72" s="12" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5929,9 +5959,11 @@
       <c r="B73" s="9">
         <v>46162.79242041666</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="9">
+        <v>46245.6956700463</v>
+      </c>
       <c r="D73" s="9">
-        <v>46198.78273341435</v>
+        <v>46245.69567159722</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>189</v>
@@ -5982,9 +6014,11 @@
       <c r="B74" s="5">
         <v>46162.79243321759</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46245.695675462965</v>
+      </c>
       <c r="D74" s="5">
-        <v>46198.78272657408</v>
+        <v>46245.695676979165</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>189</v>
@@ -6035,9 +6069,11 @@
       <c r="B75" s="9">
         <v>46162.79243956019</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9">
+        <v>46245.69567946759</v>
+      </c>
       <c r="D75" s="9">
-        <v>46198.78272707176</v>
+        <v>46245.69568078704</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>189</v>
@@ -6088,9 +6124,11 @@
       <c r="B76" s="5">
         <v>46162.79244651621</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46245.69568694444</v>
+      </c>
       <c r="D76" s="5">
-        <v>46198.78272166666</v>
+        <v>46245.69568829861</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>189</v>
@@ -6497,7 +6535,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46223.57585706019</v>
+        <v>46245.69568049768</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>265</v>
@@ -6560,7 +6598,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46223.575943020835</v>
+        <v>46245.695676504634</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>189</v>
@@ -6613,7 +6651,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46223.57594232639</v>
+        <v>46245.69568125</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>189</v>
@@ -6666,7 +6704,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46223.57594163195</v>
+        <v>46245.695686527775</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>189</v>
@@ -6719,7 +6757,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46223.57594097222</v>
+        <v>46245.69569986111</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>189</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -4885,7 +4885,7 @@
         <v>46217.587680173616</v>
       </c>
       <c r="D55" s="9">
-        <v>46217.58769918981</v>
+        <v>46246.20191841435</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>198</v>
@@ -4929,8 +4929,8 @@
       <c r="R55" s="9">
         <v>46253</v>
       </c>
-      <c r="S55" s="7" t="s">
-        <v>53</v>
+      <c r="S55" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -5015,7 +5015,7 @@
         <v>46217.58814275463</v>
       </c>
       <c r="D57" s="9">
-        <v>46217.58816130787</v>
+        <v>46246.20191923611</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -5059,8 +5059,8 @@
       <c r="R57" s="9">
         <v>46253</v>
       </c>
-      <c r="S57" s="7" t="s">
-        <v>53</v>
+      <c r="S57" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T57" s="10">
         <v>1</v>
@@ -5145,7 +5145,7 @@
         <v>46217.588267430554</v>
       </c>
       <c r="D59" s="9">
-        <v>46217.58828952546</v>
+        <v>46246.201918506944</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>211</v>
@@ -5189,8 +5189,8 @@
       <c r="R59" s="9">
         <v>46253</v>
       </c>
-      <c r="S59" s="7" t="s">
-        <v>53</v>
+      <c r="S59" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -194,9 +194,6 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1214982558008041</t>
   </si>
   <si>
@@ -299,6 +296,9 @@
   </si>
   <si>
     <t>Generación OC Rodete,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214982558032148</t>
@@ -2113,9 +2113,11 @@
       <c r="B9" s="9">
         <v>46162.79178665509</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="9">
+        <v>46247.657245254624</v>
+      </c>
       <c r="D9" s="9">
-        <v>46197.77681821759</v>
+        <v>46247.657267118055</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>
@@ -2150,14 +2152,16 @@
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="12" t="s">
-        <v>46</v>
+      <c r="T9" s="10">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="5">
         <v>46162.7919078125</v>
@@ -2169,16 +2173,16 @@
         <v>46197.776808263894</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="I10" s="5">
         <v>46149</v>
@@ -2190,7 +2194,7 @@
         <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>26</v>
@@ -2202,7 +2206,7 @@
         <v>38</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="5">
         <v>46149</v>
@@ -2211,7 +2215,7 @@
         <v>46150</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T10" s="6">
         <v>1</v>
@@ -2222,7 +2226,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="9">
         <v>46162.79191291667</v>
@@ -2234,16 +2238,16 @@
         <v>46197.77680832176</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="I11" s="9">
         <v>46149</v>
@@ -2255,7 +2259,7 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
@@ -2267,7 +2271,7 @@
         <v>38</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q11" s="9">
         <v>46149</v>
@@ -2276,7 +2280,7 @@
         <v>46157</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T11" s="10">
         <v>1</v>
@@ -2287,7 +2291,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="5">
         <v>46162.791918055555</v>
@@ -2299,16 +2303,16 @@
         <v>46197.776808344905</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="I12" s="5">
         <v>46149</v>
@@ -2320,7 +2324,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2332,7 +2336,7 @@
         <v>38</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q12" s="5">
         <v>46149</v>
@@ -2341,7 +2345,7 @@
         <v>46157</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
@@ -2352,7 +2356,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="9">
         <v>46162.791791192125</v>
@@ -2364,7 +2368,7 @@
         <v>46204.89769989584</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>25</v>
@@ -2388,7 +2392,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P13" s="10" t="s">
         <v>26</v>
@@ -2405,7 +2409,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
         <v>46162.79193019676</v>
@@ -2417,16 +2421,16 @@
         <v>46198.68142037037</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="I14" s="5">
         <v>46153</v>
@@ -2444,13 +2448,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="5">
         <v>46153</v>
@@ -2459,7 +2463,7 @@
         <v>46154</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T14" s="6">
         <v>1</v>
@@ -2470,7 +2474,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="9">
         <v>46162.7919353125</v>
@@ -2482,16 +2486,16 @@
         <v>46198.68143896991</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="I15" s="9">
         <v>46160</v>
@@ -2509,13 +2513,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q15" s="9">
         <v>46160</v>
@@ -2524,7 +2528,7 @@
         <v>46161</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T15" s="10">
         <v>1</v>
@@ -2535,7 +2539,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="5">
         <v>46162.79194023148</v>
@@ -2547,16 +2551,16 @@
         <v>46223.575690763886</v>
       </c>
       <c r="E16" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="6" t="s">
+      <c r="H16" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I16" s="5">
         <v>46160</v>
@@ -2574,13 +2578,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="5">
         <v>46160</v>
@@ -2589,13 +2593,13 @@
         <v>46161</v>
       </c>
       <c r="S16" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -2618,10 +2622,10 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I17" s="9">
         <v>46237</v>
@@ -2639,7 +2643,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>78</v>
@@ -2683,10 +2687,10 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I18" s="5">
         <v>46237</v>
@@ -2704,7 +2708,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>78</v>
@@ -2748,10 +2752,10 @@
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I19" s="9">
         <v>46237</v>
@@ -2769,7 +2773,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>78</v>
@@ -2813,10 +2817,10 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I20" s="5">
         <v>46237</v>
@@ -2834,7 +2838,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>78</v>
@@ -2967,7 +2971,7 @@
         <v>46276</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -3020,7 +3024,7 @@
         <v>93</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>99</v>
@@ -3028,7 +3032,7 @@
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
@@ -3089,7 +3093,7 @@
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
@@ -3207,7 +3211,7 @@
         <v>105</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>109</v>
@@ -3215,7 +3219,7 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3276,7 +3280,7 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3341,7 +3345,7 @@
         <v>46301</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3394,7 +3398,7 @@
         <v>114</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>118</v>
@@ -3402,7 +3406,7 @@
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
@@ -3463,7 +3467,7 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3524,7 +3528,7 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
@@ -3650,7 +3654,7 @@
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
       <c r="S33" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T33" s="10">
         <v>0</v>
@@ -3711,7 +3715,7 @@
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3951,7 +3955,7 @@
         <v>46279</v>
       </c>
       <c r="S38" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
@@ -4395,7 +4399,7 @@
         <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>174</v>
@@ -4600,7 +4604,7 @@
         <v>46322</v>
       </c>
       <c r="S49" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T49" s="10">
         <v>0</v>
@@ -4995,7 +4999,7 @@
         <v>46255</v>
       </c>
       <c r="S56" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5125,7 +5129,7 @@
         <v>46255</v>
       </c>
       <c r="S58" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5255,7 +5259,7 @@
         <v>46255</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5373,7 +5377,7 @@
         <v>46266</v>
       </c>
       <c r="S62" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5658,7 +5662,7 @@
         <v>46288</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T67" s="10">
         <v>1</v>
@@ -5943,13 +5947,13 @@
         <v>46290</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
       </c>
       <c r="U72" s="12" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -6218,7 +6222,7 @@
       <c r="S77" s="10"/>
       <c r="T77" s="10"/>
       <c r="U77" s="12" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -6342,7 +6346,7 @@
         <v>46280</v>
       </c>
       <c r="S79" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T79" s="10">
         <v>1</v>
@@ -6407,7 +6411,7 @@
         <v>46303</v>
       </c>
       <c r="S80" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6470,13 +6474,13 @@
         <v>46281</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="12" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6544,10 +6548,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I83" s="9">
         <v>46293</v>
@@ -6580,7 +6584,7 @@
         <v>46310</v>
       </c>
       <c r="S83" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T83" s="10">
         <v>0</v>
@@ -6607,10 +6611,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I84" s="5">
         <v>46293</v>
@@ -6660,10 +6664,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I85" s="9">
         <v>46293</v>
@@ -6713,10 +6717,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I86" s="5">
         <v>46293</v>
@@ -6766,10 +6770,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I87" s="9">
         <v>46293</v>
@@ -6819,10 +6823,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I88" s="5">
         <v>46311</v>
@@ -6855,7 +6859,7 @@
         <v>46314</v>
       </c>
       <c r="S88" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
@@ -6882,10 +6886,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I89" s="9">
         <v>46311</v>
@@ -6935,10 +6939,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I90" s="5">
         <v>46311</v>
@@ -6988,10 +6992,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I91" s="9">
         <v>46311</v>
@@ -7041,10 +7045,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I92" s="5">
         <v>46311</v>
@@ -7094,10 +7098,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I93" s="9">
         <v>46315</v>
@@ -7130,7 +7134,7 @@
         <v>46316</v>
       </c>
       <c r="S93" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T93" s="10">
         <v>0</v>
@@ -7157,10 +7161,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I94" s="5">
         <v>46315</v>
@@ -7210,10 +7214,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H95" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I95" s="9">
         <v>46315</v>
@@ -7263,10 +7267,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I96" s="5">
         <v>46315</v>
@@ -7316,10 +7320,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I97" s="9">
         <v>46315</v>
@@ -7369,10 +7373,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I98" s="5">
         <v>46317</v>
@@ -7405,7 +7409,7 @@
         <v>46318</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
@@ -7432,10 +7436,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I99" s="9">
         <v>46317</v>
@@ -7485,10 +7489,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I100" s="5">
         <v>46317</v>
@@ -7538,10 +7542,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I101" s="9">
         <v>46317</v>
@@ -7591,10 +7595,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I102" s="5">
         <v>46317</v>
@@ -7644,10 +7648,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H103" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I103" s="9">
         <v>46321</v>
@@ -7680,7 +7684,7 @@
         <v>46321</v>
       </c>
       <c r="S103" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T103" s="10">
         <v>0</v>
@@ -7707,10 +7711,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I104" s="5">
         <v>46321</v>
@@ -7760,10 +7764,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I105" s="9">
         <v>46321</v>
@@ -7813,10 +7817,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I106" s="5">
         <v>46321</v>
@@ -7866,10 +7870,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H107" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I107" s="9">
         <v>46321</v>
@@ -7919,10 +7923,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I108" s="6"/>
       <c r="J108" s="5">
@@ -7953,7 +7957,7 @@
         <v>46323</v>
       </c>
       <c r="S108" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
@@ -7980,10 +7984,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H109" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I109" s="9">
         <v>46323</v>
@@ -8033,10 +8037,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H110" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I110" s="5">
         <v>46323</v>
@@ -8086,10 +8090,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H111" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I111" s="9">
         <v>46323</v>
@@ -8139,10 +8143,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I112" s="5">
         <v>46323</v>
@@ -8275,7 +8279,7 @@
         <v>46324</v>
       </c>
       <c r="S114" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>
@@ -8514,10 +8518,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I119" s="9">
         <v>46325</v>
@@ -8550,7 +8554,7 @@
         <v>46325</v>
       </c>
       <c r="S119" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T119" s="10">
         <v>0</v>
@@ -8577,10 +8581,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I120" s="5">
         <v>46325</v>
@@ -8630,10 +8634,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I121" s="9">
         <v>46325</v>
@@ -8683,10 +8687,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="I122" s="5">
         <v>46325</v>
@@ -8736,10 +8740,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="I123" s="9">
         <v>46325</v>
@@ -8825,7 +8829,7 @@
         <v>46328</v>
       </c>
       <c r="S124" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T124" s="6">
         <v>0</v>
@@ -9100,7 +9104,7 @@
         <v>46329</v>
       </c>
       <c r="S129" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T129" s="10">
         <v>0</v>
@@ -9422,7 +9426,7 @@
         <v>46338</v>
       </c>
       <c r="S135" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T135" s="10">
         <v>0</v>
@@ -9449,10 +9453,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="I136" s="5">
         <v>46330</v>
@@ -9485,7 +9489,7 @@
         <v>46338</v>
       </c>
       <c r="S136" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T136" s="6">
         <v>0</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -4954,7 +4954,7 @@
         <v>46217.58784472222</v>
       </c>
       <c r="D56" s="5">
-        <v>46217.58785994213</v>
+        <v>46248.205163148144</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>203</v>
@@ -4998,8 +4998,8 @@
       <c r="R56" s="5">
         <v>46255</v>
       </c>
-      <c r="S56" s="7" t="s">
-        <v>52</v>
+      <c r="S56" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5084,7 +5084,7 @@
         <v>46217.58818075231</v>
       </c>
       <c r="D58" s="5">
-        <v>46217.588195752316</v>
+        <v>46248.205163969906</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>207</v>
@@ -5128,8 +5128,8 @@
       <c r="R58" s="5">
         <v>46255</v>
       </c>
-      <c r="S58" s="7" t="s">
-        <v>52</v>
+      <c r="S58" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5214,7 +5214,7 @@
         <v>46217.58830322917</v>
       </c>
       <c r="D60" s="5">
-        <v>46217.58832047453</v>
+        <v>46248.20516423611</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>212</v>
@@ -5258,8 +5258,8 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="7" t="s">
-        <v>52</v>
+      <c r="S60" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1922,7 +1922,7 @@
         <v>46183.58130109953</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.70988059028</v>
+        <v>46248.929306307866</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46164.69027550926</v>
+        <v>46249.38595430556</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>184</v>
@@ -5279,7 +5279,7 @@
         <v>46245.69603590277</v>
       </c>
       <c r="D61" s="9">
-        <v>46245.69605130787</v>
+        <v>46249.391917719906</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>215</v>
@@ -5332,7 +5332,7 @@
         <v>46245.69554533565</v>
       </c>
       <c r="D62" s="5">
-        <v>46245.69555737269</v>
+        <v>46249.076365416666</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>218</v>
@@ -5617,7 +5617,7 @@
         <v>46245.69565657407</v>
       </c>
       <c r="D67" s="9">
-        <v>46245.69566960648</v>
+        <v>46249.076454594906</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>231</v>
@@ -5902,7 +5902,7 @@
         <v>46226.72415461806</v>
       </c>
       <c r="D72" s="5">
-        <v>46245.69596915509</v>
+        <v>46249.07653208333</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>240</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46164.68453591435</v>
+        <v>46249.39574378473</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46245.69568049768</v>
+        <v>46249.07679348379</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>265</v>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46223.575856435185</v>
+        <v>46249.076895833336</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>275</v>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46223.57585581018</v>
+        <v>46249.07699912037</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>284</v>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46223.57585515046</v>
+        <v>46249.077753958336</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>295</v>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46223.57585453703</v>
+        <v>46249.077842858795</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>305</v>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46223.57585388889</v>
+        <v>46249.3861862037</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>313</v>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46164.6922515162</v>
+        <v>46249.0779596875</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>324</v>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46223.57655457176</v>
+        <v>46249.07802223379</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>335</v>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46164.69248696759</v>
+        <v>46249.07808491898</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>343</v>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46164.69262644676</v>
+        <v>46249.07820238426</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>352</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -463,220 +463,220 @@
     <t xml:space="preserve">Generación OC materiales corte Laser,Fabricacion Corte Laser </t>
   </si>
   <si>
+    <t>1214982558049172</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser,Fabricacion Corte Laser </t>
+  </si>
+  <si>
+    <t>1214982595219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser</t>
+  </si>
+  <si>
+    <t>1214982595219197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma ,Fabricación Corte Plasma </t>
+  </si>
+  <si>
+    <t>1214982558071444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma ,Fabricación Corte Plasma </t>
+  </si>
+  <si>
+    <t>1214982558071461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Materiales corte plasma,Materiales Corte Plasma </t>
+  </si>
+  <si>
+    <t>1214995680413404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo,Generacion OC Fabricación Externa</t>
+  </si>
+  <si>
+    <t>1214995680413416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación estructura proveedor externo,Fabricación Externa </t>
+  </si>
+  <si>
+    <t>1214982388058454</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa ,Control de calidad fabricación externa ,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214982388058471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad fabricación externa </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214982595261918</t>
+  </si>
+  <si>
+    <t>Mecanizado</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado,Fabricación Mecanizado</t>
+  </si>
+  <si>
+    <t>1214982595261930</t>
+  </si>
+  <si>
+    <t>Mecanizado,Fabricación Mecanizado</t>
+  </si>
+  <si>
+    <t>1214995680427506</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado</t>
+  </si>
+  <si>
+    <t>1214969047721209</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214995680427525</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1214995680435931</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214995680437154</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,propuesta Corte Laser,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,Propuesta Corte plasma ,Propuesta Mecanizado,Propuesta Fabricación externa ,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982817921526</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>1214982817921538</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
+    <t>OT 4326- ZVN 1-12-55/4,check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214982817946368</t>
+  </si>
+  <si>
+    <t>1214982817946380</t>
+  </si>
+  <si>
+    <t>1214982817946387</t>
+  </si>
+  <si>
+    <t>1214982817921593</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214982817921605</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214982558049172</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser,Fabricacion Corte Laser </t>
-  </si>
-  <si>
-    <t>1214982595219177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser</t>
-  </si>
-  <si>
-    <t>1214982595219197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma ,Fabricación Corte Plasma </t>
-  </si>
-  <si>
-    <t>1214982558071444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma ,Fabricación Corte Plasma </t>
-  </si>
-  <si>
-    <t>1214982558071461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Materiales corte plasma,Materiales Corte Plasma </t>
-  </si>
-  <si>
-    <t>1214995680413404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo,Generacion OC Fabricación Externa</t>
-  </si>
-  <si>
-    <t>1214995680413416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación estructura proveedor externo,Fabricación Externa </t>
-  </si>
-  <si>
-    <t>1214982388058454</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa ,Control de calidad fabricación externa ,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214982388058471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad fabricación externa </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214982595261918</t>
-  </si>
-  <si>
-    <t>Mecanizado</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado,Fabricación Mecanizado</t>
-  </si>
-  <si>
-    <t>1214982595261930</t>
-  </si>
-  <si>
-    <t>Mecanizado,Fabricación Mecanizado</t>
-  </si>
-  <si>
-    <t>1214995680427506</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado</t>
-  </si>
-  <si>
-    <t>1214969047721209</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214995680427525</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1214995680435931</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214995680437154</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,propuesta Corte Laser,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,Propuesta Corte plasma ,Propuesta Mecanizado,Propuesta Fabricación externa ,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982817921526</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>1214982817921538</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>OT 4326- ZVN 1-12-55/4,check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214982817946368</t>
-  </si>
-  <si>
-    <t>1214982817946380</t>
-  </si>
-  <si>
-    <t>1214982817946387</t>
-  </si>
-  <si>
-    <t>1214982817921593</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214982817921605</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1214982388114004</t>
@@ -3548,7 +3548,7 @@
         <v>46209.817423472225</v>
       </c>
       <c r="D32" s="5">
-        <v>46244.19278438657</v>
+        <v>46252.179607199076</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>126</v>
@@ -3592,8 +3592,8 @@
       <c r="R32" s="5">
         <v>46251</v>
       </c>
-      <c r="S32" s="12" t="s">
-        <v>130</v>
+      <c r="S32" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3616,7 +3616,7 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3649,7 +3649,7 @@
         <v>77</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3677,7 +3677,7 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3707,10 +3707,10 @@
         <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3735,10 +3735,10 @@
         <v>46209.81753880787</v>
       </c>
       <c r="D35" s="9">
-        <v>46244.19278449074</v>
+        <v>46252.17960721065</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3768,7 +3768,7 @@
         <v>90</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3779,8 +3779,8 @@
       <c r="R35" s="9">
         <v>46251</v>
       </c>
-      <c r="S35" s="12" t="s">
-        <v>130</v>
+      <c r="S35" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3791,7 +3791,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3830,13 +3830,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3858,7 +3858,7 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3885,13 +3885,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3913,16 +3913,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3943,7 +3943,7 @@
         <v>90</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3984,10 +3984,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -4005,13 +4005,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4033,16 +4033,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4060,13 +4060,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4076,7 +4076,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4086,16 +4086,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="H41" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4113,10 +4113,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4138,10 +4138,10 @@
         <v>46205.61214109954</v>
       </c>
       <c r="D42" s="5">
-        <v>46244.1927846412</v>
+        <v>46252.17961203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4171,7 +4171,7 @@
         <v>90</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4182,8 +4182,8 @@
       <c r="R42" s="5">
         <v>46251</v>
       </c>
-      <c r="S42" s="12" t="s">
-        <v>130</v>
+      <c r="S42" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T42" s="6">
         <v>1</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4233,13 +4233,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4261,7 +4261,7 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4288,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4316,7 +4316,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4340,7 +4340,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4357,7 +4357,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4369,16 +4369,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4396,13 +4396,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4422,7 +4422,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4434,16 +4434,16 @@
         <v>46234.17771361111</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4461,13 +4461,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4487,7 +4487,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4505,10 +4505,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4526,13 +4526,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4552,7 +4552,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4562,16 +4562,16 @@
         <v>46249.38595430556</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4589,10 +4589,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4615,7 +4615,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4625,16 +4625,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4652,13 +4652,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4678,16 +4678,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4705,13 +4705,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4721,7 +4721,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4731,16 +4731,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4758,13 +4758,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4784,16 +4784,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4811,13 +4811,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4827,7 +4827,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4839,7 +4839,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4863,7 +4863,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4892,16 +4892,16 @@
         <v>46246.20191841435</v>
       </c>
       <c r="E55" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="H55" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4919,13 +4919,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4934,7 +4934,7 @@
         <v>46253</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4963,10 +4963,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4984,10 +4984,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>204</v>
@@ -4999,7 +4999,7 @@
         <v>46255</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5028,10 +5028,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5049,10 +5049,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>207</v>
@@ -5064,7 +5064,7 @@
         <v>46253</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="T57" s="10">
         <v>1</v>
@@ -5093,10 +5093,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5114,7 +5114,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>206</v>
@@ -5129,7 +5129,7 @@
         <v>46255</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5158,10 +5158,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5179,10 +5179,10 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P59" s="10" t="s">
         <v>212</v>
@@ -5194,7 +5194,7 @@
         <v>46253</v>
       </c>
       <c r="S59" s="12" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -5223,10 +5223,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5244,7 +5244,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>211</v>
@@ -5259,7 +5259,7 @@
         <v>46255</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5400,7 +5400,7 @@
         <v>46245.69551650463</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5455,7 +5455,7 @@
         <v>46245.695510509264</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5510,7 +5510,7 @@
         <v>46245.695528564815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5565,7 +5565,7 @@
         <v>46245.69553246528</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5685,7 +5685,7 @@
         <v>46245.69562136574</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5740,7 +5740,7 @@
         <v>46245.69562572917</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5795,7 +5795,7 @@
         <v>46245.69563821759</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5850,7 +5850,7 @@
         <v>46245.69564313657</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5911,10 +5911,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5970,16 +5970,16 @@
         <v>46245.69567159722</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I73" s="9">
         <v>46289</v>
@@ -6025,16 +6025,16 @@
         <v>46245.695676979165</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I74" s="5">
         <v>46289</v>
@@ -6080,16 +6080,16 @@
         <v>46245.69568078704</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>157</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>158</v>
       </c>
       <c r="I75" s="9">
         <v>46289</v>
@@ -6135,16 +6135,16 @@
         <v>46245.69568829861</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="I76" s="5">
         <v>46289</v>
@@ -6188,7 +6188,7 @@
         <v>46212.65565390047</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6245,10 +6245,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I78" s="5">
         <v>46169</v>
@@ -6266,7 +6266,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>111</v>
@@ -6310,10 +6310,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I79" s="9">
         <v>46279</v>
@@ -6331,7 +6331,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>102</v>
@@ -6375,10 +6375,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I80" s="5">
         <v>46302</v>
@@ -6396,7 +6396,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>120</v>
@@ -6438,10 +6438,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="I81" s="9">
         <v>46280</v>
@@ -6459,10 +6459,10 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>260</v>
@@ -6605,7 +6605,7 @@
         <v>46245.695676504634</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6658,7 +6658,7 @@
         <v>46245.69568125</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6711,7 +6711,7 @@
         <v>46245.695686527775</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6741,7 +6741,7 @@
         <v>265</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>271</v>
@@ -6764,7 +6764,7 @@
         <v>46245.69569986111</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6794,7 +6794,7 @@
         <v>265</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>273</v>
@@ -6880,7 +6880,7 @@
         <v>46223.576037604165</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6933,7 +6933,7 @@
         <v>46223.57603699074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6986,7 +6986,7 @@
         <v>46223.57603633102</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -7039,7 +7039,7 @@
         <v>46223.576035659724</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7155,7 +7155,7 @@
         <v>46223.5761230787</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7208,7 +7208,7 @@
         <v>46223.57612246528</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7261,7 +7261,7 @@
         <v>46223.57612182871</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7314,7 +7314,7 @@
         <v>46223.57612121528</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7430,7 +7430,7 @@
         <v>46223.57621322917</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7483,7 +7483,7 @@
         <v>46223.576212500004</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7536,7 +7536,7 @@
         <v>46223.57621184028</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7589,7 +7589,7 @@
         <v>46223.57621119213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7705,7 +7705,7 @@
         <v>46223.57630975694</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7735,7 +7735,7 @@
         <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>307</v>
@@ -7758,7 +7758,7 @@
         <v>46223.57630916667</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7788,7 +7788,7 @@
         <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>309</v>
@@ -7811,7 +7811,7 @@
         <v>46223.57630858796</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7841,7 +7841,7 @@
         <v>305</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>309</v>
@@ -7864,7 +7864,7 @@
         <v>46223.57630797454</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7894,7 +7894,7 @@
         <v>305</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
         <v>309</v>
@@ -7978,7 +7978,7 @@
         <v>46223.5763915162</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -8008,7 +8008,7 @@
         <v>313</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
         <v>316</v>
@@ -8031,7 +8031,7 @@
         <v>46223.576390856484</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8061,7 +8061,7 @@
         <v>313</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>316</v>
@@ -8084,7 +8084,7 @@
         <v>46223.57639018519</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8114,7 +8114,7 @@
         <v>313</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>316</v>
@@ -8137,7 +8137,7 @@
         <v>46223.57638950231</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8167,7 +8167,7 @@
         <v>313</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>316</v>
@@ -8300,7 +8300,7 @@
         <v>46164.69223148148</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8330,7 +8330,7 @@
         <v>324</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>329</v>
@@ -8353,7 +8353,7 @@
         <v>46164.69222814815</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8383,7 +8383,7 @@
         <v>324</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>329</v>
@@ -8406,7 +8406,7 @@
         <v>46164.69222525463</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8436,7 +8436,7 @@
         <v>324</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>332</v>
@@ -8459,7 +8459,7 @@
         <v>46164.69222011574</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8489,7 +8489,7 @@
         <v>324</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>332</v>
@@ -8575,7 +8575,7 @@
         <v>46223.57651084491</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8605,7 +8605,7 @@
         <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>337</v>
@@ -8628,7 +8628,7 @@
         <v>46223.57651017361</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8658,7 +8658,7 @@
         <v>335</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>337</v>
@@ -8681,7 +8681,7 @@
         <v>46223.57650946759</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8711,7 +8711,7 @@
         <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>340</v>
@@ -8734,7 +8734,7 @@
         <v>46223.57650879629</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8764,7 +8764,7 @@
         <v>335</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>337</v>
@@ -8850,7 +8850,7 @@
         <v>46164.69246075231</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8880,7 +8880,7 @@
         <v>343</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>345</v>
@@ -8903,7 +8903,7 @@
         <v>46164.692458101854</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8933,7 +8933,7 @@
         <v>343</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>345</v>
@@ -8956,7 +8956,7 @@
         <v>46164.69245559028</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8986,7 +8986,7 @@
         <v>343</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
         <v>348</v>
@@ -9009,7 +9009,7 @@
         <v>46164.69245128472</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9039,7 +9039,7 @@
         <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>350</v>
@@ -9125,7 +9125,7 @@
         <v>46164.692587303245</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9155,7 +9155,7 @@
         <v>352</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>352</v>
@@ -9178,7 +9178,7 @@
         <v>46164.69258451389</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9208,7 +9208,7 @@
         <v>352</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>352</v>
@@ -9231,7 +9231,7 @@
         <v>46164.69258188657</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9261,7 +9261,7 @@
         <v>352</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>352</v>
@@ -9284,7 +9284,7 @@
         <v>46164.69257741898</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9314,7 +9314,7 @@
         <v>352</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>352</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -676,16 +676,16 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1214982388114004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214982388114004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
   </si>
   <si>
     <t>1214982595357394</t>
@@ -4889,7 +4889,7 @@
         <v>46217.587680173616</v>
       </c>
       <c r="D55" s="9">
-        <v>46246.20191841435</v>
+        <v>46254.173978101855</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>197</v>
@@ -4933,8 +4933,8 @@
       <c r="R55" s="9">
         <v>46253</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>201</v>
+      <c r="S55" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T55" s="10">
         <v>1</v>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4957,7 +4957,7 @@
         <v>46248.205163148144</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -4990,7 +4990,7 @@
         <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4999,7 +4999,7 @@
         <v>46255</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5019,7 +5019,7 @@
         <v>46217.58814275463</v>
       </c>
       <c r="D57" s="9">
-        <v>46246.20191923611</v>
+        <v>46254.17397791667</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -5063,8 +5063,8 @@
       <c r="R57" s="9">
         <v>46253</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>201</v>
+      <c r="S57" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T57" s="10">
         <v>1</v>
@@ -5129,7 +5129,7 @@
         <v>46255</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5149,7 +5149,7 @@
         <v>46217.588267430554</v>
       </c>
       <c r="D59" s="9">
-        <v>46246.201918506944</v>
+        <v>46254.173977997685</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>211</v>
@@ -5193,8 +5193,8 @@
       <c r="R59" s="9">
         <v>46253</v>
       </c>
-      <c r="S59" s="12" t="s">
-        <v>201</v>
+      <c r="S59" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T59" s="10">
         <v>1</v>
@@ -5259,7 +5259,7 @@
         <v>46255</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -6402,7 +6402,7 @@
         <v>120</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q80" s="5">
         <v>46302</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="366">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -683,9 +683,6 @@
   </si>
   <si>
     <t>Bodega:,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214982595357394</t>
@@ -4954,7 +4951,7 @@
         <v>46217.58784472222</v>
       </c>
       <c r="D56" s="5">
-        <v>46248.205163148144</v>
+        <v>46256.17331716436</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -4998,8 +4995,8 @@
       <c r="R56" s="5">
         <v>46255</v>
       </c>
-      <c r="S56" s="12" t="s">
-        <v>204</v>
+      <c r="S56" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5010,7 +5007,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -5022,7 +5019,7 @@
         <v>46254.17397791667</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
@@ -5055,7 +5052,7 @@
         <v>142</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5075,7 +5072,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5084,10 +5081,10 @@
         <v>46217.58818075231</v>
       </c>
       <c r="D58" s="5">
-        <v>46248.205163969906</v>
+        <v>46256.17331711805</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5117,10 +5114,10 @@
         <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5128,8 +5125,8 @@
       <c r="R58" s="5">
         <v>46255</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>204</v>
+      <c r="S58" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T58" s="6">
         <v>1</v>
@@ -5140,7 +5137,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5152,7 +5149,7 @@
         <v>46254.173977997685</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5185,7 +5182,7 @@
         <v>164</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5205,7 +5202,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5214,10 +5211,10 @@
         <v>46217.58830322917</v>
       </c>
       <c r="D60" s="5">
-        <v>46248.20516423611</v>
+        <v>46256.173317152774</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5247,10 +5244,10 @@
         <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5258,8 +5255,8 @@
       <c r="R60" s="5">
         <v>46255</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>204</v>
+      <c r="S60" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5270,7 +5267,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5282,7 +5279,7 @@
         <v>46249.391917719906</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5306,7 +5303,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5323,7 +5320,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5335,16 +5332,16 @@
         <v>46249.076365416666</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5362,13 +5359,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5388,7 +5385,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5406,10 +5403,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5427,13 +5424,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5443,7 +5440,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5461,10 +5458,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5482,13 +5479,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5498,7 +5495,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5516,10 +5513,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5537,13 +5534,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5553,7 +5550,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5571,10 +5568,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5592,13 +5589,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5608,7 +5605,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5620,16 +5617,16 @@
         <v>46249.076454594906</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5647,13 +5644,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5673,7 +5670,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5691,10 +5688,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5712,13 +5709,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5728,7 +5725,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5746,10 +5743,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5767,13 +5764,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5783,7 +5780,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5801,10 +5798,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5822,13 +5819,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5838,7 +5835,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5856,10 +5853,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5877,13 +5874,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5893,7 +5890,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5905,7 +5902,7 @@
         <v>46249.07653208333</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5932,13 +5929,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5958,7 +5955,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5997,13 +5994,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6013,7 +6010,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -6052,13 +6049,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6068,7 +6065,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6107,13 +6104,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6123,7 +6120,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6162,13 +6159,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6178,7 +6175,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6212,7 +6209,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6227,7 +6224,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6239,7 +6236,7 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6272,7 +6269,7 @@
         <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6292,7 +6289,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6304,7 +6301,7 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6337,7 +6334,7 @@
         <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6357,7 +6354,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6369,7 +6366,7 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6422,7 +6419,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6432,7 +6429,7 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6465,7 +6462,7 @@
         <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6485,7 +6482,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6495,7 +6492,7 @@
         <v>46249.39574378473</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6519,7 +6516,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6532,7 +6529,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6542,7 +6539,7 @@
         <v>46249.07679348379</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6569,13 +6566,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6595,7 +6592,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6632,10 +6629,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6648,7 +6645,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6685,10 +6682,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6701,7 +6698,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6738,13 +6735,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6754,7 +6751,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6791,13 +6788,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6807,7 +6804,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6817,7 +6814,7 @@
         <v>46249.076895833336</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6844,13 +6841,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6870,7 +6867,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6907,13 +6904,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6923,7 +6920,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6960,13 +6957,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6976,7 +6973,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -7013,13 +7010,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7029,7 +7026,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -7066,13 +7063,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7082,7 +7079,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7092,7 +7089,7 @@
         <v>46249.07699912037</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7119,13 +7116,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7145,7 +7142,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7182,13 +7179,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7198,7 +7195,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7235,13 +7232,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7251,7 +7248,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7288,13 +7285,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7304,7 +7301,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7341,13 +7338,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O97" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7357,7 +7354,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7367,7 +7364,7 @@
         <v>46249.077753958336</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7394,13 +7391,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7420,7 +7417,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7457,13 +7454,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O99" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P99" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P99" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7473,7 +7470,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7510,13 +7507,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7526,7 +7523,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7563,13 +7560,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7579,7 +7576,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7616,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7632,7 +7629,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7642,7 +7639,7 @@
         <v>46249.077842858795</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7669,13 +7666,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7695,7 +7692,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7732,13 +7729,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7748,7 +7745,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7785,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7801,7 +7798,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7838,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7854,7 +7851,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7891,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7907,7 +7904,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7917,7 +7914,7 @@
         <v>46249.3861862037</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7942,13 +7939,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7968,7 +7965,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -8005,13 +8002,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8021,7 +8018,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -8058,13 +8055,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8074,7 +8071,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8111,13 +8108,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8127,7 +8124,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8164,13 +8161,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8180,7 +8177,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8190,7 +8187,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8214,7 +8211,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8227,7 +8224,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8237,16 +8234,16 @@
         <v>46249.0779596875</v>
       </c>
       <c r="E114" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G114" s="6" t="s">
+      <c r="H114" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8264,13 +8261,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8290,7 +8287,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8306,10 +8303,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8327,13 +8324,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8343,7 +8340,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8359,10 +8356,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8380,13 +8377,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8396,7 +8393,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8412,10 +8409,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8433,13 +8430,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8449,7 +8446,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8465,10 +8462,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8486,13 +8483,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8502,7 +8499,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8512,7 +8509,7 @@
         <v>46249.07802223379</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8539,13 +8536,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8565,7 +8562,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8602,13 +8599,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8618,7 +8615,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8655,13 +8652,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8671,7 +8668,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8708,13 +8705,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8724,7 +8721,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8761,13 +8758,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8777,7 +8774,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8787,16 +8784,16 @@
         <v>46249.07808491898</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I124" s="5">
         <v>46328</v>
@@ -8814,13 +8811,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8840,7 +8837,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8856,10 +8853,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I125" s="9">
         <v>46328</v>
@@ -8877,13 +8874,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8893,7 +8890,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8909,10 +8906,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8930,13 +8927,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8946,7 +8943,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8962,10 +8959,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I127" s="9">
         <v>46328</v>
@@ -8983,13 +8980,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8999,7 +8996,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -9015,10 +9012,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -9036,13 +9033,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9052,7 +9049,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9062,16 +9059,16 @@
         <v>46249.07820238426</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H129" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I129" s="9">
         <v>46329</v>
@@ -9089,13 +9086,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9115,7 +9112,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9131,10 +9128,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I130" s="5">
         <v>46329</v>
@@ -9152,13 +9149,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9168,7 +9165,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9184,10 +9181,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H131" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I131" s="9">
         <v>46329</v>
@@ -9205,13 +9202,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9221,7 +9218,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9237,10 +9234,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I132" s="5">
         <v>46329</v>
@@ -9258,13 +9255,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9274,7 +9271,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9290,10 +9287,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H133" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="I133" s="9">
         <v>46329</v>
@@ -9311,13 +9308,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9327,7 +9324,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9337,7 +9334,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9361,7 +9358,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9374,7 +9371,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9384,16 +9381,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="F135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="10" t="s">
+      <c r="H135" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>364</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9411,13 +9408,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9437,7 +9434,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9447,7 +9444,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9474,13 +9471,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -1801,7 +1801,7 @@
         <v>46183.58133199074</v>
       </c>
       <c r="D4" s="5">
-        <v>46183.58134738426</v>
+        <v>46257.32524290509</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -4554,9 +4554,11 @@
       <c r="B49" s="9">
         <v>46162.79214709491</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46258.543760092594</v>
+      </c>
       <c r="D49" s="9">
-        <v>46249.38595430556</v>
+        <v>46258.5437854051</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4604,10 +4606,10 @@
         <v>52</v>
       </c>
       <c r="T49" s="10">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="367">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -731,6 +731,9 @@
   </si>
   <si>
     <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214982595382876</t>
@@ -5331,7 +5334,7 @@
         <v>46245.69554533565</v>
       </c>
       <c r="D62" s="5">
-        <v>46249.076365416666</v>
+        <v>46259.19917611111</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>217</v>
@@ -5375,8 +5378,8 @@
       <c r="R62" s="5">
         <v>46266</v>
       </c>
-      <c r="S62" s="7" t="s">
-        <v>52</v>
+      <c r="S62" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5429,10 +5432,10 @@
         <v>217</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5442,7 +5445,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5484,10 +5487,10 @@
         <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5497,7 +5500,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5539,10 +5542,10 @@
         <v>217</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5552,7 +5555,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5594,10 +5597,10 @@
         <v>217</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5607,7 +5610,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5619,7 +5622,7 @@
         <v>46249.076454594906</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5672,7 +5675,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5711,13 +5714,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5727,7 +5730,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5766,13 +5769,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5782,7 +5785,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5821,13 +5824,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5837,7 +5840,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5876,13 +5879,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5892,7 +5895,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5904,7 +5907,7 @@
         <v>46249.07653208333</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5957,7 +5960,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5996,13 +5999,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6012,7 +6015,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -6051,13 +6054,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6067,7 +6070,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6106,13 +6109,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6122,7 +6125,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6161,13 +6164,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6177,7 +6180,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6211,7 +6214,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6226,7 +6229,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6238,7 +6241,7 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6271,7 +6274,7 @@
         <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6291,7 +6294,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6303,7 +6306,7 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6336,7 +6339,7 @@
         <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6356,7 +6359,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6368,7 +6371,7 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6421,7 +6424,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6431,7 +6434,7 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6464,7 +6467,7 @@
         <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6484,7 +6487,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6494,7 +6497,7 @@
         <v>46249.39574378473</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6518,7 +6521,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6531,7 +6534,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6541,7 +6544,7 @@
         <v>46249.07679348379</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6568,13 +6571,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6594,7 +6597,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6631,10 +6634,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6647,7 +6650,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6684,10 +6687,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6700,7 +6703,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6737,13 +6740,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6753,7 +6756,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6790,13 +6793,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6806,7 +6809,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6816,7 +6819,7 @@
         <v>46249.076895833336</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6843,13 +6846,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6869,7 +6872,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6906,13 +6909,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6922,7 +6925,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6959,13 +6962,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6975,7 +6978,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -7012,13 +7015,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7028,7 +7031,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -7065,13 +7068,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7081,7 +7084,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7091,7 +7094,7 @@
         <v>46249.07699912037</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7118,13 +7121,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7144,7 +7147,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7181,13 +7184,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7197,7 +7200,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7234,13 +7237,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7250,7 +7253,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7287,13 +7290,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7303,7 +7306,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7340,13 +7343,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7356,7 +7359,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7366,7 +7369,7 @@
         <v>46249.077753958336</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7393,13 +7396,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7419,7 +7422,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7456,13 +7459,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7472,7 +7475,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7509,13 +7512,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7525,7 +7528,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7562,13 +7565,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7578,7 +7581,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7615,13 +7618,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7631,7 +7634,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7641,7 +7644,7 @@
         <v>46249.077842858795</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7668,13 +7671,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7694,7 +7697,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7731,13 +7734,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7747,7 +7750,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7784,13 +7787,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7800,7 +7803,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7837,13 +7840,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7853,7 +7856,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7890,13 +7893,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7906,7 +7909,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7916,7 +7919,7 @@
         <v>46249.3861862037</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7941,13 +7944,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7967,7 +7970,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -8004,13 +8007,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8020,7 +8023,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -8057,13 +8060,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8073,7 +8076,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8110,13 +8113,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8126,7 +8129,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8163,13 +8166,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8179,7 +8182,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8189,7 +8192,7 @@
         <v>46164.68546163195</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8213,7 +8216,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8226,7 +8229,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8236,16 +8239,16 @@
         <v>46249.0779596875</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8263,13 +8266,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8289,7 +8292,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8305,10 +8308,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8326,13 +8329,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8342,7 +8345,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8358,10 +8361,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8379,13 +8382,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8395,7 +8398,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8411,10 +8414,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8432,13 +8435,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8448,7 +8451,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8464,10 +8467,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8485,13 +8488,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8501,7 +8504,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8511,7 +8514,7 @@
         <v>46249.07802223379</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8538,13 +8541,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8564,7 +8567,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8601,13 +8604,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8617,7 +8620,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8654,13 +8657,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8670,7 +8673,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8707,13 +8710,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8723,7 +8726,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8760,13 +8763,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8776,7 +8779,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8786,7 +8789,7 @@
         <v>46249.07808491898</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8813,13 +8816,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8839,7 +8842,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8876,13 +8879,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8892,7 +8895,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8929,13 +8932,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8945,7 +8948,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -8982,13 +8985,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8998,7 +9001,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -9035,13 +9038,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9051,7 +9054,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9061,7 +9064,7 @@
         <v>46249.07820238426</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9088,13 +9091,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O129" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9114,7 +9117,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9151,13 +9154,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9167,7 +9170,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9204,13 +9207,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9220,7 +9223,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9257,13 +9260,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9273,7 +9276,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9310,13 +9313,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9326,7 +9329,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9336,7 +9339,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9360,7 +9363,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9373,7 +9376,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9383,16 +9386,16 @@
         <v>46164.69269384259</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9410,13 +9413,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9436,7 +9439,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9446,7 +9449,7 @@
         <v>46197.77680827546</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9473,13 +9476,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="367">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -6492,9 +6492,11 @@
       <c r="B82" s="5">
         <v>46162.79250947917</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46260.59740648148</v>
+      </c>
       <c r="D82" s="5">
-        <v>46249.39574378473</v>
+        <v>46260.597421099534</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>262</v>
@@ -6529,8 +6531,12 @@
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
       <c r="S82" s="6"/>
-      <c r="T82" s="6"/>
-      <c r="U82" s="6"/>
+      <c r="T82" s="6">
+        <v>1</v>
+      </c>
+      <c r="U82" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
@@ -6539,9 +6545,11 @@
       <c r="B83" s="9">
         <v>46162.79251295139</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="9">
+        <v>46260.596982476854</v>
+      </c>
       <c r="D83" s="9">
-        <v>46249.07679348379</v>
+        <v>46260.5969977662</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>265</v>
@@ -6589,10 +6597,10 @@
         <v>52</v>
       </c>
       <c r="T83" s="10">
-        <v>0</v>
-      </c>
-      <c r="U83" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U83" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -6814,9 +6822,11 @@
       <c r="B88" s="5">
         <v>46162.792612743055</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46260.597228715276</v>
+      </c>
       <c r="D88" s="5">
-        <v>46249.076895833336</v>
+        <v>46260.597246053236</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>275</v>
@@ -6864,10 +6874,10 @@
         <v>52</v>
       </c>
       <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U88" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7089,9 +7099,11 @@
       <c r="B93" s="9">
         <v>46162.79268604166</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="9">
+        <v>46260.5972707176</v>
+      </c>
       <c r="D93" s="9">
-        <v>46249.07699912037</v>
+        <v>46260.597285254626</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>284</v>
@@ -7139,10 +7151,10 @@
         <v>52</v>
       </c>
       <c r="T93" s="10">
-        <v>0</v>
-      </c>
-      <c r="U93" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U93" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7364,9 +7376,11 @@
       <c r="B98" s="5">
         <v>46162.792744861115</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46260.59731136574</v>
+      </c>
       <c r="D98" s="5">
-        <v>46249.077753958336</v>
+        <v>46260.5973271875</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>295</v>
@@ -7414,10 +7428,10 @@
         <v>52</v>
       </c>
       <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U98" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7639,9 +7653,11 @@
       <c r="B103" s="9">
         <v>46162.79285696759</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C103" s="9">
+        <v>46260.59734818287</v>
+      </c>
       <c r="D103" s="9">
-        <v>46249.077842858795</v>
+        <v>46260.5973682176</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>305</v>
@@ -7689,10 +7705,10 @@
         <v>52</v>
       </c>
       <c r="T103" s="10">
-        <v>0</v>
-      </c>
-      <c r="U103" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U103" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7914,9 +7930,11 @@
       <c r="B108" s="5">
         <v>46162.792907696756</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46260.59739072916</v>
+      </c>
       <c r="D108" s="5">
-        <v>46249.3861862037</v>
+        <v>46260.59740690972</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>313</v>
@@ -7962,10 +7980,10 @@
         <v>52</v>
       </c>
       <c r="T108" s="6">
-        <v>0</v>
-      </c>
-      <c r="U108" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U108" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8189,7 +8207,7 @@
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46164.68546163195</v>
+        <v>46260.59684777778</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>321</v>
@@ -8236,7 +8254,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46249.0779596875</v>
+        <v>46260.59739923611</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>324</v>
@@ -8509,9 +8527,11 @@
       <c r="B119" s="9">
         <v>46162.79306296296</v>
       </c>
-      <c r="C119" s="10"/>
+      <c r="C119" s="9">
+        <v>46260.5967861574</v>
+      </c>
       <c r="D119" s="9">
-        <v>46249.07802223379</v>
+        <v>46260.596804953704</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>335</v>
@@ -8559,10 +8579,10 @@
         <v>52</v>
       </c>
       <c r="T119" s="10">
-        <v>0</v>
-      </c>
-      <c r="U119" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U119" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -8784,9 +8804,11 @@
       <c r="B124" s="5">
         <v>46162.79314625</v>
       </c>
-      <c r="C124" s="6"/>
+      <c r="C124" s="5">
+        <v>46260.59664043981</v>
+      </c>
       <c r="D124" s="5">
-        <v>46249.07808491898</v>
+        <v>46260.59674144676</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>343</v>
@@ -8834,10 +8856,10 @@
         <v>52</v>
       </c>
       <c r="T124" s="6">
-        <v>0</v>
-      </c>
-      <c r="U124" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U124" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -8847,9 +8869,11 @@
       <c r="B125" s="9">
         <v>46162.793151550926</v>
       </c>
-      <c r="C125" s="10"/>
+      <c r="C125" s="9">
+        <v>46260.59673373842</v>
+      </c>
       <c r="D125" s="9">
-        <v>46164.69246075231</v>
+        <v>46260.596735405095</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>188</v>
@@ -9059,9 +9083,11 @@
       <c r="B129" s="9">
         <v>46162.79319725695</v>
       </c>
-      <c r="C129" s="10"/>
+      <c r="C129" s="9">
+        <v>46260.59684162037</v>
+      </c>
       <c r="D129" s="9">
-        <v>46249.07820238426</v>
+        <v>46260.596857384255</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>352</v>
@@ -9109,10 +9135,10 @@
         <v>52</v>
       </c>
       <c r="T129" s="10">
-        <v>0</v>
-      </c>
-      <c r="U129" s="11" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="U129" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -9124,7 +9150,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46164.692587303245</v>
+        <v>46260.59674087963</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>188</v>
@@ -9383,7 +9409,7 @@
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46164.69269384259</v>
+        <v>46260.59685918981</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>362</v>
@@ -9433,8 +9459,8 @@
       <c r="T135" s="10">
         <v>0</v>
       </c>
-      <c r="U135" s="11" t="s">
-        <v>100</v>
+      <c r="U135" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9446,7 +9472,7 @@
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46197.77680827546</v>
+        <v>46260.59685829861</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>366</v>
@@ -9496,8 +9522,8 @@
       <c r="T136" s="6">
         <v>0</v>
       </c>
-      <c r="U136" s="11" t="s">
-        <v>100</v>
+      <c r="U136" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -2117,7 +2117,7 @@
         <v>46247.657245254624</v>
       </c>
       <c r="D9" s="9">
-        <v>46247.657267118055</v>
+        <v>46264.29977650463</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>45</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="366">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -731,9 +731,6 @@
   </si>
   <si>
     <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214982595382876</t>
@@ -5334,7 +5331,7 @@
         <v>46245.69554533565</v>
       </c>
       <c r="D62" s="5">
-        <v>46259.19917611111</v>
+        <v>46267.20458883102</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>217</v>
@@ -5378,8 +5375,8 @@
       <c r="R62" s="5">
         <v>46266</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>220</v>
+      <c r="S62" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5390,7 +5387,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5432,10 +5429,10 @@
         <v>217</v>
       </c>
       <c r="O63" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="P63" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="P63" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5445,7 +5442,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5487,10 +5484,10 @@
         <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5500,7 +5497,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5542,10 +5539,10 @@
         <v>217</v>
       </c>
       <c r="O65" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P65" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="P65" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5555,7 +5552,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5597,10 +5594,10 @@
         <v>217</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5610,7 +5607,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5622,7 +5619,7 @@
         <v>46249.076454594906</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5675,7 +5672,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5714,13 +5711,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>233</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5730,7 +5727,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5769,13 +5766,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5785,7 +5782,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5824,13 +5821,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5840,7 +5837,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5879,13 +5876,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5895,7 +5892,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5907,7 +5904,7 @@
         <v>46249.07653208333</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5960,7 +5957,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5999,13 +5996,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -6015,7 +6012,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46162.79243321759</v>
@@ -6054,13 +6051,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6070,7 +6067,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46162.79243956019</v>
@@ -6109,13 +6106,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6125,7 +6122,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46162.79244651621</v>
@@ -6164,13 +6161,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6180,7 +6177,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46162.79247811342</v>
@@ -6214,7 +6211,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6229,7 +6226,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46162.792481805554</v>
@@ -6241,7 +6238,7 @@
         <v>46212.65536587963</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6274,7 +6271,7 @@
         <v>111</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="5">
         <v>46169</v>
@@ -6294,7 +6291,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46162.79248949074</v>
@@ -6306,7 +6303,7 @@
         <v>46212.655404537036</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6339,7 +6336,7 @@
         <v>102</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9">
         <v>46279</v>
@@ -6359,7 +6356,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46162.79249689815</v>
@@ -6371,7 +6368,7 @@
         <v>46212.65570653936</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6424,7 +6421,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46162.79250443287</v>
@@ -6434,7 +6431,7 @@
         <v>46209.62459446759</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6467,7 +6464,7 @@
         <v>152</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q81" s="9">
         <v>46280</v>
@@ -6487,7 +6484,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46162.79250947917</v>
@@ -6499,7 +6496,7 @@
         <v>46260.597421099534</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6523,7 +6520,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6540,7 +6537,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46162.79251295139</v>
@@ -6552,7 +6549,7 @@
         <v>46260.5969977662</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6579,13 +6576,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="9">
         <v>46293</v>
@@ -6605,7 +6602,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46162.79252873843</v>
@@ -6642,10 +6639,10 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6658,7 +6655,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46162.792533518514</v>
@@ -6695,10 +6692,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>26</v>
@@ -6711,7 +6708,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B86" s="5">
         <v>46162.79253825231</v>
@@ -6748,13 +6745,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6764,7 +6761,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
         <v>46162.792543206015</v>
@@ -6801,13 +6798,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6817,7 +6814,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46162.792612743055</v>
@@ -6829,7 +6826,7 @@
         <v>46260.597246053236</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6856,13 +6853,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q88" s="5">
         <v>46311</v>
@@ -6882,7 +6879,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
         <v>46162.79261844908</v>
@@ -6919,13 +6916,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6935,7 +6932,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46162.7926247338</v>
@@ -6972,13 +6969,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>277</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6988,7 +6985,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B91" s="9">
         <v>46162.792630682874</v>
@@ -7025,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -7041,7 +7038,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46162.79263777778</v>
@@ -7078,13 +7075,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7094,7 +7091,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="9">
         <v>46162.79268604166</v>
@@ -7106,7 +7103,7 @@
         <v>46260.597285254626</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7133,13 +7130,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q93" s="9">
         <v>46315</v>
@@ -7159,7 +7156,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46162.79269070602</v>
@@ -7196,13 +7193,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7212,7 +7209,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B95" s="9">
         <v>46162.79269707176</v>
@@ -7249,13 +7246,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7265,7 +7262,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46162.792703576386</v>
@@ -7302,13 +7299,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7318,7 +7315,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B97" s="9">
         <v>46162.79271046296</v>
@@ -7355,13 +7352,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O97" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="P97" s="10" t="s">
         <v>292</v>
-      </c>
-      <c r="P97" s="10" t="s">
-        <v>293</v>
       </c>
       <c r="Q97" s="10"/>
       <c r="R97" s="10"/>
@@ -7371,7 +7368,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46162.792744861115</v>
@@ -7383,7 +7380,7 @@
         <v>46260.5973271875</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7410,13 +7407,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q98" s="5">
         <v>46317</v>
@@ -7436,7 +7433,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B99" s="9">
         <v>46162.79274982639</v>
@@ -7473,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O99" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="P99" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="P99" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7489,7 +7486,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B100" s="5">
         <v>46162.79275559028</v>
@@ -7526,13 +7523,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>297</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>298</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7542,7 +7539,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B101" s="9">
         <v>46162.79276118056</v>
@@ -7579,13 +7576,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7595,7 +7592,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B102" s="5">
         <v>46162.792767754625</v>
@@ -7632,13 +7629,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7648,7 +7645,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B103" s="9">
         <v>46162.79285696759</v>
@@ -7660,7 +7657,7 @@
         <v>46260.5973682176</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7687,13 +7684,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O103" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q103" s="9">
         <v>46321</v>
@@ -7713,7 +7710,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B104" s="5">
         <v>46162.792862511575</v>
@@ -7750,13 +7747,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7766,7 +7763,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B105" s="9">
         <v>46162.792868125005</v>
@@ -7803,13 +7800,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O105" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7819,7 +7816,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B106" s="5">
         <v>46162.792873750004</v>
@@ -7856,13 +7853,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7872,7 +7869,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B107" s="9">
         <v>46162.7928793287</v>
@@ -7909,13 +7906,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O107" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7925,7 +7922,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
         <v>46162.792907696756</v>
@@ -7937,7 +7934,7 @@
         <v>46260.59740690972</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7962,13 +7959,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q108" s="5">
         <v>46323</v>
@@ -7988,7 +7985,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B109" s="9">
         <v>46162.79291289352</v>
@@ -8025,13 +8022,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O109" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -8041,7 +8038,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46162.79291758101</v>
@@ -8078,13 +8075,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8094,7 +8091,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B111" s="9">
         <v>46162.79292245371</v>
@@ -8131,13 +8128,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O111" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8147,7 +8144,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B112" s="5">
         <v>46162.79293256944</v>
@@ -8184,13 +8181,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8200,7 +8197,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B113" s="9">
         <v>46162.7930040625</v>
@@ -8210,7 +8207,7 @@
         <v>46260.59684777778</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8234,7 +8231,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8247,7 +8244,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B114" s="5">
         <v>46162.79300806713</v>
@@ -8257,16 +8254,16 @@
         <v>46260.59739923611</v>
       </c>
       <c r="E114" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G114" s="6" t="s">
+      <c r="H114" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8284,13 +8281,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q114" s="5">
         <v>46324</v>
@@ -8310,7 +8307,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B115" s="9">
         <v>46162.79301847222</v>
@@ -8326,10 +8323,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="I115" s="9">
         <v>46324</v>
@@ -8347,13 +8344,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O115" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8363,7 +8360,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B116" s="5">
         <v>46162.79302525463</v>
@@ -8379,10 +8376,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8400,13 +8397,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8416,7 +8413,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B117" s="9">
         <v>46162.79303010416</v>
@@ -8432,10 +8429,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>325</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>326</v>
       </c>
       <c r="I117" s="9">
         <v>46324</v>
@@ -8453,13 +8450,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O117" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8469,7 +8466,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B118" s="5">
         <v>46162.79303482639</v>
@@ -8485,10 +8482,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>325</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>326</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8506,13 +8503,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8522,7 +8519,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B119" s="9">
         <v>46162.79306296296</v>
@@ -8534,7 +8531,7 @@
         <v>46260.596804953704</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8561,13 +8558,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q119" s="9">
         <v>46325</v>
@@ -8587,7 +8584,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B120" s="5">
         <v>46162.7930678125</v>
@@ -8624,13 +8621,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8640,7 +8637,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B121" s="9">
         <v>46162.793072280096</v>
@@ -8677,13 +8674,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8693,7 +8690,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B122" s="5">
         <v>46162.79307696759</v>
@@ -8730,13 +8727,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8746,7 +8743,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B123" s="9">
         <v>46162.79308175926</v>
@@ -8783,13 +8780,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8799,7 +8796,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B124" s="5">
         <v>46162.79314625</v>
@@ -8811,7 +8808,7 @@
         <v>46260.59674144676</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8838,13 +8835,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>208</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q124" s="5">
         <v>46328</v>
@@ -8864,7 +8861,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B125" s="9">
         <v>46162.793151550926</v>
@@ -8903,13 +8900,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8919,7 +8916,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5">
         <v>46162.79315885417</v>
@@ -8956,13 +8953,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8972,7 +8969,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B127" s="9">
         <v>46162.79316501158</v>
@@ -9009,13 +9006,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -9025,7 +9022,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46162.79316986111</v>
@@ -9062,13 +9059,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9078,7 +9075,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B129" s="9">
         <v>46162.79319725695</v>
@@ -9090,7 +9087,7 @@
         <v>46260.596857384255</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9117,13 +9114,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O129" s="10" t="s">
         <v>208</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q129" s="9">
         <v>46329</v>
@@ -9143,7 +9140,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B130" s="5">
         <v>46162.79320210648</v>
@@ -9180,13 +9177,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9196,7 +9193,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B131" s="9">
         <v>46162.793206111106</v>
@@ -9233,13 +9230,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9249,7 +9246,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46162.7932099537</v>
@@ -9286,13 +9283,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9302,7 +9299,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B133" s="9">
         <v>46162.79321400463</v>
@@ -9339,13 +9336,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>188</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9355,7 +9352,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B134" s="5">
         <v>46162.79323766204</v>
@@ -9365,7 +9362,7 @@
         <v>46164.685922812496</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>25</v>
@@ -9389,7 +9386,7 @@
         <v>26</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>26</v>
@@ -9402,7 +9399,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B135" s="9">
         <v>46162.79324063657</v>
@@ -9412,16 +9409,16 @@
         <v>46260.59685918981</v>
       </c>
       <c r="E135" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="F135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="10" t="s">
+      <c r="H135" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="H135" s="10" t="s">
-        <v>364</v>
       </c>
       <c r="I135" s="9">
         <v>46330</v>
@@ -9439,13 +9436,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q135" s="9">
         <v>46330</v>
@@ -9465,7 +9462,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B136" s="5">
         <v>46162.79324528935</v>
@@ -9475,7 +9472,7 @@
         <v>46260.59685829861</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9502,13 +9499,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q136" s="5">
         <v>46330</v>

--- a/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
+++ b/data/50001553 - ZITRON COLOMBIA ARIS OT4326.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="367">
   <si>
     <t xml:space="preserve"> 50001553- ZITRON COLOMBIA ARIS MINING SEGOVIA - OT4326</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Fabricación Alabe,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214982580348412</t>
@@ -2923,7 +2926,7 @@
         <v>46198.68595238426</v>
       </c>
       <c r="D22" s="5">
-        <v>46198.68596357639</v>
+        <v>46269.176564849535</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2967,8 +2970,8 @@
       <c r="R22" s="5">
         <v>46276</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>52</v>
+      <c r="S22" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2979,7 +2982,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="9">
         <v>46162.791964375</v>
@@ -2991,7 +2994,7 @@
         <v>46198.68590748843</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -3024,7 +3027,7 @@
         <v>68</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
@@ -3035,12 +3038,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46162.79196883102</v>
@@ -3052,7 +3055,7 @@
         <v>46198.6859406713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3082,10 +3085,10 @@
         <v>93</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -3096,12 +3099,12 @@
         <v>0</v>
       </c>
       <c r="U24" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9">
         <v>46162.79197329861</v>
@@ -3113,7 +3116,7 @@
         <v>46212.65520907407</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -3143,7 +3146,7 @@
         <v>90</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>90</v>
@@ -3166,7 +3169,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46162.791977500005</v>
@@ -3178,7 +3181,7 @@
         <v>46212.65503678241</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3205,13 +3208,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -3222,12 +3225,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="9">
         <v>46162.79198199074</v>
@@ -3239,7 +3242,7 @@
         <v>46212.65507065972</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3266,13 +3269,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3283,12 +3286,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B28" s="5">
         <v>46162.79198653935</v>
@@ -3300,7 +3303,7 @@
         <v>46198.68573546296</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3330,7 +3333,7 @@
         <v>90</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>90</v>
@@ -3353,7 +3356,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B29" s="9">
         <v>46162.79199082176</v>
@@ -3365,7 +3368,7 @@
         <v>46198.68152484954</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3392,13 +3395,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
@@ -3409,12 +3412,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46162.791995312495</v>
@@ -3426,7 +3429,7 @@
         <v>46198.68567791667</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3453,13 +3456,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3470,12 +3473,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46162.79199990741</v>
@@ -3487,7 +3490,7 @@
         <v>46198.68156315973</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3514,13 +3517,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3531,12 +3534,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46162.792004421295</v>
@@ -3548,16 +3551,16 @@
         <v>46252.179607199076</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I32" s="5">
         <v>46239</v>
@@ -3578,7 +3581,7 @@
         <v>90</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>90</v>
@@ -3601,7 +3604,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B33" s="9">
         <v>46162.79200878472</v>
@@ -3613,16 +3616,16 @@
         <v>46205.6112640625</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I33" s="9">
         <v>46239</v>
@@ -3640,13 +3643,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>77</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3657,12 +3660,12 @@
         <v>0</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46162.792013391205</v>
@@ -3674,16 +3677,16 @@
         <v>46209.81741092593</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3701,13 +3704,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3718,12 +3721,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B35" s="9">
         <v>46162.79201809027</v>
@@ -3735,16 +3738,16 @@
         <v>46252.17960721065</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I35" s="9">
         <v>46239</v>
@@ -3765,7 +3768,7 @@
         <v>90</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3788,7 +3791,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46162.79207501157</v>
@@ -3806,10 +3809,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
         <v>46239</v>
@@ -3827,13 +3830,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>81</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3843,7 +3846,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46162.79208025463</v>
@@ -3855,16 +3858,16 @@
         <v>46209.817526388884</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I37" s="9">
         <v>46241</v>
@@ -3882,13 +3885,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3898,7 +3901,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46162.792085</v>
@@ -3910,16 +3913,16 @@
         <v>46209.62468003472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46239</v>
@@ -3940,7 +3943,7 @@
         <v>90</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3963,7 +3966,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="9">
         <v>46162.792089166665</v>
@@ -3981,10 +3984,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I39" s="9">
         <v>46239</v>
@@ -4002,13 +4005,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4018,7 +4021,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46162.792093599535</v>
@@ -4030,16 +4033,16 @@
         <v>46209.62457706018</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I40" s="5">
         <v>46248</v>
@@ -4057,13 +4060,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4073,7 +4076,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B41" s="9">
         <v>46162.79210385417</v>
@@ -4083,16 +4086,16 @@
         <v>46209.62458533565</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I41" s="9">
         <v>46279</v>
@@ -4110,10 +4113,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>26</v>
@@ -4126,7 +4129,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46162.79210730324</v>
@@ -4138,16 +4141,16 @@
         <v>46252.17961203704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I42" s="5">
         <v>46239</v>
@@ -4168,7 +4171,7 @@
         <v>90</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4191,7 +4194,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9">
         <v>46162.792111180555</v>
@@ -4209,10 +4212,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I43" s="9">
         <v>46239</v>
@@ -4230,13 +4233,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>84</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4246,7 +4249,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46162.79211601852</v>
@@ -4258,16 +4261,16 @@
         <v>46205.61212924769</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4285,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4301,7 +4304,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46162.791800798615</v>
@@ -4313,7 +4316,7 @@
         <v>46210.52939782407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>25</v>
@@ -4337,7 +4340,7 @@
         <v>26</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
@@ -4354,7 +4357,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46162.79212121527</v>
@@ -4366,16 +4369,16 @@
         <v>46197.68073020833</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46160</v>
@@ -4393,13 +4396,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q46" s="5">
         <v>46160</v>
@@ -4419,7 +4422,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46162.79212670139</v>
@@ -4431,16 +4434,16 @@
         <v>46234.17771361111</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46216</v>
@@ -4458,13 +4461,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9">
         <v>46216</v>
@@ -4484,7 +4487,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46162.792133090275</v>
@@ -4502,10 +4505,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I48" s="5">
         <v>46234</v>
@@ -4523,13 +4526,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="5">
         <v>46234</v>
@@ -4549,7 +4552,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="9">
         <v>46162.79214709491</v>
@@ -4561,16 +4564,16 @@
         <v>46258.5437854051</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I49" s="9">
         <v>46322</v>
@@ -4588,10 +4591,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4614,7 +4617,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="5">
         <v>46162.792150775465</v>
@@ -4624,16 +4627,16 @@
         <v>46164.69036847222</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46322</v>
@@ -4651,13 +4654,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4667,7 +4670,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46162.792154849536</v>
@@ -4677,16 +4680,16 @@
         <v>46164.69036586805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I51" s="9">
         <v>46322</v>
@@ -4704,13 +4707,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4720,7 +4723,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46162.79215875</v>
@@ -4730,16 +4733,16 @@
         <v>46164.69036304398</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46322</v>
@@ -4757,13 +4760,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4773,7 +4776,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="9">
         <v>46162.79216164352</v>
@@ -4783,16 +4786,16 @@
         <v>46164.690358935186</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46322</v>
@@ -4810,13 +4813,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4826,7 +4829,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46162.7922118287</v>
@@ -4838,7 +4841,7 @@
         <v>46217.58833277778</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4862,7 +4865,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4879,7 +4882,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="9">
         <v>46162.7922200926</v>
@@ -4891,16 +4894,16 @@
         <v>46254.173978101855</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I55" s="9">
         <v>46252</v>
@@ -4918,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q55" s="9">
         <v>46252</v>
@@ -4944,7 +4947,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46162.792225625</v>
@@ -4956,16 +4959,16 @@
         <v>46256.17331716436</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4983,13 +4986,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -5009,7 +5012,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46162.79223230324</v>
@@ -5021,16 +5024,16 @@
         <v>46254.17397791667</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I57" s="9">
         <v>46252</v>
@@ -5048,13 +5051,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q57" s="9">
         <v>46252</v>
@@ -5074,7 +5077,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46162.79223737269</v>
@@ -5086,16 +5089,16 @@
         <v>46256.17331711805</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -5113,13 +5116,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5139,7 +5142,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
         <v>46162.7922424537</v>
@@ -5151,16 +5154,16 @@
         <v>46254.173977997685</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I59" s="9">
         <v>46252</v>
@@ -5178,13 +5181,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q59" s="9">
         <v>46252</v>
@@ -5204,7 +5207,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46162.792246909725</v>
@@ -5216,16 +5219,16 @@
         <v>46256.173317152774</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5243,13 +5246,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5269,7 +5272,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B61" s="9">
         <v>46162.79225168981</v>
@@ -5281,7 +5284,7 @@
         <v>46249.391917719906</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5305,7 +5308,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5322,7 +5325,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B62" s="5">
         <v>46162.792254479165</v>
@@ -5334,16 +5337,16 @@
         <v>46267.20458883102</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5361,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46162.79225922454</v>
@@ -5399,16 +5402,16 @@
         <v>46245.69551650463</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5426,13 +5429,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q63" s="10"/>
       <c r="R63" s="10"/>
@@ -5442,7 +5445,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46162.792265578704</v>
@@ -5454,16 +5457,16 @@
         <v>46245.695510509264</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5481,13 +5484,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5497,7 +5500,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46162.79227201389</v>
@@ -5509,16 +5512,16 @@
         <v>46245.695528564815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="9">
         <v>46258</v>
@@ -5536,13 +5539,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5552,7 +5555,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B66" s="5">
         <v>46162.79227828704</v>
@@ -5564,16 +5567,16 @@
         <v>46245.69553246528</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5591,13 +5594,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5607,7 +5610,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46162.79232202546</v>
@@ -5619,16 +5622,16 @@
         <v>46249.076454594906</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I67" s="9">
         <v>46267</v>
@@ -5646,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="9">
         <v>46267</v>
@@ -5672,7 +5675,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46162.79232653935</v>
@@ -5684,16 +5687,16 @@
         <v>46245.69562136574</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46267</v>
@@ -5711,13 +5714,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5727,7 +5730,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B69" s="9">
         <v>46162.79233265047</v>
@@ -5739,16 +5742,16 @@
         <v>46245.69562572917</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I69" s="9">
         <v>46267</v>
@@ -5766,13 +5769,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5782,7 +5785,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46162.79233820602</v>
@@ -5794,16 +5797,16 @@
         <v>46245.69563821759</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5821,13 +5824,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5837,7 +5840,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46162.79234384259</v>
@@ -5849,16 +5852,16 @@
         <v>46245.69564313657</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5876,13 +5879,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5892,7 +5895,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46162.79241414352</v>
@@ -5904,16 +5907,16 @@
         <v>46249.07653208333</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I72" s="5">
         <v>46289</v>
@@ -5931,13 +5934,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q72" s="5">
         <v>46289</v>
@@ -5957,7 +5960,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46162.79242041666</v>
@@ -5969,16 +5972,16 @@
         <v>46245.69567159722</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c 